--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F318FE2F-75F5-4E9F-96A6-504F8209A892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F2D750-68F9-4791-8CC7-3994B78666A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2958,12 +2958,12 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="I4">
-            <v>470.25</v>
+            <v>513</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>234391.06483649998</v>
+            <v>255699.34345799999</v>
           </cell>
         </row>
         <row r="7">
@@ -3002,28 +3002,28 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>198.37</v>
+            <v>167.35</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>22758.8770291</v>
+            <v>18988.883522699998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1325.2719999999999</v>
+            <v>1155.7940000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>271.07600000000002</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3417,12 +3417,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>2078</v>
+            <v>2020</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>217849.56333799998</v>
+            <v>211769.06542</v>
           </cell>
         </row>
         <row r="5">
@@ -4015,22 +4015,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>108.4</v>
+            <v>96.16</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>7370.5144783999995</v>
+            <v>6538.271884159999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>182.05</v>
+            <v>243.84100000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>284.83199999999999</v>
+            <v>7.04</v>
           </cell>
         </row>
       </sheetData>
@@ -4804,7 +4804,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="Main"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5036,7 +5036,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="Main"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -5610,7 +5610,22 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1">
+        <row r="20">
+          <cell r="C20">
+            <v>146688</v>
+          </cell>
+          <cell r="G20">
+            <v>157556</v>
+          </cell>
+          <cell r="H20">
+            <v>146661</v>
+          </cell>
+          <cell r="I20">
+            <v>146735</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5903,22 +5918,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>3.94</v>
+            <v>2.4</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>412.44010619999995</v>
+            <v>252.04949999999997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>54.338999999999999</v>
+            <v>23.693000000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>296.625</v>
+            <v>284.517</v>
           </cell>
         </row>
       </sheetData>
@@ -6811,15 +6826,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1750187.3906775631</v>
+        <v>1761228.3661985935</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>19145.380205200006</v>
+        <v>18709.153885200012</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1769332.7708827639</v>
+        <v>1779937.5200837941</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6829,11 +6844,11 @@
       </c>
       <c r="L4" s="20">
         <f>+MEDIAN(L6:L153)</f>
-        <v>0.09</v>
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="M4" s="19">
         <f>SUM(M6:M85)</f>
-        <v>78834.799999999988</v>
+        <v>82599.931999999986</v>
       </c>
       <c r="N4" s="19">
         <f>SUM(N6:N85)</f>
@@ -6870,15 +6885,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22729.706372435885</v>
+        <v>22873.0956649168</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>248.64130136623385</v>
+        <v>242.97602448311704</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>22978.347673802127</v>
+        <v>23116.071689399923</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -6888,11 +6903,11 @@
       </c>
       <c r="L5" s="23">
         <f>AVERAGE(L6:L182)</f>
-        <v>5.9941176470588241E-2</v>
+        <v>6.1055555555555557E-2</v>
       </c>
       <c r="M5" s="19">
         <f t="shared" ref="M5:AA5" si="0">AVERAGE(M6:M85)</f>
-        <v>5255.6533333333327</v>
+        <v>5162.4957499999991</v>
       </c>
       <c r="N5" s="19">
         <f t="shared" si="0"/>
@@ -6900,19 +6915,19 @@
       </c>
       <c r="O5" s="23">
         <f t="shared" si="0"/>
-        <v>0.54400000000000015</v>
+        <v>0.54437500000000005</v>
       </c>
       <c r="P5" s="23">
         <f t="shared" si="0"/>
-        <v>0.1555511968163622</v>
+        <v>0.15707924701533954</v>
       </c>
       <c r="Q5" s="24">
         <f t="shared" si="0"/>
-        <v>29.104285714285716</v>
+        <v>27.98</v>
       </c>
       <c r="R5" s="24">
         <f t="shared" si="0"/>
-        <v>28.9925</v>
+        <v>29.475000000000001</v>
       </c>
       <c r="S5" s="24">
         <f t="shared" si="0"/>
@@ -6924,11 +6939,11 @@
       </c>
       <c r="U5" s="24">
         <f t="shared" si="0"/>
-        <v>8.8771428571428572</v>
+        <v>7.2519999999999998</v>
       </c>
       <c r="V5" s="24">
         <f t="shared" si="0"/>
-        <v>4.7485714285714291</v>
+        <v>4.020999999999999</v>
       </c>
       <c r="W5" s="24">
         <f t="shared" si="0"/>
@@ -6971,11 +6986,11 @@
       </c>
       <c r="E6" s="26">
         <f>+[1]Main!$I$4</f>
-        <v>470.25</v>
+        <v>513</v>
       </c>
       <c r="F6" s="19">
         <f>+[1]Main!$I$6*FX!C3</f>
-        <v>243766.70742995999</v>
+        <v>265927.31719631999</v>
       </c>
       <c r="G6" s="19">
         <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
@@ -6983,7 +6998,7 @@
       </c>
       <c r="H6" s="19">
         <f>F6+G6</f>
-        <v>258539.90742996</v>
+        <v>280700.51719632</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>149</v>
@@ -7017,7 +7032,7 @@
         <v>25.7</v>
       </c>
       <c r="R6" s="24">
-        <v>23.95</v>
+        <v>23.3</v>
       </c>
       <c r="S6" s="24">
         <v>1.752</v>
@@ -7026,10 +7041,10 @@
         <v>-11.97</v>
       </c>
       <c r="U6" s="24">
-        <v>5.73</v>
+        <v>3.4</v>
       </c>
       <c r="V6" s="24">
-        <v>4.4800000000000004</v>
+        <v>3.1</v>
       </c>
       <c r="W6" s="29">
         <v>13.73</v>
@@ -7074,11 +7089,11 @@
       </c>
       <c r="E7" s="31">
         <f>+[2]Main!$K$2</f>
-        <v>2078</v>
+        <v>2020</v>
       </c>
       <c r="F7" s="19">
         <f>+[2]Main!$K$4*FX!C3</f>
-        <v>226563.54587151998</v>
+        <v>220239.8280368</v>
       </c>
       <c r="G7" s="19">
         <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
@@ -7086,7 +7101,7 @@
       </c>
       <c r="H7" s="19">
         <f>F7+G7</f>
-        <v>215862.98587151998</v>
+        <v>209539.2680368</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>149</v>
@@ -7119,7 +7134,7 @@
         <v>55.2</v>
       </c>
       <c r="R7" s="24">
-        <v>44.9</v>
+        <v>46.9</v>
       </c>
       <c r="S7" s="24">
         <f>155.7/100</f>
@@ -7129,10 +7144,10 @@
         <v>2.4</v>
       </c>
       <c r="U7" s="24">
-        <v>13.7</v>
+        <v>11.1</v>
       </c>
       <c r="V7" s="24">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="W7" s="29">
         <v>32.200000000000003</v>
@@ -7219,10 +7234,10 @@
         <v>0.19</v>
       </c>
       <c r="Q8" s="24">
-        <v>26.13</v>
+        <v>22.6</v>
       </c>
       <c r="R8" s="29">
-        <v>27.22</v>
+        <v>21.4</v>
       </c>
       <c r="S8" s="29">
         <v>1.7</v>
@@ -7231,10 +7246,10 @@
         <v>3.9</v>
       </c>
       <c r="U8" s="24">
-        <v>6.32</v>
+        <v>7.3</v>
       </c>
       <c r="V8" s="24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="W8" s="29">
         <v>12.81</v>
@@ -7316,18 +7331,20 @@
         <v>0.11</v>
       </c>
       <c r="Q9" s="24">
-        <v>24</v>
-      </c>
-      <c r="R9" s="29"/>
+        <v>32.1</v>
+      </c>
+      <c r="R9" s="29">
+        <v>29.4</v>
+      </c>
       <c r="S9" s="24">
         <v>2</v>
       </c>
       <c r="T9" s="24"/>
       <c r="U9" s="24">
-        <v>14</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="V9" s="24">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="W9" s="29">
         <v>17</v>
@@ -7484,10 +7501,10 @@
         <v>0.12</v>
       </c>
       <c r="Q11" s="24">
-        <v>38.700000000000003</v>
+        <v>34.9</v>
       </c>
       <c r="R11" s="29">
-        <v>19.899999999999999</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="S11" s="24">
         <v>0.56999999999999995</v>
@@ -7496,10 +7513,10 @@
         <v>1.27</v>
       </c>
       <c r="U11" s="24">
-        <v>13.57</v>
+        <v>7.2</v>
       </c>
       <c r="V11" s="24">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="W11" s="29">
         <v>25.2</v>
@@ -7566,17 +7583,34 @@
         <f>2301122*FX!C5</f>
         <v>14497.068600000001</v>
       </c>
-      <c r="L12" s="23"/>
-      <c r="M12" s="19"/>
+      <c r="L12" s="23">
+        <v>0.08</v>
+      </c>
+      <c r="M12" s="19">
+        <f>+SUM([7]Model!$G$20:$I$20,[7]Model!$C$20)*FX!C5</f>
+        <v>3765.1320000000001</v>
+      </c>
       <c r="N12" s="19"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="29"/>
+      <c r="O12" s="23">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="P12" s="23">
+        <v>0.18</v>
+      </c>
+      <c r="Q12" s="24">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="R12" s="29">
+        <v>35.6</v>
+      </c>
       <c r="S12" s="24"/>
       <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
+      <c r="U12" s="24">
+        <v>6.9</v>
+      </c>
+      <c r="V12" s="24">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="W12" s="29"/>
       <c r="X12" s="24"/>
       <c r="Y12" s="30"/>
@@ -7760,25 +7794,25 @@
       </c>
       <c r="E15" s="26">
         <f>+[10]Main!$I$2</f>
-        <v>198.37</v>
+        <v>167.35</v>
       </c>
       <c r="F15" s="19">
         <f>+[10]Main!$I$4</f>
-        <v>22758.8770291</v>
+        <v>18988.883522699998</v>
       </c>
       <c r="G15" s="19">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
-        <v>-1054.1959999999999</v>
+        <v>-1155.7940000000001</v>
       </c>
       <c r="H15" s="19">
         <f>F15+G15</f>
-        <v>21704.6810291</v>
+        <v>17833.089522699996</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>432</v>
+        <v>149</v>
       </c>
       <c r="J15" s="28">
-        <v>45904</v>
+        <v>45995</v>
       </c>
       <c r="K15" s="19">
         <v>9619.2999999999993</v>
@@ -8044,12 +8078,20 @@
       <c r="N18" s="19"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
+      <c r="Q18" s="24">
+        <v>19.5</v>
+      </c>
+      <c r="R18" s="24">
+        <v>19.5</v>
+      </c>
       <c r="S18" s="24"/>
       <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
+      <c r="U18" s="24">
+        <v>3.2</v>
+      </c>
+      <c r="V18" s="24">
+        <v>3</v>
+      </c>
       <c r="W18" s="29"/>
       <c r="X18" s="24"/>
       <c r="Y18" s="30"/>
@@ -8107,12 +8149,20 @@
       <c r="N19" s="19"/>
       <c r="O19" s="23"/>
       <c r="P19" s="23"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
+      <c r="Q19" s="24">
+        <v>19</v>
+      </c>
+      <c r="R19" s="24">
+        <v>19.399999999999999</v>
+      </c>
       <c r="S19" s="24"/>
       <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
+      <c r="U19" s="24">
+        <v>7.2</v>
+      </c>
+      <c r="V19" s="24">
+        <v>3.3</v>
+      </c>
       <c r="W19" s="29"/>
       <c r="X19" s="24"/>
       <c r="Y19" s="30"/>
@@ -9322,19 +9372,19 @@
       </c>
       <c r="E38" s="26">
         <f>+[33]Main!$J$2</f>
-        <v>108.4</v>
+        <v>96.16</v>
       </c>
       <c r="F38" s="19">
         <f>+[33]Main!$J$4*FX!C3</f>
-        <v>7665.335057536</v>
+        <v>6799.8027595263993</v>
       </c>
       <c r="G38" s="19">
         <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
-        <v>106.89327999999999</v>
+        <v>-246.27304000000004</v>
       </c>
       <c r="H38" s="19">
         <f>F38+G38</f>
-        <v>7772.2283375360003</v>
+        <v>6553.5297195263993</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>338</v>
@@ -10443,15 +10493,15 @@
         <v>124</v>
       </c>
       <c r="E56" s="26">
-        <f>+[51]Sheet1!$I$2</f>
+        <f>+[51]Main!$I$2</f>
         <v>2816.5</v>
       </c>
       <c r="F56" s="19">
-        <f>+[51]Sheet1!$I$4*FX!C5</f>
+        <f>+[51]Main!$I$4*FX!C5</f>
         <v>4393.7011297651507</v>
       </c>
       <c r="G56" s="19">
-        <f>+([51]Sheet1!$I$6-[51]Sheet1!$I$5)*FX!C5</f>
+        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
         <v>-837.64170000000001</v>
       </c>
       <c r="H56" s="19">
@@ -10803,15 +10853,15 @@
         <v>21</v>
       </c>
       <c r="E62" s="26">
-        <f>+[57]Sheet1!$J$2</f>
+        <f>+[57]Main!$J$2</f>
         <v>208.43</v>
       </c>
       <c r="F62" s="19">
-        <f>+[57]Sheet1!$J$4</f>
+        <f>+[57]Main!$J$4</f>
         <v>3869.6348861900005</v>
       </c>
       <c r="G62" s="19">
-        <f>+[57]Sheet1!$J$6-[57]Sheet1!$J$5</f>
+        <f>+[57]Main!$J$6-[57]Main!$J$5</f>
         <v>-180.98000000000002</v>
       </c>
       <c r="H62" s="19">
@@ -13705,19 +13755,19 @@
       </c>
       <c r="E123" s="26">
         <f>+[77]Main!$H$2</f>
-        <v>3.94</v>
+        <v>2.4</v>
       </c>
       <c r="F123" s="19">
         <f>+[77]Main!$H$4</f>
-        <v>412.44010619999995</v>
+        <v>252.04949999999997</v>
       </c>
       <c r="G123" s="19">
         <f>+[77]Main!$H$6-[77]Main!$H$5</f>
-        <v>242.286</v>
+        <v>260.82400000000001</v>
       </c>
       <c r="H123" s="19">
         <f>+F123+G123</f>
-        <v>654.7261062</v>
+        <v>512.87349999999992</v>
       </c>
       <c r="I123" s="18" t="s">
         <v>148</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F2D750-68F9-4791-8CC7-3994B78666A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F888859-6BBB-41FF-A41A-F3CF648066AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="2295" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3021,9 +3021,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3931,28 +3931,28 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Financials"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="I2">
-            <v>21.9</v>
+          <cell r="J2">
+            <v>22.05</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="I4">
-            <v>8241.3403727999994</v>
+          <cell r="J4">
+            <v>8181.5913333000008</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="I5">
-            <v>2146</v>
+          <cell r="J5">
+            <v>2432</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="I6">
-            <v>1489</v>
+          <cell r="J6">
+            <v>1491</v>
           </cell>
         </row>
       </sheetData>
@@ -4054,26 +4054,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>56.5</v>
+            <v>76.81</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>8580.9375</v>
+            <v>11580.02922</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>75.495999999999995</v>
+            <v>86.016000000000005</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1803.6</v>
+            <v>1856.34</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6826,15 +6826,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1761228.3661985935</v>
+        <v>1764167.7088790936</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18709.153885200012</v>
+        <v>18467.373885200013</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1779937.5200837941</v>
+        <v>1782635.0827642942</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6885,15 +6885,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22873.0956649168</v>
+        <v>22911.268946481734</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>242.97602448311704</v>
+        <v>239.83602448311706</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>23116.071689399923</v>
+        <v>23151.104970964861</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -9233,20 +9233,20 @@
         <v>21</v>
       </c>
       <c r="E36" s="26">
-        <f>+[31]Main!$I$2</f>
-        <v>21.9</v>
+        <f>+[31]Main!$J$2</f>
+        <v>22.05</v>
       </c>
       <c r="F36" s="19">
-        <f>+[31]Main!$I$4</f>
-        <v>8241.3403727999994</v>
+        <f>+[31]Main!$J$4</f>
+        <v>8181.5913333000008</v>
       </c>
       <c r="G36" s="19">
-        <f>+[31]Main!$I$6-[31]Main!$I$5</f>
-        <v>-657</v>
+        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
+        <v>-941</v>
       </c>
       <c r="H36" s="19">
         <f>+G36+F36</f>
-        <v>7584.3403727999994</v>
+        <v>7240.5913333000008</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>149</v>
@@ -9435,24 +9435,26 @@
       </c>
       <c r="E39" s="26">
         <f>+[34]Main!$I$2</f>
-        <v>56.5</v>
+        <v>76.81</v>
       </c>
       <c r="F39" s="19">
         <f>+[34]Main!$I$4</f>
-        <v>8580.9375</v>
+        <v>11580.02922</v>
       </c>
       <c r="G39" s="19">
         <f>+[34]Main!$I$6-[34]Main!$I$5</f>
-        <v>1728.1039999999998</v>
+        <v>1770.3239999999998</v>
       </c>
       <c r="H39" s="19">
         <f>F39+G39</f>
-        <v>10309.041499999999</v>
+        <v>13350.353220000001</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="J39" s="28"/>
+        <v>149</v>
+      </c>
+      <c r="J39" s="28">
+        <v>45960</v>
+      </c>
       <c r="K39" s="19"/>
       <c r="L39" s="23"/>
       <c r="M39" s="19"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F888859-6BBB-41FF-A41A-F3CF648066AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAD1F73-361A-4C03-8DD8-8291E6CD0B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2295" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3857,28 +3857,28 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>46.8</v>
+            <v>45.46</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>145793.12908680001</v>
+            <v>141644.79719985998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>10785</v>
+            <v>10013</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>7</v>
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4073,7 +4073,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6826,15 +6826,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1764167.7088790936</v>
+        <v>1759853.443716676</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18467.373885200013</v>
+        <v>19264.013885200009</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1782635.0827642942</v>
+        <v>1779117.4576018767</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6885,15 +6885,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22911.268946481734</v>
+        <v>22855.239528787999</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>239.83602448311706</v>
+        <v>250.18199850909102</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>23151.104970964861</v>
+        <v>23105.421527297101</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7192,25 +7192,25 @@
       </c>
       <c r="E8" s="26">
         <f>+[3]Main!$J$3</f>
-        <v>46.8</v>
+        <v>45.46</v>
       </c>
       <c r="F8" s="19">
         <f>+[3]Main!$J$5*FX!C3</f>
-        <v>151624.85425027201</v>
+        <v>147310.58908785437</v>
       </c>
       <c r="G8" s="19">
         <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
-        <v>-11209.12</v>
+        <v>-10412.48</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" ref="H8:H35" si="1">F8+G8</f>
-        <v>140415.73425027201</v>
+        <v>136898.10908785436</v>
       </c>
       <c r="I8" s="27" t="s">
-        <v>432</v>
+        <v>149</v>
       </c>
       <c r="J8" s="28">
-        <v>45910</v>
+        <v>45994</v>
       </c>
       <c r="K8" s="19">
         <f>35947*FX!C3</f>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAD1F73-361A-4C03-8DD8-8291E6CD0B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC7431F-C1A0-4796-90A1-44AC4FF39944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3876,9 +3876,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC7431F-C1A0-4796-90A1-44AC4FF39944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1C8501-266A-46D8-9217-25FB55321DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3537,26 +3537,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>101.55</v>
+            <v>118.8</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>12799.768199999999</v>
+            <v>13911.48</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>153.6</v>
+            <v>441.1</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>863.5</v>
+            <v>781.30000000000007</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6826,15 +6826,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1759853.443716676</v>
+        <v>1761231.966348676</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>19264.013885200009</v>
+        <v>18805.585885200013</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1779117.4576018767</v>
+        <v>1780037.5522338767</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6885,15 +6885,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22855.239528787999</v>
+        <v>22873.142420112676</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>250.18199850909102</v>
+        <v>244.22838811948068</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>23105.421527297101</v>
+        <v>23117.370808232165</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -8636,25 +8636,25 @@
       </c>
       <c r="E27" s="26">
         <f>+[22]Main!$I$2</f>
-        <v>101.55</v>
+        <v>118.8</v>
       </c>
       <c r="F27" s="19">
         <f>+[22]Main!$I$4*FX!C8</f>
-        <v>15871.712567999999</v>
+        <v>17250.235199999999</v>
       </c>
       <c r="G27" s="19">
         <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C8</f>
-        <v>880.27599999999995</v>
+        <v>421.84800000000007</v>
       </c>
       <c r="H27" s="19">
         <f>F27+G27</f>
-        <v>16751.988568000001</v>
+        <v>17672.083200000001</v>
       </c>
       <c r="I27" s="27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J27" s="28">
-        <v>45736</v>
+        <v>45959</v>
       </c>
       <c r="K27" s="26"/>
       <c r="L27" s="23"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1C8501-266A-46D8-9217-25FB55321DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7FA2A7-BE14-4437-9841-98100EB1D216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="821">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2596,6 +2596,9 @@
   </si>
   <si>
     <t>NI</t>
+  </si>
+  <si>
+    <t>Acquired</t>
   </si>
 </sst>
 </file>
@@ -3556,7 +3559,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4132,26 +4135,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>16460</v>
+            <v>17935</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>30547.949400000001</v>
+            <v>33272.832649999997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1581</v>
+            <v>1643</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1047</v>
+            <v>2042</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5840,22 +5843,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>12.38</v>
+            <v>16.75</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>637.03569158000005</v>
+            <v>872.38125524999998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>140.911</v>
+            <v>189.63499999999999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>621.75900000000001</v>
+            <v>623.71199999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -6826,15 +6829,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1761231.966348676</v>
+        <v>1762148.5327248459</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18805.585885200013</v>
+        <v>18992.064885200012</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1780037.5522338767</v>
+        <v>1781140.5976100466</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6885,15 +6888,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22873.142420112676</v>
+        <v>22885.045879543453</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>244.22838811948068</v>
+        <v>246.65019331428587</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>23117.370808232165</v>
+        <v>23131.696072857747</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -9326,8 +9329,8 @@
       <c r="I37" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="J37" s="28">
-        <v>45771</v>
+      <c r="J37" s="32" t="s">
+        <v>820</v>
       </c>
       <c r="K37" s="19"/>
       <c r="L37" s="23"/>
@@ -9573,24 +9576,26 @@
       </c>
       <c r="E41" s="26">
         <f>+[36]Main!$I$2</f>
-        <v>16460</v>
+        <v>17935</v>
       </c>
       <c r="F41" s="19">
         <f>+[36]Main!$I$4*FX!C11</f>
-        <v>7636.9873500000003</v>
+        <v>8318.2081624999992</v>
       </c>
       <c r="G41" s="19">
         <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
-        <v>-133.5</v>
+        <v>99.75</v>
       </c>
       <c r="H41" s="19">
         <f>+F41+G41</f>
-        <v>7503.4873500000003</v>
+        <v>8417.9581624999992</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="J41" s="3"/>
+        <v>432</v>
+      </c>
+      <c r="J41" s="28">
+        <v>45925</v>
+      </c>
       <c r="K41" s="19"/>
       <c r="L41" s="23"/>
       <c r="M41" s="19"/>
@@ -12785,22 +12790,22 @@
       </c>
       <c r="E101" s="26">
         <f>+[75]Main!$I$2</f>
-        <v>12.38</v>
+        <v>16.75</v>
       </c>
       <c r="F101" s="19">
         <f>+[75]Main!$I$4</f>
-        <v>637.03569158000005</v>
+        <v>872.38125524999998</v>
       </c>
       <c r="G101" s="19">
         <f>+[75]Main!$I$6-[75]Main!$I$5</f>
-        <v>480.84800000000001</v>
+        <v>434.077</v>
       </c>
       <c r="H101" s="19">
         <f>+F101+G101</f>
-        <v>1117.88369158</v>
+        <v>1306.4582552500001</v>
       </c>
       <c r="I101" s="18" t="s">
-        <v>337</v>
+        <v>149</v>
       </c>
       <c r="J101" s="3"/>
       <c r="K101" s="19"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7FA2A7-BE14-4437-9841-98100EB1D216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F143D504-3377-4B1B-9B4C-267F00190B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -4154,7 +4154,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5999,26 +5999,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>14.08</v>
+            <v>29.25</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1131.6316492799999</v>
+            <v>2376.6897667500002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>152.1</v>
+            <v>141</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>648</v>
+            <v>698.5</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -15166,24 +15166,26 @@
       </c>
       <c r="E155" s="26">
         <f>+[79]Main!$J$2</f>
-        <v>14.08</v>
+        <v>29.25</v>
       </c>
       <c r="F155" s="19">
         <f>+[79]Main!$J$4</f>
-        <v>1131.6316492799999</v>
+        <v>2376.6897667500002</v>
       </c>
       <c r="G155" s="19">
         <f>+[79]Main!$J$6-[79]Main!$J$5</f>
-        <v>495.9</v>
+        <v>557.5</v>
       </c>
       <c r="H155" s="19">
         <f>+F155+G155</f>
-        <v>1627.5316492799998</v>
+        <v>2934.1897667500002</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="J155" s="3"/>
+        <v>149</v>
+      </c>
+      <c r="J155" s="28">
+        <v>45967</v>
+      </c>
       <c r="K155" s="26"/>
       <c r="L155" s="23"/>
       <c r="M155" s="26"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F143D504-3377-4B1B-9B4C-267F00190B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99E08C0-DC38-4BCB-BF76-9B824A2C8E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -111,6 +111,7 @@
     <externalReference r:id="rId94"/>
     <externalReference r:id="rId95"/>
     <externalReference r:id="rId96"/>
+    <externalReference r:id="rId97"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$AE$181</definedName>
@@ -136,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="822">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2599,6 +2600,9 @@
   </si>
   <si>
     <t>Acquired</t>
+  </si>
+  <si>
+    <t>Q325</t>
   </si>
 </sst>
 </file>
@@ -2612,7 +2616,7 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2629,14 +2633,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2765,102 +2761,21 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2880,7 +2795,88 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2900,24 +2896,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2927,7 +2923,7 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -3005,12 +3001,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>167.35</v>
+            <v>177.4</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>18988.883522699998</v>
+            <v>20129.237746800001</v>
           </cell>
         </row>
         <row r="5">
@@ -3216,22 +3212,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>134.9</v>
+            <v>171.25</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>216445.83590000001</v>
+            <v>274654.17499999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>16262</v>
+            <v>20363</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>75359</v>
+            <v>75377</v>
           </cell>
         </row>
       </sheetData>
@@ -4018,12 +4014,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>96.16</v>
+            <v>85.3</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>6538.271884159999</v>
+            <v>5799.8605627999996</v>
           </cell>
         </row>
         <row r="5">
@@ -4213,26 +4209,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>47278</v>
+            <v>41240</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>527334.08420000004</v>
+            <v>459995.53764</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>59638.020000000004</v>
+            <v>45360.78</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>0</v>
+            <v>52633.11</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4439,7 +4435,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5960,22 +5956,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>2540</v>
+            <v>17.79</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>64964.434459999997</v>
+            <v>270.90115659000003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>33044</v>
+            <v>45.523000000000003</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>13470</v>
+            <v>70.016000000000005</v>
           </cell>
         </row>
       </sheetData>
@@ -5998,27 +5994,27 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="J2">
-            <v>29.25</v>
+          <cell r="I2">
+            <v>2540</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="J4">
-            <v>2376.6897667500002</v>
+          <cell r="I4">
+            <v>64964.434459999997</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>141</v>
+          <cell r="I5">
+            <v>33044</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>698.5</v>
+          <cell r="I6">
+            <v>13470</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6077,6 +6073,45 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
+            <v>29.25</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2376.6897667500002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>141</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>698.5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
             <v>180.8</v>
           </cell>
         </row>
@@ -6102,7 +6137,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6143,7 +6178,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6184,7 +6219,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6223,7 +6258,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6829,15 +6864,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1762148.5327248459</v>
+        <v>1767580.9085336619</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18992.064885200012</v>
+        <v>19364.686735200008</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1781140.5976100466</v>
+        <v>1786945.5952688619</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6888,15 +6923,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22885.045879543453</v>
+        <v>22661.293699149512</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>246.65019331428587</v>
+        <v>248.26521455384625</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>23131.696072857747</v>
+        <v>22909.558913703357</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7797,11 +7832,11 @@
       </c>
       <c r="E15" s="26">
         <f>+[10]Main!$I$2</f>
-        <v>167.35</v>
+        <v>177.4</v>
       </c>
       <c r="F15" s="19">
         <f>+[10]Main!$I$4</f>
-        <v>18988.883522699998</v>
+        <v>20129.237746800001</v>
       </c>
       <c r="G15" s="19">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
@@ -7809,7 +7844,7 @@
       </c>
       <c r="H15" s="19">
         <f>F15+G15</f>
-        <v>17833.089522699996</v>
+        <v>18973.4437468</v>
       </c>
       <c r="I15" s="27" t="s">
         <v>149</v>
@@ -8197,25 +8232,25 @@
       </c>
       <c r="E20" s="26">
         <f>+[15]Main!$I$2</f>
-        <v>134.9</v>
+        <v>171.25</v>
       </c>
       <c r="F20" s="19">
         <f>+[15]Main!$I$4*FX!C4</f>
-        <v>20562.3544105</v>
+        <v>26092.146624999998</v>
       </c>
       <c r="G20" s="19">
         <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C4</f>
-        <v>5614.2150000000001</v>
+        <v>5226.33</v>
       </c>
       <c r="H20" s="19">
         <f t="shared" si="1"/>
-        <v>26176.5694105</v>
+        <v>31318.476624999996</v>
       </c>
       <c r="I20" s="27" t="s">
-        <v>149</v>
+        <v>821</v>
       </c>
       <c r="J20" s="28">
-        <v>45925</v>
+        <v>46051</v>
       </c>
       <c r="K20" s="19">
         <f>234478*FX!C4</f>
@@ -9375,11 +9410,11 @@
       </c>
       <c r="E38" s="26">
         <f>+[33]Main!$J$2</f>
-        <v>96.16</v>
+        <v>85.3</v>
       </c>
       <c r="F38" s="19">
         <f>+[33]Main!$J$4*FX!C3</f>
-        <v>6799.8027595263993</v>
+        <v>6031.8549853119994</v>
       </c>
       <c r="G38" s="19">
         <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
@@ -9387,7 +9422,7 @@
       </c>
       <c r="H38" s="19">
         <f>F38+G38</f>
-        <v>6553.5297195263993</v>
+        <v>5785.5819453119993</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>338</v>
@@ -9694,24 +9729,26 @@
       </c>
       <c r="E43" s="26">
         <f>+[38]Main!$H$2</f>
-        <v>47278</v>
+        <v>41240</v>
       </c>
       <c r="F43" s="19">
         <f>+[38]Main!$H$4*FX!C12</f>
-        <v>5800.6749262000003</v>
+        <v>5059.9509140399996</v>
       </c>
       <c r="G43" s="19">
         <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
-        <v>-656.01822000000004</v>
+        <v>79.99563000000002</v>
       </c>
       <c r="H43" s="19">
         <f>+F43+G43</f>
-        <v>5144.6567062000004</v>
+        <v>5139.9465440399999</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="J43" s="3"/>
+        <v>719</v>
+      </c>
+      <c r="J43" s="28">
+        <v>45975</v>
+      </c>
       <c r="K43" s="19"/>
       <c r="L43" s="23"/>
       <c r="M43" s="19"/>
@@ -13851,7 +13888,7 @@
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="46" t="s">
         <v>246</v>
       </c>
       <c r="C125" s="4" t="s">
@@ -13860,11 +13897,25 @@
       <c r="D125" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E125" s="26"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="19"/>
-      <c r="H125" s="19"/>
-      <c r="I125" s="18"/>
+      <c r="E125" s="26">
+        <f>+[78]Main!$I$2</f>
+        <v>17.79</v>
+      </c>
+      <c r="F125" s="19">
+        <f>+[78]Main!$I$4</f>
+        <v>270.90115659000003</v>
+      </c>
+      <c r="G125" s="19">
+        <f>+[78]Main!$I$6-[78]Main!$I$5</f>
+        <v>24.493000000000002</v>
+      </c>
+      <c r="H125" s="19">
+        <f>+F125+G125</f>
+        <v>295.39415659000002</v>
+      </c>
+      <c r="I125" s="18" t="s">
+        <v>149</v>
+      </c>
       <c r="J125" s="3"/>
       <c r="K125" s="19"/>
       <c r="L125" s="23"/>
@@ -15108,15 +15159,15 @@
         <v>124</v>
       </c>
       <c r="E154" s="26">
-        <f>+[78]Main!$I$2</f>
+        <f>+[79]Main!$I$2</f>
         <v>2540</v>
       </c>
       <c r="F154" s="19">
-        <f>+[78]Main!$I$4*FX!C5</f>
+        <f>+[79]Main!$I$4*FX!C5</f>
         <v>409.27593709799999</v>
       </c>
       <c r="G154" s="19">
-        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
+        <f>+([79]Main!$I$6-[79]Main!$I$5)*FX!C5</f>
         <v>-123.31619999999999</v>
       </c>
       <c r="H154" s="19">
@@ -15165,15 +15216,15 @@
         <v>21</v>
       </c>
       <c r="E155" s="26">
-        <f>+[79]Main!$J$2</f>
+        <f>+[80]Main!$J$2</f>
         <v>29.25</v>
       </c>
       <c r="F155" s="19">
-        <f>+[79]Main!$J$4</f>
+        <f>+[80]Main!$J$4</f>
         <v>2376.6897667500002</v>
       </c>
       <c r="G155" s="19">
-        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
+        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
         <v>557.5</v>
       </c>
       <c r="H155" s="19">
@@ -17279,9 +17330,10 @@
     <hyperlink ref="B22" r:id="rId77" xr:uid="{568F05A9-6D0C-4F83-9B4F-EADBE5B3D36E}"/>
     <hyperlink ref="B155" r:id="rId78" xr:uid="{9178234D-93D7-4722-B414-1ED85B69D113}"/>
     <hyperlink ref="B154" r:id="rId79" xr:uid="{5AF15AA0-C03A-41B5-87FB-E2EC2E8EDE78}"/>
+    <hyperlink ref="B125" r:id="rId80" xr:uid="{3E3906F5-51B3-405C-ACE3-A12F1DE77816}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId80"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
 </worksheet>
 </file>
 
@@ -19540,15 +19592,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="47">
-        <f>+[80]Main!$J$2</f>
+        <f>+[81]Main!$J$2</f>
         <v>180.8</v>
       </c>
       <c r="F20" s="58">
-        <f>+[80]Main!$J$4</f>
+        <f>+[81]Main!$J$4</f>
         <v>14437.908028799999</v>
       </c>
       <c r="G20" s="58">
-        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
+        <f>+[81]Main!$J$6-[81]Main!$J$5</f>
         <v>-205.72299999999996</v>
       </c>
       <c r="H20" s="58">
@@ -38260,15 +38312,15 @@
         <v>20</v>
       </c>
       <c r="E4" s="60">
-        <f>+[81]Main!$I$2</f>
+        <f>+[82]Main!$I$2</f>
         <v>257.3</v>
       </c>
       <c r="F4" s="58">
-        <f>+[81]Main!$I$4*FX!C3</f>
+        <f>+[82]Main!$I$4*FX!C3</f>
         <v>121467.16982951201</v>
       </c>
       <c r="G4" s="58">
-        <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
+        <f>+([82]Main!$I$6-[82]Main!$I$5)*FX!C3</f>
         <v>7610.72</v>
       </c>
       <c r="H4" s="58">
@@ -38326,15 +38378,15 @@
         <v>85</v>
       </c>
       <c r="E5" s="60">
-        <f>+[82]Main!$J$2</f>
+        <f>+[83]Main!$J$2</f>
         <v>149.9</v>
       </c>
       <c r="F5" s="58">
-        <f>+[82]Main!$J$5*FX!C7</f>
+        <f>+[83]Main!$J$5*FX!C7</f>
         <v>104409.88297600002</v>
       </c>
       <c r="G5" s="58">
-        <f>+([82]Main!$J$7-[82]Main!$J$6)*FX!C7</f>
+        <f>+([83]Main!$J$7-[83]Main!$J$6)*FX!C7</f>
         <v>-8980.1600000000017</v>
       </c>
       <c r="H5" s="58">
@@ -38392,15 +38444,15 @@
         <v>21</v>
       </c>
       <c r="E6" s="60">
-        <f>+[83]Main!$K$2</f>
+        <f>+[84]Main!$K$2</f>
         <v>63.49</v>
       </c>
       <c r="F6" s="58">
-        <f>+[83]Main!$K$4</f>
+        <f>+[84]Main!$K$4</f>
         <v>22840.653210200002</v>
       </c>
       <c r="G6" s="58">
-        <f>+([83]Main!$K$6-[83]Main!$K$5)</f>
+        <f>+([84]Main!$K$6-[84]Main!$K$5)</f>
         <v>4670</v>
       </c>
       <c r="H6" s="58">
@@ -38456,15 +38508,15 @@
         <v>85</v>
       </c>
       <c r="E7" s="60">
-        <f>+[84]Main!$I$3</f>
+        <f>+[85]Main!$I$3</f>
         <v>140.1</v>
       </c>
       <c r="F7" s="58">
-        <f>+[84]Main!$I$5*FX!C7</f>
+        <f>+[85]Main!$I$5*FX!C7</f>
         <v>8097.3307833600002</v>
       </c>
       <c r="G7" s="58">
-        <f>+([84]Main!$I$7-[84]Main!$I$6)*FX!C7</f>
+        <f>+([85]Main!$I$7-[85]Main!$I$6)*FX!C7</f>
         <v>-1219.68</v>
       </c>
       <c r="H7" s="58">

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99E08C0-DC38-4BCB-BF76-9B824A2C8E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43C0FE8-803E-44A9-A1FA-5FAD1CE17E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="824">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -1534,12 +1534,6 @@
     <t>Resort/Cruise</t>
   </si>
   <si>
-    <t>Mai/Juni</t>
-  </si>
-  <si>
-    <t>November/Dezember</t>
-  </si>
-  <si>
     <t>Haupt-Kollektion September/Oktober</t>
   </si>
   <si>
@@ -2603,6 +2597,18 @@
   </si>
   <si>
     <t>Q325</t>
+  </si>
+  <si>
+    <t>Nebenkollektion November/Dezember</t>
+  </si>
+  <si>
+    <t>Nebenkollektion Mai/Juni</t>
+  </si>
+  <si>
+    <t>androgyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vereinigung von weiblichen und männlichen Elementen </t>
   </si>
 </sst>
 </file>
@@ -2616,13 +2622,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2760,22 +2772,103 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2795,132 +2888,52 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
@@ -4228,7 +4241,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4416,17 +4429,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>70.400000000000006</v>
+            <v>86.42</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>7939.9936000000007</v>
+            <v>9891.3739399999995</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>207.00700000000001</v>
+            <v>292.61099999999999</v>
           </cell>
         </row>
         <row r="6">
@@ -4435,7 +4448,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4575,21 +4588,21 @@
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3020.8319999999999</v>
+            <v>3001.5878640000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>283.89999999999998</v>
+            <v>292.60000000000002</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1307.1999999999998</v>
+            <v>1343.9</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4771,22 +4784,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>82.63</v>
+            <v>88.25</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>3972.2819055999998</v>
+            <v>4246.5707615000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>191</v>
+            <v>248.8</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>2347.3000000000002</v>
+            <v>2256</v>
           </cell>
         </row>
       </sheetData>
@@ -5278,22 +5291,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>34.99</v>
+            <v>26.13</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2750.9694340999999</v>
+            <v>2094.6979930499997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>161</v>
+            <v>188</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1418</v>
+            <v>1052</v>
           </cell>
         </row>
       </sheetData>
@@ -5317,22 +5330,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>37.49</v>
+            <v>33.92</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>2706.44148976</v>
+            <v>2464.3691366400003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>150.47799999999998</v>
+            <v>111.31400000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>0</v>
+            <v>293.49</v>
           </cell>
         </row>
       </sheetData>
@@ -5356,22 +5369,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>17.25</v>
+            <v>19.670000000000002</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2045.4005512499998</v>
+            <v>2341.6752811900001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>166</v>
+            <v>129</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1500</v>
+            <v>1671</v>
           </cell>
         </row>
       </sheetData>
@@ -6790,10 +6803,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>89</v>
@@ -6864,15 +6877,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1767580.9085336619</v>
+        <v>1768579.5668584921</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>19364.686735200008</v>
+        <v>19333.293975200009</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1786945.5952688619</v>
+        <v>1787912.8608336926</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6923,15 +6936,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22661.293699149512</v>
+        <v>22674.09701100631</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>248.26521455384625</v>
+        <v>247.86274327179498</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>22909.558913703357</v>
+        <v>22921.959754278108</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7345,7 +7358,7 @@
         <v>155866</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="J9" s="28">
         <v>45980</v>
@@ -7515,7 +7528,7 @@
         <v>101145.31</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="J11" s="28">
         <v>45930</v>
@@ -7697,7 +7710,7 @@
         <v>89405.746979000003</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="J13" s="28">
         <v>45924</v>
@@ -7772,7 +7785,7 @@
         <v>46200.047905979998</v>
       </c>
       <c r="I14" s="27" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="J14" s="28">
         <v>45981</v>
@@ -8176,7 +8189,7 @@
         <v>16062.453125000002</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="J19" s="28">
         <v>45953</v>
@@ -8247,7 +8260,7 @@
         <v>31318.476624999996</v>
       </c>
       <c r="I20" s="27" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="J20" s="28">
         <v>46051</v>
@@ -8500,7 +8513,7 @@
         <v>18910.983003599998</v>
       </c>
       <c r="I24" s="27" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="J24" s="28">
         <v>45897</v>
@@ -8941,7 +8954,7 @@
         <v>17673.234662639996</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="J31" s="28">
         <v>45916</v>
@@ -9161,7 +9174,7 @@
         <v>9041.9433313400004</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J34" s="28">
         <v>45957</v>
@@ -9265,7 +9278,7 @@
         <v>111</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>21</v>
@@ -9365,7 +9378,7 @@
         <v>337</v>
       </c>
       <c r="J37" s="32" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="K37" s="19"/>
       <c r="L37" s="23"/>
@@ -9744,7 +9757,7 @@
         <v>5139.9465440399999</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J43" s="28">
         <v>45975</v>
@@ -9977,24 +9990,26 @@
       </c>
       <c r="E47" s="26">
         <f>+[42]Main!$H$2</f>
-        <v>70.400000000000006</v>
+        <v>86.42</v>
       </c>
       <c r="F47" s="19">
         <f>+[42]Main!$H$4*FX!C13</f>
-        <v>5478.5955839999997</v>
+        <v>6825.0480185999995</v>
       </c>
       <c r="G47" s="19">
         <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
-        <v>-142.83482999999998</v>
+        <v>-201.90158999999997</v>
       </c>
       <c r="H47" s="19">
         <f>+F47+G47</f>
-        <v>5335.7607539999999</v>
+        <v>6623.1464285999991</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="J47" s="3"/>
+        <v>717</v>
+      </c>
+      <c r="J47" s="28">
+        <v>45939</v>
+      </c>
       <c r="K47" s="19"/>
       <c r="L47" s="23"/>
       <c r="M47" s="19"/>
@@ -10167,7 +10182,7 @@
         <v>5728.3105543299998</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="J50" s="28">
         <v>45986</v>
@@ -10215,21 +10230,21 @@
       </c>
       <c r="F51" s="19">
         <f>+[46]Main!$I$4*FX!C3</f>
-        <v>3141.6652800000002</v>
+        <v>3121.65137856</v>
       </c>
       <c r="G51" s="19">
         <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
-        <v>1064.232</v>
+        <v>1093.3520000000003</v>
       </c>
       <c r="H51" s="19">
         <f t="shared" si="3"/>
-        <v>4205.8972800000001</v>
+        <v>4215.0033785600008</v>
       </c>
       <c r="I51" s="18" t="s">
-        <v>432</v>
+        <v>149</v>
       </c>
       <c r="J51" s="28">
-        <v>45869</v>
+        <v>45960</v>
       </c>
       <c r="K51" s="19"/>
       <c r="L51" s="23"/>
@@ -10475,25 +10490,25 @@
       </c>
       <c r="E55" s="26">
         <f>+[50]Main!$J$2</f>
-        <v>82.63</v>
+        <v>88.25</v>
       </c>
       <c r="F55" s="19">
         <f>+[50]Main!$J$4</f>
-        <v>3972.2819055999998</v>
+        <v>4246.5707615000001</v>
       </c>
       <c r="G55" s="19">
         <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
-        <v>2156.3000000000002</v>
+        <v>2007.2</v>
       </c>
       <c r="H55" s="19">
         <f>F55+G55</f>
-        <v>6128.5819056</v>
+        <v>6253.7707614999999</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>432</v>
+        <v>149</v>
       </c>
       <c r="J55" s="28">
-        <v>45896</v>
+        <v>45995</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="23"/>
@@ -10948,7 +10963,7 @@
         <v>53</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>82</v>
@@ -11189,25 +11204,25 @@
       </c>
       <c r="E67" s="26">
         <f>+[62]Main!$I$2</f>
-        <v>34.99</v>
+        <v>26.13</v>
       </c>
       <c r="F67" s="19">
         <f>+[62]Main!$I$4</f>
-        <v>2750.9694340999999</v>
+        <v>2094.6979930499997</v>
       </c>
       <c r="G67" s="19">
         <f>+[62]Main!$I$6-[62]Main!$I$5</f>
-        <v>1257</v>
+        <v>864</v>
       </c>
       <c r="H67" s="19">
         <f>F67+G67</f>
-        <v>4007.9694340999999</v>
+        <v>2958.6979930499997</v>
       </c>
       <c r="I67" s="27" t="s">
-        <v>337</v>
+        <v>149</v>
       </c>
       <c r="J67" s="28">
-        <v>45722</v>
+        <v>45996</v>
       </c>
       <c r="K67" s="26"/>
       <c r="L67" s="23"/>
@@ -11252,24 +11267,26 @@
       </c>
       <c r="E68" s="26">
         <f>+[63]Main!$H$2</f>
-        <v>37.49</v>
+        <v>33.92</v>
       </c>
       <c r="F68" s="19">
         <f>+[63]Main!$H$4</f>
-        <v>2706.44148976</v>
+        <v>2464.3691366400003</v>
       </c>
       <c r="G68" s="19">
         <f>+[63]Main!$H$6-[63]Main!$H$5</f>
-        <v>-150.47799999999998</v>
+        <v>182.17599999999999</v>
       </c>
       <c r="H68" s="19">
         <f>+F68+G68</f>
-        <v>2555.9634897599999</v>
+        <v>2646.5451366400002</v>
       </c>
       <c r="I68" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="J68" s="3"/>
+        <v>149</v>
+      </c>
+      <c r="J68" s="28">
+        <v>45967</v>
+      </c>
       <c r="K68" s="19"/>
       <c r="L68" s="23"/>
       <c r="M68" s="19"/>
@@ -11309,19 +11326,19 @@
       </c>
       <c r="E69" s="26">
         <f>+[64]Main!$I$2</f>
-        <v>17.25</v>
+        <v>19.670000000000002</v>
       </c>
       <c r="F69" s="19">
         <f>+[64]Main!$I$4</f>
-        <v>2045.4005512499998</v>
+        <v>2341.6752811900001</v>
       </c>
       <c r="G69" s="19">
         <f>+[64]Main!$I$6-[64]Main!$I$5</f>
-        <v>1334</v>
+        <v>1542</v>
       </c>
       <c r="H69" s="19">
         <f>+F69+G69</f>
-        <v>3379.4005512499998</v>
+        <v>3883.6752811900001</v>
       </c>
       <c r="I69" s="18" t="s">
         <v>380</v>
@@ -12642,7 +12659,7 @@
         <v>1178.0758231121999</v>
       </c>
       <c r="I97" s="18" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J97" s="28"/>
       <c r="K97" s="19"/>
@@ -15150,10 +15167,10 @@
         <v>149</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>124</v>
@@ -15207,10 +15224,10 @@
         <v>150</v>
       </c>
       <c r="B155" s="25" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>21</v>
@@ -15266,10 +15283,10 @@
         <v>151</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>124</v>
@@ -15309,10 +15326,10 @@
         <v>152</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>21</v>
@@ -15352,10 +15369,10 @@
         <v>153</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>124</v>
@@ -15395,10 +15412,10 @@
         <v>154</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>21</v>
@@ -15438,10 +15455,10 @@
         <v>155</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>294</v>
@@ -15481,10 +15498,10 @@
         <v>156</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>156</v>
@@ -15524,10 +15541,10 @@
         <v>157</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>185</v>
@@ -15567,10 +15584,10 @@
         <v>158</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>21</v>
@@ -15610,10 +15627,10 @@
         <v>159</v>
       </c>
       <c r="B164" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>501</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>21</v>
@@ -15653,10 +15670,10 @@
         <v>160</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>502</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>156</v>
@@ -15696,10 +15713,10 @@
         <v>161</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>352</v>
@@ -15739,10 +15756,10 @@
         <v>162</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>21</v>
@@ -15782,13 +15799,13 @@
         <v>163</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>378</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E168" s="26"/>
       <c r="F168" s="19"/>
@@ -15825,10 +15842,10 @@
         <v>164</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>21</v>
@@ -15868,10 +15885,10 @@
         <v>165</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>21</v>
@@ -15911,10 +15928,10 @@
         <v>166</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>219</v>
@@ -15954,10 +15971,10 @@
         <v>167</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>185</v>
@@ -15997,10 +16014,10 @@
         <v>168</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>21</v>
@@ -16040,10 +16057,10 @@
         <v>169</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>21</v>
@@ -16083,10 +16100,10 @@
         <v>170</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>21</v>
@@ -16126,10 +16143,10 @@
         <v>171</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>21</v>
@@ -16169,10 +16186,10 @@
         <v>172</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>21</v>
@@ -16212,13 +16229,13 @@
         <v>173</v>
       </c>
       <c r="B178" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="C178" s="4" t="s">
-        <v>529</v>
-      </c>
       <c r="D178" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E178" s="26"/>
       <c r="F178" s="19"/>
@@ -16255,10 +16272,10 @@
         <v>174</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>21</v>
@@ -16298,10 +16315,10 @@
         <v>175</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>21</v>
@@ -16341,10 +16358,10 @@
         <v>176</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>21</v>
@@ -17376,13 +17393,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="47" t="s">
+        <v>723</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>724</v>
+      </c>
+      <c r="E2" s="47" t="s">
         <v>725</v>
-      </c>
-      <c r="D2" s="47" t="s">
-        <v>726</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>727</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>126</v>
@@ -17401,16 +17418,16 @@
     <row r="3" spans="1:16">
       <c r="A3" s="47"/>
       <c r="B3" s="47" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -17427,16 +17444,16 @@
     <row r="4" spans="1:16">
       <c r="A4" s="47"/>
       <c r="B4" s="47" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="47"/>
@@ -17453,19 +17470,19 @@
     <row r="5" spans="1:16">
       <c r="A5" s="47"/>
       <c r="B5" s="47" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G5" s="47"/>
       <c r="H5" s="47"/>
@@ -17481,16 +17498,16 @@
     <row r="6" spans="1:16">
       <c r="A6" s="47"/>
       <c r="B6" s="47" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -17507,19 +17524,19 @@
     <row r="7" spans="1:16">
       <c r="A7" s="47"/>
       <c r="B7" s="47" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
@@ -17538,16 +17555,16 @@
         <v>135</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>135</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="47"/>
@@ -17563,19 +17580,19 @@
     <row r="9" spans="1:16">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
+        <v>753</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>754</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>682</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>752</v>
+      </c>
+      <c r="F9" s="47" t="s">
         <v>755</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>756</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>684</v>
-      </c>
-      <c r="E9" s="47" t="s">
-        <v>754</v>
-      </c>
-      <c r="F9" s="47" t="s">
-        <v>757</v>
       </c>
       <c r="G9" s="47"/>
       <c r="H9" s="47"/>
@@ -17591,19 +17608,19 @@
     <row r="10" spans="1:16">
       <c r="A10" s="47"/>
       <c r="B10" s="47" t="s">
+        <v>756</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>757</v>
+      </c>
+      <c r="D10" s="47" t="s">
         <v>758</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="E10" s="47" t="s">
+        <v>752</v>
+      </c>
+      <c r="F10" s="47" t="s">
         <v>759</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>760</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>754</v>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>761</v>
       </c>
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
@@ -17619,19 +17636,19 @@
     <row r="11" spans="1:16">
       <c r="A11" s="47"/>
       <c r="B11" s="47" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G11" s="47"/>
       <c r="H11" s="47"/>
@@ -17647,19 +17664,19 @@
     <row r="12" spans="1:16">
       <c r="A12" s="47"/>
       <c r="B12" s="47" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D12" s="47" t="s">
         <v>123</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G12" s="47"/>
       <c r="H12" s="47"/>
@@ -17675,16 +17692,16 @@
     <row r="13" spans="1:16">
       <c r="A13" s="47"/>
       <c r="B13" s="47" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>135</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="F13" s="47"/>
       <c r="G13" s="47"/>
@@ -17701,16 +17718,16 @@
     <row r="14" spans="1:16">
       <c r="A14" s="47"/>
       <c r="B14" s="47" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F14" s="47"/>
       <c r="G14" s="47"/>
@@ -17727,16 +17744,16 @@
     <row r="15" spans="1:16">
       <c r="A15" s="47"/>
       <c r="B15" s="47" t="s">
+        <v>773</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>774</v>
+      </c>
+      <c r="D15" s="47" t="s">
         <v>775</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="E15" s="47" t="s">
         <v>776</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>777</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>778</v>
       </c>
       <c r="F15" s="47"/>
       <c r="G15" s="47"/>
@@ -17753,19 +17770,19 @@
     <row r="16" spans="1:16">
       <c r="A16" s="47"/>
       <c r="B16" s="47" t="s">
+        <v>778</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>779</v>
+      </c>
+      <c r="D16" s="47" t="s">
         <v>780</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="E16" s="47" t="s">
         <v>781</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="F16" s="47" t="s">
         <v>782</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>783</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>784</v>
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="47"/>
@@ -17781,16 +17798,16 @@
     <row r="17" spans="1:16">
       <c r="A17" s="47"/>
       <c r="B17" s="47" t="s">
+        <v>783</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>784</v>
+      </c>
+      <c r="D17" s="47" t="s">
         <v>785</v>
       </c>
-      <c r="C17" s="47" t="s">
-        <v>786</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>787</v>
-      </c>
       <c r="E17" s="47" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="F17" s="47"/>
       <c r="G17" s="47"/>
@@ -17842,7 +17859,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="76" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B20" s="76"/>
       <c r="C20" s="47"/>
@@ -17863,10 +17880,10 @@
     <row r="21" spans="1:16">
       <c r="A21" s="47"/>
       <c r="B21" s="47" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -17885,10 +17902,10 @@
     <row r="22" spans="1:16">
       <c r="A22" s="47"/>
       <c r="B22" s="47" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
@@ -17907,10 +17924,10 @@
     <row r="23" spans="1:16">
       <c r="A23" s="47"/>
       <c r="B23" s="47" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
@@ -17929,10 +17946,10 @@
     <row r="24" spans="1:16">
       <c r="A24" s="47"/>
       <c r="B24" s="47" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D24" s="47"/>
       <c r="E24" s="47"/>
@@ -17954,7 +17971,7 @@
         <v>98</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D25" s="47"/>
       <c r="E25" s="47"/>
@@ -17973,10 +17990,10 @@
     <row r="26" spans="1:16">
       <c r="A26" s="47"/>
       <c r="B26" s="47" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D26" s="47"/>
       <c r="E26" s="47"/>
@@ -17995,10 +18012,10 @@
     <row r="27" spans="1:16">
       <c r="A27" s="47"/>
       <c r="B27" s="47" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D27" s="47"/>
       <c r="E27" s="47"/>
@@ -18017,10 +18034,10 @@
     <row r="28" spans="1:16">
       <c r="A28" s="47"/>
       <c r="B28" s="47" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
@@ -18087,7 +18104,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="47" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -18148,7 +18165,7 @@
     <row r="3" spans="1:17">
       <c r="A3" s="47"/>
       <c r="B3" s="74" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="47"/>
@@ -18172,7 +18189,7 @@
         <v>434</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D4" s="47"/>
       <c r="E4" s="60"/>
@@ -18192,16 +18209,16 @@
     <row r="5" spans="1:17">
       <c r="A5" s="47"/>
       <c r="B5" s="47" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>124</v>
       </c>
       <c r="E5" s="60" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F5" s="58"/>
       <c r="G5" s="58"/>
@@ -18219,7 +18236,7 @@
     <row r="6" spans="1:17">
       <c r="A6" s="47"/>
       <c r="B6" s="47" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="47"/>
@@ -18240,7 +18257,7 @@
     <row r="7" spans="1:17">
       <c r="A7" s="47"/>
       <c r="B7" s="47" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C7" s="59"/>
       <c r="D7" s="47"/>
@@ -18261,7 +18278,7 @@
     <row r="8" spans="1:17">
       <c r="A8" s="47"/>
       <c r="B8" s="47" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C8" s="59"/>
       <c r="D8" s="47"/>
@@ -18282,7 +18299,7 @@
     <row r="9" spans="1:17">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="47"/>
@@ -18303,7 +18320,7 @@
     <row r="10" spans="1:17">
       <c r="A10" s="47"/>
       <c r="B10" s="47" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C10" s="59"/>
       <c r="D10" s="47"/>
@@ -18324,7 +18341,7 @@
     <row r="11" spans="1:17">
       <c r="A11" s="47"/>
       <c r="B11" s="47" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C11" s="59"/>
       <c r="D11" s="47"/>
@@ -18345,7 +18362,7 @@
     <row r="12" spans="1:17">
       <c r="A12" s="47"/>
       <c r="B12" s="47" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C12" s="59"/>
       <c r="D12" s="47"/>
@@ -18366,7 +18383,7 @@
     <row r="13" spans="1:17">
       <c r="A13" s="47"/>
       <c r="B13" s="47" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C13" s="47"/>
       <c r="D13" s="47"/>
@@ -18387,7 +18404,7 @@
     <row r="14" spans="1:17">
       <c r="A14" s="47"/>
       <c r="B14" s="47" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C14" s="59"/>
       <c r="D14" s="47"/>
@@ -18408,7 +18425,7 @@
     <row r="15" spans="1:17">
       <c r="A15" s="47"/>
       <c r="B15" s="47" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C15" s="59"/>
       <c r="D15" s="47"/>
@@ -18429,7 +18446,7 @@
     <row r="16" spans="1:17">
       <c r="A16" s="47"/>
       <c r="B16" s="47" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C16" s="59"/>
       <c r="D16" s="47"/>
@@ -18450,7 +18467,7 @@
     <row r="17" spans="1:17">
       <c r="A17" s="47"/>
       <c r="B17" s="47" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C17" s="59"/>
       <c r="D17" s="47"/>
@@ -18471,14 +18488,14 @@
     <row r="18" spans="1:17">
       <c r="A18" s="47"/>
       <c r="B18" s="47" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D18" s="47"/>
       <c r="E18" s="60" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="58"/>
@@ -18897,13 +18914,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C6" s="47" t="s">
         <v>106</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E6" s="47"/>
       <c r="F6" s="58"/>
@@ -18946,7 +18963,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C7" s="59" t="s">
         <v>447</v>
@@ -18995,7 +19012,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C8" s="47" t="s">
         <v>17</v>
@@ -19093,7 +19110,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C10" s="47" t="s">
         <v>23</v>
@@ -19191,7 +19208,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C12" s="47" t="s">
         <v>29</v>
@@ -19246,7 +19263,7 @@
         <v>39</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E13" s="47"/>
       <c r="F13" s="58"/>
@@ -19485,7 +19502,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C18" s="47" t="s">
         <v>280</v>
@@ -19534,10 +19551,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>21</v>
@@ -19583,10 +19600,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>21</v>
@@ -19646,10 +19663,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C21" s="59" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D21" s="47" t="s">
         <v>124</v>
@@ -19695,10 +19712,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D22" s="47" t="s">
         <v>124</v>
@@ -19744,16 +19761,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D23" s="47" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F23" s="58"/>
       <c r="G23" s="58"/>
@@ -19795,10 +19812,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D24" s="47" t="s">
         <v>21</v>
@@ -19844,10 +19861,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D25" s="47" t="s">
         <v>21</v>
@@ -19893,7 +19910,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C26" s="47" t="s">
         <v>43</v>
@@ -19942,10 +19959,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D27" s="47" t="s">
         <v>21</v>
@@ -19991,10 +20008,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D28" s="47" t="s">
         <v>165</v>
@@ -20040,7 +20057,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C29" s="47" t="s">
         <v>162</v>
@@ -20089,10 +20106,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D30" s="47" t="s">
         <v>21</v>
@@ -20138,10 +20155,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>21</v>
@@ -20187,10 +20204,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D32" s="47" t="s">
         <v>21</v>
@@ -20236,13 +20253,13 @@
         <v>30</v>
       </c>
       <c r="B33" s="47" t="s">
+        <v>525</v>
+      </c>
+      <c r="C33" s="47" t="s">
         <v>527</v>
       </c>
-      <c r="C33" s="47" t="s">
-        <v>529</v>
-      </c>
       <c r="D33" s="47" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E33" s="47"/>
       <c r="F33" s="58"/>
@@ -20285,10 +20302,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D34" s="47" t="s">
         <v>21</v>
@@ -20334,10 +20351,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D35" s="47" t="s">
         <v>21</v>
@@ -20383,10 +20400,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="47" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D36" s="47" t="s">
         <v>21</v>
@@ -38394,7 +38411,7 @@
         <v>95429.722976000019</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J5" s="62">
         <v>45975</v>
@@ -38435,10 +38452,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="46" t="s">
+        <v>697</v>
+      </c>
+      <c r="C6" s="59" t="s">
         <v>699</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>701</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>21</v>
@@ -39666,7 +39683,7 @@
         <v>429</v>
       </c>
       <c r="C30" s="59" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D30" s="47"/>
       <c r="E30" s="60"/>
@@ -39711,10 +39728,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C31" s="59" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>124</v>
@@ -39761,10 +39778,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C32" s="59" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D32" s="47" t="s">
         <v>21</v>
@@ -39811,10 +39828,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C33" s="59" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D33" s="47" t="s">
         <v>82</v>
@@ -39861,13 +39878,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="47" t="s">
+        <v>540</v>
+      </c>
+      <c r="C34" s="59" t="s">
+        <v>541</v>
+      </c>
+      <c r="D34" s="47" t="s">
         <v>542</v>
-      </c>
-      <c r="C34" s="59" t="s">
-        <v>543</v>
-      </c>
-      <c r="D34" s="47" t="s">
-        <v>544</v>
       </c>
       <c r="E34" s="47"/>
       <c r="F34" s="47"/>
@@ -39911,10 +39928,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C35" s="59" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D35" s="47" t="s">
         <v>21</v>
@@ -39961,10 +39978,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="47" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C36" s="59" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D36" s="47" t="s">
         <v>21</v>
@@ -40011,10 +40028,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="47" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C37" s="59" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D37" s="47" t="s">
         <v>109</v>
@@ -40061,10 +40078,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="47" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C38" s="59" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D38" s="47" t="s">
         <v>124</v>
@@ -40111,10 +40128,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="47" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C39" s="59" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D39" s="47" t="s">
         <v>165</v>
@@ -40161,13 +40178,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="47" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C40" s="59" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D40" s="47" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E40" s="47"/>
       <c r="F40" s="47"/>
@@ -40211,10 +40228,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="47" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C41" s="59" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D41" s="47" t="s">
         <v>82</v>
@@ -40261,10 +40278,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="47" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C42" s="59" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D42" s="47" t="s">
         <v>21</v>
@@ -40311,10 +40328,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="47" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C43" s="59" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D43" s="47" t="s">
         <v>219</v>
@@ -40361,10 +40378,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="47" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C44" s="59" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D44" s="47" t="s">
         <v>21</v>
@@ -40411,10 +40428,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="47" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D45" s="47" t="s">
         <v>85</v>
@@ -40461,10 +40478,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="47" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C46" s="47" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D46" s="47" t="s">
         <v>21</v>
@@ -40511,10 +40528,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="47" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D47" s="47" t="s">
         <v>82</v>
@@ -40561,10 +40578,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="47" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C48" s="47" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D48" s="47" t="s">
         <v>100</v>
@@ -40661,10 +40678,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="47" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D50" s="47" t="s">
         <v>21</v>
@@ -40711,10 +40728,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="47" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="D51" s="47" t="s">
         <v>20</v>
@@ -40761,10 +40778,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="47" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D52" s="47" t="s">
         <v>124</v>
@@ -40811,10 +40828,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="47" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D53" s="47" t="s">
         <v>223</v>
@@ -40861,13 +40878,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="47" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C54" s="47" t="s">
+        <v>576</v>
+      </c>
+      <c r="D54" s="47" t="s">
         <v>578</v>
-      </c>
-      <c r="D54" s="47" t="s">
-        <v>580</v>
       </c>
       <c r="E54" s="47"/>
       <c r="F54" s="47"/>
@@ -42882,10 +42899,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>21</v>
@@ -42929,10 +42946,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>21</v>
@@ -42976,10 +42993,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>21</v>
@@ -43023,10 +43040,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>352</v>
@@ -43070,10 +43087,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>21</v>
@@ -43117,10 +43134,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>21</v>
@@ -43164,10 +43181,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D10" s="47" t="s">
         <v>21</v>
@@ -43211,10 +43228,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>21</v>
@@ -43258,10 +43275,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D12" s="47" t="s">
         <v>109</v>
@@ -43305,10 +43322,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>21</v>
@@ -43352,10 +43369,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>21</v>
@@ -43399,13 +43416,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D15" s="47" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E15" s="47"/>
       <c r="F15" s="47"/>
@@ -43446,10 +43463,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D16" s="47" t="s">
         <v>21</v>
@@ -43493,10 +43510,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>352</v>
@@ -43540,13 +43557,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E18" s="47"/>
       <c r="F18" s="47"/>
@@ -43587,10 +43604,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>21</v>
@@ -43634,10 +43651,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>223</v>
@@ -43681,13 +43698,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E21" s="47"/>
       <c r="F21" s="47"/>
@@ -43728,7 +43745,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="47"/>
@@ -43771,10 +43788,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D23" s="47" t="s">
         <v>124</v>
@@ -43818,13 +43835,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D24" s="47" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E24" s="47"/>
       <c r="F24" s="47"/>
@@ -43865,10 +43882,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D25" s="47" t="s">
         <v>219</v>
@@ -43912,13 +43929,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E26" s="47"/>
       <c r="F26" s="47"/>
@@ -43959,10 +43976,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D27" s="47" t="s">
         <v>21</v>
@@ -44006,10 +44023,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D28" s="47" t="s">
         <v>82</v>
@@ -44053,10 +44070,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D29" s="47" t="s">
         <v>21</v>
@@ -44100,10 +44117,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D30" s="47" t="s">
         <v>109</v>
@@ -44147,10 +44164,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C31" s="47" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>165</v>
@@ -44194,13 +44211,13 @@
         <v>29</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E32" s="47"/>
       <c r="F32" s="47"/>
@@ -44241,10 +44258,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D33" s="47" t="s">
         <v>21</v>
@@ -44288,10 +44305,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D34" s="47" t="s">
         <v>82</v>
@@ -44335,10 +44352,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D35" s="47" t="s">
         <v>21</v>
@@ -44382,10 +44399,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="47" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D36" s="47" t="s">
         <v>21</v>
@@ -44429,13 +44446,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="47" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D37" s="47" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E37" s="47"/>
       <c r="F37" s="47"/>
@@ -44476,13 +44493,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="47" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D38" s="47" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E38" s="47"/>
       <c r="F38" s="47"/>
@@ -44523,10 +44540,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="47" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C39" s="47" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D39" s="47" t="s">
         <v>21</v>
@@ -44570,10 +44587,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="47" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C40" s="47" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D40" s="47" t="s">
         <v>454</v>
@@ -44617,10 +44634,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="47" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D41" s="47" t="s">
         <v>21</v>
@@ -44664,10 +44681,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="47" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C42" s="47" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D42" s="47" t="s">
         <v>21</v>
@@ -44711,13 +44728,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="47" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D43" s="47" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E43" s="47"/>
       <c r="F43" s="47"/>
@@ -44758,10 +44775,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="47" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C44" s="47" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D44" s="47" t="s">
         <v>165</v>
@@ -44805,13 +44822,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="47" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D45" s="47" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E45" s="47"/>
       <c r="F45" s="47"/>
@@ -44852,10 +44869,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="47" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C46" s="47" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D46" s="47" t="s">
         <v>21</v>
@@ -44899,10 +44916,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="47" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D47" s="47" t="s">
         <v>21</v>
@@ -44946,10 +44963,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="47" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C48" s="47" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D48" s="47" t="s">
         <v>21</v>
@@ -49127,7 +49144,7 @@
         <v>461</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D6" s="47"/>
       <c r="E6" s="47"/>
@@ -49143,7 +49160,7 @@
         <v>462</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D7" s="47"/>
       <c r="E7" s="47"/>
@@ -49158,8 +49175,8 @@
       <c r="B8" s="47" t="s">
         <v>463</v>
       </c>
-      <c r="C8" s="47" t="s">
-        <v>465</v>
+      <c r="C8" s="81" t="s">
+        <v>821</v>
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="47"/>
@@ -49174,8 +49191,8 @@
       <c r="B9" s="47" t="s">
         <v>464</v>
       </c>
-      <c r="C9" s="47" t="s">
-        <v>466</v>
+      <c r="C9" s="81" t="s">
+        <v>820</v>
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="47"/>
@@ -49188,10 +49205,10 @@
     </row>
     <row r="10" spans="2:11">
       <c r="B10" s="47" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D10" s="47"/>
       <c r="E10" s="47"/>
@@ -49204,10 +49221,10 @@
     </row>
     <row r="11" spans="2:11">
       <c r="B11" s="47" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D11" s="47"/>
       <c r="E11" s="47"/>
@@ -49220,10 +49237,10 @@
     </row>
     <row r="12" spans="2:11">
       <c r="B12" s="47" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D12" s="47"/>
       <c r="E12" s="47"/>
@@ -49235,8 +49252,12 @@
       <c r="K12" s="47"/>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
+      <c r="B13" s="81" t="s">
+        <v>822</v>
+      </c>
+      <c r="C13" s="81" t="s">
+        <v>823</v>
+      </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
       <c r="F13" s="47"/>
@@ -49433,19 +49454,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D2" s="76" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E2" s="76" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F2" s="77" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="H2" s="77" t="s">
         <v>126</v>
@@ -49478,19 +49499,19 @@
     <row r="3" spans="1:32">
       <c r="A3" s="47"/>
       <c r="B3" s="47" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E3" s="78">
         <v>45757</v>
       </c>
       <c r="F3" s="79" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G3" s="79">
         <v>1250</v>
@@ -49524,25 +49545,25 @@
     <row r="4" spans="1:32">
       <c r="A4" s="47"/>
       <c r="B4" s="47" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E4" s="78">
         <v>45782</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G4" s="80">
         <v>9420</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="I4" s="47"/>
       <c r="J4" s="47"/>
@@ -49578,13 +49599,13 @@
         <v>128</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E5" s="78">
         <v>45637</v>
       </c>
       <c r="F5" s="79" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G5" s="80">
         <v>1100</v>
@@ -49618,13 +49639,13 @@
     <row r="6" spans="1:32">
       <c r="A6" s="47"/>
       <c r="B6" s="47" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E6" s="47"/>
       <c r="F6" s="47"/>
@@ -49664,7 +49685,7 @@
         <v>191</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E7" s="78">
         <v>45889</v>
@@ -49673,10 +49694,10 @@
         <v>16.75</v>
       </c>
       <c r="G7" s="47" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="H7" s="47" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="I7" s="47"/>
       <c r="J7" s="47"/>
@@ -49709,10 +49730,10 @@
         <v>420</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E8" s="78">
         <v>45322</v>
@@ -49722,7 +49743,7 @@
         <v>500</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="I8" s="47"/>
       <c r="J8" s="47"/>
@@ -49752,13 +49773,13 @@
     <row r="9" spans="1:32">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="D9" s="47" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E9" s="78">
         <v>45808</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43C0FE8-803E-44A9-A1FA-5FAD1CE17E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E67C82-A3D3-4ADE-9F49-870367ADB1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -4390,22 +4390,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>0.86919999999999997</v>
+            <v>0.93779999999999997</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4483.3335999999999</v>
+            <v>4808.1005999999998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>731</v>
+            <v>531</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>679</v>
+            <v>656</v>
           </cell>
         </row>
       </sheetData>
@@ -4602,7 +4602,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4706,17 +4706,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>82.85</v>
+            <v>52.35</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4693.9495999999999</v>
+            <v>2867.2130074500001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>815.47700000000009</v>
+            <v>578.30700000000002</v>
           </cell>
         </row>
         <row r="6">
@@ -4899,17 +4899,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>137.26</v>
+            <v>165.1</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4194.5283399999998</v>
+            <v>5044.7333572999996</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>152.91399999999999</v>
+            <v>95.319000000000003</v>
           </cell>
         </row>
         <row r="6">
@@ -4938,26 +4938,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>74.06</v>
+            <v>78.680000000000007</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4097.4471148800003</v>
+            <v>4372.5807311200006</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>344.06599999999997</v>
+            <v>107.482</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>740.31500000000005</v>
+            <v>1366.51</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6877,15 +6877,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1768579.5668584921</v>
+        <v>1768280.8799794824</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>19333.293975200009</v>
+        <v>20710.317975200011</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1787912.8608336926</v>
+        <v>1788991.1979546824</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6936,15 +6936,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22674.09701100631</v>
+        <v>22670.267692044647</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>247.86274327179498</v>
+        <v>265.51689711794887</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>22921.959754278108</v>
+        <v>22935.784589162595</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -9927,25 +9927,25 @@
       </c>
       <c r="E46" s="26">
         <f>+[41]Main!$I$2</f>
-        <v>0.86919999999999997</v>
+        <v>0.93779999999999997</v>
       </c>
       <c r="F46" s="19">
         <f>+[41]Main!$I$4*FX!C8</f>
-        <v>5559.3336639999998</v>
+        <v>5962.0447439999998</v>
       </c>
       <c r="G46" s="19">
         <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
-        <v>-64.48</v>
+        <v>155</v>
       </c>
       <c r="H46" s="19">
         <f>F46+G46</f>
-        <v>5494.8536640000002</v>
+        <v>6117.0447439999998</v>
       </c>
       <c r="I46" s="27" t="s">
-        <v>422</v>
+        <v>813</v>
       </c>
       <c r="J46" s="28">
-        <v>45896</v>
+        <v>45981</v>
       </c>
       <c r="K46" s="26"/>
       <c r="L46" s="23"/>
@@ -10427,25 +10427,25 @@
       </c>
       <c r="E54" s="26">
         <f>+[49]Main!$I$2</f>
-        <v>82.85</v>
+        <v>52.35</v>
       </c>
       <c r="F54" s="19">
         <f>+[49]Main!$I$4</f>
-        <v>4693.9495999999999</v>
+        <v>2867.2130074500001</v>
       </c>
       <c r="G54" s="19">
         <f>+[49]Main!$I$6-[49]Main!$I$5</f>
-        <v>-815.47700000000009</v>
+        <v>-578.30700000000002</v>
       </c>
       <c r="H54" s="19">
         <f t="shared" si="3"/>
-        <v>3878.4726000000001</v>
+        <v>2288.9060074500003</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>338</v>
+        <v>149</v>
       </c>
       <c r="J54" s="28">
-        <v>45771</v>
+        <v>45959</v>
       </c>
       <c r="K54" s="19"/>
       <c r="L54" s="23"/>
@@ -10675,25 +10675,25 @@
       </c>
       <c r="E58" s="26">
         <f>+[53]Main!$I$2</f>
-        <v>137.26</v>
+        <v>165.1</v>
       </c>
       <c r="F58" s="19">
         <f>+[53]Main!$I$4</f>
-        <v>4194.5283399999998</v>
+        <v>5044.7333572999996</v>
       </c>
       <c r="G58" s="19">
         <f>+[53]Main!$I$6-[53]Main!$I$5</f>
-        <v>-152.91399999999999</v>
+        <v>-95.319000000000003</v>
       </c>
       <c r="H58" s="19">
         <f t="shared" si="3"/>
-        <v>4041.6143400000001</v>
+        <v>4949.4143572999992</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>380</v>
+        <v>717</v>
       </c>
       <c r="J58" s="28">
-        <v>45791</v>
+        <v>45957</v>
       </c>
       <c r="K58" s="19"/>
       <c r="L58" s="23"/>
@@ -10738,24 +10738,26 @@
       </c>
       <c r="E59" s="26">
         <f>+[54]Main!$I$2</f>
-        <v>74.06</v>
+        <v>78.680000000000007</v>
       </c>
       <c r="F59" s="19">
         <f>+[54]Main!$I$4</f>
-        <v>4097.4471148800003</v>
+        <v>4372.5807311200006</v>
       </c>
       <c r="G59" s="19">
         <f>+[54]Main!$I$6-[54]Main!$I$5</f>
-        <v>396.24900000000008</v>
+        <v>1259.028</v>
       </c>
       <c r="H59" s="19">
         <f t="shared" si="3"/>
-        <v>4493.6961148800001</v>
+        <v>5631.6087311200008</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="J59" s="28"/>
+        <v>149</v>
+      </c>
+      <c r="J59" s="28">
+        <v>45960</v>
+      </c>
       <c r="K59" s="19"/>
       <c r="L59" s="23"/>
       <c r="M59" s="19"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E67C82-A3D3-4ADE-9F49-870367ADB1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EFA1BF-E16A-41B7-B8AB-B21FFE03884D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -111,7 +111,6 @@
     <externalReference r:id="rId94"/>
     <externalReference r:id="rId95"/>
     <externalReference r:id="rId96"/>
-    <externalReference r:id="rId97"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$AE$181</definedName>
@@ -137,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="825">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2609,6 +2608,9 @@
   </si>
   <si>
     <t xml:space="preserve">Vereinigung von weiblichen und männlichen Elementen </t>
+  </si>
+  <si>
+    <t>Private by Nordstorm family</t>
   </si>
 </sst>
 </file>
@@ -3014,12 +3016,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>177.4</v>
+            <v>178.72</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>20129.237746800001</v>
+            <v>20279.01561504</v>
           </cell>
         </row>
         <row r="5">
@@ -4027,12 +4029,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>85.3</v>
+            <v>93</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5799.8605627999996</v>
+            <v>6323.4118679999992</v>
           </cell>
         </row>
         <row r="5">
@@ -4144,26 +4146,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>17935</v>
+            <v>17550</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>33272.832649999997</v>
+            <v>32570.869500000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1643</v>
+            <v>1577</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>2042</v>
+            <v>2262</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4957,52 +4959,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>24.29</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4005.5894754400001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>397</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2617</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5041,7 +5004,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5078,7 +5041,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5117,7 +5080,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5156,52 +5119,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financials"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="CoC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>69.3</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>102335.31</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>9151</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>7961</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5240,7 +5158,52 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financials"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="CoC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>71.94</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>106226.60399999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>8575</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>7996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5277,7 +5240,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5316,7 +5279,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5355,7 +5318,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5394,7 +5357,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5433,7 +5396,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5472,7 +5435,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5511,7 +5474,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5550,7 +5513,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5575,6 +5538,45 @@
         <row r="5">
           <cell r="I5">
             <v>325.44000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>24.73</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1761.5194085300002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>256.60000000000002</v>
           </cell>
         </row>
         <row r="6">
@@ -5657,45 +5659,6 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>24.73</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1761.5194085300002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>256.60000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
             <v>27.07</v>
           </cell>
         </row>
@@ -5721,7 +5684,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5760,7 +5723,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5799,7 +5762,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5838,7 +5801,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5877,7 +5840,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5916,7 +5879,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5955,7 +5918,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5994,7 +5957,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6024,6 +5987,45 @@
         <row r="6">
           <cell r="I6">
             <v>13470</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>29.25</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2376.6897667500002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>141</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>698.5</v>
           </cell>
         </row>
       </sheetData>
@@ -6086,45 +6088,6 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>29.25</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2376.6897667500002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>141</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>698.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
             <v>180.8</v>
           </cell>
         </row>
@@ -6150,7 +6113,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6191,7 +6154,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6232,7 +6195,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6271,7 +6234,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6877,15 +6840,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1768280.8799794824</v>
+        <v>1768685.36494219</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>20710.317975200011</v>
+        <v>19172.817975200011</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1788991.1979546824</v>
+        <v>1787858.1829173903</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6936,15 +6899,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22670.267692044647</v>
+        <v>22969.939804444028</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>265.51689711794887</v>
+        <v>248.99763604155856</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>22935.784589162595</v>
+        <v>23218.937440485588</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7513,25 +7476,25 @@
       </c>
       <c r="E11" s="26">
         <f>+[6]Main!$I$3</f>
-        <v>69.3</v>
+        <v>71.94</v>
       </c>
       <c r="F11" s="19">
         <f>+[6]Main!$I$5</f>
-        <v>102335.31</v>
+        <v>106226.60399999999</v>
       </c>
       <c r="G11" s="19">
         <f>+[6]Main!$I$7-[6]Main!$I$6</f>
-        <v>-1190</v>
+        <v>-579</v>
       </c>
       <c r="H11" s="19">
         <f t="shared" si="1"/>
-        <v>101145.31</v>
+        <v>105647.60399999999</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="J11" s="28">
-        <v>45930</v>
+        <v>46009</v>
       </c>
       <c r="K11" s="19">
         <v>51362</v>
@@ -7845,11 +7808,11 @@
       </c>
       <c r="E15" s="26">
         <f>+[10]Main!$I$2</f>
-        <v>177.4</v>
+        <v>178.72</v>
       </c>
       <c r="F15" s="19">
         <f>+[10]Main!$I$4</f>
-        <v>20129.237746800001</v>
+        <v>20279.01561504</v>
       </c>
       <c r="G15" s="19">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
@@ -7857,7 +7820,7 @@
       </c>
       <c r="H15" s="19">
         <f>F15+G15</f>
-        <v>18973.4437468</v>
+        <v>19123.221615039998</v>
       </c>
       <c r="I15" s="27" t="s">
         <v>149</v>
@@ -9423,11 +9386,11 @@
       </c>
       <c r="E38" s="26">
         <f>+[33]Main!$J$2</f>
-        <v>85.3</v>
+        <v>93</v>
       </c>
       <c r="F38" s="19">
         <f>+[33]Main!$J$4*FX!C3</f>
-        <v>6031.8549853119994</v>
+        <v>6576.348342719999</v>
       </c>
       <c r="G38" s="19">
         <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
@@ -9435,7 +9398,7 @@
       </c>
       <c r="H38" s="19">
         <f>F38+G38</f>
-        <v>5785.5819453119993</v>
+        <v>6330.0753027199989</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>338</v>
@@ -9624,25 +9587,25 @@
       </c>
       <c r="E41" s="26">
         <f>+[36]Main!$I$2</f>
-        <v>17935</v>
+        <v>17550</v>
       </c>
       <c r="F41" s="19">
         <f>+[36]Main!$I$4*FX!C11</f>
-        <v>8318.2081624999992</v>
+        <v>8142.7173750000002</v>
       </c>
       <c r="G41" s="19">
         <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
-        <v>99.75</v>
+        <v>171.25</v>
       </c>
       <c r="H41" s="19">
         <f>+F41+G41</f>
-        <v>8417.9581624999992</v>
+        <v>8313.9673750000002</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>432</v>
+        <v>149</v>
       </c>
       <c r="J41" s="28">
-        <v>45925</v>
+        <v>46002</v>
       </c>
       <c r="K41" s="19"/>
       <c r="L41" s="23"/>
@@ -10799,22 +10762,12 @@
       <c r="D60" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E60" s="26">
-        <f>+[55]Main!$I$2</f>
-        <v>24.29</v>
-      </c>
-      <c r="F60" s="19">
-        <f>+[55]Main!$I$4</f>
-        <v>4005.5894754400001</v>
-      </c>
-      <c r="G60" s="19">
-        <f>+[55]Main!$I$6-[55]Main!$I$5</f>
-        <v>2220</v>
-      </c>
-      <c r="H60" s="19">
-        <f>+F60+G60</f>
-        <v>6225.5894754399997</v>
-      </c>
+      <c r="E60" s="26" t="s">
+        <v>824</v>
+      </c>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
       <c r="I60" s="18"/>
       <c r="J60" s="3"/>
       <c r="K60" s="26"/>
@@ -10857,15 +10810,15 @@
         <v>433</v>
       </c>
       <c r="E61" s="26">
-        <f>+[56]Main!$J$2</f>
+        <f>+[55]Main!$J$2</f>
         <v>132.5</v>
       </c>
       <c r="F61" s="19">
-        <f>+[56]Main!$J$4*FX!C15</f>
+        <f>+[55]Main!$J$4*FX!C15</f>
         <v>3925.244925</v>
       </c>
       <c r="G61" s="19">
-        <f>+([56]Main!$J$6-[56]Main!$J$5)*FX!C15</f>
+        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
         <v>122.75229000000002</v>
       </c>
       <c r="H61" s="19">
@@ -10914,15 +10867,15 @@
         <v>21</v>
       </c>
       <c r="E62" s="26">
-        <f>+[57]Main!$J$2</f>
+        <f>+[56]Main!$J$2</f>
         <v>208.43</v>
       </c>
       <c r="F62" s="19">
-        <f>+[57]Main!$J$4</f>
+        <f>+[56]Main!$J$4</f>
         <v>3869.6348861900005</v>
       </c>
       <c r="G62" s="19">
-        <f>+[57]Main!$J$6-[57]Main!$J$5</f>
+        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
         <v>-180.98000000000002</v>
       </c>
       <c r="H62" s="19">
@@ -10971,15 +10924,15 @@
         <v>82</v>
       </c>
       <c r="E63" s="26">
-        <f>+[58]Main!$J$2</f>
+        <f>+[57]Main!$J$2</f>
         <v>41.48</v>
       </c>
       <c r="F63" s="19">
-        <f>+[58]Main!$J$4*FX!C3</f>
+        <f>+[57]Main!$J$4*FX!C3</f>
         <v>3036.9996799999999</v>
       </c>
       <c r="G63" s="19">
-        <f>+([58]Main!$J$6-[58]Main!$J$5)*FX!C3</f>
+        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
         <v>201.76000000000002</v>
       </c>
       <c r="H63" s="19">
@@ -11030,15 +10983,15 @@
         <v>21</v>
       </c>
       <c r="E64" s="26">
-        <f>+[59]Main!$I$2</f>
+        <f>+[58]Main!$I$2</f>
         <v>5.0599999999999996</v>
       </c>
       <c r="F64" s="19">
-        <f>+[59]Main!$I$4</f>
+        <f>+[58]Main!$I$4</f>
         <v>2169.8306218600001</v>
       </c>
       <c r="G64" s="19">
-        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
+        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
         <v>78.228999999999928</v>
       </c>
       <c r="H64" s="19">
@@ -11089,15 +11042,15 @@
         <v>21</v>
       </c>
       <c r="E65" s="26">
-        <f>+[60]Main!$I$2</f>
+        <f>+[59]Main!$I$2</f>
         <v>14.35</v>
       </c>
       <c r="F65" s="19">
-        <f>+[60]Main!$I$4</f>
+        <f>+[59]Main!$I$4</f>
         <v>2756.6605860499999</v>
       </c>
       <c r="G65" s="19">
-        <f>+[60]Main!$I$6-[60]Main!$I$5</f>
+        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
         <v>-160.19499999999999</v>
       </c>
       <c r="H65" s="19">
@@ -11148,15 +11101,15 @@
         <v>185</v>
       </c>
       <c r="E66" s="26">
-        <f>+[61]Main!$I$2</f>
+        <f>+[60]Main!$I$2</f>
         <v>263.45</v>
       </c>
       <c r="F66" s="19">
-        <f>+[61]Main!$I$4*FX!C12</f>
+        <f>+[60]Main!$I$4*FX!C12</f>
         <v>2976.4027894628493</v>
       </c>
       <c r="G66" s="19">
-        <f>+([61]Main!$I$6-[61]Main!$I$5)*FX!C12</f>
+        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
         <v>26.92503</v>
       </c>
       <c r="H66" s="19">
@@ -11205,15 +11158,15 @@
         <v>21</v>
       </c>
       <c r="E67" s="26">
-        <f>+[62]Main!$I$2</f>
+        <f>+[61]Main!$I$2</f>
         <v>26.13</v>
       </c>
       <c r="F67" s="19">
-        <f>+[62]Main!$I$4</f>
+        <f>+[61]Main!$I$4</f>
         <v>2094.6979930499997</v>
       </c>
       <c r="G67" s="19">
-        <f>+[62]Main!$I$6-[62]Main!$I$5</f>
+        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
         <v>864</v>
       </c>
       <c r="H67" s="19">
@@ -11268,15 +11221,15 @@
         <v>21</v>
       </c>
       <c r="E68" s="26">
-        <f>+[63]Main!$H$2</f>
+        <f>+[62]Main!$H$2</f>
         <v>33.92</v>
       </c>
       <c r="F68" s="19">
-        <f>+[63]Main!$H$4</f>
+        <f>+[62]Main!$H$4</f>
         <v>2464.3691366400003</v>
       </c>
       <c r="G68" s="19">
-        <f>+[63]Main!$H$6-[63]Main!$H$5</f>
+        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
         <v>182.17599999999999</v>
       </c>
       <c r="H68" s="19">
@@ -11327,15 +11280,15 @@
         <v>219</v>
       </c>
       <c r="E69" s="26">
-        <f>+[64]Main!$I$2</f>
+        <f>+[63]Main!$I$2</f>
         <v>19.670000000000002</v>
       </c>
       <c r="F69" s="19">
-        <f>+[64]Main!$I$4</f>
+        <f>+[63]Main!$I$4</f>
         <v>2341.6752811900001</v>
       </c>
       <c r="G69" s="19">
-        <f>+[64]Main!$I$6-[64]Main!$I$5</f>
+        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
         <v>1542</v>
       </c>
       <c r="H69" s="19">
@@ -11390,15 +11343,15 @@
         <v>165</v>
       </c>
       <c r="E70" s="26">
-        <f>+[65]Main!$J$2</f>
+        <f>+[64]Main!$J$2</f>
         <v>9.08</v>
       </c>
       <c r="F70" s="19">
-        <f>+[65]Main!$J$4*FX!C3</f>
+        <f>+[64]Main!$J$4*FX!C3</f>
         <v>2366.7544664192001</v>
       </c>
       <c r="G70" s="19">
-        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C3</f>
+        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
         <v>167.21016000000003</v>
       </c>
       <c r="H70" s="19">
@@ -11449,15 +11402,15 @@
         <v>185</v>
       </c>
       <c r="E71" s="26">
-        <f>+[66]Main!$J$2</f>
+        <f>+[65]Main!$J$2</f>
         <v>828.4</v>
       </c>
       <c r="F71" s="19">
-        <f>+[66]Main!$J$4*FX!C12</f>
+        <f>+[65]Main!$J$4*FX!C12</f>
         <v>2214.6636811287999</v>
       </c>
       <c r="G71" s="19">
-        <f>+([66]Main!$J$6-[66]Main!$J$5)*FX!C12</f>
+        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
         <v>-1.8833099999999996</v>
       </c>
       <c r="H71" s="19">
@@ -11959,15 +11912,15 @@
         <v>21</v>
       </c>
       <c r="E83" s="26">
-        <f>+[67]Main!$I$2</f>
+        <f>+[66]Main!$I$2</f>
         <v>5.82</v>
       </c>
       <c r="F83" s="19">
-        <f>+[67]Main!$I$4</f>
+        <f>+[66]Main!$I$4</f>
         <v>2055.0937514400002</v>
       </c>
       <c r="G83" s="19">
-        <f>+[67]Main!$I$6-[67]Main!$I$5</f>
+        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
         <v>1971.2029999999997</v>
       </c>
       <c r="H83" s="19">
@@ -12227,15 +12180,15 @@
         <v>21</v>
       </c>
       <c r="E89" s="26">
-        <f>+[68]Main!$H$2</f>
+        <f>+[67]Main!$H$2</f>
         <v>41.42</v>
       </c>
       <c r="F89" s="19">
-        <f>+[68]Main!$H$4</f>
+        <f>+[67]Main!$H$4</f>
         <v>1491.5652650000002</v>
       </c>
       <c r="G89" s="19">
-        <f>+[68]Main!$H$6-[68]Main!$H$5</f>
+        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
         <v>85.194000000000017</v>
       </c>
       <c r="H89" s="19">
@@ -12284,15 +12237,15 @@
         <v>21</v>
       </c>
       <c r="E90" s="26">
-        <f>+[69]Main!$I$2</f>
+        <f>+[68]Main!$I$2</f>
         <v>38.119999999999997</v>
       </c>
       <c r="F90" s="19">
-        <f>+[69]Main!$I$4</f>
+        <f>+[68]Main!$I$4</f>
         <v>1935.4971035199997</v>
       </c>
       <c r="G90" s="19">
-        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
+        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
         <v>-325.44000000000005</v>
       </c>
       <c r="H90" s="19">
@@ -12341,15 +12294,15 @@
         <v>21</v>
       </c>
       <c r="E91" s="26">
-        <f>+[70]Main!$I$2</f>
+        <f>+[69]Main!$I$2</f>
         <v>24.73</v>
       </c>
       <c r="F91" s="19">
-        <f>+[70]Main!$I$4</f>
+        <f>+[69]Main!$I$4</f>
         <v>1761.5194085300002</v>
       </c>
       <c r="G91" s="19">
-        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
+        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
         <v>-256.60000000000002</v>
       </c>
       <c r="H91" s="19">
@@ -12531,15 +12484,15 @@
         <v>21</v>
       </c>
       <c r="E95" s="26">
-        <f>+[71]Main!$I$2</f>
+        <f>+[70]Main!$I$2</f>
         <v>27.07</v>
       </c>
       <c r="F95" s="19">
-        <f>+[71]Main!$I$4</f>
+        <f>+[70]Main!$I$4</f>
         <v>1188.01315849</v>
       </c>
       <c r="G95" s="19">
-        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
+        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
         <v>119.48899999999998</v>
       </c>
       <c r="H95" s="19">
@@ -12588,15 +12541,15 @@
         <v>21</v>
       </c>
       <c r="E96" s="26">
-        <f>+[72]Main!$I$2</f>
+        <f>+[71]Main!$I$2</f>
         <v>59.85</v>
       </c>
       <c r="F96" s="19">
-        <f>+[72]Main!$I$4</f>
+        <f>+[71]Main!$I$4</f>
         <v>939.70682505000002</v>
       </c>
       <c r="G96" s="19">
-        <f>+[72]Main!$I$6-[72]Main!$I$5</f>
+        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
         <v>50.789000000000001</v>
       </c>
       <c r="H96" s="19">
@@ -12645,15 +12598,15 @@
         <v>107</v>
       </c>
       <c r="E97" s="26">
-        <f>+[73]Main!$J$2</f>
+        <f>+[72]Main!$J$2</f>
         <v>15.34</v>
       </c>
       <c r="F97" s="19">
-        <f>+[73]Main!$J$4*FX!C13</f>
+        <f>+[72]Main!$J$4*FX!C13</f>
         <v>1025.7928231121998</v>
       </c>
       <c r="G97" s="19">
-        <f>+([73]Main!$J$6-[73]Main!$J$5)*FX!C13</f>
+        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
         <v>152.28300000000002</v>
       </c>
       <c r="H97" s="19">
@@ -12788,15 +12741,15 @@
         <v>21</v>
       </c>
       <c r="E100" s="26">
-        <f>+[74]Main!$I$2</f>
+        <f>+[73]Main!$I$2</f>
         <v>4.53</v>
       </c>
       <c r="F100" s="19">
-        <f>+[74]Main!$I$4</f>
+        <f>+[73]Main!$I$4</f>
         <v>736.21656488999997</v>
       </c>
       <c r="G100" s="19">
-        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
+        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
         <v>-235.51</v>
       </c>
       <c r="H100" s="19">
@@ -12845,15 +12798,15 @@
         <v>21</v>
       </c>
       <c r="E101" s="26">
-        <f>+[75]Main!$I$2</f>
+        <f>+[74]Main!$I$2</f>
         <v>16.75</v>
       </c>
       <c r="F101" s="19">
-        <f>+[75]Main!$I$4</f>
+        <f>+[74]Main!$I$4</f>
         <v>872.38125524999998</v>
       </c>
       <c r="G101" s="19">
-        <f>+[75]Main!$I$6-[75]Main!$I$5</f>
+        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
         <v>434.077</v>
       </c>
       <c r="H101" s="19">
@@ -13504,15 +13457,15 @@
         <v>219</v>
       </c>
       <c r="E116" s="26">
-        <f>+'[76]Main '!$F$2</f>
+        <f>+'[75]Main '!$F$2</f>
         <v>4.3620000000000001</v>
       </c>
       <c r="F116" s="19">
-        <f>+'[76]Main '!$F$4*FX!C8</f>
+        <f>+'[75]Main '!$F$4*FX!C8</f>
         <v>644.11734022080009</v>
       </c>
       <c r="G116" s="19">
-        <f>+('[76]Main '!$F$6-'[76]Main '!$F$5)*FX!C8</f>
+        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
         <v>368.40400000000005</v>
       </c>
       <c r="H116" s="19">
@@ -13817,15 +13770,15 @@
         <v>21</v>
       </c>
       <c r="E123" s="26">
-        <f>+[77]Main!$H$2</f>
+        <f>+[76]Main!$H$2</f>
         <v>2.4</v>
       </c>
       <c r="F123" s="19">
-        <f>+[77]Main!$H$4</f>
+        <f>+[76]Main!$H$4</f>
         <v>252.04949999999997</v>
       </c>
       <c r="G123" s="19">
-        <f>+[77]Main!$H$6-[77]Main!$H$5</f>
+        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
         <v>260.82400000000001</v>
       </c>
       <c r="H123" s="19">
@@ -13917,15 +13870,15 @@
         <v>21</v>
       </c>
       <c r="E125" s="26">
-        <f>+[78]Main!$I$2</f>
+        <f>+[77]Main!$I$2</f>
         <v>17.79</v>
       </c>
       <c r="F125" s="19">
-        <f>+[78]Main!$I$4</f>
+        <f>+[77]Main!$I$4</f>
         <v>270.90115659000003</v>
       </c>
       <c r="G125" s="19">
-        <f>+[78]Main!$I$6-[78]Main!$I$5</f>
+        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
         <v>24.493000000000002</v>
       </c>
       <c r="H125" s="19">
@@ -15178,15 +15131,15 @@
         <v>124</v>
       </c>
       <c r="E154" s="26">
-        <f>+[79]Main!$I$2</f>
+        <f>+[78]Main!$I$2</f>
         <v>2540</v>
       </c>
       <c r="F154" s="19">
-        <f>+[79]Main!$I$4*FX!C5</f>
+        <f>+[78]Main!$I$4*FX!C5</f>
         <v>409.27593709799999</v>
       </c>
       <c r="G154" s="19">
-        <f>+([79]Main!$I$6-[79]Main!$I$5)*FX!C5</f>
+        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
         <v>-123.31619999999999</v>
       </c>
       <c r="H154" s="19">
@@ -15235,15 +15188,15 @@
         <v>21</v>
       </c>
       <c r="E155" s="26">
-        <f>+[80]Main!$J$2</f>
+        <f>+[79]Main!$J$2</f>
         <v>29.25</v>
       </c>
       <c r="F155" s="19">
-        <f>+[80]Main!$J$4</f>
+        <f>+[79]Main!$J$4</f>
         <v>2376.6897667500002</v>
       </c>
       <c r="G155" s="19">
-        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
+        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
         <v>557.5</v>
       </c>
       <c r="H155" s="19">
@@ -19611,15 +19564,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="47">
-        <f>+[81]Main!$J$2</f>
+        <f>+[80]Main!$J$2</f>
         <v>180.8</v>
       </c>
       <c r="F20" s="58">
-        <f>+[81]Main!$J$4</f>
+        <f>+[80]Main!$J$4</f>
         <v>14437.908028799999</v>
       </c>
       <c r="G20" s="58">
-        <f>+[81]Main!$J$6-[81]Main!$J$5</f>
+        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
         <v>-205.72299999999996</v>
       </c>
       <c r="H20" s="58">
@@ -38331,15 +38284,15 @@
         <v>20</v>
       </c>
       <c r="E4" s="60">
-        <f>+[82]Main!$I$2</f>
+        <f>+[81]Main!$I$2</f>
         <v>257.3</v>
       </c>
       <c r="F4" s="58">
-        <f>+[82]Main!$I$4*FX!C3</f>
+        <f>+[81]Main!$I$4*FX!C3</f>
         <v>121467.16982951201</v>
       </c>
       <c r="G4" s="58">
-        <f>+([82]Main!$I$6-[82]Main!$I$5)*FX!C3</f>
+        <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
         <v>7610.72</v>
       </c>
       <c r="H4" s="58">
@@ -38397,15 +38350,15 @@
         <v>85</v>
       </c>
       <c r="E5" s="60">
-        <f>+[83]Main!$J$2</f>
+        <f>+[82]Main!$J$2</f>
         <v>149.9</v>
       </c>
       <c r="F5" s="58">
-        <f>+[83]Main!$J$5*FX!C7</f>
+        <f>+[82]Main!$J$5*FX!C7</f>
         <v>104409.88297600002</v>
       </c>
       <c r="G5" s="58">
-        <f>+([83]Main!$J$7-[83]Main!$J$6)*FX!C7</f>
+        <f>+([82]Main!$J$7-[82]Main!$J$6)*FX!C7</f>
         <v>-8980.1600000000017</v>
       </c>
       <c r="H5" s="58">
@@ -38463,15 +38416,15 @@
         <v>21</v>
       </c>
       <c r="E6" s="60">
-        <f>+[84]Main!$K$2</f>
+        <f>+[83]Main!$K$2</f>
         <v>63.49</v>
       </c>
       <c r="F6" s="58">
-        <f>+[84]Main!$K$4</f>
+        <f>+[83]Main!$K$4</f>
         <v>22840.653210200002</v>
       </c>
       <c r="G6" s="58">
-        <f>+([84]Main!$K$6-[84]Main!$K$5)</f>
+        <f>+([83]Main!$K$6-[83]Main!$K$5)</f>
         <v>4670</v>
       </c>
       <c r="H6" s="58">
@@ -38527,15 +38480,15 @@
         <v>85</v>
       </c>
       <c r="E7" s="60">
-        <f>+[85]Main!$I$3</f>
+        <f>+[84]Main!$I$3</f>
         <v>140.1</v>
       </c>
       <c r="F7" s="58">
-        <f>+[85]Main!$I$5*FX!C7</f>
+        <f>+[84]Main!$I$5*FX!C7</f>
         <v>8097.3307833600002</v>
       </c>
       <c r="G7" s="58">
-        <f>+([85]Main!$I$7-[85]Main!$I$6)*FX!C7</f>
+        <f>+([84]Main!$I$7-[84]Main!$I$6)*FX!C7</f>
         <v>-1219.68</v>
       </c>
       <c r="H7" s="58">

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EFA1BF-E16A-41B7-B8AB-B21FFE03884D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A100C5-FBB5-47A3-8935-BB5110C298CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2972,12 +2972,12 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="I4">
-            <v>513</v>
+            <v>605.70000000000005</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>255699.34345799999</v>
+            <v>301904.66341620003</v>
           </cell>
         </row>
         <row r="7">
@@ -3016,12 +3016,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>178.72</v>
+            <v>174.02</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>20279.01561504</v>
+            <v>19745.715629639999</v>
           </cell>
         </row>
         <row r="5">
@@ -3103,12 +3103,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>216.1</v>
+            <v>331.65</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>26493.762538899999</v>
+            <v>40660.140425849997</v>
           </cell>
         </row>
         <row r="5">
@@ -3188,17 +3188,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="M2">
-            <v>119</v>
+            <v>87.2</v>
           </cell>
         </row>
         <row r="4">
           <cell r="M4">
-            <v>17782.869125000001</v>
+            <v>13030.808300000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>1720.4159999999999</v>
+            <v>1414.479</v>
           </cell>
         </row>
         <row r="6">
@@ -3431,12 +3431,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>2020</v>
+            <v>2186</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>211769.06542</v>
+            <v>229171.86980599997</v>
           </cell>
         </row>
         <row r="5">
@@ -4107,22 +4107,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>21.82</v>
+            <v>22.77</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>8633.1799026200006</v>
+            <v>8899.1889901200011</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>736.7</v>
+            <v>707.5</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1033.7</v>
+            <v>1042.8</v>
           </cell>
         </row>
       </sheetData>
@@ -4165,7 +4165,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4267,30 +4267,30 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>55.783000000000001</v>
+            <v>81.19</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>3046.7200813140003</v>
+            <v>4215.0321918300006</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>200.61099999999999</v>
+            <v>153.97</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1379.1120000000001</v>
+            <v>1318.498</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5012,22 +5012,23 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>208.43</v>
+            <v>161.28</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>3869.6348861900005</v>
+            <v>2990.6024601600002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>180.98000000000002</v>
+            <v>211.91</v>
           </cell>
         </row>
         <row r="6">
@@ -5036,6 +5037,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5371,22 +5373,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>9.08</v>
+            <v>9.6300000000000008</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2275.7254484800001</v>
+            <v>2436.6190977000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>225.316</v>
+            <v>231.22499999999997</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>386.09500000000003</v>
+            <v>348.65300000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -5605,22 +5607,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>43500</v>
+            <v>48290</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>13344857.920500001</v>
+            <v>14814725.010580001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1628202</v>
+            <v>1792940</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>330069</v>
+            <v>315917</v>
           </cell>
         </row>
       </sheetData>
@@ -6840,15 +6842,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1768685.36494219</v>
+        <v>1854268.2672868653</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>19172.817975200011</v>
+        <v>18300.05993520001</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1787858.1829173903</v>
+        <v>1872568.3272220658</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6899,15 +6901,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>22969.939804444028</v>
+        <v>24081.406068660588</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>248.99763604155856</v>
+        <v>237.66311604155857</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>23218.937440485588</v>
+        <v>24319.069184702152</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7000,11 +7002,11 @@
       </c>
       <c r="E6" s="26">
         <f>+[1]Main!$I$4</f>
-        <v>513</v>
+        <v>605.70000000000005</v>
       </c>
       <c r="F6" s="19">
         <f>+[1]Main!$I$6*FX!C3</f>
-        <v>265927.31719631999</v>
+        <v>313980.84995284805</v>
       </c>
       <c r="G6" s="19">
         <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
@@ -7012,13 +7014,13 @@
       </c>
       <c r="H6" s="19">
         <f>F6+G6</f>
-        <v>280700.51719632</v>
+        <v>328754.04995284806</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>149</v>
+        <v>819</v>
       </c>
       <c r="J6" s="28">
-        <v>45944</v>
+        <v>46080</v>
       </c>
       <c r="K6" s="19">
         <f>84683*FX!C3</f>
@@ -7103,11 +7105,11 @@
       </c>
       <c r="E7" s="31">
         <f>+[2]Main!$K$2</f>
-        <v>2020</v>
+        <v>2186</v>
       </c>
       <c r="F7" s="19">
         <f>+[2]Main!$K$4*FX!C3</f>
-        <v>220239.8280368</v>
+        <v>238338.74459823998</v>
       </c>
       <c r="G7" s="19">
         <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
@@ -7115,13 +7117,13 @@
       </c>
       <c r="H7" s="19">
         <f>F7+G7</f>
-        <v>209539.2680368</v>
+        <v>227638.18459823998</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>149</v>
+        <v>819</v>
       </c>
       <c r="J7" s="28">
-        <v>45953</v>
+        <v>46034</v>
       </c>
       <c r="K7" s="19">
         <f>13427*1.08</f>
@@ -7573,25 +7575,25 @@
       </c>
       <c r="E12" s="31">
         <f>+[7]Main!$J$3</f>
-        <v>43500</v>
+        <v>48290</v>
       </c>
       <c r="F12" s="19">
         <f>+[7]Main!$J$5*FX!C5</f>
-        <v>84072.604899149999</v>
+        <v>93332.767566654016</v>
       </c>
       <c r="G12" s="19">
         <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
-        <v>-8178.2379000000001</v>
+        <v>-9305.2448999999997</v>
       </c>
       <c r="H12" s="19">
         <f t="shared" si="1"/>
-        <v>75894.366999149992</v>
+        <v>84027.522666654011</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>380</v>
+        <v>715</v>
       </c>
       <c r="J12" s="28">
-        <v>45939</v>
+        <v>46030</v>
       </c>
       <c r="K12" s="19">
         <f>2301122*FX!C5</f>
@@ -7808,11 +7810,11 @@
       </c>
       <c r="E15" s="26">
         <f>+[10]Main!$I$2</f>
-        <v>178.72</v>
+        <v>174.02</v>
       </c>
       <c r="F15" s="19">
         <f>+[10]Main!$I$4</f>
-        <v>20279.01561504</v>
+        <v>19745.715629639999</v>
       </c>
       <c r="G15" s="19">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
@@ -7820,7 +7822,7 @@
       </c>
       <c r="H15" s="19">
         <f>F15+G15</f>
-        <v>19123.221615039998</v>
+        <v>18589.921629639997</v>
       </c>
       <c r="I15" s="27" t="s">
         <v>149</v>
@@ -7961,11 +7963,11 @@
       </c>
       <c r="E17" s="26">
         <f>+[12]Main!$H$2</f>
-        <v>216.1</v>
+        <v>331.65</v>
       </c>
       <c r="F17" s="19">
         <f>+[12]Main!$H$4*FX!C3</f>
-        <v>27553.513040456</v>
+        <v>42286.546042884002</v>
       </c>
       <c r="G17" s="19">
         <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
@@ -7973,10 +7975,10 @@
       </c>
       <c r="H17" s="19">
         <f t="shared" si="1"/>
-        <v>37436.633040455999</v>
+        <v>52169.666042884004</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>149</v>
+        <v>819</v>
       </c>
       <c r="J17" s="28">
         <v>45952</v>
@@ -8137,25 +8139,25 @@
       </c>
       <c r="E19" s="26">
         <f>+[14]Main!$M$2</f>
-        <v>119</v>
+        <v>87.2</v>
       </c>
       <c r="F19" s="19">
         <f>+[14]Main!$M$4</f>
-        <v>17782.869125000001</v>
+        <v>13030.808300000001</v>
       </c>
       <c r="G19" s="19">
         <f>+[14]Main!$M$6-[14]Main!$M$5</f>
-        <v>-1720.4159999999999</v>
+        <v>-1414.479</v>
       </c>
       <c r="H19" s="19">
         <f>F19+G19</f>
-        <v>16062.453125000002</v>
+        <v>11616.329300000001</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>714</v>
+        <v>813</v>
       </c>
       <c r="J19" s="28">
-        <v>45953</v>
+        <v>46051</v>
       </c>
       <c r="K19" s="26"/>
       <c r="L19" s="23"/>
@@ -9512,25 +9514,25 @@
       </c>
       <c r="E40" s="26">
         <f>+[35]Main!$I$2</f>
-        <v>21.82</v>
+        <v>22.77</v>
       </c>
       <c r="F40" s="19">
         <f>+[35]Main!$I$4</f>
-        <v>8633.1799026200006</v>
+        <v>8899.1889901200011</v>
       </c>
       <c r="G40" s="19">
         <f>+[35]Main!$I$6-[35]Main!$I$5</f>
-        <v>297</v>
+        <v>335.29999999999995</v>
       </c>
       <c r="H40" s="19">
         <f>F40+G40</f>
-        <v>8930.1799026200006</v>
+        <v>9234.4889901200004</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>149</v>
+        <v>819</v>
       </c>
       <c r="J40" s="28">
-        <v>45931</v>
+        <v>46050</v>
       </c>
       <c r="K40" s="19">
         <v>6179</v>
@@ -9764,25 +9766,25 @@
       </c>
       <c r="E44" s="26">
         <f>+[39]Main!$H$2</f>
-        <v>55.783000000000001</v>
+        <v>81.19</v>
       </c>
       <c r="F44" s="19">
         <f>+[39]Main!$H$4</f>
-        <v>3046.7200813140003</v>
+        <v>4215.0321918300006</v>
       </c>
       <c r="G44" s="19">
         <f>+[39]Main!$H$6-[39]Main!$H$5</f>
-        <v>1178.5010000000002</v>
+        <v>1164.528</v>
       </c>
       <c r="H44" s="19">
         <f>F44+G44</f>
-        <v>4225.2210813140009</v>
+        <v>5379.5601918300008</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>149</v>
+        <v>819</v>
       </c>
       <c r="J44" s="28">
-        <v>45958</v>
+        <v>46065</v>
       </c>
       <c r="K44" s="19"/>
       <c r="L44" s="23"/>
@@ -10868,24 +10870,26 @@
       </c>
       <c r="E62" s="26">
         <f>+[56]Main!$J$2</f>
-        <v>208.43</v>
+        <v>161.28</v>
       </c>
       <c r="F62" s="19">
         <f>+[56]Main!$J$4</f>
-        <v>3869.6348861900005</v>
+        <v>2990.6024601600002</v>
       </c>
       <c r="G62" s="19">
         <f>+[56]Main!$J$6-[56]Main!$J$5</f>
-        <v>-180.98000000000002</v>
+        <v>-211.91</v>
       </c>
       <c r="H62" s="19">
         <f>+F62+G62</f>
-        <v>3688.6548861900005</v>
+        <v>2778.6924601600003</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>432</v>
-      </c>
-      <c r="J62" s="3"/>
+        <v>819</v>
+      </c>
+      <c r="J62" s="28">
+        <v>45952</v>
+      </c>
       <c r="K62" s="19"/>
       <c r="L62" s="23"/>
       <c r="M62" s="19"/>
@@ -10999,10 +11003,10 @@
         <v>2248.0596218599999</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>334</v>
+        <v>717</v>
       </c>
       <c r="J64" s="28">
-        <v>45789</v>
+        <v>45967</v>
       </c>
       <c r="K64" s="19"/>
       <c r="L64" s="23"/>
@@ -11344,25 +11348,25 @@
       </c>
       <c r="E70" s="26">
         <f>+[64]Main!$J$2</f>
-        <v>9.08</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="F70" s="19">
         <f>+[64]Main!$J$4*FX!C3</f>
-        <v>2366.7544664192001</v>
+        <v>2534.083861608</v>
       </c>
       <c r="G70" s="19">
         <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
-        <v>167.21016000000003</v>
+        <v>122.12512000000007</v>
       </c>
       <c r="H70" s="19">
         <f>+F70+G70</f>
-        <v>2533.9646264192002</v>
+        <v>2656.2089816080002</v>
       </c>
       <c r="I70" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J70" s="28">
-        <v>45743</v>
+        <v>45953</v>
       </c>
       <c r="K70" s="19"/>
       <c r="L70" s="23"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A100C5-FBB5-47A3-8935-BB5110C298CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35DA42D-18E7-48E2-B55E-94DB4F521CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="825">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -4286,11 +4286,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6051,26 +6051,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>216.5</v>
+            <v>183</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>87244.720979000005</v>
+            <v>73541.602073999995</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>263.97300000000001</v>
+            <v>138.143</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>2424.9989999999998</v>
+            <v>2425.7570000000001</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6842,15 +6842,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1854268.2672868653</v>
+        <v>1840565.1483818654</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18300.05993520001</v>
+        <v>18426.64793520001</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1872568.3272220658</v>
+        <v>1858991.7963170654</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6901,15 +6901,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>24081.406068660588</v>
+        <v>23903.443485478772</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>237.66311604155857</v>
+        <v>239.30711604155857</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>24319.069184702152</v>
+        <v>24142.750601520329</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7420,8 +7420,8 @@
       <c r="I10" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="J10" s="28">
-        <v>45500</v>
+      <c r="J10" s="32" t="s">
+        <v>474</v>
       </c>
       <c r="K10" s="19">
         <v>86153</v>
@@ -7660,25 +7660,25 @@
       </c>
       <c r="E13" s="26">
         <f>+[8]Main!$K$2</f>
-        <v>216.5</v>
+        <v>183</v>
       </c>
       <c r="F13" s="19">
         <f>+[8]Main!$K$4</f>
-        <v>87244.720979000005</v>
+        <v>73541.602073999995</v>
       </c>
       <c r="G13" s="19">
         <f>+[8]Main!$K$6-[8]Main!$K$5</f>
-        <v>2161.0259999999998</v>
+        <v>2287.614</v>
       </c>
       <c r="H13" s="19">
         <f t="shared" si="1"/>
-        <v>89405.746979000003</v>
+        <v>75829.216073999996</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="J13" s="28">
-        <v>45924</v>
+        <v>46009</v>
       </c>
       <c r="K13" s="19">
         <v>8815.7999999999993</v>
@@ -7981,7 +7981,7 @@
         <v>819</v>
       </c>
       <c r="J17" s="28">
-        <v>45952</v>
+        <v>46063</v>
       </c>
       <c r="K17" s="19">
         <f>17194*FX!C3</f>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35DA42D-18E7-48E2-B55E-94DB4F521CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854AD670-AF68-4F48-8A25-0F1232F6F705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3057,26 +3057,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>166.9</v>
+            <v>157.55000000000001</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>29799.842119599998</v>
+            <v>28130.408184200001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1529</v>
+            <v>1030</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>3100</v>
+            <v>2475</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3168,7 +3168,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3289,11 +3289,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3714,27 +3714,27 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>298.52</v>
+            <v>324.72000000000003</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>18082.634662639997</v>
+            <v>19691.234465760001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>2276.7999999999997</v>
+            <v>1645.5</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1867.4</v>
+            <v>1462.1000000000001</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6070,7 +6070,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6842,15 +6842,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1840565.1483818654</v>
+        <v>1840437.5368921694</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18426.64793520001</v>
+        <v>18521.607935200009</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1858991.7963170654</v>
+        <v>1858959.1448273696</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6901,15 +6901,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>23903.443485478772</v>
+        <v>23901.786193404798</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>239.30711604155857</v>
+        <v>240.5403627948053</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>24142.750601520329</v>
+        <v>24142.326556199605</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7885,25 +7885,25 @@
       </c>
       <c r="E16" s="26">
         <f>+[11]Main!$I$2</f>
-        <v>166.9</v>
+        <v>157.55000000000001</v>
       </c>
       <c r="F16" s="19">
         <f>+[11]Main!$I$4*FX!C3</f>
-        <v>30991.835804383998</v>
+        <v>29255.624511568003</v>
       </c>
       <c r="G16" s="19">
         <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
-        <v>1633.8400000000001</v>
+        <v>1502.8</v>
       </c>
       <c r="H16" s="19">
         <f>F16+G16</f>
-        <v>32625.675804383998</v>
+        <v>30758.424511568002</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>338</v>
+        <v>819</v>
       </c>
       <c r="J16" s="28">
-        <v>45959</v>
+        <v>46090</v>
       </c>
       <c r="K16" s="19">
         <f>21427*FX!C3</f>
@@ -8293,10 +8293,10 @@
         <v>12596.627189120001</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>149</v>
+        <v>819</v>
       </c>
       <c r="J21" s="28">
-        <v>45953</v>
+        <v>46084</v>
       </c>
       <c r="K21" s="26"/>
       <c r="L21" s="23"/>
@@ -8904,25 +8904,25 @@
       </c>
       <c r="E31" s="26">
         <f>+[26]Main!$H$2</f>
-        <v>298.52</v>
+        <v>324.72000000000003</v>
       </c>
       <c r="F31" s="19">
         <f>+[26]Main!$H$4</f>
-        <v>18082.634662639997</v>
+        <v>19691.234465760001</v>
       </c>
       <c r="G31" s="19">
         <f>+[26]Main!$H$6-[26]Main!$H$5</f>
-        <v>-409.39999999999964</v>
+        <v>-183.39999999999986</v>
       </c>
       <c r="H31" s="19">
         <f t="shared" si="1"/>
-        <v>17673.234662639996</v>
+        <v>19507.834465759999</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>714</v>
+        <v>813</v>
       </c>
       <c r="J31" s="28">
-        <v>45916</v>
+        <v>46058</v>
       </c>
       <c r="K31" s="19">
         <v>6631.4</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854AD670-AF68-4F48-8A25-0F1232F6F705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB521E3-CEF6-455C-9731-75581ABAF29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="824">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2278,9 +2278,6 @@
   </si>
   <si>
     <t>BGFV</t>
-  </si>
-  <si>
-    <t>Q126</t>
   </si>
   <si>
     <t>FQ425</t>
@@ -3076,7 +3073,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3168,7 +3165,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3289,11 +3286,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3321,14 +3318,8 @@
             <v>1856195.55198455</v>
           </cell>
         </row>
-        <row r="5">
-          <cell r="I5"/>
-        </row>
-        <row r="6">
-          <cell r="I6"/>
-        </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3368,8 +3359,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3389,26 +3380,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>279.45999999999998</v>
+            <v>279</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>17630.198003599999</v>
+            <v>17826.147000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>371.09199999999998</v>
+            <v>747.61900000000003</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1651.8770000000002</v>
+            <v>2039.3050000000001</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3473,26 +3464,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>99.39</v>
+            <v>100.74</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>20685.40738692</v>
+            <v>20616.416016480001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>1119.5999999999999</v>
+            <v>743.2</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>2394.6</v>
+            <v>2635.4</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3593,29 +3584,29 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>49.4</v>
+            <v>42.48</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>12305.073552849997</v>
+            <v>10705.028957783998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>898.4</v>
+            <v>961.8</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>53.5</v>
+            <v>56.2</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3733,8 +3724,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3830,26 +3821,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>13.17</v>
+            <v>15.1</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>5144.4193313400001</v>
+            <v>5899.9438458000004</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>642.38599999999997</v>
+            <v>419.11500000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>4539.91</v>
+            <v>4046.326</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6768,10 +6759,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="N3" s="11" t="s">
         <v>816</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>817</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>89</v>
@@ -6842,15 +6833,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1840437.5368921694</v>
+        <v>1839527.9690861157</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18521.607935200009</v>
+        <v>18811.411935200009</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1858959.1448273696</v>
+        <v>1858339.3810213157</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6901,15 +6892,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>23901.786193404798</v>
+        <v>23889.973624495011</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>240.5403627948053</v>
+        <v>244.30405110649363</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>24142.326556199605</v>
+        <v>24134.277675601501</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7017,7 +7008,7 @@
         <v>328754.04995284806</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J6" s="28">
         <v>46080</v>
@@ -7120,7 +7111,7 @@
         <v>227638.18459823998</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J7" s="28">
         <v>46034</v>
@@ -7323,7 +7314,7 @@
         <v>155866</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J9" s="28">
         <v>45980</v>
@@ -7493,7 +7484,7 @@
         <v>105647.60399999999</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J11" s="28">
         <v>46009</v>
@@ -7590,7 +7581,7 @@
         <v>84027.522666654011</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J12" s="28">
         <v>46030</v>
@@ -7675,7 +7666,7 @@
         <v>75829.216073999996</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J13" s="28">
         <v>46009</v>
@@ -7750,7 +7741,7 @@
         <v>46200.047905979998</v>
       </c>
       <c r="I14" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J14" s="28">
         <v>45981</v>
@@ -7900,7 +7891,7 @@
         <v>30758.424511568002</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J16" s="28">
         <v>46090</v>
@@ -7978,7 +7969,7 @@
         <v>52169.666042884004</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J17" s="28">
         <v>46063</v>
@@ -8154,7 +8145,7 @@
         <v>11616.329300000001</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J19" s="28">
         <v>46051</v>
@@ -8225,7 +8216,7 @@
         <v>31318.476624999996</v>
       </c>
       <c r="I20" s="27" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J20" s="28">
         <v>46051</v>
@@ -8293,7 +8284,7 @@
         <v>12596.627189120001</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J21" s="28">
         <v>46084</v>
@@ -8358,9 +8349,7 @@
       <c r="I22" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="J22" s="28">
-        <v>45772</v>
-      </c>
+      <c r="J22" s="28"/>
       <c r="K22" s="26"/>
       <c r="L22" s="23"/>
       <c r="M22" s="26"/>
@@ -8415,10 +8404,10 @@
         <v>13882.1833317856</v>
       </c>
       <c r="I23" s="27" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J23" s="28">
-        <v>45958</v>
+        <v>46072</v>
       </c>
       <c r="K23" s="26"/>
       <c r="L23" s="23"/>
@@ -8463,25 +8452,25 @@
       </c>
       <c r="E24" s="26">
         <f>+[19]Main!$I$2</f>
-        <v>279.45999999999998</v>
+        <v>279</v>
       </c>
       <c r="F24" s="19">
         <f>+[19]Main!$I$4</f>
-        <v>17630.198003599999</v>
+        <v>17826.147000000001</v>
       </c>
       <c r="G24" s="19">
         <f>+[19]Main!$I$6-[19]Main!$I$5</f>
-        <v>1280.7850000000003</v>
+        <v>1291.6860000000001</v>
       </c>
       <c r="H24" s="19">
         <f>F24+G24</f>
-        <v>18910.983003599998</v>
+        <v>19117.833000000002</v>
       </c>
       <c r="I24" s="27" t="s">
-        <v>714</v>
+        <v>149</v>
       </c>
       <c r="J24" s="28">
-        <v>45897</v>
+        <v>45986</v>
       </c>
       <c r="K24" s="26"/>
       <c r="L24" s="23"/>
@@ -8526,25 +8515,25 @@
       </c>
       <c r="E25" s="26">
         <f>+[20]Main!$J$2</f>
-        <v>99.39</v>
+        <v>100.74</v>
       </c>
       <c r="F25" s="19">
         <f>+[20]Main!$J$4</f>
-        <v>20685.40738692</v>
+        <v>20616.416016480001</v>
       </c>
       <c r="G25" s="19">
         <f>+[20]Main!$J$6-[20]Main!$J$5</f>
-        <v>1275</v>
+        <v>1892.2</v>
       </c>
       <c r="H25" s="19">
         <f t="shared" si="1"/>
-        <v>21960.40738692</v>
+        <v>22508.616016480002</v>
       </c>
       <c r="I25" s="27" t="s">
-        <v>422</v>
+        <v>716</v>
       </c>
       <c r="J25" s="28">
-        <v>45967</v>
+        <v>46058</v>
       </c>
       <c r="K25" s="26"/>
       <c r="L25" s="23"/>
@@ -8715,25 +8704,25 @@
       </c>
       <c r="E28" s="26">
         <f>+[23]Main!$H$2</f>
-        <v>49.4</v>
+        <v>42.48</v>
       </c>
       <c r="F28" s="19">
         <f>+[23]Main!$H$5*FX!C7</f>
-        <v>13781.682379191998</v>
+        <v>11989.632432718079</v>
       </c>
       <c r="G28" s="19">
         <f>+([23]Main!$H$7-[23]Main!$H$6)*FX!C7</f>
-        <v>-946.28800000000001</v>
+        <v>-1014.272</v>
       </c>
       <c r="H28" s="19">
         <f>F28+G28</f>
-        <v>12835.394379191997</v>
+        <v>10975.360432718078</v>
       </c>
       <c r="I28" s="27" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J28" s="28">
-        <v>45972</v>
+        <v>46085</v>
       </c>
       <c r="K28" s="26"/>
       <c r="L28" s="23"/>
@@ -8919,7 +8908,7 @@
         <v>19507.834465759999</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J31" s="28">
         <v>46058</v>
@@ -9124,25 +9113,25 @@
       </c>
       <c r="E34" s="26">
         <f>+[29]Main!$H$2</f>
-        <v>13.17</v>
+        <v>15.1</v>
       </c>
       <c r="F34" s="19">
         <f>+[29]Main!$H$4</f>
-        <v>5144.4193313400001</v>
+        <v>5899.9438458000004</v>
       </c>
       <c r="G34" s="19">
         <f>+[29]Main!$H$6-[29]Main!$H$5</f>
-        <v>3897.5239999999999</v>
+        <v>3627.2110000000002</v>
       </c>
       <c r="H34" s="19">
         <f>+G34+F34</f>
-        <v>9041.9433313400004</v>
+        <v>9527.1548457999997</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>717</v>
+        <v>800</v>
       </c>
       <c r="J34" s="28">
-        <v>45957</v>
+        <v>46050</v>
       </c>
       <c r="K34" s="19"/>
       <c r="L34" s="23"/>
@@ -9243,7 +9232,7 @@
         <v>111</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>21</v>
@@ -9343,7 +9332,7 @@
         <v>337</v>
       </c>
       <c r="J37" s="32" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="K37" s="19"/>
       <c r="L37" s="23"/>
@@ -9529,7 +9518,7 @@
         <v>9234.4889901200004</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J40" s="28">
         <v>46050</v>
@@ -9722,7 +9711,7 @@
         <v>5139.9465440399999</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J43" s="28">
         <v>45975</v>
@@ -9781,7 +9770,7 @@
         <v>5379.5601918300008</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J44" s="28">
         <v>46065</v>
@@ -9907,7 +9896,7 @@
         <v>6117.0447439999998</v>
       </c>
       <c r="I46" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J46" s="28">
         <v>45981</v>
@@ -9970,7 +9959,7 @@
         <v>6623.1464285999991</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J47" s="28">
         <v>45939</v>
@@ -10147,7 +10136,7 @@
         <v>5728.3105543299998</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J50" s="28">
         <v>45986</v>
@@ -10655,7 +10644,7 @@
         <v>4949.4143572999992</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J58" s="28">
         <v>45957</v>
@@ -10765,7 +10754,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
@@ -10885,7 +10874,7 @@
         <v>2778.6924601600003</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J62" s="28">
         <v>45952</v>
@@ -11003,7 +10992,7 @@
         <v>2248.0596218599999</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J64" s="28">
         <v>45967</v>
@@ -12618,7 +12607,7 @@
         <v>1178.0758231121999</v>
       </c>
       <c r="I97" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J97" s="28"/>
       <c r="K97" s="19"/>
@@ -17352,13 +17341,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="47" t="s">
+        <v>722</v>
+      </c>
+      <c r="D2" s="47" t="s">
         <v>723</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="E2" s="47" t="s">
         <v>724</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>725</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>126</v>
@@ -17377,16 +17366,16 @@
     <row r="3" spans="1:16">
       <c r="A3" s="47"/>
       <c r="B3" s="47" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -17403,16 +17392,16 @@
     <row r="4" spans="1:16">
       <c r="A4" s="47"/>
       <c r="B4" s="47" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="47"/>
@@ -17429,19 +17418,19 @@
     <row r="5" spans="1:16">
       <c r="A5" s="47"/>
       <c r="B5" s="47" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G5" s="47"/>
       <c r="H5" s="47"/>
@@ -17457,16 +17446,16 @@
     <row r="6" spans="1:16">
       <c r="A6" s="47"/>
       <c r="B6" s="47" t="s">
+        <v>742</v>
+      </c>
+      <c r="C6" s="47" t="s">
         <v>743</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>744</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -17483,19 +17472,19 @@
     <row r="7" spans="1:16">
       <c r="A7" s="47"/>
       <c r="B7" s="47" t="s">
+        <v>746</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>747</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>748</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
@@ -17514,16 +17503,16 @@
         <v>135</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>135</v>
       </c>
       <c r="E8" s="47" t="s">
+        <v>750</v>
+      </c>
+      <c r="F8" s="47" t="s">
         <v>751</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>752</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="47"/>
@@ -17539,19 +17528,19 @@
     <row r="9" spans="1:16">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
+        <v>752</v>
+      </c>
+      <c r="C9" s="47" t="s">
         <v>753</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>754</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>682</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G9" s="47"/>
       <c r="H9" s="47"/>
@@ -17567,19 +17556,19 @@
     <row r="10" spans="1:16">
       <c r="A10" s="47"/>
       <c r="B10" s="47" t="s">
+        <v>755</v>
+      </c>
+      <c r="C10" s="47" t="s">
         <v>756</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="D10" s="47" t="s">
         <v>757</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="E10" s="47" t="s">
+        <v>751</v>
+      </c>
+      <c r="F10" s="47" t="s">
         <v>758</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>752</v>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>759</v>
       </c>
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
@@ -17595,19 +17584,19 @@
     <row r="11" spans="1:16">
       <c r="A11" s="47"/>
       <c r="B11" s="47" t="s">
+        <v>760</v>
+      </c>
+      <c r="C11" s="47" t="s">
         <v>761</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>762</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G11" s="47"/>
       <c r="H11" s="47"/>
@@ -17623,19 +17612,19 @@
     <row r="12" spans="1:16">
       <c r="A12" s="47"/>
       <c r="B12" s="47" t="s">
+        <v>763</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>764</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>765</v>
       </c>
       <c r="D12" s="47" t="s">
         <v>123</v>
       </c>
       <c r="E12" s="47" t="s">
+        <v>766</v>
+      </c>
+      <c r="F12" s="47" t="s">
         <v>767</v>
-      </c>
-      <c r="F12" s="47" t="s">
-        <v>768</v>
       </c>
       <c r="G12" s="47"/>
       <c r="H12" s="47"/>
@@ -17651,16 +17640,16 @@
     <row r="13" spans="1:16">
       <c r="A13" s="47"/>
       <c r="B13" s="47" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>135</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F13" s="47"/>
       <c r="G13" s="47"/>
@@ -17677,16 +17666,16 @@
     <row r="14" spans="1:16">
       <c r="A14" s="47"/>
       <c r="B14" s="47" t="s">
+        <v>770</v>
+      </c>
+      <c r="C14" s="47" t="s">
         <v>771</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>772</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>677</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F14" s="47"/>
       <c r="G14" s="47"/>
@@ -17703,16 +17692,16 @@
     <row r="15" spans="1:16">
       <c r="A15" s="47"/>
       <c r="B15" s="47" t="s">
+        <v>772</v>
+      </c>
+      <c r="C15" s="47" t="s">
         <v>773</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="D15" s="47" t="s">
         <v>774</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="E15" s="47" t="s">
         <v>775</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>776</v>
       </c>
       <c r="F15" s="47"/>
       <c r="G15" s="47"/>
@@ -17729,19 +17718,19 @@
     <row r="16" spans="1:16">
       <c r="A16" s="47"/>
       <c r="B16" s="47" t="s">
+        <v>777</v>
+      </c>
+      <c r="C16" s="47" t="s">
         <v>778</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="D16" s="47" t="s">
         <v>779</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="E16" s="47" t="s">
         <v>780</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="F16" s="47" t="s">
         <v>781</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>782</v>
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="47"/>
@@ -17757,16 +17746,16 @@
     <row r="17" spans="1:16">
       <c r="A17" s="47"/>
       <c r="B17" s="47" t="s">
+        <v>782</v>
+      </c>
+      <c r="C17" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="D17" s="47" t="s">
         <v>784</v>
       </c>
-      <c r="D17" s="47" t="s">
-        <v>785</v>
-      </c>
       <c r="E17" s="47" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F17" s="47"/>
       <c r="G17" s="47"/>
@@ -17818,7 +17807,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="76" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B20" s="76"/>
       <c r="C20" s="47"/>
@@ -17839,10 +17828,10 @@
     <row r="21" spans="1:16">
       <c r="A21" s="47"/>
       <c r="B21" s="47" t="s">
+        <v>785</v>
+      </c>
+      <c r="C21" s="47" t="s">
         <v>786</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>787</v>
       </c>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -17861,10 +17850,10 @@
     <row r="22" spans="1:16">
       <c r="A22" s="47"/>
       <c r="B22" s="47" t="s">
+        <v>787</v>
+      </c>
+      <c r="C22" s="47" t="s">
         <v>788</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>789</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
@@ -17883,10 +17872,10 @@
     <row r="23" spans="1:16">
       <c r="A23" s="47"/>
       <c r="B23" s="47" t="s">
+        <v>789</v>
+      </c>
+      <c r="C23" s="47" t="s">
         <v>790</v>
-      </c>
-      <c r="C23" s="47" t="s">
-        <v>791</v>
       </c>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
@@ -17905,10 +17894,10 @@
     <row r="24" spans="1:16">
       <c r="A24" s="47"/>
       <c r="B24" s="47" t="s">
+        <v>791</v>
+      </c>
+      <c r="C24" s="47" t="s">
         <v>792</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>793</v>
       </c>
       <c r="D24" s="47"/>
       <c r="E24" s="47"/>
@@ -17930,7 +17919,7 @@
         <v>98</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D25" s="47"/>
       <c r="E25" s="47"/>
@@ -17949,10 +17938,10 @@
     <row r="26" spans="1:16">
       <c r="A26" s="47"/>
       <c r="B26" s="47" t="s">
+        <v>794</v>
+      </c>
+      <c r="C26" s="47" t="s">
         <v>795</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>796</v>
       </c>
       <c r="D26" s="47"/>
       <c r="E26" s="47"/>
@@ -17971,10 +17960,10 @@
     <row r="27" spans="1:16">
       <c r="A27" s="47"/>
       <c r="B27" s="47" t="s">
+        <v>796</v>
+      </c>
+      <c r="C27" s="47" t="s">
         <v>797</v>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>798</v>
       </c>
       <c r="D27" s="47"/>
       <c r="E27" s="47"/>
@@ -17993,10 +17982,10 @@
     <row r="28" spans="1:16">
       <c r="A28" s="47"/>
       <c r="B28" s="47" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
@@ -18063,7 +18052,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="47" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -18124,7 +18113,7 @@
     <row r="3" spans="1:17">
       <c r="A3" s="47"/>
       <c r="B3" s="74" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="47"/>
@@ -18148,7 +18137,7 @@
         <v>434</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D4" s="47"/>
       <c r="E4" s="60"/>
@@ -18447,14 +18436,14 @@
     <row r="18" spans="1:17">
       <c r="A18" s="47"/>
       <c r="B18" s="47" t="s">
+        <v>805</v>
+      </c>
+      <c r="C18" s="59" t="s">
         <v>806</v>
-      </c>
-      <c r="C18" s="59" t="s">
-        <v>807</v>
       </c>
       <c r="D18" s="47"/>
       <c r="E18" s="60" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="58"/>
@@ -19729,7 +19718,7 @@
         <v>21</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F23" s="58"/>
       <c r="G23" s="58"/>
@@ -38370,7 +38359,7 @@
         <v>95429.722976000019</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J5" s="62">
         <v>45975</v>
@@ -49135,7 +49124,7 @@
         <v>463</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="47"/>
@@ -49151,7 +49140,7 @@
         <v>464</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="47"/>
@@ -49212,10 +49201,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="81" t="s">
+        <v>821</v>
+      </c>
+      <c r="C13" s="81" t="s">
         <v>822</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>823</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
@@ -49413,19 +49402,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D2" s="76" t="s">
+        <v>718</v>
+      </c>
+      <c r="E2" s="76" t="s">
         <v>719</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>720</v>
       </c>
       <c r="F2" s="77" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2" s="77" t="s">
         <v>126</v>
@@ -49458,13 +49447,13 @@
     <row r="3" spans="1:32">
       <c r="A3" s="47"/>
       <c r="B3" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="C3" s="46" t="s">
         <v>721</v>
       </c>
-      <c r="C3" s="46" t="s">
-        <v>722</v>
-      </c>
       <c r="D3" s="47" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E3" s="78">
         <v>45757</v>
@@ -49510,19 +49499,19 @@
         <v>692</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E4" s="78">
         <v>45782</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G4" s="80">
         <v>9420</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="I4" s="47"/>
       <c r="J4" s="47"/>
@@ -49558,7 +49547,7 @@
         <v>128</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E5" s="78">
         <v>45637</v>
@@ -49598,13 +49587,13 @@
     <row r="6" spans="1:32">
       <c r="A6" s="47"/>
       <c r="B6" s="47" t="s">
+        <v>732</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>732</v>
+      </c>
+      <c r="D6" s="47" t="s">
         <v>733</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>733</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>734</v>
       </c>
       <c r="E6" s="47"/>
       <c r="F6" s="47"/>
@@ -49653,10 +49642,10 @@
         <v>16.75</v>
       </c>
       <c r="G7" s="47" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H7" s="47" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="I7" s="47"/>
       <c r="J7" s="47"/>
@@ -49692,7 +49681,7 @@
         <v>476</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E8" s="78">
         <v>45322</v>
@@ -49702,7 +49691,7 @@
         <v>500</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I8" s="47"/>
       <c r="J8" s="47"/>
@@ -49732,10 +49721,10 @@
     <row r="9" spans="1:32">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
+        <v>813</v>
+      </c>
+      <c r="C9" s="47" t="s">
         <v>814</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>815</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>689</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB521E3-CEF6-455C-9731-75581ABAF29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FDDF54-0E0D-42EE-9606-51E916DE5EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,11 @@
     <sheet name="FX" sheetId="2" r:id="rId8"/>
     <sheet name="Acquisitions" sheetId="9" r:id="rId9"/>
     <sheet name="People" sheetId="10" r:id="rId10"/>
-    <sheet name="Market" sheetId="11" r:id="rId11"/>
-    <sheet name="Private" sheetId="12" r:id="rId12"/>
+    <sheet name="Shoes" sheetId="13" r:id="rId11"/>
+    <sheet name="Market" sheetId="11" r:id="rId12"/>
+    <sheet name="Private" sheetId="12" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
@@ -111,6 +111,7 @@
     <externalReference r:id="rId94"/>
     <externalReference r:id="rId95"/>
     <externalReference r:id="rId96"/>
+    <externalReference r:id="rId97"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$AE$181</definedName>
@@ -136,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="826">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2608,6 +2609,12 @@
   </si>
   <si>
     <t>Private by Nordstorm family</t>
+  </si>
+  <si>
+    <t>FQ326</t>
+  </si>
+  <si>
+    <t>Q326</t>
   </si>
 </sst>
 </file>
@@ -3005,7 +3012,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Financials"/>
+      <sheetName val="Model"/>
       <sheetName val="Ratios"/>
       <sheetName val="DCF"/>
     </sheetNames>
@@ -3013,17 +3020,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>174.02</v>
+            <v>204.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>19745.715629639999</v>
+            <v>22942.8633845</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1155.7940000000001</v>
+            <v>1035.8620000000001</v>
           </cell>
         </row>
         <row r="6">
@@ -3318,8 +3325,14 @@
             <v>1856195.55198455</v>
           </cell>
         </row>
+        <row r="5">
+          <cell r="I5"/>
+        </row>
+        <row r="6">
+          <cell r="I6"/>
+        </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3359,8 +3372,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3380,26 +3393,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>279</v>
+            <v>252.2</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>17826.147000000001</v>
+            <v>15870.190913199998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>747.61900000000003</v>
+            <v>584.07899999999995</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>2039.3050000000001</v>
+            <v>2035.424</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3483,7 +3496,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3503,22 +3516,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>4245</v>
+            <v>3710</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3117877.0918199997</v>
+            <v>2653960.5315300003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>124662</v>
+            <v>123998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>60000</v>
+            <v>35000</v>
           </cell>
         </row>
       </sheetData>
@@ -3603,10 +3616,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3626,22 +3639,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>36.65</v>
+            <v>34.25</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>20355.443827949999</v>
+            <v>19049.829518499999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>303.39999999999998</v>
+            <v>353.3</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>934.7</v>
+            <v>1051.4000000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -3782,22 +3795,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>23.72</v>
+            <v>23.02</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>6174.3159999999998</v>
+            <v>5992.1059999999998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>2183</v>
+            <v>1437</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1092.2</v>
+            <v>754.9</v>
           </cell>
         </row>
       </sheetData>
@@ -3840,7 +3853,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3862,17 +3875,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>45.46</v>
+            <v>54.86</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>141644.79719985998</v>
+            <v>170943.68955976001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>10013</v>
+            <v>11269</v>
           </cell>
         </row>
         <row r="7">
@@ -3942,17 +3955,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>22.05</v>
+            <v>27.09</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>8181.5913333000008</v>
+            <v>10075.3599366</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>2432</v>
+            <v>2517</v>
           </cell>
         </row>
         <row r="6">
@@ -4059,26 +4072,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>76.81</v>
+            <v>60</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>11580.02922</v>
+            <v>8953.7999999999993</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>86.016000000000005</v>
+            <v>112.633</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1856.34</v>
+            <v>1754.22</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4303,22 +4316,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>139.75</v>
+            <v>152.19999999999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>157638</v>
+            <v>171377.19999999998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>4639</v>
+            <v>4640</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>2867</v>
+            <v>2869</v>
           </cell>
         </row>
       </sheetData>
@@ -4537,17 +4550,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>70.83</v>
+            <v>77.23</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>6351.1455543299999</v>
+            <v>6928.0655860600009</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>622.83500000000004</v>
+            <v>611.73299999999995</v>
           </cell>
         </row>
         <row r="6">
@@ -4657,17 +4670,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>96.69</v>
+            <v>97.7</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4597.6094999999996</v>
+            <v>4576.4633999999996</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>603.52499999999998</v>
+            <v>631.03800000000001</v>
           </cell>
         </row>
         <row r="6">
@@ -4699,17 +4712,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>52.35</v>
+            <v>56.66</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2867.2130074500001</v>
+            <v>3053.3446207199995</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>578.30700000000002</v>
+            <v>236.02699999999999</v>
           </cell>
         </row>
         <row r="6">
@@ -4718,7 +4731,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4777,26 +4790,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>88.25</v>
+            <v>76.37</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>4246.5707615000001</v>
+            <v>3497.9518935199999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>248.8</v>
+            <v>158.19999999999999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>2256</v>
+            <v>2258.7999999999997</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5048,12 +5061,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>41.48</v>
+            <v>36.520000000000003</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2920.192</v>
+            <v>2571.0080000000003</v>
           </cell>
         </row>
         <row r="5">
@@ -5247,22 +5260,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>26.13</v>
+            <v>54.91</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2094.6979930499997</v>
+            <v>4407.5666168399994</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>188</v>
+            <v>249</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1052</v>
+            <v>1351</v>
           </cell>
         </row>
       </sheetData>
@@ -6274,28 +6287,28 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Financials"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="H3">
-            <v>148.38</v>
+            <v>176.36</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>48530.723905979998</v>
+            <v>56659.177199999998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>3847.0160000000001</v>
+            <v>4061.1729999999998</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>1516.34</v>
+            <v>1516.972</v>
           </cell>
         </row>
       </sheetData>
@@ -6833,15 +6846,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1839527.9690861157</v>
+        <v>1889900.4183873252</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18811.411935200009</v>
+        <v>18354.30113520001</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1858339.3810213157</v>
+        <v>1908254.7195225244</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6892,15 +6905,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>23889.973624495011</v>
+        <v>24544.16127775747</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>244.30405110649363</v>
+        <v>238.36754721038974</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>24134.277675601501</v>
+        <v>24782.528824967849</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7199,25 +7212,25 @@
       </c>
       <c r="E8" s="26">
         <f>+[3]Main!$J$3</f>
-        <v>45.46</v>
+        <v>54.86</v>
       </c>
       <c r="F8" s="19">
         <f>+[3]Main!$J$5*FX!C3</f>
-        <v>147310.58908785437</v>
+        <v>177781.43714215042</v>
       </c>
       <c r="G8" s="19">
         <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
-        <v>-10412.48</v>
+        <v>-11718.720000000001</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" ref="H8:H35" si="1">F8+G8</f>
-        <v>136898.10908785436</v>
+        <v>166062.71714215042</v>
       </c>
       <c r="I8" s="27" t="s">
         <v>149</v>
       </c>
       <c r="J8" s="28">
-        <v>45994</v>
+        <v>46092</v>
       </c>
       <c r="K8" s="19">
         <f>35947*FX!C3</f>
@@ -7299,25 +7312,25 @@
       </c>
       <c r="E9" s="26">
         <f>+[4]Main!$I$3</f>
-        <v>139.75</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="F9" s="19">
         <f>+[4]Main!$I$5</f>
-        <v>157638</v>
+        <v>171377.19999999998</v>
       </c>
       <c r="G9" s="19">
         <f>+[4]Main!$I$7-[4]Main!$I$6</f>
-        <v>-1772</v>
+        <v>-1771</v>
       </c>
       <c r="H9" s="19">
         <f>F9+G9</f>
-        <v>155866</v>
+        <v>169606.19999999998</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>800</v>
+        <v>824</v>
       </c>
       <c r="J9" s="28">
-        <v>45980</v>
+        <v>46078</v>
       </c>
       <c r="K9" s="26">
         <v>54217</v>
@@ -7726,25 +7739,25 @@
       </c>
       <c r="E14" s="26">
         <f>+[9]Main!$H$3</f>
-        <v>148.38</v>
+        <v>176.36</v>
       </c>
       <c r="F14" s="19">
         <f>+[9]Main!$H$5</f>
-        <v>48530.723905979998</v>
+        <v>56659.177199999998</v>
       </c>
       <c r="G14" s="19">
         <f>+[9]Main!$H$7-[9]Main!$H$6</f>
-        <v>-2330.6760000000004</v>
+        <v>-2544.201</v>
       </c>
       <c r="H14" s="19">
         <f t="shared" si="1"/>
-        <v>46200.047905979998</v>
+        <v>54114.976199999997</v>
       </c>
       <c r="I14" s="27" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="J14" s="28">
-        <v>45981</v>
+        <v>46086</v>
       </c>
       <c r="K14" s="19">
         <v>20376.900000000001</v>
@@ -7801,25 +7814,25 @@
       </c>
       <c r="E15" s="26">
         <f>+[10]Main!$I$2</f>
-        <v>174.02</v>
+        <v>204.5</v>
       </c>
       <c r="F15" s="19">
         <f>+[10]Main!$I$4</f>
-        <v>19745.715629639999</v>
+        <v>22942.8633845</v>
       </c>
       <c r="G15" s="19">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
-        <v>-1155.7940000000001</v>
+        <v>-1035.8620000000001</v>
       </c>
       <c r="H15" s="19">
         <f>F15+G15</f>
-        <v>18589.921629639997</v>
+        <v>21907.001384499999</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J15" s="28">
-        <v>45995</v>
+        <v>46108</v>
       </c>
       <c r="K15" s="19">
         <v>9619.2999999999993</v>
@@ -8452,25 +8465,25 @@
       </c>
       <c r="E24" s="26">
         <f>+[19]Main!$I$2</f>
-        <v>279</v>
+        <v>252.2</v>
       </c>
       <c r="F24" s="19">
         <f>+[19]Main!$I$4</f>
-        <v>17826.147000000001</v>
+        <v>15870.190913199998</v>
       </c>
       <c r="G24" s="19">
         <f>+[19]Main!$I$6-[19]Main!$I$5</f>
-        <v>1291.6860000000001</v>
+        <v>1451.345</v>
       </c>
       <c r="H24" s="19">
         <f>F24+G24</f>
-        <v>19117.833000000002</v>
+        <v>17321.535913199998</v>
       </c>
       <c r="I24" s="27" t="s">
         <v>149</v>
       </c>
       <c r="J24" s="28">
-        <v>45986</v>
+        <v>46086</v>
       </c>
       <c r="K24" s="26"/>
       <c r="L24" s="23"/>
@@ -8578,25 +8591,25 @@
       </c>
       <c r="E26" s="26">
         <f>+[21]Main!$I$2</f>
-        <v>4245</v>
+        <v>3710</v>
       </c>
       <c r="F26" s="19">
         <f>+[21]Main!$I$4*FX!C5</f>
-        <v>19642.625678466</v>
+        <v>16719.951348639002</v>
       </c>
       <c r="G26" s="19">
         <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C5</f>
-        <v>-407.37060000000002</v>
+        <v>-560.68740000000003</v>
       </c>
       <c r="H26" s="19">
         <f>F26+G26</f>
-        <v>19235.255078466002</v>
+        <v>16159.263948639002</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J26" s="28">
-        <v>45968</v>
+        <v>46066</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="23"/>
@@ -8659,7 +8672,7 @@
         <v>149</v>
       </c>
       <c r="J27" s="28">
-        <v>45959</v>
+        <v>46028</v>
       </c>
       <c r="K27" s="26"/>
       <c r="L27" s="23"/>
@@ -8767,25 +8780,25 @@
       </c>
       <c r="E29" s="26">
         <f>+[24]Main!$J$2</f>
-        <v>36.65</v>
+        <v>34.25</v>
       </c>
       <c r="F29" s="19">
         <f>+[24]Main!$J$4</f>
-        <v>20355.443827949999</v>
+        <v>19049.829518499999</v>
       </c>
       <c r="G29" s="19">
         <f>+[24]Main!$J$6-[24]Main!$J$5</f>
-        <v>631.30000000000007</v>
+        <v>698.10000000000014</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="1"/>
-        <v>20986.743827949998</v>
+        <v>19747.929518499997</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J29" s="28">
-        <v>45979</v>
+        <v>46078</v>
       </c>
       <c r="K29" s="26"/>
       <c r="L29" s="23"/>
@@ -9050,25 +9063,25 @@
       </c>
       <c r="E33" s="26">
         <f>+[28]Main!$I$2</f>
-        <v>23.72</v>
+        <v>23.02</v>
       </c>
       <c r="F33" s="19">
         <f>+[28]Main!$I$4*FX!C3</f>
-        <v>6421.2886399999998</v>
+        <v>6231.7902400000003</v>
       </c>
       <c r="G33" s="19">
         <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
-        <v>-1134.432</v>
+        <v>-709.38400000000001</v>
       </c>
       <c r="H33" s="19">
         <f>F33+G33</f>
-        <v>5286.85664</v>
+        <v>5522.4062400000003</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J33" s="28">
-        <v>45967</v>
+        <v>46093</v>
       </c>
       <c r="K33" s="26"/>
       <c r="L33" s="23"/>
@@ -9239,25 +9252,25 @@
       </c>
       <c r="E36" s="26">
         <f>+[31]Main!$J$2</f>
-        <v>22.05</v>
+        <v>27.09</v>
       </c>
       <c r="F36" s="19">
         <f>+[31]Main!$J$4</f>
-        <v>8181.5913333000008</v>
+        <v>10075.3599366</v>
       </c>
       <c r="G36" s="19">
         <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
-        <v>-941</v>
+        <v>-1026</v>
       </c>
       <c r="H36" s="19">
         <f>+G36+F36</f>
-        <v>7240.5913333000008</v>
+        <v>9049.3599365999999</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J36" s="28">
-        <v>45980</v>
+        <v>46086</v>
       </c>
       <c r="K36" s="19">
         <v>14889</v>
@@ -9392,10 +9405,10 @@
         <v>6330.0753027199989</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>338</v>
+        <v>149</v>
       </c>
       <c r="J38" s="28">
-        <v>45897</v>
+        <v>46034</v>
       </c>
       <c r="K38" s="19"/>
       <c r="L38" s="23"/>
@@ -9440,25 +9453,25 @@
       </c>
       <c r="E39" s="26">
         <f>+[34]Main!$I$2</f>
-        <v>76.81</v>
+        <v>60</v>
       </c>
       <c r="F39" s="19">
         <f>+[34]Main!$I$4</f>
-        <v>11580.02922</v>
+        <v>8953.7999999999993</v>
       </c>
       <c r="G39" s="19">
         <f>+[34]Main!$I$6-[34]Main!$I$5</f>
-        <v>1770.3239999999998</v>
+        <v>1641.587</v>
       </c>
       <c r="H39" s="19">
         <f>F39+G39</f>
-        <v>13350.353220000001</v>
+        <v>10595.386999999999</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J39" s="28">
-        <v>45960</v>
+        <v>46076</v>
       </c>
       <c r="K39" s="19"/>
       <c r="L39" s="23"/>
@@ -10121,25 +10134,25 @@
       </c>
       <c r="E50" s="26">
         <f>+[45]Main!$J$2</f>
-        <v>70.83</v>
+        <v>77.23</v>
       </c>
       <c r="F50" s="19">
         <f>+[45]Main!$J$4</f>
-        <v>6351.1455543299999</v>
+        <v>6928.0655860600009</v>
       </c>
       <c r="G50" s="19">
         <f>+[45]Main!$J$6-[45]Main!$J$5</f>
-        <v>-622.83500000000004</v>
+        <v>-611.73299999999995</v>
       </c>
       <c r="H50" s="19">
         <f>+F50+G50</f>
-        <v>5728.3105543299998</v>
+        <v>6316.3325860600007</v>
       </c>
       <c r="I50" s="18" t="s">
         <v>812</v>
       </c>
       <c r="J50" s="28">
-        <v>45986</v>
+        <v>46077</v>
       </c>
       <c r="K50" s="19"/>
       <c r="L50" s="23"/>
@@ -10306,25 +10319,25 @@
       </c>
       <c r="E53" s="26">
         <f>+[48]Main!$I$2</f>
-        <v>96.69</v>
+        <v>97.7</v>
       </c>
       <c r="F53" s="19">
         <f>+[48]Main!$I$4</f>
-        <v>4597.6094999999996</v>
+        <v>4576.4633999999996</v>
       </c>
       <c r="G53" s="19">
         <f>+[48]Main!$I$6-[48]Main!$I$5</f>
-        <v>-603.52499999999998</v>
+        <v>-631.03800000000001</v>
       </c>
       <c r="H53" s="19">
         <f>F53+G53</f>
-        <v>3994.0844999999995</v>
+        <v>3945.4253999999996</v>
       </c>
       <c r="I53" s="27" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J53" s="28">
-        <v>45986</v>
+        <v>46085</v>
       </c>
       <c r="K53" s="19">
         <v>4280.7</v>
@@ -10381,25 +10394,25 @@
       </c>
       <c r="E54" s="26">
         <f>+[49]Main!$I$2</f>
-        <v>52.35</v>
+        <v>56.66</v>
       </c>
       <c r="F54" s="19">
         <f>+[49]Main!$I$4</f>
-        <v>2867.2130074500001</v>
+        <v>3053.3446207199995</v>
       </c>
       <c r="G54" s="19">
         <f>+[49]Main!$I$6-[49]Main!$I$5</f>
-        <v>-578.30700000000002</v>
+        <v>-236.02699999999999</v>
       </c>
       <c r="H54" s="19">
         <f t="shared" si="3"/>
-        <v>2288.9060074500003</v>
+        <v>2817.3176207199995</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J54" s="28">
-        <v>45959</v>
+        <v>46056</v>
       </c>
       <c r="K54" s="19"/>
       <c r="L54" s="23"/>
@@ -10444,25 +10457,25 @@
       </c>
       <c r="E55" s="26">
         <f>+[50]Main!$J$2</f>
-        <v>88.25</v>
+        <v>76.37</v>
       </c>
       <c r="F55" s="19">
         <f>+[50]Main!$J$4</f>
-        <v>4246.5707615000001</v>
+        <v>3497.9518935199999</v>
       </c>
       <c r="G55" s="19">
         <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
-        <v>2007.2</v>
+        <v>2100.6</v>
       </c>
       <c r="H55" s="19">
         <f>F55+G55</f>
-        <v>6253.7707614999999</v>
+        <v>5598.5518935199998</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J55" s="28">
-        <v>45995</v>
+        <v>46108</v>
       </c>
       <c r="K55" s="19"/>
       <c r="L55" s="23"/>
@@ -10918,11 +10931,11 @@
       </c>
       <c r="E63" s="26">
         <f>+[57]Main!$J$2</f>
-        <v>41.48</v>
+        <v>36.520000000000003</v>
       </c>
       <c r="F63" s="19">
         <f>+[57]Main!$J$4*FX!C3</f>
-        <v>3036.9996799999999</v>
+        <v>2673.8483200000005</v>
       </c>
       <c r="G63" s="19">
         <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
@@ -10930,13 +10943,13 @@
       </c>
       <c r="H63" s="19">
         <f>+F63+G63</f>
-        <v>3238.7596800000001</v>
+        <v>2875.6083200000007</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J63" s="28">
-        <v>45965</v>
+        <v>46091</v>
       </c>
       <c r="K63" s="19"/>
       <c r="L63" s="23"/>
@@ -11152,25 +11165,25 @@
       </c>
       <c r="E67" s="26">
         <f>+[61]Main!$I$2</f>
-        <v>26.13</v>
+        <v>54.91</v>
       </c>
       <c r="F67" s="19">
         <f>+[61]Main!$I$4</f>
-        <v>2094.6979930499997</v>
+        <v>4407.5666168399994</v>
       </c>
       <c r="G67" s="19">
         <f>+[61]Main!$I$6-[61]Main!$I$5</f>
-        <v>864</v>
+        <v>1102</v>
       </c>
       <c r="H67" s="19">
         <f>F67+G67</f>
-        <v>2958.6979930499997</v>
+        <v>5509.5666168399994</v>
       </c>
       <c r="I67" s="27" t="s">
-        <v>149</v>
+        <v>818</v>
       </c>
       <c r="J67" s="28">
-        <v>45996</v>
+        <v>46085</v>
       </c>
       <c r="K67" s="26"/>
       <c r="L67" s="23"/>
@@ -18046,6 +18059,37 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C032625C-E19A-4813-ABA6-8D106ACC7803}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="46" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
+        <v>695</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{DC140323-43D4-490C-89F0-35533960EF2D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEACE1C4-97F2-4C2B-8888-284E30CF8393}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18060,7 +18104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0FC56C3-8711-45A1-8A34-862C4185F0B3}">
   <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FDDF54-0E0D-42EE-9606-51E916DE5EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D0FC7A-41E7-4BF8-8BF4-702D91913CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3916,26 +3916,26 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>42.33</v>
+            <v>36.1845</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>7893.6705468599994</v>
+            <v>6654.5486833320001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>261.834</v>
+            <v>329.06700000000001</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>1181.6599999999999</v>
+            <v>1149.345</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4091,7 +4091,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4731,7 +4731,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4809,7 +4809,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5172,7 +5172,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Financials"/>
+      <sheetName val="Model"/>
       <sheetName val="Ratios"/>
       <sheetName val="DCF"/>
       <sheetName val="CoC"/>
@@ -5181,29 +5181,29 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>71.94</v>
+            <v>58.85</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>106226.60399999999</v>
+            <v>87068.574999999997</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>8575</v>
+            <v>8345</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>7996</v>
+            <v>8015</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6055,26 +6055,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>183</v>
+            <v>187.97</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>73541.602073999995</v>
+            <v>75466.759510000004</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>138.143</v>
+            <v>200.84200000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>2425.7570000000001</v>
+            <v>2977.279</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6846,15 +6846,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1889900.4183873252</v>
+        <v>1871378.8600852559</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18354.30113520001</v>
+        <v>18988.59421520001</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1908254.7195225244</v>
+        <v>1890367.4543004551</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6905,15 +6905,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>24544.16127775747</v>
+        <v>24303.621559548777</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>238.36754721038974</v>
+        <v>246.6051196779222</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>24782.528824967849</v>
+        <v>24550.226679226689</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7482,25 +7482,25 @@
       </c>
       <c r="E11" s="26">
         <f>+[6]Main!$I$3</f>
-        <v>71.94</v>
+        <v>58.85</v>
       </c>
       <c r="F11" s="19">
         <f>+[6]Main!$I$5</f>
-        <v>106226.60399999999</v>
+        <v>87068.574999999997</v>
       </c>
       <c r="G11" s="19">
         <f>+[6]Main!$I$7-[6]Main!$I$6</f>
-        <v>-579</v>
+        <v>-330</v>
       </c>
       <c r="H11" s="19">
         <f t="shared" si="1"/>
-        <v>105647.60399999999</v>
+        <v>86738.574999999997</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>716</v>
+        <v>800</v>
       </c>
       <c r="J11" s="28">
-        <v>46009</v>
+        <v>46100</v>
       </c>
       <c r="K11" s="19">
         <v>51362</v>
@@ -7664,25 +7664,25 @@
       </c>
       <c r="E13" s="26">
         <f>+[8]Main!$K$2</f>
-        <v>183</v>
+        <v>187.97</v>
       </c>
       <c r="F13" s="19">
         <f>+[8]Main!$K$4</f>
-        <v>73541.602073999995</v>
+        <v>75466.759510000004</v>
       </c>
       <c r="G13" s="19">
         <f>+[8]Main!$K$6-[8]Main!$K$5</f>
-        <v>2287.614</v>
+        <v>2776.4369999999999</v>
       </c>
       <c r="H13" s="19">
         <f t="shared" si="1"/>
-        <v>75829.216073999996</v>
+        <v>78243.196510000009</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>716</v>
+        <v>800</v>
       </c>
       <c r="J13" s="28">
-        <v>46009</v>
+        <v>46106</v>
       </c>
       <c r="K13" s="19">
         <v>8815.7999999999993</v>
@@ -9189,25 +9189,25 @@
       </c>
       <c r="E35" s="26">
         <f>+[30]Main!$I$3</f>
-        <v>42.33</v>
+        <v>36.1845</v>
       </c>
       <c r="F35" s="19">
         <f>+[30]Main!$I$5*FX!C3</f>
-        <v>8209.4173687343991</v>
+        <v>6920.7306306652799</v>
       </c>
       <c r="G35" s="19">
         <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
-        <v>956.61903999999981</v>
+        <v>853.08912000000009</v>
       </c>
       <c r="H35" s="19">
         <f t="shared" si="1"/>
-        <v>9166.0364087343987</v>
+        <v>7773.8197506652796</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>149</v>
+        <v>422</v>
       </c>
       <c r="J35" s="28">
-        <v>46009</v>
+        <v>46072</v>
       </c>
       <c r="K35" s="19"/>
       <c r="L35" s="23"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D0FC7A-41E7-4BF8-8BF4-702D91913CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9884E27B-F2E1-48B5-93C4-0908048EB94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="829">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2494,9 +2494,6 @@
     <t>Tom Ford</t>
   </si>
   <si>
-    <t>Saint Lauren</t>
-  </si>
-  <si>
     <t>Yves</t>
   </si>
   <si>
@@ -2554,9 +2551,6 @@
     <t>https://investors.skechers.com/press-releases/detail/665/skechers-agrees-to-be-acquired-by-3g-capital</t>
   </si>
   <si>
-    <t>Marc'o Polo</t>
-  </si>
-  <si>
     <t>630 Mio Rev in 2024</t>
   </si>
   <si>
@@ -2615,6 +2609,21 @@
   </si>
   <si>
     <t>Q326</t>
+  </si>
+  <si>
+    <t>Bankrupt</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Marc'o Polo bought 75%</t>
+  </si>
+  <si>
+    <t>Saint Laurent</t>
+  </si>
+  <si>
+    <t>Coco Chanel</t>
   </si>
 </sst>
 </file>
@@ -2628,13 +2637,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2778,22 +2793,103 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2813,132 +2909,52 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -3935,7 +3951,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5200,10 +5216,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5899,26 +5915,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>2.4</v>
+            <v>0.98</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>252.04949999999997</v>
+            <v>97.21301296</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>23.693000000000001</v>
+            <v>17.213000000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>284.517</v>
+            <v>291.31400000000002</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6016,26 +6032,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>29.25</v>
+            <v>18</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2376.6897667500002</v>
+            <v>1475.4221459999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>141</v>
+            <v>133.9</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>698.5</v>
+            <v>676.4</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6074,7 +6090,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6772,10 +6788,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>89</v>
@@ -6846,15 +6862,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1871378.8600852559</v>
+        <v>1871224.023598216</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>18988.59421520001</v>
+        <v>19001.871215200008</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1890367.4543004551</v>
+        <v>1890225.8948134151</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6905,15 +6921,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>24303.621559548777</v>
+        <v>24301.610696080726</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>246.6051196779222</v>
+        <v>246.77754824935076</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>24550.226679226689</v>
+        <v>24548.388244330068</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7021,7 +7037,7 @@
         <v>328754.04995284806</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J6" s="28">
         <v>46080</v>
@@ -7124,7 +7140,7 @@
         <v>227638.18459823998</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J7" s="28">
         <v>46034</v>
@@ -7327,7 +7343,7 @@
         <v>169606.19999999998</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="J9" s="28">
         <v>46078</v>
@@ -7497,7 +7513,7 @@
         <v>86738.574999999997</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J11" s="28">
         <v>46100</v>
@@ -7679,7 +7695,7 @@
         <v>78243.196510000009</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J13" s="28">
         <v>46106</v>
@@ -7754,7 +7770,7 @@
         <v>54114.976199999997</v>
       </c>
       <c r="I14" s="27" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="J14" s="28">
         <v>46086</v>
@@ -7829,7 +7845,7 @@
         <v>21907.001384499999</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J15" s="28">
         <v>46108</v>
@@ -7904,7 +7920,7 @@
         <v>30758.424511568002</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J16" s="28">
         <v>46090</v>
@@ -7982,7 +7998,7 @@
         <v>52169.666042884004</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J17" s="28">
         <v>46063</v>
@@ -8158,7 +8174,7 @@
         <v>11616.329300000001</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="J19" s="28">
         <v>46051</v>
@@ -8229,7 +8245,7 @@
         <v>31318.476624999996</v>
       </c>
       <c r="I20" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J20" s="28">
         <v>46051</v>
@@ -8297,7 +8313,7 @@
         <v>12596.627189120001</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J21" s="28">
         <v>46084</v>
@@ -8417,7 +8433,7 @@
         <v>13882.1833317856</v>
       </c>
       <c r="I23" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J23" s="28">
         <v>46072</v>
@@ -8606,7 +8622,7 @@
         <v>16159.263948639002</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J26" s="28">
         <v>46066</v>
@@ -8732,7 +8748,7 @@
         <v>10975.360432718078</v>
       </c>
       <c r="I28" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J28" s="28">
         <v>46085</v>
@@ -8795,7 +8811,7 @@
         <v>19747.929518499997</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J29" s="28">
         <v>46078</v>
@@ -8921,7 +8937,7 @@
         <v>19507.834465759999</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="J31" s="28">
         <v>46058</v>
@@ -9078,7 +9094,7 @@
         <v>5522.4062400000003</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J33" s="28">
         <v>46093</v>
@@ -9141,7 +9157,7 @@
         <v>9527.1548457999997</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J34" s="28">
         <v>46050</v>
@@ -9267,7 +9283,7 @@
         <v>9049.3599365999999</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J36" s="28">
         <v>46086</v>
@@ -9345,7 +9361,7 @@
         <v>337</v>
       </c>
       <c r="J37" s="32" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="K37" s="19"/>
       <c r="L37" s="23"/>
@@ -9468,7 +9484,7 @@
         <v>10595.386999999999</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J39" s="28">
         <v>46076</v>
@@ -9531,7 +9547,7 @@
         <v>9234.4889901200004</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J40" s="28">
         <v>46050</v>
@@ -9783,7 +9799,7 @@
         <v>5379.5601918300008</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J44" s="28">
         <v>46065</v>
@@ -9909,7 +9925,7 @@
         <v>6117.0447439999998</v>
       </c>
       <c r="I46" s="27" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="J46" s="28">
         <v>45981</v>
@@ -10149,7 +10165,7 @@
         <v>6316.3325860600007</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="J50" s="28">
         <v>46077</v>
@@ -10334,7 +10350,7 @@
         <v>3945.4253999999996</v>
       </c>
       <c r="I53" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J53" s="28">
         <v>46085</v>
@@ -10409,7 +10425,7 @@
         <v>2817.3176207199995</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J54" s="28">
         <v>46056</v>
@@ -10472,7 +10488,7 @@
         <v>5598.5518935199998</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J55" s="28">
         <v>46108</v>
@@ -10767,7 +10783,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
@@ -10887,7 +10903,7 @@
         <v>2778.6924601600003</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J62" s="28">
         <v>45952</v>
@@ -10946,7 +10962,7 @@
         <v>2875.6083200000007</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J63" s="28">
         <v>46091</v>
@@ -11180,7 +11196,7 @@
         <v>5509.5666168399994</v>
       </c>
       <c r="I67" s="27" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="J67" s="28">
         <v>46085</v>
@@ -13777,22 +13793,22 @@
       </c>
       <c r="E123" s="26">
         <f>+[76]Main!$H$2</f>
-        <v>2.4</v>
+        <v>0.98</v>
       </c>
       <c r="F123" s="19">
         <f>+[76]Main!$H$4</f>
-        <v>252.04949999999997</v>
+        <v>97.21301296</v>
       </c>
       <c r="G123" s="19">
         <f>+[76]Main!$H$6-[76]Main!$H$5</f>
-        <v>260.82400000000001</v>
+        <v>274.101</v>
       </c>
       <c r="H123" s="19">
         <f>+F123+G123</f>
-        <v>512.87349999999992</v>
+        <v>371.31401296000001</v>
       </c>
       <c r="I123" s="18" t="s">
-        <v>148</v>
+        <v>816</v>
       </c>
       <c r="J123" s="3"/>
       <c r="K123" s="19"/>
@@ -15195,25 +15211,25 @@
       </c>
       <c r="E155" s="26">
         <f>+[79]Main!$J$2</f>
-        <v>29.25</v>
+        <v>18</v>
       </c>
       <c r="F155" s="19">
         <f>+[79]Main!$J$4</f>
-        <v>2376.6897667500002</v>
+        <v>1475.4221459999999</v>
       </c>
       <c r="G155" s="19">
         <f>+[79]Main!$J$6-[79]Main!$J$5</f>
-        <v>557.5</v>
+        <v>542.5</v>
       </c>
       <c r="H155" s="19">
         <f>+F155+G155</f>
-        <v>2934.1897667500002</v>
+        <v>2017.9221459999999</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>149</v>
+        <v>816</v>
       </c>
       <c r="J155" s="28">
-        <v>45967</v>
+        <v>45706</v>
       </c>
       <c r="K155" s="26"/>
       <c r="L155" s="23"/>
@@ -17820,7 +17836,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="76" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B20" s="76"/>
       <c r="C20" s="47"/>
@@ -17840,14 +17856,18 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="47"/>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="82" t="s">
+        <v>827</v>
+      </c>
+      <c r="C21" s="47" t="s">
         <v>785</v>
       </c>
-      <c r="C21" s="47" t="s">
-        <v>786</v>
-      </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
+      <c r="D21" s="82" t="s">
+        <v>827</v>
+      </c>
+      <c r="E21" s="82" t="s">
+        <v>751</v>
+      </c>
       <c r="F21" s="47"/>
       <c r="G21" s="47"/>
       <c r="H21" s="47"/>
@@ -17863,12 +17883,14 @@
     <row r="22" spans="1:16">
       <c r="A22" s="47"/>
       <c r="B22" s="47" t="s">
+        <v>786</v>
+      </c>
+      <c r="C22" s="47" t="s">
         <v>787</v>
       </c>
-      <c r="C22" s="47" t="s">
-        <v>788</v>
-      </c>
-      <c r="D22" s="47"/>
+      <c r="D22" s="82" t="s">
+        <v>828</v>
+      </c>
       <c r="E22" s="47"/>
       <c r="F22" s="47"/>
       <c r="G22" s="47"/>
@@ -17885,13 +17907,17 @@
     <row r="23" spans="1:16">
       <c r="A23" s="47"/>
       <c r="B23" s="47" t="s">
+        <v>788</v>
+      </c>
+      <c r="C23" s="47" t="s">
         <v>789</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>790</v>
-      </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
+      <c r="D23" s="82" t="s">
+        <v>788</v>
+      </c>
+      <c r="E23" s="82" t="s">
+        <v>751</v>
+      </c>
       <c r="F23" s="47"/>
       <c r="G23" s="47"/>
       <c r="H23" s="47"/>
@@ -17907,13 +17933,17 @@
     <row r="24" spans="1:16">
       <c r="A24" s="47"/>
       <c r="B24" s="47" t="s">
+        <v>790</v>
+      </c>
+      <c r="C24" s="47" t="s">
         <v>791</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>792</v>
-      </c>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
+      <c r="D24" s="82" t="s">
+        <v>790</v>
+      </c>
+      <c r="E24" s="82" t="s">
+        <v>751</v>
+      </c>
       <c r="F24" s="47"/>
       <c r="G24" s="47"/>
       <c r="H24" s="47"/>
@@ -17932,10 +17962,14 @@
         <v>98</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>793</v>
-      </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
+        <v>792</v>
+      </c>
+      <c r="D25" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="82" t="s">
+        <v>751</v>
+      </c>
       <c r="F25" s="47"/>
       <c r="G25" s="47"/>
       <c r="H25" s="47"/>
@@ -17951,13 +17985,17 @@
     <row r="26" spans="1:16">
       <c r="A26" s="47"/>
       <c r="B26" s="47" t="s">
+        <v>793</v>
+      </c>
+      <c r="C26" s="47" t="s">
         <v>794</v>
       </c>
-      <c r="C26" s="47" t="s">
-        <v>795</v>
-      </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
+      <c r="D26" s="82" t="s">
+        <v>793</v>
+      </c>
+      <c r="E26" s="82" t="s">
+        <v>751</v>
+      </c>
       <c r="F26" s="47"/>
       <c r="G26" s="47"/>
       <c r="H26" s="47"/>
@@ -17973,13 +18011,17 @@
     <row r="27" spans="1:16">
       <c r="A27" s="47"/>
       <c r="B27" s="47" t="s">
+        <v>795</v>
+      </c>
+      <c r="C27" s="47" t="s">
         <v>796</v>
       </c>
-      <c r="C27" s="47" t="s">
-        <v>797</v>
-      </c>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
+      <c r="D27" s="82" t="s">
+        <v>795</v>
+      </c>
+      <c r="E27" s="82" t="s">
+        <v>751</v>
+      </c>
       <c r="F27" s="47"/>
       <c r="G27" s="47"/>
       <c r="H27" s="47"/>
@@ -17998,10 +18040,14 @@
         <v>720</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>798</v>
-      </c>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
+        <v>797</v>
+      </c>
+      <c r="D28" s="82" t="s">
+        <v>720</v>
+      </c>
+      <c r="E28" s="82" t="s">
+        <v>751</v>
+      </c>
       <c r="F28" s="47"/>
       <c r="G28" s="47"/>
       <c r="H28" s="47"/>
@@ -18016,8 +18062,8 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="47"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
       <c r="D29" s="47"/>
       <c r="E29" s="47"/>
       <c r="F29" s="47"/>
@@ -18060,26 +18106,683 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C032625C-E19A-4813-ABA6-8D106ACC7803}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:34">
       <c r="A1" s="46" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="B9" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="B10" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="82"/>
+      <c r="U1" s="82"/>
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="82"/>
+      <c r="Z1" s="82"/>
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="82"/>
+      <c r="AE1" s="82"/>
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+    </row>
+    <row r="2" spans="1:34">
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="82"/>
+      <c r="U2" s="82"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="82"/>
+      <c r="X2" s="82"/>
+      <c r="Y2" s="82"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
+      <c r="AB2" s="82"/>
+      <c r="AC2" s="82"/>
+      <c r="AD2" s="82"/>
+      <c r="AE2" s="82"/>
+      <c r="AF2" s="82"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="82"/>
+    </row>
+    <row r="3" spans="1:34">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="82"/>
+      <c r="AH3" s="82"/>
+    </row>
+    <row r="4" spans="1:34">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="82"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="82"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="82"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="82"/>
+      <c r="W4" s="82"/>
+      <c r="X4" s="82"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
+      <c r="AB4" s="82"/>
+      <c r="AC4" s="82"/>
+      <c r="AD4" s="82"/>
+      <c r="AE4" s="82"/>
+      <c r="AF4" s="82"/>
+      <c r="AG4" s="82"/>
+      <c r="AH4" s="82"/>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="82"/>
+      <c r="W5" s="82"/>
+      <c r="X5" s="82"/>
+      <c r="Y5" s="82"/>
+      <c r="Z5" s="82"/>
+      <c r="AA5" s="82"/>
+      <c r="AB5" s="82"/>
+      <c r="AC5" s="82"/>
+      <c r="AD5" s="82"/>
+      <c r="AE5" s="82"/>
+      <c r="AF5" s="82"/>
+      <c r="AG5" s="82"/>
+      <c r="AH5" s="82"/>
+    </row>
+    <row r="6" spans="1:34">
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="82"/>
+      <c r="X6" s="82"/>
+      <c r="Y6" s="82"/>
+      <c r="Z6" s="82"/>
+      <c r="AA6" s="82"/>
+      <c r="AB6" s="82"/>
+      <c r="AC6" s="82"/>
+      <c r="AD6" s="82"/>
+      <c r="AE6" s="82"/>
+      <c r="AF6" s="82"/>
+      <c r="AG6" s="82"/>
+      <c r="AH6" s="82"/>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="82"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="82"/>
+      <c r="U7" s="82"/>
+      <c r="V7" s="82"/>
+      <c r="W7" s="82"/>
+      <c r="X7" s="82"/>
+      <c r="Y7" s="82"/>
+      <c r="Z7" s="82"/>
+      <c r="AA7" s="82"/>
+      <c r="AB7" s="82"/>
+      <c r="AC7" s="82"/>
+      <c r="AD7" s="82"/>
+      <c r="AE7" s="82"/>
+      <c r="AF7" s="82"/>
+      <c r="AG7" s="82"/>
+      <c r="AH7" s="82"/>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
+      <c r="M8" s="82"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="82"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="82"/>
+      <c r="Y8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="82"/>
+      <c r="AC8" s="82"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="82"/>
+      <c r="AF8" s="82"/>
+      <c r="AG8" s="82"/>
+      <c r="AH8" s="82"/>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="B9" s="82" t="s">
+        <v>808</v>
+      </c>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="82"/>
+      <c r="O9" s="82"/>
+      <c r="P9" s="82"/>
+      <c r="Q9" s="82"/>
+      <c r="R9" s="82"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="82"/>
+      <c r="W9" s="82"/>
+      <c r="X9" s="82"/>
+      <c r="Y9" s="82"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="82"/>
+      <c r="AC9" s="82"/>
+      <c r="AD9" s="82"/>
+      <c r="AE9" s="82"/>
+      <c r="AF9" s="82"/>
+      <c r="AG9" s="82"/>
+      <c r="AH9" s="82"/>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="B10" s="82" t="s">
         <v>695</v>
       </c>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="82"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="82"/>
+      <c r="AC10" s="82"/>
+      <c r="AD10" s="82"/>
+      <c r="AE10" s="82"/>
+      <c r="AF10" s="82"/>
+      <c r="AG10" s="82"/>
+      <c r="AH10" s="82"/>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="82"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="82"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="82"/>
+      <c r="AG12" s="82"/>
+      <c r="AH12" s="82"/>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="82"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="82"/>
+      <c r="AC13" s="82"/>
+      <c r="AD13" s="82"/>
+      <c r="AE13" s="82"/>
+      <c r="AF13" s="82"/>
+      <c r="AG13" s="82"/>
+      <c r="AH13" s="82"/>
+    </row>
+    <row r="14" spans="1:34">
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
+      <c r="L14" s="82"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="82"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82"/>
+      <c r="R14" s="82"/>
+      <c r="S14" s="82"/>
+      <c r="T14" s="82"/>
+      <c r="U14" s="82"/>
+      <c r="V14" s="82"/>
+      <c r="W14" s="82"/>
+      <c r="X14" s="82"/>
+      <c r="Y14" s="82"/>
+      <c r="Z14" s="82"/>
+      <c r="AA14" s="82"/>
+      <c r="AB14" s="82"/>
+      <c r="AC14" s="82"/>
+      <c r="AD14" s="82"/>
+      <c r="AE14" s="82"/>
+      <c r="AF14" s="82"/>
+      <c r="AG14" s="82"/>
+      <c r="AH14" s="82"/>
+    </row>
+    <row r="15" spans="1:34">
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="82"/>
+      <c r="M15" s="82"/>
+      <c r="N15" s="82"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="82"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="82"/>
+      <c r="U15" s="82"/>
+      <c r="V15" s="82"/>
+      <c r="W15" s="82"/>
+      <c r="X15" s="82"/>
+      <c r="Y15" s="82"/>
+      <c r="Z15" s="82"/>
+      <c r="AA15" s="82"/>
+      <c r="AB15" s="82"/>
+      <c r="AC15" s="82"/>
+      <c r="AD15" s="82"/>
+      <c r="AE15" s="82"/>
+      <c r="AF15" s="82"/>
+      <c r="AG15" s="82"/>
+      <c r="AH15" s="82"/>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+      <c r="L16" s="82"/>
+      <c r="M16" s="82"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="82"/>
+      <c r="P16" s="82"/>
+      <c r="Q16" s="82"/>
+      <c r="R16" s="82"/>
+      <c r="S16" s="82"/>
+      <c r="T16" s="82"/>
+      <c r="U16" s="82"/>
+      <c r="V16" s="82"/>
+      <c r="W16" s="82"/>
+      <c r="X16" s="82"/>
+      <c r="Y16" s="82"/>
+      <c r="Z16" s="82"/>
+      <c r="AA16" s="82"/>
+      <c r="AB16" s="82"/>
+      <c r="AC16" s="82"/>
+      <c r="AD16" s="82"/>
+      <c r="AE16" s="82"/>
+      <c r="AF16" s="82"/>
+      <c r="AG16" s="82"/>
+      <c r="AH16" s="82"/>
+    </row>
+    <row r="17" spans="2:34">
+      <c r="B17" s="82"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="82"/>
+      <c r="M17" s="82"/>
+      <c r="N17" s="82"/>
+      <c r="O17" s="82"/>
+      <c r="P17" s="82"/>
+      <c r="Q17" s="82"/>
+      <c r="R17" s="82"/>
+      <c r="S17" s="82"/>
+      <c r="T17" s="82"/>
+      <c r="U17" s="82"/>
+      <c r="V17" s="82"/>
+      <c r="W17" s="82"/>
+      <c r="X17" s="82"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="82"/>
+      <c r="AA17" s="82"/>
+      <c r="AB17" s="82"/>
+      <c r="AC17" s="82"/>
+      <c r="AD17" s="82"/>
+      <c r="AE17" s="82"/>
+      <c r="AF17" s="82"/>
+      <c r="AG17" s="82"/>
+      <c r="AH17" s="82"/>
+    </row>
+    <row r="18" spans="2:34">
+      <c r="B18" s="82"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="82"/>
+      <c r="L18" s="82"/>
+      <c r="M18" s="82"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="82"/>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="82"/>
+      <c r="R18" s="82"/>
+      <c r="S18" s="82"/>
+      <c r="T18" s="82"/>
+      <c r="U18" s="82"/>
+      <c r="V18" s="82"/>
+      <c r="W18" s="82"/>
+      <c r="X18" s="82"/>
+      <c r="Y18" s="82"/>
+      <c r="Z18" s="82"/>
+      <c r="AA18" s="82"/>
+      <c r="AB18" s="82"/>
+      <c r="AC18" s="82"/>
+      <c r="AD18" s="82"/>
+      <c r="AE18" s="82"/>
+      <c r="AF18" s="82"/>
+      <c r="AG18" s="82"/>
+      <c r="AH18" s="82"/>
+    </row>
+    <row r="19" spans="2:34">
+      <c r="B19" s="82"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="82"/>
+      <c r="K19" s="82"/>
+      <c r="L19" s="82"/>
+      <c r="M19" s="82"/>
+      <c r="N19" s="82"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82"/>
+      <c r="R19" s="82"/>
+      <c r="S19" s="82"/>
+      <c r="T19" s="82"/>
+      <c r="U19" s="82"/>
+      <c r="V19" s="82"/>
+      <c r="W19" s="82"/>
+      <c r="X19" s="82"/>
+      <c r="Y19" s="82"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82"/>
+      <c r="AB19" s="82"/>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="82"/>
+      <c r="AE19" s="82"/>
+      <c r="AF19" s="82"/>
+      <c r="AG19" s="82"/>
+      <c r="AH19" s="82"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18096,7 +18799,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="47" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -18157,7 +18860,7 @@
     <row r="3" spans="1:17">
       <c r="A3" s="47"/>
       <c r="B3" s="74" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="47"/>
@@ -18479,15 +19182,12 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="47"/>
-      <c r="B18" s="47" t="s">
-        <v>805</v>
-      </c>
       <c r="C18" s="59" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D18" s="47"/>
       <c r="E18" s="60" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="58"/>
@@ -18523,7 +19223,9 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
+      <c r="B20" s="82" t="s">
+        <v>824</v>
+      </c>
       <c r="C20" s="59"/>
       <c r="D20" s="47"/>
       <c r="E20" s="60"/>
@@ -18542,8 +19244,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="59"/>
+      <c r="B21" s="82" t="s">
+        <v>825</v>
+      </c>
+      <c r="C21" s="82" t="s">
+        <v>826</v>
+      </c>
       <c r="D21" s="47"/>
       <c r="E21" s="60"/>
       <c r="F21" s="58"/>
@@ -49168,7 +49874,7 @@
         <v>463</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="47"/>
@@ -49184,7 +49890,7 @@
         <v>464</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="47"/>
@@ -49245,10 +49951,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="81" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
@@ -49458,7 +50164,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2" s="77" t="s">
         <v>126</v>
@@ -49555,7 +50261,7 @@
         <v>9420</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I4" s="47"/>
       <c r="J4" s="47"/>
@@ -49686,10 +50392,10 @@
         <v>16.75</v>
       </c>
       <c r="G7" s="47" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H7" s="47" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="I7" s="47"/>
       <c r="J7" s="47"/>
@@ -49725,7 +50431,7 @@
         <v>476</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E8" s="78">
         <v>45322</v>
@@ -49735,7 +50441,7 @@
         <v>500</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="I8" s="47"/>
       <c r="J8" s="47"/>
@@ -49765,10 +50471,10 @@
     <row r="9" spans="1:32">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>689</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9884E27B-F2E1-48B5-93C4-0908048EB94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1E35DB-B611-4A55-8194-F96BBB66F88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="828">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2279,9 +2279,6 @@
   </si>
   <si>
     <t>BGFV</t>
-  </si>
-  <si>
-    <t>FQ425</t>
   </si>
   <si>
     <t>Acquired by Dicks Sporting Goods for 2.4 billion USD</t>
@@ -5627,22 +5624,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>48290</v>
+            <v>62750</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>14814725.010580001</v>
+            <v>19253241.140000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1792940</v>
+            <v>1983578</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>315917</v>
+            <v>315443</v>
           </cell>
         </row>
       </sheetData>
@@ -5934,7 +5931,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6051,7 +6048,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6788,10 +6785,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="N3" s="11" t="s">
         <v>813</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>814</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>89</v>
@@ -6862,15 +6859,15 @@
       <c r="E4" s="18"/>
       <c r="F4" s="19">
         <f>SUM(F6:F153)</f>
-        <v>1871224.023598216</v>
+        <v>1899186.6752135619</v>
       </c>
       <c r="G4" s="19">
         <f>+SUM(G6:G153)</f>
-        <v>19001.871215200008</v>
+        <v>17797.865615200008</v>
       </c>
       <c r="H4" s="19">
         <f>SUM(H6:H153)</f>
-        <v>1890225.8948134151</v>
+        <v>1916984.5408287612</v>
       </c>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -6921,15 +6918,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="19">
         <f>AVERAGE(F6:F153)</f>
-        <v>24301.610696080726</v>
+        <v>24664.762015760545</v>
       </c>
       <c r="G5" s="19">
         <f>AVERAGE(G6:G153)</f>
-        <v>246.77754824935076</v>
+        <v>231.14111188571439</v>
       </c>
       <c r="H5" s="19">
         <f>AVERAGE(H6:H153)</f>
-        <v>24548.388244330068</v>
+        <v>24895.903127646248</v>
       </c>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -7037,7 +7034,7 @@
         <v>328754.04995284806</v>
       </c>
       <c r="I6" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J6" s="28">
         <v>46080</v>
@@ -7140,7 +7137,7 @@
         <v>227638.18459823998</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J7" s="28">
         <v>46034</v>
@@ -7343,7 +7340,7 @@
         <v>169606.19999999998</v>
       </c>
       <c r="I9" s="27" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J9" s="28">
         <v>46078</v>
@@ -7513,7 +7510,7 @@
         <v>86738.574999999997</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J11" s="28">
         <v>46100</v>
@@ -7595,25 +7592,25 @@
       </c>
       <c r="E12" s="31">
         <f>+[7]Main!$J$3</f>
-        <v>48290</v>
+        <v>62750</v>
       </c>
       <c r="F12" s="19">
         <f>+[7]Main!$J$5*FX!C5</f>
-        <v>93332.767566654016</v>
+        <v>121295.419182</v>
       </c>
       <c r="G12" s="19">
         <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
-        <v>-9305.2448999999997</v>
+        <v>-10509.2505</v>
       </c>
       <c r="H12" s="19">
         <f t="shared" si="1"/>
-        <v>84027.522666654011</v>
+        <v>110786.168682</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J12" s="28">
-        <v>46030</v>
+        <v>46121</v>
       </c>
       <c r="K12" s="19">
         <f>2301122*FX!C5</f>
@@ -7695,7 +7692,7 @@
         <v>78243.196510000009</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J13" s="28">
         <v>46106</v>
@@ -7770,7 +7767,7 @@
         <v>54114.976199999997</v>
       </c>
       <c r="I14" s="27" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="J14" s="28">
         <v>46086</v>
@@ -7845,7 +7842,7 @@
         <v>21907.001384499999</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J15" s="28">
         <v>46108</v>
@@ -7920,7 +7917,7 @@
         <v>30758.424511568002</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J16" s="28">
         <v>46090</v>
@@ -7998,7 +7995,7 @@
         <v>52169.666042884004</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J17" s="28">
         <v>46063</v>
@@ -8174,7 +8171,7 @@
         <v>11616.329300000001</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J19" s="28">
         <v>46051</v>
@@ -8245,7 +8242,7 @@
         <v>31318.476624999996</v>
       </c>
       <c r="I20" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J20" s="28">
         <v>46051</v>
@@ -8313,7 +8310,7 @@
         <v>12596.627189120001</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J21" s="28">
         <v>46084</v>
@@ -8433,7 +8430,7 @@
         <v>13882.1833317856</v>
       </c>
       <c r="I23" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J23" s="28">
         <v>46072</v>
@@ -8559,7 +8556,7 @@
         <v>22508.616016480002</v>
       </c>
       <c r="I25" s="27" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J25" s="28">
         <v>46058</v>
@@ -8622,7 +8619,7 @@
         <v>16159.263948639002</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J26" s="28">
         <v>46066</v>
@@ -8748,7 +8745,7 @@
         <v>10975.360432718078</v>
       </c>
       <c r="I28" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J28" s="28">
         <v>46085</v>
@@ -8811,7 +8808,7 @@
         <v>19747.929518499997</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J29" s="28">
         <v>46078</v>
@@ -8937,7 +8934,7 @@
         <v>19507.834465759999</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J31" s="28">
         <v>46058</v>
@@ -9094,7 +9091,7 @@
         <v>5522.4062400000003</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J33" s="28">
         <v>46093</v>
@@ -9157,7 +9154,7 @@
         <v>9527.1548457999997</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J34" s="28">
         <v>46050</v>
@@ -9261,7 +9258,7 @@
         <v>111</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>21</v>
@@ -9283,7 +9280,7 @@
         <v>9049.3599365999999</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J36" s="28">
         <v>46086</v>
@@ -9361,7 +9358,7 @@
         <v>337</v>
       </c>
       <c r="J37" s="32" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="K37" s="19"/>
       <c r="L37" s="23"/>
@@ -9484,7 +9481,7 @@
         <v>10595.386999999999</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J39" s="28">
         <v>46076</v>
@@ -9547,7 +9544,7 @@
         <v>9234.4889901200004</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J40" s="28">
         <v>46050</v>
@@ -9740,7 +9737,7 @@
         <v>5139.9465440399999</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J43" s="28">
         <v>45975</v>
@@ -9799,7 +9796,7 @@
         <v>5379.5601918300008</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J44" s="28">
         <v>46065</v>
@@ -9925,7 +9922,7 @@
         <v>6117.0447439999998</v>
       </c>
       <c r="I46" s="27" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J46" s="28">
         <v>45981</v>
@@ -9988,7 +9985,7 @@
         <v>6623.1464285999991</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J47" s="28">
         <v>45939</v>
@@ -10165,7 +10162,7 @@
         <v>6316.3325860600007</v>
       </c>
       <c r="I50" s="18" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="J50" s="28">
         <v>46077</v>
@@ -10350,7 +10347,7 @@
         <v>3945.4253999999996</v>
       </c>
       <c r="I53" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J53" s="28">
         <v>46085</v>
@@ -10425,7 +10422,7 @@
         <v>2817.3176207199995</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J54" s="28">
         <v>46056</v>
@@ -10488,7 +10485,7 @@
         <v>5598.5518935199998</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J55" s="28">
         <v>46108</v>
@@ -10673,7 +10670,7 @@
         <v>4949.4143572999992</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J58" s="28">
         <v>45957</v>
@@ -10783,7 +10780,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F60" s="19"/>
       <c r="G60" s="19"/>
@@ -10903,7 +10900,7 @@
         <v>2778.6924601600003</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J62" s="28">
         <v>45952</v>
@@ -10962,7 +10959,7 @@
         <v>2875.6083200000007</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J63" s="28">
         <v>46091</v>
@@ -11021,7 +11018,7 @@
         <v>2248.0596218599999</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J64" s="28">
         <v>45967</v>
@@ -11196,7 +11193,7 @@
         <v>5509.5666168399994</v>
       </c>
       <c r="I67" s="27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J67" s="28">
         <v>46085</v>
@@ -12636,7 +12633,7 @@
         <v>1178.0758231121999</v>
       </c>
       <c r="I97" s="18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J97" s="28"/>
       <c r="K97" s="19"/>
@@ -13808,7 +13805,7 @@
         <v>371.31401296000001</v>
       </c>
       <c r="I123" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J123" s="3"/>
       <c r="K123" s="19"/>
@@ -15226,7 +15223,7 @@
         <v>2017.9221459999999</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="J155" s="28">
         <v>45706</v>
@@ -17370,13 +17367,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="47" t="s">
+        <v>721</v>
+      </c>
+      <c r="D2" s="47" t="s">
         <v>722</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="E2" s="47" t="s">
         <v>723</v>
-      </c>
-      <c r="E2" s="47" t="s">
-        <v>724</v>
       </c>
       <c r="F2" s="47" t="s">
         <v>126</v>
@@ -17395,16 +17392,16 @@
     <row r="3" spans="1:16">
       <c r="A3" s="47"/>
       <c r="B3" s="47" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D3" s="47" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F3" s="47"/>
       <c r="G3" s="47"/>
@@ -17421,16 +17418,16 @@
     <row r="4" spans="1:16">
       <c r="A4" s="47"/>
       <c r="B4" s="47" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D4" s="47" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="47" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="F4" s="47"/>
       <c r="G4" s="47"/>
@@ -17447,19 +17444,19 @@
     <row r="5" spans="1:16">
       <c r="A5" s="47"/>
       <c r="B5" s="47" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D5" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="47" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F5" s="47" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G5" s="47"/>
       <c r="H5" s="47"/>
@@ -17475,16 +17472,16 @@
     <row r="6" spans="1:16">
       <c r="A6" s="47"/>
       <c r="B6" s="47" t="s">
+        <v>741</v>
+      </c>
+      <c r="C6" s="47" t="s">
         <v>742</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>743</v>
       </c>
       <c r="D6" s="47" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -17501,19 +17498,19 @@
     <row r="7" spans="1:16">
       <c r="A7" s="47"/>
       <c r="B7" s="47" t="s">
+        <v>745</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>746</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>747</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
@@ -17532,16 +17529,16 @@
         <v>135</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D8" s="47" t="s">
         <v>135</v>
       </c>
       <c r="E8" s="47" t="s">
+        <v>749</v>
+      </c>
+      <c r="F8" s="47" t="s">
         <v>750</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>751</v>
       </c>
       <c r="G8" s="47"/>
       <c r="H8" s="47"/>
@@ -17557,19 +17554,19 @@
     <row r="9" spans="1:16">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
+        <v>751</v>
+      </c>
+      <c r="C9" s="47" t="s">
         <v>752</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>753</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>682</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G9" s="47"/>
       <c r="H9" s="47"/>
@@ -17585,19 +17582,19 @@
     <row r="10" spans="1:16">
       <c r="A10" s="47"/>
       <c r="B10" s="47" t="s">
+        <v>754</v>
+      </c>
+      <c r="C10" s="47" t="s">
         <v>755</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="D10" s="47" t="s">
         <v>756</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="E10" s="47" t="s">
+        <v>750</v>
+      </c>
+      <c r="F10" s="47" t="s">
         <v>757</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>751</v>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>758</v>
       </c>
       <c r="G10" s="47"/>
       <c r="H10" s="47"/>
@@ -17613,19 +17610,19 @@
     <row r="11" spans="1:16">
       <c r="A11" s="47"/>
       <c r="B11" s="47" t="s">
+        <v>759</v>
+      </c>
+      <c r="C11" s="47" t="s">
         <v>760</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>761</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G11" s="47"/>
       <c r="H11" s="47"/>
@@ -17641,19 +17638,19 @@
     <row r="12" spans="1:16">
       <c r="A12" s="47"/>
       <c r="B12" s="47" t="s">
+        <v>762</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>763</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>764</v>
       </c>
       <c r="D12" s="47" t="s">
         <v>123</v>
       </c>
       <c r="E12" s="47" t="s">
+        <v>765</v>
+      </c>
+      <c r="F12" s="47" t="s">
         <v>766</v>
-      </c>
-      <c r="F12" s="47" t="s">
-        <v>767</v>
       </c>
       <c r="G12" s="47"/>
       <c r="H12" s="47"/>
@@ -17669,16 +17666,16 @@
     <row r="13" spans="1:16">
       <c r="A13" s="47"/>
       <c r="B13" s="47" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D13" s="47" t="s">
         <v>135</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F13" s="47"/>
       <c r="G13" s="47"/>
@@ -17695,16 +17692,16 @@
     <row r="14" spans="1:16">
       <c r="A14" s="47"/>
       <c r="B14" s="47" t="s">
+        <v>769</v>
+      </c>
+      <c r="C14" s="47" t="s">
         <v>770</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>771</v>
       </c>
       <c r="D14" s="47" t="s">
         <v>677</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F14" s="47"/>
       <c r="G14" s="47"/>
@@ -17721,16 +17718,16 @@
     <row r="15" spans="1:16">
       <c r="A15" s="47"/>
       <c r="B15" s="47" t="s">
+        <v>771</v>
+      </c>
+      <c r="C15" s="47" t="s">
         <v>772</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="D15" s="47" t="s">
         <v>773</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="E15" s="47" t="s">
         <v>774</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>775</v>
       </c>
       <c r="F15" s="47"/>
       <c r="G15" s="47"/>
@@ -17747,19 +17744,19 @@
     <row r="16" spans="1:16">
       <c r="A16" s="47"/>
       <c r="B16" s="47" t="s">
+        <v>776</v>
+      </c>
+      <c r="C16" s="47" t="s">
         <v>777</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="D16" s="47" t="s">
         <v>778</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="E16" s="47" t="s">
         <v>779</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="F16" s="47" t="s">
         <v>780</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>781</v>
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="47"/>
@@ -17775,16 +17772,16 @@
     <row r="17" spans="1:16">
       <c r="A17" s="47"/>
       <c r="B17" s="47" t="s">
+        <v>781</v>
+      </c>
+      <c r="C17" s="47" t="s">
         <v>782</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="D17" s="47" t="s">
         <v>783</v>
       </c>
-      <c r="D17" s="47" t="s">
-        <v>784</v>
-      </c>
       <c r="E17" s="47" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F17" s="47"/>
       <c r="G17" s="47"/>
@@ -17836,7 +17833,7 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="76" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B20" s="76"/>
       <c r="C20" s="47"/>
@@ -17857,16 +17854,16 @@
     <row r="21" spans="1:16">
       <c r="A21" s="47"/>
       <c r="B21" s="82" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D21" s="82" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E21" s="82" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F21" s="47"/>
       <c r="G21" s="47"/>
@@ -17883,13 +17880,13 @@
     <row r="22" spans="1:16">
       <c r="A22" s="47"/>
       <c r="B22" s="47" t="s">
+        <v>785</v>
+      </c>
+      <c r="C22" s="47" t="s">
         <v>786</v>
       </c>
-      <c r="C22" s="47" t="s">
-        <v>787</v>
-      </c>
       <c r="D22" s="82" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E22" s="47"/>
       <c r="F22" s="47"/>
@@ -17907,16 +17904,16 @@
     <row r="23" spans="1:16">
       <c r="A23" s="47"/>
       <c r="B23" s="47" t="s">
+        <v>787</v>
+      </c>
+      <c r="C23" s="47" t="s">
         <v>788</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>789</v>
-      </c>
       <c r="D23" s="82" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E23" s="82" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F23" s="47"/>
       <c r="G23" s="47"/>
@@ -17933,16 +17930,16 @@
     <row r="24" spans="1:16">
       <c r="A24" s="47"/>
       <c r="B24" s="47" t="s">
+        <v>789</v>
+      </c>
+      <c r="C24" s="47" t="s">
         <v>790</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>791</v>
-      </c>
       <c r="D24" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E24" s="82" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F24" s="47"/>
       <c r="G24" s="47"/>
@@ -17962,13 +17959,13 @@
         <v>98</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D25" s="82" t="s">
         <v>98</v>
       </c>
       <c r="E25" s="82" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F25" s="47"/>
       <c r="G25" s="47"/>
@@ -17985,16 +17982,16 @@
     <row r="26" spans="1:16">
       <c r="A26" s="47"/>
       <c r="B26" s="47" t="s">
+        <v>792</v>
+      </c>
+      <c r="C26" s="47" t="s">
         <v>793</v>
       </c>
-      <c r="C26" s="47" t="s">
-        <v>794</v>
-      </c>
       <c r="D26" s="82" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E26" s="82" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F26" s="47"/>
       <c r="G26" s="47"/>
@@ -18011,16 +18008,16 @@
     <row r="27" spans="1:16">
       <c r="A27" s="47"/>
       <c r="B27" s="47" t="s">
+        <v>794</v>
+      </c>
+      <c r="C27" s="47" t="s">
         <v>795</v>
       </c>
-      <c r="C27" s="47" t="s">
-        <v>796</v>
-      </c>
       <c r="D27" s="82" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E27" s="82" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F27" s="47"/>
       <c r="G27" s="47"/>
@@ -18037,16 +18034,16 @@
     <row r="28" spans="1:16">
       <c r="A28" s="47"/>
       <c r="B28" s="47" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D28" s="82" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E28" s="82" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F28" s="47"/>
       <c r="G28" s="47"/>
@@ -18397,7 +18394,7 @@
     </row>
     <row r="9" spans="1:34">
       <c r="B9" s="82" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C9" s="82"/>
       <c r="D9" s="82"/>
@@ -18799,7 +18796,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="47" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -18860,7 +18857,7 @@
     <row r="3" spans="1:17">
       <c r="A3" s="47"/>
       <c r="B3" s="74" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="47"/>
@@ -18884,7 +18881,7 @@
         <v>434</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D4" s="47"/>
       <c r="E4" s="60"/>
@@ -19183,11 +19180,11 @@
     <row r="18" spans="1:17">
       <c r="A18" s="47"/>
       <c r="C18" s="59" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D18" s="47"/>
       <c r="E18" s="60" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="58"/>
@@ -19224,7 +19221,7 @@
     <row r="20" spans="1:17">
       <c r="A20" s="47"/>
       <c r="B20" s="82" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C20" s="59"/>
       <c r="D20" s="47"/>
@@ -19245,10 +19242,10 @@
     <row r="21" spans="1:17">
       <c r="A21" s="47"/>
       <c r="B21" s="82" t="s">
+        <v>824</v>
+      </c>
+      <c r="C21" s="82" t="s">
         <v>825</v>
-      </c>
-      <c r="C21" s="82" t="s">
-        <v>826</v>
       </c>
       <c r="D21" s="47"/>
       <c r="E21" s="60"/>
@@ -20468,7 +20465,7 @@
         <v>21</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F23" s="58"/>
       <c r="G23" s="58"/>
@@ -39109,7 +39106,7 @@
         <v>95429.722976000019</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J5" s="62">
         <v>45975</v>
@@ -49874,7 +49871,7 @@
         <v>463</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D8" s="47"/>
       <c r="E8" s="47"/>
@@ -49890,7 +49887,7 @@
         <v>464</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="47"/>
@@ -49951,10 +49948,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="81" t="s">
+        <v>818</v>
+      </c>
+      <c r="C13" s="81" t="s">
         <v>819</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>820</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
@@ -50152,19 +50149,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="76" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D2" s="76" t="s">
+        <v>717</v>
+      </c>
+      <c r="E2" s="76" t="s">
         <v>718</v>
-      </c>
-      <c r="E2" s="76" t="s">
-        <v>719</v>
       </c>
       <c r="F2" s="77" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="77" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2" s="77" t="s">
         <v>126</v>
@@ -50197,13 +50194,13 @@
     <row r="3" spans="1:32">
       <c r="A3" s="47"/>
       <c r="B3" s="47" t="s">
+        <v>719</v>
+      </c>
+      <c r="C3" s="46" t="s">
         <v>720</v>
       </c>
-      <c r="C3" s="46" t="s">
-        <v>721</v>
-      </c>
       <c r="D3" s="47" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E3" s="78">
         <v>45757</v>
@@ -50249,19 +50246,19 @@
         <v>692</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E4" s="78">
         <v>45782</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G4" s="80">
         <v>9420</v>
       </c>
       <c r="H4" s="47" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I4" s="47"/>
       <c r="J4" s="47"/>
@@ -50297,7 +50294,7 @@
         <v>128</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E5" s="78">
         <v>45637</v>
@@ -50337,13 +50334,13 @@
     <row r="6" spans="1:32">
       <c r="A6" s="47"/>
       <c r="B6" s="47" t="s">
+        <v>731</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>731</v>
+      </c>
+      <c r="D6" s="47" t="s">
         <v>732</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>732</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>733</v>
       </c>
       <c r="E6" s="47"/>
       <c r="F6" s="47"/>
@@ -50392,10 +50389,10 @@
         <v>16.75</v>
       </c>
       <c r="G7" s="47" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H7" s="47" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="I7" s="47"/>
       <c r="J7" s="47"/>
@@ -50431,7 +50428,7 @@
         <v>476</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E8" s="78">
         <v>45322</v>
@@ -50441,7 +50438,7 @@
         <v>500</v>
       </c>
       <c r="H8" s="47" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I8" s="47"/>
       <c r="J8" s="47"/>
@@ -50471,10 +50468,10 @@
     <row r="9" spans="1:32">
       <c r="A9" s="47"/>
       <c r="B9" s="47" t="s">
+        <v>810</v>
+      </c>
+      <c r="C9" s="47" t="s">
         <v>811</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>812</v>
       </c>
       <c r="D9" s="47" t="s">
         <v>689</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43F623D-577F-44E0-8DD6-032C96361919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A862115-ADC9-4F35-BD7B-82FE30F78DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -2989,29 +2989,29 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="I4">
-            <v>605.70000000000005</v>
+            <v>549</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>301904.66341620003</v>
+            <v>273230.13006</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>8176</v>
+            <v>8794</v>
           </cell>
         </row>
         <row r="8">
           <cell r="I8">
-            <v>22381</v>
+            <v>20343</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4898,7 +4898,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6859,15 +6859,15 @@
       <c r="E4" s="17"/>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1898885.408013562</v>
+        <v>1869063.8933231139</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>17863.385615200004</v>
+        <v>15101.145615200001</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1916748.7936287613</v>
+        <v>1884165.038938313</v>
       </c>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
@@ -6918,15 +6918,15 @@
       <c r="E5" s="3"/>
       <c r="F5" s="18">
         <f>+AVERAGE(F6:F181)</f>
-        <v>24060.381089831139</v>
+        <v>23682.893562103949</v>
       </c>
       <c r="G5" s="18">
         <f>AVERAGE(G6:G153)</f>
-        <v>231.99202097662342</v>
+        <v>196.11877422337665</v>
       </c>
       <c r="H5" s="18">
         <f>AVERAGE(H6:H153)</f>
-        <v>24892.841475698198</v>
+        <v>24469.675830367702</v>
       </c>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
@@ -7019,22 +7019,22 @@
       </c>
       <c r="E6" s="25">
         <f>+[1]Main!$I$4</f>
-        <v>605.70000000000005</v>
+        <v>549</v>
       </c>
       <c r="F6" s="18">
         <f>+[1]Main!$I$6*FX!C3</f>
-        <v>313980.84995284805</v>
+        <v>284159.33526239998</v>
       </c>
       <c r="G6" s="18">
         <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
-        <v>14773.2</v>
+        <v>12010.960000000001</v>
       </c>
       <c r="H6" s="18">
         <f>F6+G6</f>
-        <v>328754.04995284806</v>
+        <v>296170.2952624</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J6" s="27">
         <v>46080</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A862115-ADC9-4F35-BD7B-82FE30F78DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2988CF-04FA-4B44-8F5E-E2D394C1F7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -136,8 +136,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="829">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2621,6 +2643,9 @@
   </si>
   <si>
     <t>Coco Chanel</t>
+  </si>
+  <si>
+    <t>/</t>
   </si>
 </sst>
 </file>
@@ -2742,7 +2767,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2787,13 +2812,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2953,6 +2987,24 @@
     <xf numFmtId="2" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
@@ -3008,10 +3060,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3731,22 +3783,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>324.72000000000003</v>
+            <v>338.01</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>19691.234465760001</v>
+            <v>20461.91295813</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>1645.5</v>
+            <v>2250.8000000000002</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1462.1000000000001</v>
+            <v>1238.3</v>
           </cell>
         </row>
       </sheetData>
@@ -4143,7 +4195,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5113,26 +5165,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>5.0599999999999996</v>
+            <v>7.47</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2169.8306218600001</v>
+            <v>3181.39830747</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>910.98500000000001</v>
+            <v>464.64800000000002</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>989.21399999999994</v>
+            <v>989.73099999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5756,22 +5808,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>15.34</v>
+            <v>14.56</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1486.6562653799999</v>
+            <v>1413.6025904000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>180.5</v>
+            <v>346.9</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>401.20000000000005</v>
+            <v>415.1</v>
           </cell>
         </row>
       </sheetData>
@@ -6854,30 +6906,42 @@
       <c r="B4" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="17"/>
+      <c r="C4" s="16">
+        <f>+COUNTA(C6:C181)</f>
+        <v>176</v>
+      </c>
+      <c r="D4" s="16">
+        <f>+COUNTA(_xlfn.UNIQUE(D6:D181))</f>
+        <v>31</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>828</v>
+      </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1869063.8933231139</v>
+        <v>1870795.7324653578</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>15101.145615200001</v>
+        <v>14613.674615200003</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1884165.038938313</v>
-      </c>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
+        <v>1885409.4070805567</v>
+      </c>
+      <c r="I4" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>828</v>
+      </c>
       <c r="K4" s="18">
         <f>SUM(K6:K153)</f>
         <v>488291.97860000003</v>
       </c>
       <c r="L4" s="19">
-        <f>+MEDIAN(L6:L153)</f>
-        <v>8.4999999999999992E-2</v>
+        <f>SUMPRODUCT(L6:L182,K6:K182)/SUM(K6:K1820)</f>
+        <v>4.5446103889776254E-2</v>
       </c>
       <c r="M4" s="18">
         <f>SUM(M6:M85)</f>
@@ -6906,103 +6970,116 @@
       <c r="AE4" s="16"/>
       <c r="AF4" s="3"/>
     </row>
-    <row r="5" spans="1:34">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:34" ht="14.25" thickBot="1">
+      <c r="A5" s="84" t="s">
         <v>315</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="18">
+      <c r="C5" s="84" t="s">
+        <v>828</v>
+      </c>
+      <c r="D5" s="86" t="str" cm="1">
+        <f t="array" ref="D5">_xlfn.LET(_xlpm.rng,D6:D182,INDEX(_xlpm.rng,MATCH(MAX(COUNTIF(_xlpm.rng,_xlpm.rng)),COUNTIF(_xlpm.rng,_xlpm.rng),0)))</f>
+        <v>US</v>
+      </c>
+      <c r="E5" s="84" t="s">
+        <v>828</v>
+      </c>
+      <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23682.893562103949</v>
-      </c>
-      <c r="G5" s="18">
+        <v>23704.815576562731</v>
+      </c>
+      <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>196.11877422337665</v>
-      </c>
-      <c r="H5" s="18">
+        <v>189.78798201558445</v>
+      </c>
+      <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24469.675830367702</v>
-      </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18">
+        <v>24485.836455591645</v>
+      </c>
+      <c r="I5" s="88" t="s">
+        <v>422</v>
+      </c>
+      <c r="J5" s="84" t="s">
+        <v>828</v>
+      </c>
+      <c r="K5" s="87">
         <f>AVERAGE(K6:K153)</f>
         <v>27127.332144444445</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="89">
         <f>AVERAGE(L6:L182)</f>
         <v>6.1055555555555557E-2</v>
       </c>
-      <c r="M5" s="18">
+      <c r="M5" s="87">
         <f t="shared" ref="M5:AA5" si="0">AVERAGE(M6:M85)</f>
         <v>5162.4957499999991</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="87">
         <f t="shared" si="0"/>
         <v>3185.9719999999998</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="89">
         <f t="shared" si="0"/>
         <v>0.54437500000000005</v>
       </c>
-      <c r="P5" s="22">
+      <c r="P5" s="89">
         <f t="shared" si="0"/>
         <v>0.15707924701533954</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="90">
         <f t="shared" si="0"/>
         <v>29.227272727272727</v>
       </c>
-      <c r="R5" s="23">
+      <c r="R5" s="90">
         <f t="shared" si="0"/>
         <v>30.644444444444439</v>
       </c>
-      <c r="S5" s="23">
+      <c r="S5" s="90">
         <f t="shared" si="0"/>
         <v>1.1667142857142856</v>
       </c>
-      <c r="T5" s="23">
+      <c r="T5" s="90">
         <f t="shared" si="0"/>
         <v>-1.1000000000000001</v>
       </c>
-      <c r="U5" s="23">
+      <c r="U5" s="90">
         <f t="shared" si="0"/>
         <v>7.2519999999999998</v>
       </c>
-      <c r="V5" s="23">
+      <c r="V5" s="90">
         <f t="shared" si="0"/>
         <v>4.020999999999999</v>
       </c>
-      <c r="W5" s="23">
+      <c r="W5" s="90">
         <f t="shared" si="0"/>
         <v>16.98714285714286</v>
       </c>
-      <c r="X5" s="23">
+      <c r="X5" s="90">
         <f t="shared" si="0"/>
         <v>0.78666666666666663</v>
       </c>
-      <c r="Y5" s="22">
+      <c r="Y5" s="89">
         <f t="shared" si="0"/>
         <v>0.27285714285714285</v>
       </c>
-      <c r="Z5" s="22">
+      <c r="Z5" s="89">
         <f t="shared" si="0"/>
         <v>0.25428571428571434</v>
       </c>
-      <c r="AA5" s="22">
+      <c r="AA5" s="89">
         <f t="shared" si="0"/>
         <v>0.19857142857142862</v>
       </c>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
+      <c r="AB5" s="87"/>
+      <c r="AC5" s="87"/>
+      <c r="AD5" s="91"/>
+      <c r="AE5" s="86"/>
+      <c r="AF5" s="86"/>
+      <c r="AG5" s="92"/>
+      <c r="AH5" s="92"/>
     </row>
     <row r="6" spans="1:34">
       <c r="A6" s="16">
@@ -8923,25 +9000,25 @@
       </c>
       <c r="E31" s="25">
         <f>+[26]Main!$H$2</f>
-        <v>324.72000000000003</v>
+        <v>338.01</v>
       </c>
       <c r="F31" s="18">
         <f>+[26]Main!$H$4</f>
-        <v>19691.234465760001</v>
+        <v>20461.91295813</v>
       </c>
       <c r="G31" s="18">
         <f>+[26]Main!$H$6-[26]Main!$H$5</f>
-        <v>-183.39999999999986</v>
+        <v>-1012.5000000000002</v>
       </c>
       <c r="H31" s="18">
         <f t="shared" si="1"/>
-        <v>19507.834465759999</v>
+        <v>19449.41295813</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>809</v>
+        <v>822</v>
       </c>
       <c r="J31" s="27">
-        <v>46058</v>
+        <v>46163</v>
       </c>
       <c r="K31" s="18">
         <v>6631.4</v>
@@ -11007,25 +11084,25 @@
       </c>
       <c r="E64" s="25">
         <f>+[58]Main!$I$2</f>
-        <v>5.0599999999999996</v>
+        <v>7.47</v>
       </c>
       <c r="F64" s="18">
         <f>+[58]Main!$I$4</f>
-        <v>2169.8306218600001</v>
+        <v>3181.39830747</v>
       </c>
       <c r="G64" s="18">
         <f>+[58]Main!$I$6-[58]Main!$I$5</f>
-        <v>78.228999999999928</v>
+        <v>525.08299999999997</v>
       </c>
       <c r="H64" s="18">
         <f>+F64+G64</f>
-        <v>2248.0596218599999</v>
+        <v>3706.48130747</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>715</v>
+        <v>821</v>
       </c>
       <c r="J64" s="27">
-        <v>45967</v>
+        <v>46156</v>
       </c>
       <c r="K64" s="18"/>
       <c r="L64" s="22"/>
@@ -12622,24 +12699,26 @@
       </c>
       <c r="E97" s="25">
         <f>+[72]Main!$J$2</f>
-        <v>15.34</v>
+        <v>14.56</v>
       </c>
       <c r="F97" s="18">
         <f>+[72]Main!$J$4*FX!C13</f>
-        <v>1025.7928231121998</v>
+        <v>975.38578737599994</v>
       </c>
       <c r="G97" s="18">
         <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
-        <v>152.28300000000002</v>
+        <v>47.058000000000028</v>
       </c>
       <c r="H97" s="18">
         <f>+F97+G97</f>
-        <v>1178.0758231121999</v>
+        <v>1022.4437873759999</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>715</v>
-      </c>
-      <c r="J97" s="27"/>
+        <v>821</v>
+      </c>
+      <c r="J97" s="27">
+        <v>46162</v>
+      </c>
       <c r="K97" s="18"/>
       <c r="L97" s="22"/>
       <c r="M97" s="18"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2988CF-04FA-4B44-8F5E-E2D394C1F7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACE3869-8B5A-48A9-BCCE-56DAA394B0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3172,33 +3172,33 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>331.65</v>
+            <v>284.8</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>40660.140425849997</v>
+            <v>34917.850457599998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>4240</v>
+            <v>4313</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>13743</v>
+            <v>12562</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3257,17 +3257,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="M2">
-            <v>87.2</v>
+            <v>115.3</v>
           </cell>
         </row>
         <row r="4">
           <cell r="M4">
-            <v>13030.808300000001</v>
+            <v>16366.831656300001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>1414.479</v>
+            <v>2086.7460000000001</v>
           </cell>
         </row>
         <row r="6">
@@ -3276,7 +3276,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3500,29 +3500,29 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>2186</v>
+            <v>2146</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>229171.86980599997</v>
+            <v>226551.95815200001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>10321</v>
+            <v>12239</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>32</v>
+            <v>34</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3542,26 +3542,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>100.74</v>
+            <v>154.69999999999999</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>20616.416016480001</v>
+            <v>31321.2152981</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>743.2</v>
+            <v>1077.7</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>2635.4</v>
+            <v>2396.4</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4195,7 +4195,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5184,7 +5184,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6919,15 +6919,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1870795.7324653578</v>
+        <v>1876139.8654161377</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>14613.674615200003</v>
+        <v>10071.107615200001</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1885409.4070805567</v>
+        <v>1886210.9730313367</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -6989,15 +6989,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23704.815576562731</v>
+        <v>23772.46282910425</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>189.78798201558445</v>
+        <v>130.79360539220781</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24485.836455591645</v>
+        <v>24496.246403004374</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7199,25 +7199,25 @@
       </c>
       <c r="E7" s="30">
         <f>+[2]Main!$K$2</f>
-        <v>2186</v>
+        <v>2146</v>
       </c>
       <c r="F7" s="18">
         <f>+[2]Main!$K$4*FX!C3</f>
-        <v>238338.74459823998</v>
+        <v>235614.03647808</v>
       </c>
       <c r="G7" s="18">
         <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
-        <v>-10700.56</v>
+        <v>-12693.2</v>
       </c>
       <c r="H7" s="18">
         <f>F7+G7</f>
-        <v>227638.18459823998</v>
+        <v>222920.83647807999</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>815</v>
+        <v>338</v>
       </c>
       <c r="J7" s="27">
-        <v>46034</v>
+        <v>46127</v>
       </c>
       <c r="K7" s="18">
         <f>13427*1.08</f>
@@ -8061,25 +8061,25 @@
       </c>
       <c r="E17" s="25">
         <f>+[12]Main!$H$2</f>
-        <v>331.65</v>
+        <v>284.8</v>
       </c>
       <c r="F17" s="18">
         <f>+[12]Main!$H$4*FX!C3</f>
-        <v>42286.546042884002</v>
+        <v>36314.564475904001</v>
       </c>
       <c r="G17" s="18">
         <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
-        <v>9883.1200000000008</v>
+        <v>8578.9600000000009</v>
       </c>
       <c r="H17" s="18">
         <f t="shared" si="1"/>
-        <v>52169.666042884004</v>
+        <v>44893.524475904</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J17" s="27">
-        <v>46063</v>
+        <v>46133</v>
       </c>
       <c r="K17" s="18">
         <f>17194*FX!C3</f>
@@ -8237,25 +8237,25 @@
       </c>
       <c r="E19" s="25">
         <f>+[14]Main!$M$2</f>
-        <v>87.2</v>
+        <v>115.3</v>
       </c>
       <c r="F19" s="18">
         <f>+[14]Main!$M$4</f>
-        <v>13030.808300000001</v>
+        <v>16366.831656300001</v>
       </c>
       <c r="G19" s="18">
         <f>+[14]Main!$M$6-[14]Main!$M$5</f>
-        <v>-1414.479</v>
+        <v>-2086.7460000000001</v>
       </c>
       <c r="H19" s="18">
         <f>F19+G19</f>
-        <v>11616.329300000001</v>
+        <v>14280.085656300002</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>809</v>
+        <v>822</v>
       </c>
       <c r="J19" s="27">
-        <v>46051</v>
+        <v>46163</v>
       </c>
       <c r="K19" s="25"/>
       <c r="L19" s="22"/>
@@ -8622,25 +8622,25 @@
       </c>
       <c r="E25" s="25">
         <f>+[20]Main!$J$2</f>
-        <v>100.74</v>
+        <v>154.69999999999999</v>
       </c>
       <c r="F25" s="18">
         <f>+[20]Main!$J$4</f>
-        <v>20616.416016480001</v>
+        <v>31321.2152981</v>
       </c>
       <c r="G25" s="18">
         <f>+[20]Main!$J$6-[20]Main!$J$5</f>
-        <v>1892.2</v>
+        <v>1318.7</v>
       </c>
       <c r="H25" s="18">
         <f t="shared" si="1"/>
-        <v>22508.616016480002</v>
+        <v>32639.915298100001</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>715</v>
+        <v>798</v>
       </c>
       <c r="J25" s="27">
-        <v>46058</v>
+        <v>46149</v>
       </c>
       <c r="K25" s="25"/>
       <c r="L25" s="22"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACE3869-8B5A-48A9-BCCE-56DAA394B0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B0AE94-3065-4766-B80E-E63C03415F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3191,14 +3191,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3276,7 +3276,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3296,22 +3296,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>171.25</v>
+            <v>185.55</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>274654.17499999999</v>
+            <v>297628.32315000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>20363</v>
+            <v>20908</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>75377</v>
+            <v>20675</v>
           </cell>
         </row>
       </sheetData>
@@ -3519,10 +3519,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3561,7 +3561,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3581,26 +3581,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>3710</v>
+            <v>4396</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2653960.5315300003</v>
+            <v>3141807.6866959999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>123998</v>
+            <v>112267</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>35000</v>
+            <v>37500</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3620,12 +3620,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>118.8</v>
+            <v>127.35</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>13911.48</v>
+            <v>14912.684999999999</v>
           </cell>
         </row>
         <row r="5">
@@ -3639,7 +3639,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3899,22 +3899,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>15.1</v>
+            <v>20.3</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>5899.9438458000004</v>
+            <v>7942.6458629000008</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>419.11500000000001</v>
+            <v>1466.4690000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>4046.326</v>
+            <v>4155.6499999999996</v>
           </cell>
         </row>
       </sheetData>
@@ -4176,22 +4176,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>22.77</v>
+            <v>21.96</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>8899.1889901200011</v>
+            <v>8574.6616225199996</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>707.5</v>
+            <v>848.8</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1042.8</v>
+            <v>1039.2</v>
           </cell>
         </row>
       </sheetData>
@@ -4336,22 +4336,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>81.19</v>
+            <v>99.2</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>4215.0321918300006</v>
+            <v>5094.5152000000007</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>153.97</v>
+            <v>130.35400000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1318.498</v>
+            <v>1230.885</v>
           </cell>
         </row>
       </sheetData>
@@ -4654,12 +4654,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>20.399999999999999</v>
+            <v>23.45</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3001.5878640000001</v>
+            <v>3450.3546770000003</v>
           </cell>
         </row>
         <row r="5">
@@ -6919,15 +6919,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1876139.8654161377</v>
+        <v>1885701.7159111234</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>10071.107615200001</v>
+        <v>3765.3709151999997</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1886210.9730313367</v>
+        <v>1889467.0868263226</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="K4" s="18">
         <f>SUM(K6:K153)</f>
-        <v>488291.97860000003</v>
+        <v>484260.93860000005</v>
       </c>
       <c r="L4" s="19">
         <f>SUMPRODUCT(L6:L182,K6:K182)/SUM(K6:K1820)</f>
-        <v>4.5446103889776254E-2</v>
+        <v>4.0784644834453314E-2</v>
       </c>
       <c r="M4" s="18">
         <f>SUM(M6:M85)</f>
@@ -6989,15 +6989,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23772.46282910425</v>
+        <v>23893.498911319261</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>130.79360539220781</v>
+        <v>48.900920976623375</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24496.246403004374</v>
+        <v>24538.533595147048</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7007,11 +7007,11 @@
       </c>
       <c r="K5" s="87">
         <f>AVERAGE(K6:K153)</f>
-        <v>27127.332144444445</v>
+        <v>26903.385477777781</v>
       </c>
       <c r="L5" s="89">
         <f>AVERAGE(L6:L182)</f>
-        <v>6.1055555555555557E-2</v>
+        <v>5.9388888888888901E-2</v>
       </c>
       <c r="M5" s="87">
         <f t="shared" ref="M5:AA5" si="0">AVERAGE(M6:M85)</f>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="P5" s="89">
         <f t="shared" si="0"/>
-        <v>0.15707924701533954</v>
+        <v>0.15774857840286111</v>
       </c>
       <c r="Q5" s="90">
         <f t="shared" si="0"/>
@@ -7117,11 +7117,11 @@
         <v>46080</v>
       </c>
       <c r="K6" s="18">
-        <f>84683*FX!C3</f>
-        <v>88070.32</v>
+        <f>80807*FX!C3</f>
+        <v>84039.28</v>
       </c>
       <c r="L6" s="22">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="M6" s="18">
         <f>18907*FX!C3</f>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="P6" s="22">
         <f>+M6/K6</f>
-        <v>0.22326795224543297</v>
+        <v>0.23397725444577824</v>
       </c>
       <c r="Q6" s="23">
         <v>25.7</v>
@@ -8308,25 +8308,25 @@
       </c>
       <c r="E20" s="25">
         <f>+[15]Main!$I$2</f>
-        <v>171.25</v>
+        <v>185.55</v>
       </c>
       <c r="F20" s="18">
         <f>+[15]Main!$I$4*FX!C4</f>
-        <v>26092.146624999998</v>
+        <v>28274.690699250001</v>
       </c>
       <c r="G20" s="18">
         <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C4</f>
-        <v>5226.33</v>
+        <v>-22.135000000000002</v>
       </c>
       <c r="H20" s="18">
         <f t="shared" si="1"/>
-        <v>31318.476624999996</v>
+        <v>28252.555699250002</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J20" s="27">
-        <v>46051</v>
+        <v>46107</v>
       </c>
       <c r="K20" s="18">
         <f>234478*FX!C4</f>
@@ -8685,25 +8685,25 @@
       </c>
       <c r="E26" s="25">
         <f>+[21]Main!$I$2</f>
-        <v>3710</v>
+        <v>4396</v>
       </c>
       <c r="F26" s="18">
         <f>+[21]Main!$I$4*FX!C5</f>
-        <v>16719.951348639002</v>
+        <v>19793.3884261848</v>
       </c>
       <c r="G26" s="18">
         <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C5</f>
-        <v>-560.68740000000003</v>
+        <v>-471.03210000000001</v>
       </c>
       <c r="H26" s="18">
         <f>F26+G26</f>
-        <v>16159.263948639002</v>
+        <v>19322.356326184799</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J26" s="27">
-        <v>46066</v>
+        <v>46155</v>
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="22"/>
@@ -8748,11 +8748,11 @@
       </c>
       <c r="E27" s="25">
         <f>+[22]Main!$I$2</f>
-        <v>118.8</v>
+        <v>127.35</v>
       </c>
       <c r="F27" s="18">
         <f>+[22]Main!$I$4*FX!C8</f>
-        <v>17250.235199999999</v>
+        <v>18491.7294</v>
       </c>
       <c r="G27" s="18">
         <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C8</f>
@@ -8760,13 +8760,13 @@
       </c>
       <c r="H27" s="18">
         <f>F27+G27</f>
-        <v>17672.083200000001</v>
+        <v>18913.577400000002</v>
       </c>
       <c r="I27" s="26" t="s">
         <v>149</v>
       </c>
       <c r="J27" s="27">
-        <v>46028</v>
+        <v>46107</v>
       </c>
       <c r="K27" s="25"/>
       <c r="L27" s="22"/>
@@ -9220,25 +9220,25 @@
       </c>
       <c r="E34" s="25">
         <f>+[29]Main!$H$2</f>
-        <v>15.1</v>
+        <v>20.3</v>
       </c>
       <c r="F34" s="18">
         <f>+[29]Main!$H$4</f>
-        <v>5899.9438458000004</v>
+        <v>7942.6458629000008</v>
       </c>
       <c r="G34" s="18">
         <f>+[29]Main!$H$6-[29]Main!$H$5</f>
-        <v>3627.2110000000002</v>
+        <v>2689.1809999999996</v>
       </c>
       <c r="H34" s="18">
         <f>+G34+F34</f>
-        <v>9527.1548457999997</v>
+        <v>10631.826862900001</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>798</v>
+        <v>821</v>
       </c>
       <c r="J34" s="27">
-        <v>46050</v>
+        <v>46162</v>
       </c>
       <c r="K34" s="18"/>
       <c r="L34" s="22"/>
@@ -9502,7 +9502,7 @@
         <v>149</v>
       </c>
       <c r="J38" s="27">
-        <v>46034</v>
+        <v>46093</v>
       </c>
       <c r="K38" s="18"/>
       <c r="L38" s="22"/>
@@ -9610,25 +9610,25 @@
       </c>
       <c r="E40" s="25">
         <f>+[35]Main!$I$2</f>
-        <v>22.77</v>
+        <v>21.96</v>
       </c>
       <c r="F40" s="18">
         <f>+[35]Main!$I$4</f>
-        <v>8899.1889901200011</v>
+        <v>8574.6616225199996</v>
       </c>
       <c r="G40" s="18">
         <f>+[35]Main!$I$6-[35]Main!$I$5</f>
-        <v>335.29999999999995</v>
+        <v>190.40000000000009</v>
       </c>
       <c r="H40" s="18">
         <f>F40+G40</f>
-        <v>9234.4889901200004</v>
+        <v>8765.0616225199992</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J40" s="27">
-        <v>46050</v>
+        <v>46118</v>
       </c>
       <c r="K40" s="18">
         <v>6179</v>
@@ -9862,25 +9862,25 @@
       </c>
       <c r="E44" s="25">
         <f>+[39]Main!$H$2</f>
-        <v>81.19</v>
+        <v>99.2</v>
       </c>
       <c r="F44" s="18">
         <f>+[39]Main!$H$4</f>
-        <v>4215.0321918300006</v>
+        <v>5094.5152000000007</v>
       </c>
       <c r="G44" s="18">
         <f>+[39]Main!$H$6-[39]Main!$H$5</f>
-        <v>1164.528</v>
+        <v>1100.5309999999999</v>
       </c>
       <c r="H44" s="18">
         <f>F44+G44</f>
-        <v>5379.5601918300008</v>
+        <v>6195.0462000000007</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J44" s="27">
-        <v>46065</v>
+        <v>46149</v>
       </c>
       <c r="K44" s="18"/>
       <c r="L44" s="22"/>
@@ -10287,11 +10287,11 @@
       </c>
       <c r="E51" s="25">
         <f>+[46]Main!$I$2</f>
-        <v>20.399999999999999</v>
+        <v>23.45</v>
       </c>
       <c r="F51" s="18">
         <f>+[46]Main!$I$4*FX!C3</f>
-        <v>3121.65137856</v>
+        <v>3588.3688640800005</v>
       </c>
       <c r="G51" s="18">
         <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
@@ -10299,13 +10299,13 @@
       </c>
       <c r="H51" s="18">
         <f t="shared" si="3"/>
-        <v>4215.0033785600008</v>
+        <v>4681.7208640800009</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>149</v>
+        <v>815</v>
       </c>
       <c r="J51" s="27">
-        <v>45960</v>
+        <v>46079</v>
       </c>
       <c r="K51" s="18"/>
       <c r="L51" s="22"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B0AE94-3065-4766-B80E-E63C03415F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB3DFD3-8EBD-4553-933D-27B6B9826F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -2659,13 +2659,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2824,22 +2830,100 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2853,158 +2937,83 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
@@ -3418,12 +3427,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>50.68</v>
+            <v>55.15</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>13710.09920364</v>
+            <v>14919.336445949999</v>
           </cell>
         </row>
         <row r="5">
@@ -3437,8 +3446,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3600,7 +3609,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3639,7 +3648,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4098,22 +4107,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>93</v>
+            <v>86.1</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>6323.4118679999992</v>
+            <v>5854.2555035999994</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>243.84100000000001</v>
+            <v>203.84100000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>7.04</v>
+            <v>396.62300000000005</v>
           </cell>
         </row>
       </sheetData>
@@ -6199,22 +6208,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>257.3</v>
+            <v>233</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>116795.35560530001</v>
+            <v>106951.39810799999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>2251</v>
+            <v>3544</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>9569</v>
+            <v>10839</v>
           </cell>
         </row>
       </sheetData>
@@ -6280,22 +6289,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>63.49</v>
+            <v>111.2</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>22840.653210200002</v>
+            <v>40224.047181599999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>2631</v>
+            <v>3082</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>7301</v>
+            <v>7322</v>
           </cell>
         </row>
       </sheetData>
@@ -6319,12 +6328,12 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>140.1</v>
+            <v>194.55</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>7229.7596279999998</v>
+            <v>10039.612674000002</v>
           </cell>
         </row>
         <row r="6">
@@ -6919,15 +6928,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1885701.7159111234</v>
+        <v>1886471.40002415</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>3765.3709151999997</v>
+        <v>4212.1372351999989</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1889467.0868263226</v>
+        <v>1890683.5372593489</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -6937,19 +6946,19 @@
       </c>
       <c r="K4" s="18">
         <f>SUM(K6:K153)</f>
-        <v>484260.93860000005</v>
+        <v>492429.91060000006</v>
       </c>
       <c r="L4" s="19">
         <f>SUMPRODUCT(L6:L182,K6:K182)/SUM(K6:K1820)</f>
-        <v>4.0784644834453314E-2</v>
+        <v>3.9002440539402931E-2</v>
       </c>
       <c r="M4" s="18">
         <f>SUM(M6:M85)</f>
-        <v>82599.931999999986</v>
+        <v>86102.331999999995</v>
       </c>
       <c r="N4" s="18">
         <f>SUM(N6:N85)</f>
-        <v>47789.579999999994</v>
+        <v>51484.742999999995</v>
       </c>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
@@ -6989,15 +6998,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23893.498911319261</v>
+        <v>23903.241748193013</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>48.900920976623375</v>
+        <v>54.703080976623362</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24538.533595147048</v>
+        <v>24554.331652718818</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7007,27 +7016,27 @@
       </c>
       <c r="K5" s="87">
         <f>AVERAGE(K6:K153)</f>
-        <v>26903.385477777781</v>
+        <v>25917.363715789477</v>
       </c>
       <c r="L5" s="89">
         <f>AVERAGE(L6:L182)</f>
-        <v>5.9388888888888901E-2</v>
+        <v>5.8894736842105264E-2</v>
       </c>
       <c r="M5" s="87">
         <f t="shared" ref="M5:AA5" si="0">AVERAGE(M6:M85)</f>
-        <v>5162.4957499999991</v>
+        <v>4783.4628888888883</v>
       </c>
       <c r="N5" s="87">
         <f t="shared" si="0"/>
-        <v>3185.9719999999998</v>
+        <v>3028.5142941176468</v>
       </c>
       <c r="O5" s="89">
         <f t="shared" si="0"/>
-        <v>0.54437500000000005</v>
+        <v>0.54647058823529415</v>
       </c>
       <c r="P5" s="89">
         <f t="shared" si="0"/>
-        <v>0.15774857840286111</v>
+        <v>0.16238104755529126</v>
       </c>
       <c r="Q5" s="90">
         <f t="shared" si="0"/>
@@ -7220,11 +7229,11 @@
         <v>46127</v>
       </c>
       <c r="K7" s="18">
-        <f>13427*1.08</f>
-        <v>14501.160000000002</v>
+        <f>16002*FX!C3</f>
+        <v>16642.080000000002</v>
       </c>
       <c r="L7" s="22">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="M7" s="18">
         <f>5650*1.08</f>
@@ -7700,7 +7709,10 @@
         <f>+SUM([7]Model!$G$20:$I$20,[7]Model!$C$20)*FX!C5</f>
         <v>3765.1320000000001</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="18">
+        <f>433010*FX!C5</f>
+        <v>2727.9630000000002</v>
+      </c>
       <c r="O12" s="22">
         <v>0.55000000000000004</v>
       </c>
@@ -8182,13 +8194,16 @@
         <v>46099</v>
       </c>
       <c r="K18" s="18">
-        <f>63380*FX!C9</f>
-        <v>8873.2000000000007</v>
+        <f>70826*FX!C9</f>
+        <v>9915.6400000000012</v>
       </c>
       <c r="L18" s="22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M18" s="18"/>
+      <c r="M18" s="18">
+        <f>16595*FX!C9</f>
+        <v>2323.3000000000002</v>
+      </c>
       <c r="N18" s="18"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -8257,12 +8272,25 @@
       <c r="J19" s="27">
         <v>46163</v>
       </c>
-      <c r="K19" s="25"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="22"/>
+      <c r="K19" s="18">
+        <v>4985.6120000000001</v>
+      </c>
+      <c r="L19" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="M19" s="18">
+        <v>1179.0999999999999</v>
+      </c>
+      <c r="N19" s="18">
+        <v>967.2</v>
+      </c>
+      <c r="O19" s="22">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P19" s="22">
+        <f>+M19/K19</f>
+        <v>0.23650055399417361</v>
+      </c>
       <c r="Q19" s="23">
         <v>19</v>
       </c>
@@ -8496,11 +8524,11 @@
       </c>
       <c r="E23" s="25">
         <f>+[18]Main!$H$2</f>
-        <v>50.68</v>
+        <v>55.15</v>
       </c>
       <c r="F23" s="18">
         <f>+[18]Main!$H$4*FX!C3</f>
-        <v>14258.5031717856</v>
+        <v>15516.109903787999</v>
       </c>
       <c r="G23" s="18">
         <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C3</f>
@@ -8508,13 +8536,13 @@
       </c>
       <c r="H23" s="18">
         <f t="shared" si="1"/>
-        <v>13882.1833317856</v>
+        <v>15139.790063787999</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J23" s="27">
-        <v>46072</v>
+        <v>46225</v>
       </c>
       <c r="K23" s="25"/>
       <c r="L23" s="22"/>
@@ -9484,22 +9512,22 @@
       </c>
       <c r="E38" s="25">
         <f>+[33]Main!$J$2</f>
-        <v>93</v>
+        <v>86.1</v>
       </c>
       <c r="F38" s="18">
         <f>+[33]Main!$J$4*FX!C3</f>
-        <v>6576.348342719999</v>
+        <v>6088.4257237439997</v>
       </c>
       <c r="G38" s="18">
         <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
-        <v>-246.27304000000004</v>
+        <v>200.49328000000006</v>
       </c>
       <c r="H38" s="18">
         <f>F38+G38</f>
-        <v>6330.0753027199989</v>
+        <v>6288.9190037439994</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>149</v>
+        <v>422</v>
       </c>
       <c r="J38" s="27">
         <v>46093</v>
@@ -39108,25 +39136,25 @@
       </c>
       <c r="E4" s="59">
         <f>+[81]Main!$I$2</f>
-        <v>257.3</v>
+        <v>233</v>
       </c>
       <c r="F4" s="57">
         <f>+[81]Main!$I$4*FX!C3</f>
-        <v>121467.16982951201</v>
+        <v>111229.45403231999</v>
       </c>
       <c r="G4" s="57">
         <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
-        <v>7610.72</v>
+        <v>7586.8</v>
       </c>
       <c r="H4" s="57">
         <f>+F4+G4</f>
-        <v>129077.88982951202</v>
-      </c>
-      <c r="I4" s="47" t="s">
-        <v>338</v>
+        <v>118816.25403231999</v>
+      </c>
+      <c r="I4" s="93" t="s">
+        <v>422</v>
       </c>
       <c r="J4" s="61">
-        <v>45770</v>
+        <v>46134</v>
       </c>
       <c r="K4" s="59"/>
       <c r="L4" s="62"/>
@@ -39240,24 +39268,26 @@
       </c>
       <c r="E6" s="59">
         <f>+[83]Main!$K$2</f>
-        <v>63.49</v>
+        <v>111.2</v>
       </c>
       <c r="F6" s="57">
         <f>+[83]Main!$K$4</f>
-        <v>22840.653210200002</v>
+        <v>40224.047181599999</v>
       </c>
       <c r="G6" s="57">
         <f>+([83]Main!$K$6-[83]Main!$K$5)</f>
-        <v>4670</v>
+        <v>4240</v>
       </c>
       <c r="H6" s="57">
         <f t="shared" si="0"/>
-        <v>27510.653210200002</v>
-      </c>
-      <c r="I6" s="47" t="s">
-        <v>380</v>
-      </c>
-      <c r="J6" s="61"/>
+        <v>44464.047181599999</v>
+      </c>
+      <c r="I6" s="93" t="s">
+        <v>809</v>
+      </c>
+      <c r="J6" s="61">
+        <v>46143</v>
+      </c>
       <c r="K6" s="59"/>
       <c r="L6" s="62"/>
       <c r="M6" s="59"/>
@@ -39304,11 +39334,11 @@
       </c>
       <c r="E7" s="59">
         <f>+[84]Main!$I$3</f>
-        <v>140.1</v>
+        <v>194.55</v>
       </c>
       <c r="F7" s="57">
         <f>+[84]Main!$I$5*FX!C7</f>
-        <v>8097.3307833600002</v>
+        <v>11244.366194880004</v>
       </c>
       <c r="G7" s="57">
         <f>+([84]Main!$I$7-[84]Main!$I$6)*FX!C7</f>
@@ -39316,12 +39346,14 @@
       </c>
       <c r="H7" s="57">
         <f>+F7+G7</f>
-        <v>6877.6507833599999</v>
+        <v>10024.686194880003</v>
       </c>
       <c r="I7" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="J7" s="61"/>
+      <c r="J7" s="61">
+        <v>46099</v>
+      </c>
       <c r="K7" s="59"/>
       <c r="L7" s="62"/>
       <c r="M7" s="59"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB3DFD3-8EBD-4553-933D-27B6B9826F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340C71BC-EA1C-41AF-859F-EF8989DF394B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="830">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2646,6 +2646,9 @@
   </si>
   <si>
     <t>/</t>
+  </si>
+  <si>
+    <t>FQ426</t>
   </si>
 </sst>
 </file>
@@ -3446,8 +3449,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3713,22 +3716,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>34.25</v>
+            <v>40.49</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>19049.829518499999</v>
+            <v>22544.952903140002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>353.3</v>
+            <v>652.29999999999995</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1051.4000000000001</v>
+            <v>935.09999999999991</v>
           </cell>
         </row>
       </sheetData>
@@ -4390,17 +4393,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>152.19999999999999</v>
+            <v>159.05000000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>171377.19999999998</v>
+            <v>179090.30000000002</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>4640</v>
+            <v>6230</v>
           </cell>
         </row>
         <row r="7">
@@ -4409,9 +4412,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6928,15 +6931,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1886471.40002415</v>
+        <v>1897679.6234087902</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>4212.1372351999989</v>
+        <v>2206.8372351999974</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1890683.5372593489</v>
+        <v>1899886.4606439888</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -6998,15 +7001,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23903.241748193013</v>
+        <v>24045.117993568205</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>54.703080976623362</v>
+        <v>28.660223833766199</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24554.331652718818</v>
+        <v>24673.850138233622</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7411,26 +7414,24 @@
       </c>
       <c r="E9" s="25">
         <f>+[4]Main!$I$3</f>
-        <v>152.19999999999999</v>
+        <v>159.05000000000001</v>
       </c>
       <c r="F9" s="18">
         <f>+[4]Main!$I$5</f>
-        <v>171377.19999999998</v>
+        <v>179090.30000000002</v>
       </c>
       <c r="G9" s="18">
         <f>+[4]Main!$I$7-[4]Main!$I$6</f>
-        <v>-1771</v>
+        <v>-3361</v>
       </c>
       <c r="H9" s="18">
         <f>F9+G9</f>
-        <v>169606.19999999998</v>
+        <v>175729.30000000002</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>821</v>
-      </c>
-      <c r="J9" s="27">
-        <v>46078</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="J9" s="27"/>
       <c r="K9" s="25">
         <v>54217</v>
       </c>
@@ -8902,22 +8903,22 @@
       </c>
       <c r="E29" s="25">
         <f>+[24]Main!$J$2</f>
-        <v>34.25</v>
+        <v>40.49</v>
       </c>
       <c r="F29" s="18">
         <f>+[24]Main!$J$4</f>
-        <v>19049.829518499999</v>
+        <v>22544.952903140002</v>
       </c>
       <c r="G29" s="18">
         <f>+[24]Main!$J$6-[24]Main!$J$5</f>
-        <v>698.10000000000014</v>
+        <v>282.79999999999995</v>
       </c>
       <c r="H29" s="18">
         <f t="shared" si="1"/>
-        <v>19747.929518499997</v>
+        <v>22827.752903140001</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J29" s="27">
         <v>46078</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340C71BC-EA1C-41AF-859F-EF8989DF394B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E13C295-9C75-451B-B150-BBA96A144794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="832">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2649,6 +2649,12 @@
   </si>
   <si>
     <t>FQ426</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -3993,22 +3999,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>36.1845</v>
+            <v>33.710999999999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>6654.5486833320001</v>
+            <v>6199.6570538160004</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>329.06700000000001</v>
+            <v>229.227</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>1149.345</v>
+            <v>1140.2079999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -4412,9 +4418,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4627,17 +4633,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>77.23</v>
+            <v>65.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>6928.0655860600009</v>
+            <v>5874.7799535000004</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>611.73299999999995</v>
+            <v>695.93000000000006</v>
           </cell>
         </row>
         <row r="6">
@@ -4646,7 +4652,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4666,26 +4672,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>23.45</v>
+            <v>24.05</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3450.3546770000003</v>
+            <v>3545.2105000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>292.60000000000002</v>
+            <v>290</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1343.9</v>
+            <v>572</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4808,7 +4814,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6093,26 +6099,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>18</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1475.4221459999999</v>
+            <v>1638</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>133.9</v>
+            <v>206.3</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>676.4</v>
+            <v>621.70000000000005</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6931,15 +6937,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1897679.6234087902</v>
+        <v>1896251.9005374536</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>2206.8372351999974</v>
+        <v>1416.899355199997</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1899886.4606439888</v>
+        <v>1897668.7998926523</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7001,15 +7007,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>24045.117993568205</v>
+        <v>24029.103499677869</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>28.660223833766199</v>
+        <v>18.401290327272687</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24673.850138233622</v>
+        <v>24645.049349255223</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -9312,25 +9318,25 @@
       </c>
       <c r="E35" s="25">
         <f>+[30]Main!$I$3</f>
-        <v>36.1845</v>
+        <v>33.710999999999999</v>
       </c>
       <c r="F35" s="18">
         <f>+[30]Main!$I$5*FX!C3</f>
-        <v>6920.7306306652799</v>
+        <v>6447.6433359686407</v>
       </c>
       <c r="G35" s="18">
         <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
-        <v>853.08912000000009</v>
+        <v>947.42023999999992</v>
       </c>
       <c r="H35" s="18">
         <f t="shared" si="1"/>
-        <v>7773.8197506652796</v>
+        <v>7395.0635759686411</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>422</v>
+        <v>830</v>
       </c>
       <c r="J35" s="27">
-        <v>46072</v>
+        <v>46157</v>
       </c>
       <c r="K35" s="18"/>
       <c r="L35" s="22"/>
@@ -10257,25 +10263,25 @@
       </c>
       <c r="E50" s="25">
         <f>+[45]Main!$J$2</f>
-        <v>77.23</v>
+        <v>65.5</v>
       </c>
       <c r="F50" s="18">
         <f>+[45]Main!$J$4</f>
-        <v>6928.0655860600009</v>
+        <v>5874.7799535000004</v>
       </c>
       <c r="G50" s="18">
         <f>+[45]Main!$J$6-[45]Main!$J$5</f>
-        <v>-611.73299999999995</v>
+        <v>-695.93000000000006</v>
       </c>
       <c r="H50" s="18">
         <f>+F50+G50</f>
-        <v>6316.3325860600007</v>
+        <v>5178.8499535000001</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>809</v>
+        <v>831</v>
       </c>
       <c r="J50" s="27">
-        <v>46077</v>
+        <v>46161</v>
       </c>
       <c r="K50" s="18"/>
       <c r="L50" s="22"/>
@@ -10316,25 +10322,25 @@
       </c>
       <c r="E51" s="25">
         <f>+[46]Main!$I$2</f>
-        <v>23.45</v>
+        <v>24.05</v>
       </c>
       <c r="F51" s="18">
         <f>+[46]Main!$I$4*FX!C3</f>
-        <v>3588.3688640800005</v>
+        <v>3687.0189200000004</v>
       </c>
       <c r="G51" s="18">
         <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
-        <v>1093.3520000000003</v>
+        <v>293.28000000000003</v>
       </c>
       <c r="H51" s="18">
         <f t="shared" si="3"/>
-        <v>4681.7208640800009</v>
+        <v>3980.2989200000006</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J51" s="27">
-        <v>46079</v>
+        <v>46142</v>
       </c>
       <c r="K51" s="18"/>
       <c r="L51" s="22"/>
@@ -15320,25 +15326,25 @@
       </c>
       <c r="E155" s="25">
         <f>+[79]Main!$J$2</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F155" s="18">
         <f>+[79]Main!$J$4</f>
-        <v>1475.4221459999999</v>
+        <v>1638</v>
       </c>
       <c r="G155" s="18">
         <f>+[79]Main!$J$6-[79]Main!$J$5</f>
-        <v>542.5</v>
+        <v>415.40000000000003</v>
       </c>
       <c r="H155" s="18">
         <f>+F155+G155</f>
-        <v>2017.9221459999999</v>
+        <v>2053.4</v>
       </c>
       <c r="I155" s="17" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J155" s="27">
-        <v>45706</v>
+        <v>46149</v>
       </c>
       <c r="K155" s="25"/>
       <c r="L155" s="22"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E13C295-9C75-451B-B150-BBA96A144794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E28067F-BA2A-474C-BEE1-48AC0BE24866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3680,29 +3680,29 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>42.48</v>
+            <v>41.04</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>10705.028957783998</v>
+            <v>10356.130046052</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>961.8</v>
+            <v>1019.9</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>56.2</v>
+            <v>59.5</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4652,7 +4652,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4691,7 +4691,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4814,7 +4814,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6118,7 +6118,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6937,15 +6937,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1896251.9005374536</v>
+        <v>1895861.1337563137</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>1416.899355199997</v>
+        <v>1355.5233551999972</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1897668.7998926523</v>
+        <v>1897216.6571115123</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7007,15 +7007,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>24029.103499677869</v>
+        <v>24024.157084726732</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>18.401290327272687</v>
+        <v>17.604199418181782</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24645.049349255223</v>
+        <v>24639.177365084575</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -8846,25 +8846,25 @@
       </c>
       <c r="E28" s="25">
         <f>+[23]Main!$H$2</f>
-        <v>42.48</v>
+        <v>41.04</v>
       </c>
       <c r="F28" s="18">
         <f>+[23]Main!$H$5*FX!C7</f>
-        <v>11989.632432718079</v>
+        <v>11598.86565157824</v>
       </c>
       <c r="G28" s="18">
         <f>+([23]Main!$H$7-[23]Main!$H$6)*FX!C7</f>
-        <v>-1014.272</v>
+        <v>-1075.6480000000001</v>
       </c>
       <c r="H28" s="18">
         <f>F28+G28</f>
-        <v>10975.360432718078</v>
+        <v>10523.217651578241</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J28" s="27">
-        <v>46085</v>
+        <v>46154</v>
       </c>
       <c r="K28" s="25"/>
       <c r="L28" s="22"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E28067F-BA2A-474C-BEE1-48AC0BE24866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFACD153-3BAE-4274-B072-9B1605363B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3047,6 +3047,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3092,6 +3093,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3135,6 +3137,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3144,22 +3147,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>157.55000000000001</v>
+            <v>141.80000000000001</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>28130.408184200001</v>
+            <v>25319.697396000003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1030</v>
+            <v>1617</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>2475</v>
+            <v>2641</v>
           </cell>
         </row>
       </sheetData>
@@ -3174,6 +3177,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3227,6 +3231,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3266,6 +3271,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3305,6 +3311,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3344,6 +3351,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3357,30 +3365,30 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>40.6</v>
+            <v>40.880000000000003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>12466.590528000001</v>
+            <v>12552.5670144</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>597.99199999999996</v>
+            <v>1261.6759999999999</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>243.54300000000001</v>
+            <v>1732.366</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3391,6 +3399,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3426,6 +3435,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3467,6 +3477,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3506,6 +3517,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3551,6 +3563,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3590,6 +3603,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3629,6 +3643,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3668,6 +3683,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3699,10 +3715,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3713,6 +3729,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3752,6 +3769,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3791,6 +3809,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3832,6 +3851,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3869,6 +3889,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3908,6 +3929,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3947,6 +3969,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3990,6 +4013,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4029,6 +4053,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4038,12 +4063,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>27.09</v>
+            <v>25.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>10075.3599366</v>
+            <v>9484.0043700000006</v>
           </cell>
         </row>
         <row r="5">
@@ -4057,7 +4082,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4068,6 +4093,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4107,6 +4133,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4146,6 +4173,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4185,6 +4213,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4224,6 +4253,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4263,6 +4293,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4302,6 +4333,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4341,6 +4373,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4388,6 +4421,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4431,6 +4465,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4470,6 +4505,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4509,6 +4545,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4548,6 +4585,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4587,6 +4625,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4624,6 +4663,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4663,6 +4703,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4702,6 +4743,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4741,6 +4783,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4753,17 +4796,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>97.7</v>
+            <v>95.69</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4576.4633999999996</v>
+            <v>4527.9551099999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>631.03800000000001</v>
+            <v>784.57600000000002</v>
           </cell>
         </row>
         <row r="6">
@@ -4786,6 +4829,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4825,6 +4869,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4864,6 +4909,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4903,6 +4949,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4940,6 +4987,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4979,6 +5027,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5018,6 +5067,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5057,6 +5107,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5096,6 +5147,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5135,6 +5187,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5174,6 +5227,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5213,6 +5267,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5252,6 +5307,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5297,6 +5353,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5334,6 +5391,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5373,6 +5431,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5412,6 +5471,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5451,6 +5511,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5490,6 +5551,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5529,6 +5591,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5568,6 +5631,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5607,6 +5671,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5646,6 +5711,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5685,6 +5751,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5739,6 +5806,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5778,6 +5846,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5817,6 +5886,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5856,6 +5926,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5895,6 +5966,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -5934,6 +6006,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main "/>
@@ -5973,6 +6046,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6012,6 +6086,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6051,6 +6126,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6090,6 +6166,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6129,6 +6206,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6168,6 +6246,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6207,6 +6286,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6248,6 +6328,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6289,6 +6370,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6328,6 +6410,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6367,6 +6450,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -6937,15 +7021,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1895861.1337563137</v>
+        <v>1892387.5462258414</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>1355.5233551999972</v>
+        <v>1622.2899151999964</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1897216.6571115123</v>
+        <v>1894009.8361410401</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7007,15 +7091,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>24024.157084726732</v>
+        <v>23980.187622315691</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>17.604199418181782</v>
+        <v>21.068700197402549</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24639.177365084575</v>
+        <v>24597.530339494027</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -8002,25 +8086,25 @@
       </c>
       <c r="E16" s="25">
         <f>+[11]Main!$I$2</f>
-        <v>157.55000000000001</v>
+        <v>141.80000000000001</v>
       </c>
       <c r="F16" s="18">
         <f>+[11]Main!$I$4*FX!C3</f>
-        <v>29255.624511568003</v>
+        <v>26332.485291840003</v>
       </c>
       <c r="G16" s="18">
         <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
-        <v>1502.8</v>
+        <v>1064.96</v>
       </c>
       <c r="H16" s="18">
         <f>F16+G16</f>
-        <v>30758.424511568002</v>
+        <v>27397.445291840002</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J16" s="27">
-        <v>46090</v>
+        <v>46141</v>
       </c>
       <c r="K16" s="18">
         <f>21427*FX!C3</f>
@@ -8411,25 +8495,25 @@
       </c>
       <c r="E21" s="25">
         <f>+[16]Main!$H$2</f>
-        <v>40.6</v>
+        <v>40.880000000000003</v>
       </c>
       <c r="F21" s="18">
         <f>+[16]Main!$H$5*FX!C3</f>
-        <v>12965.254149120001</v>
+        <v>13054.669694976001</v>
       </c>
       <c r="G21" s="18">
         <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
-        <v>-368.62695999999994</v>
+        <v>489.51760000000007</v>
       </c>
       <c r="H21" s="18">
         <f t="shared" si="1"/>
-        <v>12596.627189120001</v>
+        <v>13544.187294976</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J21" s="27">
-        <v>46084</v>
+        <v>46142</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="22"/>
@@ -9381,11 +9465,11 @@
       </c>
       <c r="E36" s="25">
         <f>+[31]Main!$J$2</f>
-        <v>27.09</v>
+        <v>25.5</v>
       </c>
       <c r="F36" s="18">
         <f>+[31]Main!$J$4</f>
-        <v>10075.3599366</v>
+        <v>9484.0043700000006</v>
       </c>
       <c r="G36" s="18">
         <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
@@ -9393,7 +9477,7 @@
       </c>
       <c r="H36" s="18">
         <f>+G36+F36</f>
-        <v>9049.3599365999999</v>
+        <v>8458.0043700000006</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>815</v>
@@ -10448,19 +10532,19 @@
       </c>
       <c r="E53" s="25">
         <f>+[48]Main!$I$2</f>
-        <v>97.7</v>
+        <v>95.69</v>
       </c>
       <c r="F53" s="18">
         <f>+[48]Main!$I$4</f>
-        <v>4576.4633999999996</v>
+        <v>4527.9551099999999</v>
       </c>
       <c r="G53" s="18">
         <f>+[48]Main!$I$6-[48]Main!$I$5</f>
-        <v>-631.03800000000001</v>
+        <v>-784.57600000000002</v>
       </c>
       <c r="H53" s="18">
         <f>F53+G53</f>
-        <v>3945.4253999999996</v>
+        <v>3743.3791099999999</v>
       </c>
       <c r="I53" s="26" t="s">
         <v>815</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFACD153-3BAE-4274-B072-9B1605363B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65494675-DFBB-4F1E-979B-91CD29C54AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3384,11 +3384,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4082,7 +4082,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4815,10 +4815,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10547,10 +10547,10 @@
         <v>3743.3791099999999</v>
       </c>
       <c r="I53" s="26" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J53" s="27">
-        <v>46085</v>
+        <v>46169</v>
       </c>
       <c r="K53" s="18">
         <v>4280.7</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65494675-DFBB-4F1E-979B-91CD29C54AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B566C759-4A7F-4A6A-99E5-C018C4B21F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="Accessoires" sheetId="4" r:id="rId4"/>
     <sheet name="Luxury" sheetId="8" r:id="rId5"/>
     <sheet name="Furniture" sheetId="7" r:id="rId6"/>
-    <sheet name="Glossar" sheetId="3" r:id="rId7"/>
-    <sheet name="FX" sheetId="2" r:id="rId8"/>
-    <sheet name="Acquisitions" sheetId="9" r:id="rId9"/>
-    <sheet name="People" sheetId="10" r:id="rId10"/>
-    <sheet name="Shoes" sheetId="13" r:id="rId11"/>
-    <sheet name="Market" sheetId="11" r:id="rId12"/>
+    <sheet name="Shoes" sheetId="13" r:id="rId7"/>
+    <sheet name="Glossar" sheetId="3" r:id="rId8"/>
+    <sheet name="FX" sheetId="2" r:id="rId9"/>
+    <sheet name="Acquisitions" sheetId="9" r:id="rId10"/>
+    <sheet name="People" sheetId="10" r:id="rId11"/>
+    <sheet name="Industry" sheetId="11" r:id="rId12"/>
     <sheet name="Private" sheetId="12" r:id="rId13"/>
   </sheets>
   <externalReferences>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="865">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2585,9 +2585,6 @@
     <t>Private</t>
   </si>
   <si>
-    <t>https://www.mckinsey.com/industries/retail/our-insights/state-of-luxury</t>
-  </si>
-  <si>
     <t>Q226</t>
   </si>
   <si>
@@ -2655,6 +2652,108 @@
   </si>
   <si>
     <t>Q426</t>
+  </si>
+  <si>
+    <t>Essillor Luxottica</t>
+  </si>
+  <si>
+    <t>RMS.PA</t>
+  </si>
+  <si>
+    <t>Pandora</t>
+  </si>
+  <si>
+    <t>PNDORA.CO</t>
+  </si>
+  <si>
+    <t>Burberry</t>
+  </si>
+  <si>
+    <t>Signet Juwellery</t>
+  </si>
+  <si>
+    <t>Ermeneglido Zegna</t>
+  </si>
+  <si>
+    <t>Pattern Group</t>
+  </si>
+  <si>
+    <t>PTRN</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>WOSG.L</t>
+  </si>
+  <si>
+    <t>Salvatore Ferragamo</t>
+  </si>
+  <si>
+    <t>Leather Goods</t>
+  </si>
+  <si>
+    <t>Eyewear</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Jewellery</t>
+  </si>
+  <si>
+    <t>Apperal</t>
+  </si>
+  <si>
+    <t>Beauty</t>
+  </si>
+  <si>
+    <t>Este Lauder</t>
+  </si>
+  <si>
+    <t>Marc'o Polo</t>
+  </si>
+  <si>
+    <t>Ressources</t>
+  </si>
+  <si>
+    <t>https://www.mckinsey.com/industries/retail/our-insights/state-of-fashion</t>
+  </si>
+  <si>
+    <t>https://www.businessoffashion.com/reports/the-state-of-fashion-industry/</t>
+  </si>
+  <si>
+    <t>https://www.businessoffashion.com/user/newsletters/</t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>The luxury strategy</t>
+  </si>
+  <si>
+    <t>Deluxe</t>
+  </si>
+  <si>
+    <t>https://www.bain.com/insights/finding-a-new-longevity-for-luxury/</t>
+  </si>
+  <si>
+    <t>https://dressedhistory.com/</t>
+  </si>
+  <si>
+    <t>https://www.businessoffashion.com/podcasts/</t>
+  </si>
+  <si>
+    <t>https://www.vogue.com/business</t>
+  </si>
+  <si>
+    <t>https://monocle.com/newsletters/</t>
+  </si>
+  <si>
+    <t>https://www.deloitte.com/global/en/Industries/consumer/perspectives/global-powers-of-luxury.html</t>
+  </si>
+  <si>
+    <t>Thierry</t>
   </si>
 </sst>
 </file>
@@ -2668,13 +2767,25 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2767,6 +2878,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2839,190 +2958,195 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
@@ -4815,10 +4939,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5197,26 +5321,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>36.520000000000003</v>
+            <v>36.299999999999997</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2571.0080000000003</v>
+            <v>2505.286971</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>152</v>
+            <v>343.12599999999998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>346</v>
+            <v>295.77</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6339,22 +6463,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>149.9</v>
+            <v>138.30000000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>93223.109800000006</v>
+            <v>86140.984800000006</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>16768</v>
+            <v>7278</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>8750</v>
+            <v>5988</v>
           </cell>
         </row>
       </sheetData>
@@ -6939,10 +7063,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="11" t="s">
+        <v>811</v>
+      </c>
+      <c r="N3" s="11" t="s">
         <v>812</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>813</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>89</v>
@@ -7017,25 +7141,25 @@
         <v>31</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1892387.5462258414</v>
+        <v>1892319.1963556812</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>1622.2899151999964</v>
+        <v>1371.2796751999967</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1894009.8361410401</v>
+        <v>1893690.4760308799</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K4" s="18">
         <f>SUM(K6:K153)</f>
@@ -7080,32 +7204,32 @@
         <v>88</v>
       </c>
       <c r="C5" s="84" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D5" s="86" t="str" cm="1">
         <f t="array" ref="D5">_xlfn.LET(_xlpm.rng,D6:D182,INDEX(_xlpm.rng,MATCH(MAX(COUNTIF(_xlpm.rng,_xlpm.rng)),COUNTIF(_xlpm.rng,_xlpm.rng),0)))</f>
         <v>US</v>
       </c>
       <c r="E5" s="84" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23980.187622315691</v>
+        <v>23979.322434085814</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>21.068700197402549</v>
+        <v>17.808826950649308</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24597.530339494027</v>
+        <v>24593.382805595844</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
       </c>
       <c r="J5" s="84" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K5" s="87">
         <f>AVERAGE(K6:K153)</f>
@@ -7519,7 +7643,7 @@
         <v>175729.30000000002</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J9" s="27"/>
       <c r="K9" s="25">
@@ -7951,7 +8075,7 @@
         <v>54114.976199999997</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J14" s="27">
         <v>46086</v>
@@ -8026,7 +8150,7 @@
         <v>21907.001384499999</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J15" s="27">
         <v>46108</v>
@@ -8358,7 +8482,7 @@
         <v>14280.085656300002</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J19" s="27">
         <v>46163</v>
@@ -9134,7 +9258,7 @@
         <v>19449.41295813</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J31" s="27">
         <v>46163</v>
@@ -9291,7 +9415,7 @@
         <v>5522.4062400000003</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J33" s="27">
         <v>46093</v>
@@ -9354,7 +9478,7 @@
         <v>10631.826862900001</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J34" s="27">
         <v>46162</v>
@@ -9417,7 +9541,7 @@
         <v>7395.0635759686411</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J35" s="27">
         <v>46157</v>
@@ -9480,7 +9604,7 @@
         <v>8458.0043700000006</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J36" s="27">
         <v>46086</v>
@@ -9558,7 +9682,7 @@
         <v>337</v>
       </c>
       <c r="J37" s="31" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="K37" s="18"/>
       <c r="L37" s="22"/>
@@ -9681,7 +9805,7 @@
         <v>10595.386999999999</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J39" s="27">
         <v>46076</v>
@@ -10122,7 +10246,7 @@
         <v>6117.0447439999998</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="J46" s="27">
         <v>45981</v>
@@ -10362,7 +10486,7 @@
         <v>5178.8499535000001</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J50" s="27">
         <v>46161</v>
@@ -10622,7 +10746,7 @@
         <v>2817.3176207199995</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J54" s="27">
         <v>46056</v>
@@ -10685,7 +10809,7 @@
         <v>5598.5518935199998</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J55" s="27">
         <v>46108</v>
@@ -10870,7 +10994,7 @@
         <v>4949.4143572999992</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="J58" s="27">
         <v>45957</v>
@@ -10980,7 +11104,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F60" s="18"/>
       <c r="G60" s="18"/>
@@ -11100,7 +11224,7 @@
         <v>2778.6924601600003</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J62" s="27">
         <v>45952</v>
@@ -11144,25 +11268,25 @@
       </c>
       <c r="E63" s="25">
         <f>+[57]Main!$J$2</f>
-        <v>36.520000000000003</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="F63" s="18">
         <f>+[57]Main!$J$4*FX!C3</f>
-        <v>2673.8483200000005</v>
+        <v>2605.4984498399999</v>
       </c>
       <c r="G63" s="18">
         <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
-        <v>201.76000000000002</v>
+        <v>-49.250239999999998</v>
       </c>
       <c r="H63" s="18">
         <f>+F63+G63</f>
-        <v>2875.6083200000007</v>
+        <v>2556.2482098400001</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>815</v>
+        <v>422</v>
       </c>
       <c r="J63" s="27">
-        <v>46091</v>
+        <v>46147</v>
       </c>
       <c r="K63" s="18"/>
       <c r="L63" s="22"/>
@@ -11218,7 +11342,7 @@
         <v>3706.48130747</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J64" s="27">
         <v>46156</v>
@@ -11393,7 +11517,7 @@
         <v>5509.5666168399994</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J67" s="27">
         <v>46085</v>
@@ -12833,7 +12957,7 @@
         <v>1022.4437873759999</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J97" s="27">
         <v>46162</v>
@@ -14007,7 +14131,7 @@
         <v>371.31401296000001</v>
       </c>
       <c r="I123" s="17" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J123" s="3"/>
       <c r="K123" s="18"/>
@@ -17531,6 +17655,1247 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B358B9-0FBA-4749-BEFA-4DF05274EAFA}">
+  <dimension ref="A1:AF33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32">
+      <c r="A1" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+    </row>
+    <row r="2" spans="1:32">
+      <c r="A2" s="46"/>
+      <c r="B2" s="75" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="75" t="s">
+        <v>730</v>
+      </c>
+      <c r="D2" s="75" t="s">
+        <v>717</v>
+      </c>
+      <c r="E2" s="75" t="s">
+        <v>718</v>
+      </c>
+      <c r="F2" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="76" t="s">
+        <v>801</v>
+      </c>
+      <c r="H2" s="76" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+    </row>
+    <row r="3" spans="1:32">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46" t="s">
+        <v>719</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>720</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>728</v>
+      </c>
+      <c r="E3" s="77">
+        <v>45757</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>474</v>
+      </c>
+      <c r="G3" s="78">
+        <v>1250</v>
+      </c>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="46"/>
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+    </row>
+    <row r="4" spans="1:32">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46" t="s">
+        <v>692</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>692</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>726</v>
+      </c>
+      <c r="E4" s="77">
+        <v>45782</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>727</v>
+      </c>
+      <c r="G4" s="79">
+        <v>9420</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>802</v>
+      </c>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+    </row>
+    <row r="5" spans="1:32">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>729</v>
+      </c>
+      <c r="E5" s="77">
+        <v>45637</v>
+      </c>
+      <c r="F5" s="78" t="s">
+        <v>474</v>
+      </c>
+      <c r="G5" s="79">
+        <v>1100</v>
+      </c>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
+      <c r="Z5" s="46"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+    </row>
+    <row r="6" spans="1:32">
+      <c r="A6" s="46"/>
+      <c r="B6" s="46" t="s">
+        <v>731</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>731</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>732</v>
+      </c>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="46"/>
+      <c r="Z6" s="46"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+    </row>
+    <row r="7" spans="1:32">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>680</v>
+      </c>
+      <c r="E7" s="77">
+        <v>45889</v>
+      </c>
+      <c r="F7" s="46">
+        <v>16.75</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>800</v>
+      </c>
+      <c r="H7" s="46" t="s">
+        <v>799</v>
+      </c>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="46"/>
+      <c r="Y7" s="46"/>
+      <c r="Z7" s="46"/>
+      <c r="AA7" s="46"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="A8" s="46"/>
+      <c r="B8" s="46" t="s">
+        <v>420</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>476</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>805</v>
+      </c>
+      <c r="E8" s="77">
+        <v>45322</v>
+      </c>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46">
+        <v>500</v>
+      </c>
+      <c r="H8" s="46" t="s">
+        <v>806</v>
+      </c>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="46"/>
+      <c r="Y8" s="46"/>
+      <c r="Z8" s="46"/>
+      <c r="AA8" s="46"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+    </row>
+    <row r="9" spans="1:32">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46" t="s">
+        <v>809</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>810</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>689</v>
+      </c>
+      <c r="E9" s="77">
+        <v>45808</v>
+      </c>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46">
+        <v>290</v>
+      </c>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="46"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="46"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="A10" s="46"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="46"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="46"/>
+      <c r="Y10" s="46"/>
+      <c r="Z10" s="46"/>
+      <c r="AA10" s="46"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="46"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="46"/>
+      <c r="AA11" s="46"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="1"/>
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+    </row>
+    <row r="12" spans="1:32">
+      <c r="A12" s="46"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="46"/>
+      <c r="Y12" s="46"/>
+      <c r="Z12" s="46"/>
+      <c r="AA12" s="46"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="46"/>
+      <c r="Y13" s="46"/>
+      <c r="Z13" s="46"/>
+      <c r="AA13" s="46"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="1"/>
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="1"/>
+    </row>
+    <row r="14" spans="1:32">
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="46"/>
+      <c r="Y14" s="46"/>
+      <c r="Z14" s="46"/>
+      <c r="AA14" s="46"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="A15" s="46"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="46"/>
+      <c r="Y15" s="46"/>
+      <c r="Z15" s="46"/>
+      <c r="AA15" s="46"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="1"/>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="A16" s="46"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="46"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="46"/>
+      <c r="AA16" s="46"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+    </row>
+    <row r="17" spans="1:32">
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="46"/>
+      <c r="AA17" s="46"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+    </row>
+    <row r="18" spans="1:32">
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="46"/>
+      <c r="Y18" s="46"/>
+      <c r="Z18" s="46"/>
+      <c r="AA18" s="46"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+    </row>
+    <row r="19" spans="1:32">
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="46"/>
+      <c r="X19" s="46"/>
+      <c r="Y19" s="46"/>
+      <c r="Z19" s="46"/>
+      <c r="AA19" s="46"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+    </row>
+    <row r="20" spans="1:32">
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="46"/>
+      <c r="U20" s="46"/>
+      <c r="V20" s="46"/>
+      <c r="W20" s="46"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="46"/>
+      <c r="AA20" s="46"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+    </row>
+    <row r="21" spans="1:32">
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="46"/>
+      <c r="U21" s="46"/>
+      <c r="V21" s="46"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="46"/>
+      <c r="Y21" s="46"/>
+      <c r="Z21" s="46"/>
+      <c r="AA21" s="46"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+    </row>
+    <row r="22" spans="1:32">
+      <c r="A22" s="46"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="46"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
+      <c r="V22" s="46"/>
+      <c r="W22" s="46"/>
+      <c r="X22" s="46"/>
+      <c r="Y22" s="46"/>
+      <c r="Z22" s="46"/>
+      <c r="AA22" s="46"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+    </row>
+    <row r="23" spans="1:32">
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
+      <c r="O23" s="46"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="46"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="46"/>
+      <c r="U23" s="46"/>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46"/>
+      <c r="X23" s="46"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="46"/>
+      <c r="AA23" s="46"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1"/>
+    </row>
+    <row r="24" spans="1:32">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="46"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="46"/>
+      <c r="AA24" s="46"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+    </row>
+    <row r="25" spans="1:32">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="46"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="46"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="46"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="46"/>
+      <c r="Y27" s="46"/>
+      <c r="Z27" s="46"/>
+      <c r="AA27" s="46"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="46"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="46"/>
+      <c r="AA28" s="46"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="46"/>
+      <c r="S29" s="46"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="46"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="46"/>
+      <c r="AA29" s="46"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="46"/>
+      <c r="Y30" s="46"/>
+      <c r="Z30" s="46"/>
+      <c r="AA30" s="46"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+    </row>
+    <row r="31" spans="1:32">
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="46"/>
+      <c r="Y31" s="46"/>
+      <c r="Z31" s="46"/>
+      <c r="AA31" s="46"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+    </row>
+    <row r="32" spans="1:32">
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="46"/>
+      <c r="Q32" s="46"/>
+      <c r="R32" s="46"/>
+      <c r="S32" s="46"/>
+      <c r="T32" s="46"/>
+      <c r="U32" s="46"/>
+      <c r="V32" s="46"/>
+      <c r="W32" s="46"/>
+      <c r="X32" s="46"/>
+      <c r="Y32" s="46"/>
+      <c r="Z32" s="46"/>
+      <c r="AA32" s="46"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+    </row>
+    <row r="33" spans="1:32">
+      <c r="A33" s="46"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="46"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="46"/>
+      <c r="S33" s="46"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="46"/>
+      <c r="Y33" s="46"/>
+      <c r="Z33" s="46"/>
+      <c r="AA33" s="46"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{996B57F6-8038-47F6-A248-0F268F1ACEFB}"/>
+    <hyperlink ref="C4" r:id="rId1" display="SKX" xr:uid="{8E2CF5BB-29AF-4437-8F96-D294155BB64C}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{2A12F8E0-FB6F-4E0D-B2A9-CED87F005A2E}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{198927E1-7FEB-4804-8A3B-9B9BC35A8F85}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA7C47F-1AC4-4057-B9F0-395F82201EB4}">
   <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
@@ -18034,10 +19399,9 @@
       <c r="P19" s="46"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="75" t="s">
+      <c r="B20" s="75" t="s">
         <v>797</v>
       </c>
-      <c r="B20" s="75"/>
       <c r="C20" s="46"/>
       <c r="D20" s="46"/>
       <c r="E20" s="46"/>
@@ -18055,14 +19419,14 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="46"/>
-      <c r="B21" s="81" t="s">
-        <v>826</v>
+      <c r="B21" s="95" t="s">
+        <v>825</v>
       </c>
       <c r="C21" s="46" t="s">
         <v>784</v>
       </c>
       <c r="D21" s="81" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E21" s="81" t="s">
         <v>750</v>
@@ -18088,7 +19452,7 @@
         <v>786</v>
       </c>
       <c r="D22" s="81" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E22" s="46"/>
       <c r="F22" s="46"/>
@@ -18261,8 +19625,12 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="46"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
+      <c r="B29" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="95" t="s">
+        <v>864</v>
+      </c>
       <c r="D29" s="46"/>
       <c r="E29" s="46"/>
       <c r="F29" s="46"/>
@@ -18303,705 +19671,89 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C032625C-E19A-4813-ABA6-8D106ACC7803}">
-  <dimension ref="A1:AH19"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEACE1C4-97F2-4C2B-8888-284E30CF8393}">
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:2">
       <c r="A1" s="45" t="s">
         <v>459</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
-      <c r="Y1" s="81"/>
-      <c r="Z1" s="81"/>
-      <c r="AA1" s="81"/>
-      <c r="AB1" s="81"/>
-      <c r="AC1" s="81"/>
-      <c r="AD1" s="81"/>
-      <c r="AE1" s="81"/>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-    </row>
-    <row r="2" spans="1:34">
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81"/>
-      <c r="AB2" s="81"/>
-      <c r="AC2" s="81"/>
-      <c r="AD2" s="81"/>
-      <c r="AE2" s="81"/>
-      <c r="AF2" s="81"/>
-      <c r="AG2" s="81"/>
-      <c r="AH2" s="81"/>
-    </row>
-    <row r="3" spans="1:34">
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
-      <c r="Z3" s="81"/>
-      <c r="AA3" s="81"/>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-    </row>
-    <row r="4" spans="1:34">
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="81"/>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="81"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="81"/>
-      <c r="U4" s="81"/>
-      <c r="V4" s="81"/>
-      <c r="W4" s="81"/>
-      <c r="X4" s="81"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="81"/>
-      <c r="AA4" s="81"/>
-      <c r="AB4" s="81"/>
-      <c r="AC4" s="81"/>
-      <c r="AD4" s="81"/>
-      <c r="AE4" s="81"/>
-      <c r="AF4" s="81"/>
-      <c r="AG4" s="81"/>
-      <c r="AH4" s="81"/>
-    </row>
-    <row r="5" spans="1:34">
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
-      <c r="R5" s="81"/>
-      <c r="S5" s="81"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
-      <c r="X5" s="81"/>
-      <c r="Y5" s="81"/>
-      <c r="Z5" s="81"/>
-      <c r="AA5" s="81"/>
-      <c r="AB5" s="81"/>
-      <c r="AC5" s="81"/>
-      <c r="AD5" s="81"/>
-      <c r="AE5" s="81"/>
-      <c r="AF5" s="81"/>
-      <c r="AG5" s="81"/>
-      <c r="AH5" s="81"/>
-    </row>
-    <row r="6" spans="1:34">
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81"/>
-      <c r="P6" s="81"/>
-      <c r="Q6" s="81"/>
-      <c r="R6" s="81"/>
-      <c r="S6" s="81"/>
-      <c r="T6" s="81"/>
-      <c r="U6" s="81"/>
-      <c r="V6" s="81"/>
-      <c r="W6" s="81"/>
-      <c r="X6" s="81"/>
-      <c r="Y6" s="81"/>
-      <c r="Z6" s="81"/>
-      <c r="AA6" s="81"/>
-      <c r="AB6" s="81"/>
-      <c r="AC6" s="81"/>
-      <c r="AD6" s="81"/>
-      <c r="AE6" s="81"/>
-      <c r="AF6" s="81"/>
-      <c r="AG6" s="81"/>
-      <c r="AH6" s="81"/>
-    </row>
-    <row r="7" spans="1:34">
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="81"/>
-      <c r="T7" s="81"/>
-      <c r="U7" s="81"/>
-      <c r="V7" s="81"/>
-      <c r="W7" s="81"/>
-      <c r="X7" s="81"/>
-      <c r="Y7" s="81"/>
-      <c r="Z7" s="81"/>
-      <c r="AA7" s="81"/>
-      <c r="AB7" s="81"/>
-      <c r="AC7" s="81"/>
-      <c r="AD7" s="81"/>
-      <c r="AE7" s="81"/>
-      <c r="AF7" s="81"/>
-      <c r="AG7" s="81"/>
-      <c r="AH7" s="81"/>
-    </row>
-    <row r="8" spans="1:34">
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="81"/>
-      <c r="U8" s="81"/>
-      <c r="V8" s="81"/>
-      <c r="W8" s="81"/>
-      <c r="X8" s="81"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="81"/>
-      <c r="AB8" s="81"/>
-      <c r="AC8" s="81"/>
-      <c r="AD8" s="81"/>
-      <c r="AE8" s="81"/>
-      <c r="AF8" s="81"/>
-      <c r="AG8" s="81"/>
-      <c r="AH8" s="81"/>
-    </row>
-    <row r="9" spans="1:34">
-      <c r="B9" s="81" t="s">
-        <v>807</v>
-      </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="81"/>
-      <c r="T9" s="81"/>
-      <c r="U9" s="81"/>
-      <c r="V9" s="81"/>
-      <c r="W9" s="81"/>
-      <c r="X9" s="81"/>
-      <c r="Y9" s="81"/>
-      <c r="Z9" s="81"/>
-      <c r="AA9" s="81"/>
-      <c r="AB9" s="81"/>
-      <c r="AC9" s="81"/>
-      <c r="AD9" s="81"/>
-      <c r="AE9" s="81"/>
-      <c r="AF9" s="81"/>
-      <c r="AG9" s="81"/>
-      <c r="AH9" s="81"/>
-    </row>
-    <row r="10" spans="1:34">
-      <c r="B10" s="81" t="s">
-        <v>695</v>
-      </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="81"/>
-      <c r="S10" s="81"/>
-      <c r="T10" s="81"/>
-      <c r="U10" s="81"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="81"/>
-      <c r="Y10" s="81"/>
-      <c r="Z10" s="81"/>
-      <c r="AA10" s="81"/>
-      <c r="AB10" s="81"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="81"/>
-      <c r="AG10" s="81"/>
-      <c r="AH10" s="81"/>
-    </row>
-    <row r="11" spans="1:34">
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="81"/>
-      <c r="Y11" s="81"/>
-      <c r="Z11" s="81"/>
-      <c r="AA11" s="81"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="81"/>
-      <c r="AG11" s="81"/>
-      <c r="AH11" s="81"/>
-    </row>
-    <row r="12" spans="1:34">
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="81"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="81"/>
-      <c r="U12" s="81"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="81"/>
-      <c r="Y12" s="81"/>
-      <c r="Z12" s="81"/>
-      <c r="AA12" s="81"/>
-      <c r="AB12" s="81"/>
-      <c r="AC12" s="81"/>
-      <c r="AD12" s="81"/>
-      <c r="AE12" s="81"/>
-      <c r="AF12" s="81"/>
-      <c r="AG12" s="81"/>
-      <c r="AH12" s="81"/>
-    </row>
-    <row r="13" spans="1:34">
-      <c r="B13" s="81"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="81"/>
-      <c r="Y13" s="81"/>
-      <c r="Z13" s="81"/>
-      <c r="AA13" s="81"/>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="81"/>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="81"/>
-    </row>
-    <row r="14" spans="1:34">
-      <c r="B14" s="81"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="81"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="81"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="81"/>
-      <c r="U14" s="81"/>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="81"/>
-      <c r="Y14" s="81"/>
-      <c r="Z14" s="81"/>
-      <c r="AA14" s="81"/>
-      <c r="AB14" s="81"/>
-      <c r="AC14" s="81"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="81"/>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="81"/>
-    </row>
-    <row r="15" spans="1:34">
-      <c r="B15" s="81"/>
-      <c r="C15" s="81"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
-      <c r="L15" s="81"/>
-      <c r="M15" s="81"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="81"/>
-      <c r="P15" s="81"/>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81"/>
-      <c r="S15" s="81"/>
-      <c r="T15" s="81"/>
-      <c r="U15" s="81"/>
-      <c r="V15" s="81"/>
-      <c r="W15" s="81"/>
-      <c r="X15" s="81"/>
-      <c r="Y15" s="81"/>
-      <c r="Z15" s="81"/>
-      <c r="AA15" s="81"/>
-      <c r="AB15" s="81"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="81"/>
-      <c r="AF15" s="81"/>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="81"/>
-    </row>
-    <row r="16" spans="1:34">
-      <c r="B16" s="81"/>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="81"/>
-      <c r="U16" s="81"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="81"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="81"/>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="81"/>
-    </row>
-    <row r="17" spans="2:34">
-      <c r="B17" s="81"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="81"/>
-      <c r="S17" s="81"/>
-      <c r="T17" s="81"/>
-      <c r="U17" s="81"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="81"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="81"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="81"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="81"/>
-      <c r="AH17" s="81"/>
-    </row>
-    <row r="18" spans="2:34">
-      <c r="B18" s="81"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="81"/>
-      <c r="S18" s="81"/>
-      <c r="T18" s="81"/>
-      <c r="U18" s="81"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="81"/>
-      <c r="X18" s="81"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="81"/>
-      <c r="AB18" s="81"/>
-      <c r="AC18" s="81"/>
-      <c r="AD18" s="81"/>
-      <c r="AE18" s="81"/>
-      <c r="AF18" s="81"/>
-      <c r="AG18" s="81"/>
-      <c r="AH18" s="81"/>
-    </row>
-    <row r="19" spans="2:34">
-      <c r="B19" s="81"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="81"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="81"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="81"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="81"/>
-      <c r="S19" s="81"/>
-      <c r="T19" s="81"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="81"/>
-      <c r="W19" s="81"/>
-      <c r="X19" s="81"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="81"/>
-      <c r="AB19" s="81"/>
-      <c r="AC19" s="81"/>
-      <c r="AD19" s="81"/>
-      <c r="AE19" s="81"/>
-      <c r="AF19" s="81"/>
-      <c r="AG19" s="81"/>
-      <c r="AH19" s="81"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="B2" s="96" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3" s="45" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="B16" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>857</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{DC140323-43D4-490C-89F0-35533960EF2D}"/>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{34E87583-67A0-4497-BCFB-14D5F7F5F351}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{3295B675-D17D-4644-A0D7-A7C87410F137}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEACE1C4-97F2-4C2B-8888-284E30CF8393}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="46" t="s">
-        <v>808</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19381,6 +20133,9 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="46"/>
+      <c r="B18" s="95" t="s">
+        <v>850</v>
+      </c>
       <c r="C18" s="58" t="s">
         <v>803</v>
       </c>
@@ -19423,7 +20178,7 @@
     <row r="20" spans="1:17">
       <c r="A20" s="46"/>
       <c r="B20" s="81" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C20" s="58"/>
       <c r="D20" s="46"/>
@@ -19444,10 +20199,10 @@
     <row r="21" spans="1:17">
       <c r="A21" s="46"/>
       <c r="B21" s="81" t="s">
+        <v>823</v>
+      </c>
+      <c r="C21" s="81" t="s">
         <v>824</v>
-      </c>
-      <c r="C21" s="81" t="s">
-        <v>825</v>
       </c>
       <c r="D21" s="46"/>
       <c r="E21" s="59"/>
@@ -39293,25 +40048,25 @@
       </c>
       <c r="E5" s="59">
         <f>+[82]Main!$J$2</f>
-        <v>149.9</v>
+        <v>138.30000000000001</v>
       </c>
       <c r="F5" s="57">
         <f>+[82]Main!$J$5*FX!C7</f>
-        <v>104409.88297600002</v>
+        <v>96477.902976000012</v>
       </c>
       <c r="G5" s="57">
         <f>+([82]Main!$J$7-[82]Main!$J$6)*FX!C7</f>
-        <v>-8980.1600000000017</v>
+        <v>-1444.8000000000002</v>
       </c>
       <c r="H5" s="57">
         <f t="shared" ref="H5:H6" si="0">+F5+G5</f>
-        <v>95429.722976000019</v>
-      </c>
-      <c r="I5" s="47" t="s">
-        <v>715</v>
+        <v>95033.102976000009</v>
+      </c>
+      <c r="I5" s="94" t="s">
+        <v>820</v>
       </c>
       <c r="J5" s="61">
-        <v>45975</v>
+        <v>46164</v>
       </c>
       <c r="K5" s="59"/>
       <c r="L5" s="62"/>
@@ -39374,7 +40129,7 @@
         <v>44464.047181599999</v>
       </c>
       <c r="I6" s="93" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="J6" s="61">
         <v>46143</v>
@@ -42456,7 +43211,9 @@
       <c r="J3" s="70" t="s">
         <v>458</v>
       </c>
-      <c r="K3" s="68"/>
+      <c r="K3" s="68" t="s">
+        <v>845</v>
+      </c>
       <c r="L3" s="71"/>
       <c r="M3" s="68"/>
       <c r="N3" s="68"/>
@@ -42471,16 +43228,24 @@
       <c r="A4" s="56">
         <v>1</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
+      <c r="B4" s="95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="95" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="95" t="s">
+        <v>20</v>
+      </c>
       <c r="E4" s="46"/>
       <c r="F4" s="46"/>
       <c r="G4" s="46"/>
       <c r="H4" s="46"/>
       <c r="I4" s="46"/>
       <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
+      <c r="K4" s="95" t="s">
+        <v>843</v>
+      </c>
       <c r="L4" s="46"/>
       <c r="M4" s="46"/>
       <c r="N4" s="46"/>
@@ -42495,16 +43260,24 @@
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="95" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="95" t="s">
+        <v>832</v>
+      </c>
+      <c r="D5" s="95" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="46"/>
       <c r="F5" s="46"/>
       <c r="G5" s="46"/>
       <c r="H5" s="46"/>
       <c r="I5" s="46"/>
       <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="K5" s="95" t="s">
+        <v>843</v>
+      </c>
       <c r="L5" s="46"/>
       <c r="M5" s="46"/>
       <c r="N5" s="46"/>
@@ -42519,16 +43292,24 @@
         <f t="shared" ref="A6:A51" si="0">+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
+      <c r="B6" s="95" t="s">
+        <v>831</v>
+      </c>
+      <c r="C6" s="95" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="95" t="s">
+        <v>20</v>
+      </c>
       <c r="E6" s="46"/>
       <c r="F6" s="46"/>
       <c r="G6" s="46"/>
       <c r="H6" s="46"/>
       <c r="I6" s="46"/>
       <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
+      <c r="K6" s="95" t="s">
+        <v>844</v>
+      </c>
       <c r="L6" s="46"/>
       <c r="M6" s="46"/>
       <c r="N6" s="46"/>
@@ -42543,16 +43324,24 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="B7" s="95" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="95" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="95" t="s">
+        <v>85</v>
+      </c>
       <c r="E7" s="46"/>
       <c r="F7" s="46"/>
       <c r="G7" s="46"/>
       <c r="H7" s="46"/>
       <c r="I7" s="46"/>
       <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
+      <c r="K7" s="95" t="s">
+        <v>846</v>
+      </c>
       <c r="L7" s="46"/>
       <c r="M7" s="46"/>
       <c r="N7" s="46"/>
@@ -42567,16 +43356,24 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="95" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" s="95" t="s">
+        <v>20</v>
+      </c>
       <c r="E8" s="46"/>
       <c r="F8" s="46"/>
       <c r="G8" s="46"/>
       <c r="H8" s="46"/>
       <c r="I8" s="46"/>
       <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
+      <c r="K8" s="95" t="s">
+        <v>843</v>
+      </c>
       <c r="L8" s="46"/>
       <c r="M8" s="46"/>
       <c r="N8" s="46"/>
@@ -42591,16 +43388,24 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="95" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="95" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="95" t="s">
+        <v>185</v>
+      </c>
       <c r="E9" s="46"/>
       <c r="F9" s="46"/>
       <c r="G9" s="46"/>
       <c r="H9" s="46"/>
       <c r="I9" s="46"/>
       <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
+      <c r="K9" s="95" t="s">
+        <v>846</v>
+      </c>
       <c r="L9" s="46"/>
       <c r="M9" s="46"/>
       <c r="N9" s="46"/>
@@ -42615,16 +43420,24 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
+      <c r="B10" s="95" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="95" t="s">
+        <v>446</v>
+      </c>
+      <c r="D10" s="95" t="s">
+        <v>20</v>
+      </c>
       <c r="E10" s="46"/>
       <c r="F10" s="46"/>
       <c r="G10" s="46"/>
       <c r="H10" s="46"/>
       <c r="I10" s="46"/>
       <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
+      <c r="K10" s="95" t="s">
+        <v>843</v>
+      </c>
       <c r="L10" s="46"/>
       <c r="M10" s="46"/>
       <c r="N10" s="46"/>
@@ -42639,16 +43452,24 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
+      <c r="B11" s="95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="95" t="s">
+        <v>448</v>
+      </c>
+      <c r="D11" s="95" t="s">
+        <v>165</v>
+      </c>
       <c r="E11" s="46"/>
       <c r="F11" s="46"/>
       <c r="G11" s="46"/>
       <c r="H11" s="46"/>
       <c r="I11" s="46"/>
       <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
+      <c r="K11" s="95" t="s">
+        <v>847</v>
+      </c>
       <c r="L11" s="46"/>
       <c r="M11" s="46"/>
       <c r="N11" s="46"/>
@@ -42663,9 +43484,15 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
+      <c r="B12" s="95" t="s">
+        <v>339</v>
+      </c>
+      <c r="C12" s="95" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="95" t="s">
+        <v>254</v>
+      </c>
       <c r="E12" s="46"/>
       <c r="F12" s="46"/>
       <c r="G12" s="46"/>
@@ -42687,16 +43514,24 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
+      <c r="B13" s="95" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="95" t="s">
+        <v>165</v>
+      </c>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
       <c r="G13" s="46"/>
       <c r="H13" s="46"/>
       <c r="I13" s="46"/>
       <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
+      <c r="K13" s="95" t="s">
+        <v>847</v>
+      </c>
       <c r="L13" s="46"/>
       <c r="M13" s="46"/>
       <c r="N13" s="46"/>
@@ -42711,16 +43546,24 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
+      <c r="B14" s="95" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="95" t="s">
+        <v>386</v>
+      </c>
+      <c r="D14" s="95" t="s">
+        <v>165</v>
+      </c>
       <c r="E14" s="46"/>
       <c r="F14" s="46"/>
       <c r="G14" s="46"/>
       <c r="H14" s="46"/>
       <c r="I14" s="46"/>
       <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
+      <c r="K14" s="95" t="s">
+        <v>847</v>
+      </c>
       <c r="L14" s="46"/>
       <c r="M14" s="46"/>
       <c r="N14" s="46"/>
@@ -42735,9 +43578,15 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
+      <c r="B15" s="95" t="s">
+        <v>833</v>
+      </c>
+      <c r="C15" s="95" t="s">
+        <v>834</v>
+      </c>
+      <c r="D15" s="95" t="s">
+        <v>143</v>
+      </c>
       <c r="E15" s="46"/>
       <c r="F15" s="46"/>
       <c r="G15" s="46"/>
@@ -42759,16 +43608,24 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
+      <c r="B16" s="95" t="s">
+        <v>835</v>
+      </c>
+      <c r="C16" s="95" t="s">
+        <v>455</v>
+      </c>
+      <c r="D16" s="95" t="s">
+        <v>219</v>
+      </c>
       <c r="E16" s="46"/>
       <c r="F16" s="46"/>
       <c r="G16" s="46"/>
       <c r="H16" s="46"/>
       <c r="I16" s="46"/>
       <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
+      <c r="K16" s="95" t="s">
+        <v>847</v>
+      </c>
       <c r="L16" s="46"/>
       <c r="M16" s="46"/>
       <c r="N16" s="46"/>
@@ -42783,9 +43640,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
+      <c r="B17" s="95" t="s">
+        <v>836</v>
+      </c>
+      <c r="C17" s="95" t="s">
+        <v>349</v>
+      </c>
+      <c r="D17" s="95" t="s">
+        <v>347</v>
+      </c>
       <c r="E17" s="46"/>
       <c r="F17" s="46"/>
       <c r="G17" s="46"/>
@@ -42807,9 +43670,15 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
+      <c r="B18" s="95" t="s">
+        <v>837</v>
+      </c>
+      <c r="C18" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="95" t="s">
+        <v>165</v>
+      </c>
       <c r="E18" s="46"/>
       <c r="F18" s="46"/>
       <c r="G18" s="46"/>
@@ -42831,16 +43700,24 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
+      <c r="B19" s="95" t="s">
+        <v>342</v>
+      </c>
+      <c r="C19" s="95" t="s">
+        <v>341</v>
+      </c>
+      <c r="D19" s="95" t="s">
+        <v>21</v>
+      </c>
       <c r="E19" s="46"/>
       <c r="F19" s="46"/>
       <c r="G19" s="46"/>
       <c r="H19" s="46"/>
       <c r="I19" s="46"/>
       <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
+      <c r="K19" s="95" t="s">
+        <v>848</v>
+      </c>
       <c r="L19" s="46"/>
       <c r="M19" s="46"/>
       <c r="N19" s="46"/>
@@ -42855,9 +43732,15 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
+      <c r="B20" s="95" t="s">
+        <v>838</v>
+      </c>
+      <c r="C20" s="95" t="s">
+        <v>839</v>
+      </c>
+      <c r="D20" s="95" t="s">
+        <v>21</v>
+      </c>
       <c r="E20" s="46"/>
       <c r="F20" s="46"/>
       <c r="G20" s="46"/>
@@ -42879,9 +43762,15 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
+      <c r="B21" s="95" t="s">
+        <v>350</v>
+      </c>
+      <c r="C21" s="95" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21" s="95" t="s">
+        <v>840</v>
+      </c>
       <c r="E21" s="46"/>
       <c r="F21" s="46"/>
       <c r="G21" s="46"/>
@@ -42903,9 +43792,15 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
+      <c r="B22" s="95" t="s">
+        <v>532</v>
+      </c>
+      <c r="C22" s="95" t="s">
+        <v>841</v>
+      </c>
+      <c r="D22" s="95" t="s">
+        <v>219</v>
+      </c>
       <c r="E22" s="46"/>
       <c r="F22" s="46"/>
       <c r="G22" s="46"/>
@@ -42927,9 +43822,15 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
+      <c r="B23" s="95" t="s">
+        <v>421</v>
+      </c>
+      <c r="C23" s="58" t="s">
+        <v>438</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>85</v>
+      </c>
       <c r="E23" s="46"/>
       <c r="F23" s="46"/>
       <c r="G23" s="46"/>
@@ -42951,9 +43852,15 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
+      <c r="B24" s="95" t="s">
+        <v>842</v>
+      </c>
+      <c r="C24" s="95" t="s">
+        <v>357</v>
+      </c>
+      <c r="D24" s="95" t="s">
+        <v>165</v>
+      </c>
       <c r="E24" s="46"/>
       <c r="F24" s="46"/>
       <c r="G24" s="46"/>
@@ -42975,9 +43882,15 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
+      <c r="B25" s="95" t="s">
+        <v>370</v>
+      </c>
+      <c r="C25" s="95" t="s">
+        <v>378</v>
+      </c>
+      <c r="D25" s="95" t="s">
+        <v>254</v>
+      </c>
       <c r="E25" s="46"/>
       <c r="F25" s="46"/>
       <c r="G25" s="46"/>
@@ -42999,9 +43912,15 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
+      <c r="B26" s="95" t="s">
+        <v>849</v>
+      </c>
+      <c r="C26" s="95" t="s">
+        <v>699</v>
+      </c>
+      <c r="D26" s="95" t="s">
+        <v>21</v>
+      </c>
       <c r="E26" s="46"/>
       <c r="F26" s="46"/>
       <c r="G26" s="46"/>
@@ -49983,6 +50902,695 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C032625C-E19A-4813-ABA6-8D106ACC7803}">
+  <dimension ref="A1:AH20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34">
+      <c r="A1" s="45" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="81"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="81"/>
+      <c r="AF1" s="81"/>
+      <c r="AG1" s="81"/>
+      <c r="AH1" s="81"/>
+    </row>
+    <row r="2" spans="1:34">
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="81"/>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="81"/>
+      <c r="AE2" s="81"/>
+      <c r="AF2" s="81"/>
+      <c r="AG2" s="81"/>
+      <c r="AH2" s="81"/>
+    </row>
+    <row r="3" spans="1:34">
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="81"/>
+      <c r="Z3" s="81"/>
+      <c r="AA3" s="81"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="81"/>
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="81"/>
+      <c r="AG3" s="81"/>
+      <c r="AH3" s="81"/>
+    </row>
+    <row r="4" spans="1:34">
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="81"/>
+      <c r="AC4" s="81"/>
+      <c r="AD4" s="81"/>
+      <c r="AE4" s="81"/>
+      <c r="AF4" s="81"/>
+      <c r="AG4" s="81"/>
+      <c r="AH4" s="81"/>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="81"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="81"/>
+      <c r="AA5" s="81"/>
+      <c r="AB5" s="81"/>
+      <c r="AC5" s="81"/>
+      <c r="AD5" s="81"/>
+      <c r="AE5" s="81"/>
+      <c r="AF5" s="81"/>
+      <c r="AG5" s="81"/>
+      <c r="AH5" s="81"/>
+    </row>
+    <row r="6" spans="1:34">
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="81"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="81"/>
+      <c r="T6" s="81"/>
+      <c r="U6" s="81"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="81"/>
+      <c r="X6" s="81"/>
+      <c r="Y6" s="81"/>
+      <c r="Z6" s="81"/>
+      <c r="AA6" s="81"/>
+      <c r="AB6" s="81"/>
+      <c r="AC6" s="81"/>
+      <c r="AD6" s="81"/>
+      <c r="AE6" s="81"/>
+      <c r="AF6" s="81"/>
+      <c r="AG6" s="81"/>
+      <c r="AH6" s="81"/>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="81"/>
+      <c r="T7" s="81"/>
+      <c r="U7" s="81"/>
+      <c r="V7" s="81"/>
+      <c r="W7" s="81"/>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="81"/>
+      <c r="AB7" s="81"/>
+      <c r="AC7" s="81"/>
+      <c r="AD7" s="81"/>
+      <c r="AE7" s="81"/>
+      <c r="AF7" s="81"/>
+      <c r="AG7" s="81"/>
+      <c r="AH7" s="81"/>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="81"/>
+      <c r="T8" s="81"/>
+      <c r="U8" s="81"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="81"/>
+      <c r="X8" s="81"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="81"/>
+      <c r="AB8" s="81"/>
+      <c r="AC8" s="81"/>
+      <c r="AD8" s="81"/>
+      <c r="AE8" s="81"/>
+      <c r="AF8" s="81"/>
+      <c r="AG8" s="81"/>
+      <c r="AH8" s="81"/>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="81"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="81"/>
+      <c r="T9" s="81"/>
+      <c r="U9" s="81"/>
+      <c r="V9" s="81"/>
+      <c r="W9" s="81"/>
+      <c r="X9" s="81"/>
+      <c r="Y9" s="81"/>
+      <c r="Z9" s="81"/>
+      <c r="AA9" s="81"/>
+      <c r="AB9" s="81"/>
+      <c r="AC9" s="81"/>
+      <c r="AD9" s="81"/>
+      <c r="AE9" s="81"/>
+      <c r="AF9" s="81"/>
+      <c r="AG9" s="81"/>
+      <c r="AH9" s="81"/>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
+      <c r="O10" s="81"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="81"/>
+      <c r="U10" s="81"/>
+      <c r="V10" s="81"/>
+      <c r="W10" s="81"/>
+      <c r="X10" s="81"/>
+      <c r="Y10" s="81"/>
+      <c r="Z10" s="81"/>
+      <c r="AA10" s="81"/>
+      <c r="AB10" s="81"/>
+      <c r="AC10" s="81"/>
+      <c r="AD10" s="81"/>
+      <c r="AE10" s="81"/>
+      <c r="AF10" s="81"/>
+      <c r="AG10" s="81"/>
+      <c r="AH10" s="81"/>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="81"/>
+      <c r="O11" s="81"/>
+      <c r="P11" s="81"/>
+      <c r="Q11" s="81"/>
+      <c r="R11" s="81"/>
+      <c r="S11" s="81"/>
+      <c r="T11" s="81"/>
+      <c r="U11" s="81"/>
+      <c r="V11" s="81"/>
+      <c r="W11" s="81"/>
+      <c r="X11" s="81"/>
+      <c r="Y11" s="81"/>
+      <c r="Z11" s="81"/>
+      <c r="AA11" s="81"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="81"/>
+      <c r="AD11" s="81"/>
+      <c r="AE11" s="81"/>
+      <c r="AF11" s="81"/>
+      <c r="AG11" s="81"/>
+      <c r="AH11" s="81"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="81"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="81"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
+      <c r="X12" s="81"/>
+      <c r="Y12" s="81"/>
+      <c r="Z12" s="81"/>
+      <c r="AA12" s="81"/>
+      <c r="AB12" s="81"/>
+      <c r="AC12" s="81"/>
+      <c r="AD12" s="81"/>
+      <c r="AE12" s="81"/>
+      <c r="AF12" s="81"/>
+      <c r="AG12" s="81"/>
+      <c r="AH12" s="81"/>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="81"/>
+      <c r="T13" s="81"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="81"/>
+      <c r="W13" s="81"/>
+      <c r="X13" s="81"/>
+      <c r="Y13" s="81"/>
+      <c r="Z13" s="81"/>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="81"/>
+      <c r="AC13" s="81"/>
+      <c r="AD13" s="81"/>
+      <c r="AE13" s="81"/>
+      <c r="AF13" s="81"/>
+      <c r="AG13" s="81"/>
+      <c r="AH13" s="81"/>
+    </row>
+    <row r="14" spans="1:34">
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="81"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="81"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="81"/>
+      <c r="T14" s="81"/>
+      <c r="U14" s="81"/>
+      <c r="V14" s="81"/>
+      <c r="W14" s="81"/>
+      <c r="X14" s="81"/>
+      <c r="Y14" s="81"/>
+      <c r="Z14" s="81"/>
+      <c r="AA14" s="81"/>
+      <c r="AB14" s="81"/>
+      <c r="AC14" s="81"/>
+      <c r="AD14" s="81"/>
+      <c r="AE14" s="81"/>
+      <c r="AF14" s="81"/>
+      <c r="AG14" s="81"/>
+      <c r="AH14" s="81"/>
+    </row>
+    <row r="15" spans="1:34">
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="81"/>
+      <c r="U15" s="81"/>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="81"/>
+      <c r="Y15" s="81"/>
+      <c r="Z15" s="81"/>
+      <c r="AA15" s="81"/>
+      <c r="AB15" s="81"/>
+      <c r="AC15" s="81"/>
+      <c r="AD15" s="81"/>
+      <c r="AE15" s="81"/>
+      <c r="AF15" s="81"/>
+      <c r="AG15" s="81"/>
+      <c r="AH15" s="81"/>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="B16" s="81"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="81"/>
+      <c r="U16" s="81"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="81"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="81"/>
+      <c r="AA16" s="81"/>
+      <c r="AB16" s="81"/>
+      <c r="AC16" s="81"/>
+      <c r="AD16" s="81"/>
+      <c r="AE16" s="81"/>
+      <c r="AF16" s="81"/>
+      <c r="AG16" s="81"/>
+      <c r="AH16" s="81"/>
+    </row>
+    <row r="17" spans="2:34">
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="81"/>
+      <c r="T17" s="81"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="81"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="81"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="81"/>
+      <c r="AA17" s="81"/>
+      <c r="AB17" s="81"/>
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="81"/>
+      <c r="AE17" s="81"/>
+      <c r="AF17" s="81"/>
+      <c r="AG17" s="81"/>
+      <c r="AH17" s="81"/>
+    </row>
+    <row r="18" spans="2:34">
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
+      <c r="S18" s="81"/>
+      <c r="T18" s="81"/>
+      <c r="U18" s="81"/>
+      <c r="V18" s="81"/>
+      <c r="W18" s="81"/>
+      <c r="X18" s="81"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="81"/>
+      <c r="AA18" s="81"/>
+      <c r="AB18" s="81"/>
+      <c r="AC18" s="81"/>
+      <c r="AD18" s="81"/>
+      <c r="AE18" s="81"/>
+      <c r="AF18" s="81"/>
+      <c r="AG18" s="81"/>
+      <c r="AH18" s="81"/>
+    </row>
+    <row r="19" spans="2:34">
+      <c r="B19" s="81" t="s">
+        <v>807</v>
+      </c>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="81"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="81"/>
+      <c r="W19" s="81"/>
+      <c r="X19" s="81"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="81"/>
+      <c r="AA19" s="81"/>
+      <c r="AB19" s="81"/>
+      <c r="AC19" s="81"/>
+      <c r="AD19" s="81"/>
+      <c r="AE19" s="81"/>
+      <c r="AF19" s="81"/>
+      <c r="AG19" s="81"/>
+      <c r="AH19" s="81"/>
+    </row>
+    <row r="20" spans="2:34">
+      <c r="B20" s="81" t="s">
+        <v>695</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{DC140323-43D4-490C-89F0-35533960EF2D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4991721E-8381-4599-A817-7308E9F2867F}">
   <dimension ref="B3:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -50077,7 +51685,7 @@
         <v>463</v>
       </c>
       <c r="C8" s="80" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D8" s="46"/>
       <c r="E8" s="46"/>
@@ -50093,7 +51701,7 @@
         <v>464</v>
       </c>
       <c r="C9" s="80" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D9" s="46"/>
       <c r="E9" s="46"/>
@@ -50154,10 +51762,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="80" t="s">
+        <v>817</v>
+      </c>
+      <c r="C13" s="80" t="s">
         <v>818</v>
-      </c>
-      <c r="C13" s="80" t="s">
-        <v>819</v>
       </c>
       <c r="D13" s="46"/>
       <c r="E13" s="46"/>
@@ -50173,7 +51781,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{882285E6-43A5-4E02-9D6A-CBFE460AC0A7}">
   <dimension ref="B2:C16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -50299,1245 +51907,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B358B9-0FBA-4749-BEFA-4DF05274EAFA}">
-  <dimension ref="A1:AF33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:32">
-      <c r="A1" s="45" t="s">
-        <v>459</v>
-      </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-    </row>
-    <row r="2" spans="1:32">
-      <c r="A2" s="46"/>
-      <c r="B2" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="75" t="s">
-        <v>730</v>
-      </c>
-      <c r="D2" s="75" t="s">
-        <v>717</v>
-      </c>
-      <c r="E2" s="75" t="s">
-        <v>718</v>
-      </c>
-      <c r="F2" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="76" t="s">
-        <v>801</v>
-      </c>
-      <c r="H2" s="76" t="s">
-        <v>126</v>
-      </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-    </row>
-    <row r="3" spans="1:32">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46" t="s">
-        <v>719</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>720</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>728</v>
-      </c>
-      <c r="E3" s="77">
-        <v>45757</v>
-      </c>
-      <c r="F3" s="78" t="s">
-        <v>474</v>
-      </c>
-      <c r="G3" s="78">
-        <v>1250</v>
-      </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="46"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-    </row>
-    <row r="4" spans="1:32">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46" t="s">
-        <v>692</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>692</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>726</v>
-      </c>
-      <c r="E4" s="77">
-        <v>45782</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>727</v>
-      </c>
-      <c r="G4" s="79">
-        <v>9420</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>802</v>
-      </c>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-    </row>
-    <row r="5" spans="1:32">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>729</v>
-      </c>
-      <c r="E5" s="77">
-        <v>45637</v>
-      </c>
-      <c r="F5" s="78" t="s">
-        <v>474</v>
-      </c>
-      <c r="G5" s="79">
-        <v>1100</v>
-      </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="46"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46"/>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46"/>
-      <c r="Y5" s="46"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-    </row>
-    <row r="6" spans="1:32">
-      <c r="A6" s="46"/>
-      <c r="B6" s="46" t="s">
-        <v>731</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>731</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>732</v>
-      </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="46"/>
-      <c r="Y6" s="46"/>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="46"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-    </row>
-    <row r="7" spans="1:32">
-      <c r="A7" s="46"/>
-      <c r="B7" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>680</v>
-      </c>
-      <c r="E7" s="77">
-        <v>45889</v>
-      </c>
-      <c r="F7" s="46">
-        <v>16.75</v>
-      </c>
-      <c r="G7" s="46" t="s">
-        <v>800</v>
-      </c>
-      <c r="H7" s="46" t="s">
-        <v>799</v>
-      </c>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-    </row>
-    <row r="8" spans="1:32">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46" t="s">
-        <v>420</v>
-      </c>
-      <c r="C8" s="58" t="s">
-        <v>476</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>805</v>
-      </c>
-      <c r="E8" s="77">
-        <v>45322</v>
-      </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46">
-        <v>500</v>
-      </c>
-      <c r="H8" s="46" t="s">
-        <v>806</v>
-      </c>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
-      <c r="V8" s="46"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="46"/>
-      <c r="Y8" s="46"/>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="46"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-    </row>
-    <row r="9" spans="1:32">
-      <c r="A9" s="46"/>
-      <c r="B9" s="46" t="s">
-        <v>810</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>811</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>689</v>
-      </c>
-      <c r="E9" s="77">
-        <v>45808</v>
-      </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46">
-        <v>290</v>
-      </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="46"/>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="46"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-    </row>
-    <row r="10" spans="1:32">
-      <c r="A10" s="46"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46"/>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="46"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="46"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-    </row>
-    <row r="11" spans="1:32">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="46"/>
-      <c r="AA11" s="46"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-    </row>
-    <row r="12" spans="1:32">
-      <c r="A12" s="46"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
-      <c r="S12" s="46"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="46"/>
-      <c r="V12" s="46"/>
-      <c r="W12" s="46"/>
-      <c r="X12" s="46"/>
-      <c r="Y12" s="46"/>
-      <c r="Z12" s="46"/>
-      <c r="AA12" s="46"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-    </row>
-    <row r="13" spans="1:32">
-      <c r="A13" s="46"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="46"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="46"/>
-      <c r="Y13" s="46"/>
-      <c r="Z13" s="46"/>
-      <c r="AA13" s="46"/>
-      <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" s="1"/>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
-    </row>
-    <row r="14" spans="1:32">
-      <c r="A14" s="46"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46"/>
-      <c r="Q14" s="46"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="46"/>
-      <c r="Y14" s="46"/>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="46"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-    </row>
-    <row r="15" spans="1:32">
-      <c r="A15" s="46"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="46"/>
-      <c r="Y15" s="46"/>
-      <c r="Z15" s="46"/>
-      <c r="AA15" s="46"/>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-    </row>
-    <row r="16" spans="1:32">
-      <c r="A16" s="46"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="46"/>
-      <c r="Y16" s="46"/>
-      <c r="Z16" s="46"/>
-      <c r="AA16" s="46"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-    </row>
-    <row r="17" spans="1:32">
-      <c r="A17" s="46"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="46"/>
-      <c r="AA17" s="46"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
-    </row>
-    <row r="18" spans="1:32">
-      <c r="A18" s="46"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="46"/>
-      <c r="S18" s="46"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
-      <c r="V18" s="46"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="46"/>
-      <c r="Y18" s="46"/>
-      <c r="Z18" s="46"/>
-      <c r="AA18" s="46"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
-    </row>
-    <row r="19" spans="1:32">
-      <c r="A19" s="46"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46"/>
-      <c r="O19" s="46"/>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="46"/>
-      <c r="V19" s="46"/>
-      <c r="W19" s="46"/>
-      <c r="X19" s="46"/>
-      <c r="Y19" s="46"/>
-      <c r="Z19" s="46"/>
-      <c r="AA19" s="46"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
-    </row>
-    <row r="20" spans="1:32">
-      <c r="A20" s="46"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="46"/>
-      <c r="V20" s="46"/>
-      <c r="W20" s="46"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="46"/>
-      <c r="Z20" s="46"/>
-      <c r="AA20" s="46"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
-    </row>
-    <row r="21" spans="1:32">
-      <c r="A21" s="46"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="46"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="46"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="46"/>
-      <c r="Z21" s="46"/>
-      <c r="AA21" s="46"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
-    </row>
-    <row r="22" spans="1:32">
-      <c r="A22" s="46"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="46"/>
-      <c r="O22" s="46"/>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="46"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="46"/>
-      <c r="U22" s="46"/>
-      <c r="V22" s="46"/>
-      <c r="W22" s="46"/>
-      <c r="X22" s="46"/>
-      <c r="Y22" s="46"/>
-      <c r="Z22" s="46"/>
-      <c r="AA22" s="46"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
-    </row>
-    <row r="23" spans="1:32">
-      <c r="A23" s="46"/>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="46"/>
-      <c r="P23" s="46"/>
-      <c r="Q23" s="46"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="46"/>
-      <c r="T23" s="46"/>
-      <c r="U23" s="46"/>
-      <c r="V23" s="46"/>
-      <c r="W23" s="46"/>
-      <c r="X23" s="46"/>
-      <c r="Y23" s="46"/>
-      <c r="Z23" s="46"/>
-      <c r="AA23" s="46"/>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-    </row>
-    <row r="24" spans="1:32">
-      <c r="A24" s="46"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="46"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-    </row>
-    <row r="25" spans="1:32">
-      <c r="A25" s="46"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
-      <c r="P25" s="46"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46"/>
-      <c r="S25" s="46"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="46"/>
-      <c r="V25" s="46"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="46"/>
-      <c r="Y25" s="46"/>
-      <c r="Z25" s="46"/>
-      <c r="AA25" s="46"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
-    </row>
-    <row r="26" spans="1:32">
-      <c r="A26" s="46"/>
-      <c r="B26" s="46"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="46"/>
-      <c r="AA26" s="46"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1"/>
-    </row>
-    <row r="27" spans="1:32">
-      <c r="A27" s="46"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="46"/>
-      <c r="Y27" s="46"/>
-      <c r="Z27" s="46"/>
-      <c r="AA27" s="46"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
-      <c r="AF27" s="1"/>
-    </row>
-    <row r="28" spans="1:32">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="46"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="46"/>
-      <c r="AA28" s="46"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AF28" s="1"/>
-    </row>
-    <row r="29" spans="1:32">
-      <c r="A29" s="46"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="46"/>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="46"/>
-      <c r="S29" s="46"/>
-      <c r="T29" s="46"/>
-      <c r="U29" s="46"/>
-      <c r="V29" s="46"/>
-      <c r="W29" s="46"/>
-      <c r="X29" s="46"/>
-      <c r="Y29" s="46"/>
-      <c r="Z29" s="46"/>
-      <c r="AA29" s="46"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
-      <c r="AF29" s="1"/>
-    </row>
-    <row r="30" spans="1:32">
-      <c r="A30" s="46"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
-      <c r="W30" s="46"/>
-      <c r="X30" s="46"/>
-      <c r="Y30" s="46"/>
-      <c r="Z30" s="46"/>
-      <c r="AA30" s="46"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
-    </row>
-    <row r="31" spans="1:32">
-      <c r="A31" s="46"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="46"/>
-      <c r="P31" s="46"/>
-      <c r="Q31" s="46"/>
-      <c r="R31" s="46"/>
-      <c r="S31" s="46"/>
-      <c r="T31" s="46"/>
-      <c r="U31" s="46"/>
-      <c r="V31" s="46"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="46"/>
-      <c r="Z31" s="46"/>
-      <c r="AA31" s="46"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
-      <c r="AF31" s="1"/>
-    </row>
-    <row r="32" spans="1:32">
-      <c r="A32" s="46"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
-      <c r="O32" s="46"/>
-      <c r="P32" s="46"/>
-      <c r="Q32" s="46"/>
-      <c r="R32" s="46"/>
-      <c r="S32" s="46"/>
-      <c r="T32" s="46"/>
-      <c r="U32" s="46"/>
-      <c r="V32" s="46"/>
-      <c r="W32" s="46"/>
-      <c r="X32" s="46"/>
-      <c r="Y32" s="46"/>
-      <c r="Z32" s="46"/>
-      <c r="AA32" s="46"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
-      <c r="AF32" s="1"/>
-    </row>
-    <row r="33" spans="1:32">
-      <c r="A33" s="46"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="46"/>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="46"/>
-      <c r="S33" s="46"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="46"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="46"/>
-      <c r="Y33" s="46"/>
-      <c r="Z33" s="46"/>
-      <c r="AA33" s="46"/>
-      <c r="AB33" s="1"/>
-      <c r="AC33" s="1"/>
-      <c r="AD33" s="1"/>
-      <c r="AE33" s="1"/>
-      <c r="AF33" s="1"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{996B57F6-8038-47F6-A248-0F268F1ACEFB}"/>
-    <hyperlink ref="C4" r:id="rId1" display="SKX" xr:uid="{8E2CF5BB-29AF-4437-8F96-D294155BB64C}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{2A12F8E0-FB6F-4E0D-B2A9-CED87F005A2E}"/>
-    <hyperlink ref="C7" r:id="rId3" xr:uid="{198927E1-7FEB-4804-8A3B-9B9BC35A8F85}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B566C759-4A7F-4A6A-99E5-C018C4B21F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB87947-6084-4645-8661-0CD78C17F02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4023,26 +4023,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>23.02</v>
+            <v>23.62</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>5992.1059999999998</v>
+            <v>6150.6480000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1437</v>
+            <v>1877.4</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>754.9</v>
+            <v>778.6</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4105,22 +4105,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>54.86</v>
+            <v>52.82</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>170943.68955976001</v>
+            <v>164591.95229051998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>11269</v>
+            <v>10960</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
       </sheetData>
@@ -5340,7 +5340,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7145,15 +7145,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1892319.1963556812</v>
+        <v>1885878.2732756715</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>1371.2796751999967</v>
+        <v>1260.311675199996</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1893690.4760308799</v>
+        <v>1887138.5849508706</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7215,15 +7215,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23979.322434085814</v>
+        <v>23897.791762186956</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>17.808826950649308</v>
+        <v>16.36768409350644</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24593.382805595844</v>
+        <v>24508.293311050267</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7528,25 +7528,25 @@
       </c>
       <c r="E8" s="25">
         <f>+[3]Main!$J$3</f>
-        <v>54.86</v>
+        <v>52.82</v>
       </c>
       <c r="F8" s="18">
         <f>+[3]Main!$J$5*FX!C3</f>
-        <v>177781.43714215042</v>
+        <v>171175.63038214078</v>
       </c>
       <c r="G8" s="18">
         <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
-        <v>-11718.720000000001</v>
+        <v>-11396.32</v>
       </c>
       <c r="H8" s="18">
         <f t="shared" ref="H8:H35" si="1">F8+G8</f>
-        <v>166062.71714215042</v>
+        <v>159779.31038214077</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>149</v>
+        <v>422</v>
       </c>
       <c r="J8" s="27">
-        <v>46092</v>
+        <v>46183</v>
       </c>
       <c r="K8" s="18">
         <f>35947*FX!C3</f>
@@ -7645,7 +7645,9 @@
       <c r="I9" s="26" t="s">
         <v>828</v>
       </c>
-      <c r="J9" s="27"/>
+      <c r="J9" s="27">
+        <v>46162</v>
+      </c>
       <c r="K9" s="25">
         <v>54217</v>
       </c>
@@ -9400,25 +9402,25 @@
       </c>
       <c r="E33" s="25">
         <f>+[28]Main!$I$2</f>
-        <v>23.02</v>
+        <v>23.62</v>
       </c>
       <c r="F33" s="18">
         <f>+[28]Main!$I$4*FX!C3</f>
-        <v>6231.7902400000003</v>
+        <v>6396.6739200000002</v>
       </c>
       <c r="G33" s="18">
         <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
-        <v>-709.38400000000001</v>
+        <v>-1142.7520000000002</v>
       </c>
       <c r="H33" s="18">
         <f>F33+G33</f>
-        <v>5522.4062400000003</v>
+        <v>5253.9219199999998</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>814</v>
+        <v>422</v>
       </c>
       <c r="J33" s="27">
-        <v>46093</v>
+        <v>46148</v>
       </c>
       <c r="K33" s="25"/>
       <c r="L33" s="22"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB87947-6084-4645-8661-0CD78C17F02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01A55CF-D1A2-40F9-AEA0-6315A0D4D40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3337,14 +3337,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3882,7 +3882,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4042,7 +4042,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4206,7 +4206,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4963,17 +4963,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>56.66</v>
+            <v>55.02</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3053.3446207199995</v>
+            <v>2880.3823910400001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>236.02699999999999</v>
+            <v>790.7940000000001</v>
           </cell>
         </row>
         <row r="6">
@@ -4982,7 +4982,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6603,7 +6603,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7145,15 +7145,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1885878.2732756715</v>
+        <v>1885705.3110459915</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>1260.311675199996</v>
+        <v>705.54467519999628</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1887138.5849508706</v>
+        <v>1886410.8557211906</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7215,15 +7215,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23897.791762186956</v>
+        <v>23895.602366874551</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>16.36768409350644</v>
+        <v>9.1629178597402117</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24508.293311050267</v>
+        <v>24498.842282093385</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7340,7 +7340,7 @@
         <v>422</v>
       </c>
       <c r="J6" s="27">
-        <v>46080</v>
+        <v>46125</v>
       </c>
       <c r="K6" s="18">
         <f>80807*FX!C3</f>
@@ -9137,7 +9137,7 @@
         <v>422</v>
       </c>
       <c r="J29" s="27">
-        <v>46078</v>
+        <v>46161</v>
       </c>
       <c r="K29" s="25"/>
       <c r="L29" s="22"/>
@@ -9606,10 +9606,10 @@
         <v>8458.0043700000006</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>814</v>
+        <v>422</v>
       </c>
       <c r="J36" s="27">
-        <v>46086</v>
+        <v>46170</v>
       </c>
       <c r="K36" s="18">
         <v>14889</v>
@@ -10733,25 +10733,25 @@
       </c>
       <c r="E54" s="25">
         <f>+[49]Main!$I$2</f>
-        <v>56.66</v>
+        <v>55.02</v>
       </c>
       <c r="F54" s="18">
         <f>+[49]Main!$I$4</f>
-        <v>3053.3446207199995</v>
+        <v>2880.3823910400001</v>
       </c>
       <c r="G54" s="18">
         <f>+[49]Main!$I$6-[49]Main!$I$5</f>
-        <v>-236.02699999999999</v>
+        <v>-790.7940000000001</v>
       </c>
       <c r="H54" s="18">
         <f t="shared" si="3"/>
-        <v>2817.3176207199995</v>
+        <v>2089.5883910399998</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>814</v>
+        <v>422</v>
       </c>
       <c r="J54" s="27">
-        <v>46056</v>
+        <v>46142</v>
       </c>
       <c r="K54" s="18"/>
       <c r="L54" s="22"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01A55CF-D1A2-40F9-AEA0-6315A0D4D40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2798E779-F248-4382-AD93-8218CA27295F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2767,13 +2767,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2958,22 +2964,100 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2987,166 +3071,91 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
@@ -3229,17 +3238,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>204.5</v>
+            <v>156.36000000000001</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>22942.8633845</v>
+            <v>17275.07043756</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1035.8620000000001</v>
+            <v>1807.202</v>
           </cell>
         </row>
         <row r="6">
@@ -3248,9 +3257,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3882,7 +3891,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4124,9 +4133,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4206,7 +4215,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4982,7 +4991,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6544,26 +6553,26 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>194.55</v>
+            <v>177.95</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>10039.612674000002</v>
+            <v>9236.3445957900003</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1276</v>
+            <v>1231</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>187</v>
+            <v>38</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6603,7 +6612,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7145,15 +7154,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1885705.3110459915</v>
+        <v>1880037.5180990517</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>705.54467519999628</v>
+        <v>-65.795324800000117</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1886410.8557211906</v>
+        <v>1879971.7227742509</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7215,15 +7224,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23895.602366874551</v>
+        <v>23823.858152356326</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>9.1629178597402117</v>
+        <v>-0.85448473766233923</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24498.842282093385</v>
+        <v>24415.217178886374</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -8137,26 +8146,24 @@
       </c>
       <c r="E15" s="25">
         <f>+[10]Main!$I$2</f>
-        <v>204.5</v>
+        <v>156.36000000000001</v>
       </c>
       <c r="F15" s="18">
         <f>+[10]Main!$I$4</f>
-        <v>22942.8633845</v>
+        <v>17275.07043756</v>
       </c>
       <c r="G15" s="18">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
-        <v>-1035.8620000000001</v>
+        <v>-1807.202</v>
       </c>
       <c r="H15" s="18">
         <f>F15+G15</f>
-        <v>21907.001384499999</v>
+        <v>15467.868437560001</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>814</v>
-      </c>
-      <c r="J15" s="27">
-        <v>46108</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="J15" s="27"/>
       <c r="K15" s="18">
         <v>9619.2999999999993</v>
       </c>
@@ -40182,22 +40189,22 @@
       </c>
       <c r="E7" s="59">
         <f>+[84]Main!$I$3</f>
-        <v>194.55</v>
+        <v>177.95</v>
       </c>
       <c r="F7" s="57">
         <f>+[84]Main!$I$5*FX!C7</f>
-        <v>11244.366194880004</v>
+        <v>10344.705947284801</v>
       </c>
       <c r="G7" s="57">
         <f>+([84]Main!$I$7-[84]Main!$I$6)*FX!C7</f>
-        <v>-1219.68</v>
+        <v>-1336.16</v>
       </c>
       <c r="H7" s="57">
         <f>+F7+G7</f>
-        <v>10024.686194880003</v>
-      </c>
-      <c r="I7" s="47" t="s">
-        <v>149</v>
+        <v>9008.5459472848015</v>
+      </c>
+      <c r="I7" s="97" t="s">
+        <v>422</v>
       </c>
       <c r="J7" s="61">
         <v>46099</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2798E779-F248-4382-AD93-8218CA27295F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183BF855-A79E-4E1D-997C-9C79F806F5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="865">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -3184,417 +3184,29 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
       <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="I4">
-            <v>549</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>273230.13006</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>8794</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="I8">
-            <v>20343</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
+      <sheetName val="Quarter"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>156.36000000000001</v>
+            <v>233</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>17275.07043756</v>
+            <v>106951.39810799999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1807.202</v>
+            <v>3544</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>141.80000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>25319.697396000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1617</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2641</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Brands"/>
-      <sheetName val="Macro"/>
-      <sheetName val="Model"/>
-      <sheetName val="Quart"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="CoC"/>
-      <sheetName val="TradingComps"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>284.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>34917.850457599998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>4313</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>12562</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>101.6</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>265357.92597599997</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>32144</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>24040</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="M2">
-            <v>115.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="M4">
-            <v>16366.831656300001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="M5">
-            <v>2086.7460000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="M6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>185.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>297628.32315000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>20908</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>20675</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="WACC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>40.880000000000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>12552.5670144</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1261.6759999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1732.366</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5221.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1856195.55198455</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5"/>
-        </row>
-        <row r="6">
-          <cell r="I6"/>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarter"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>55.15</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>14919.336445949999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1341.982</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>980.13599999999997</v>
+            <v>10839</v>
           </cell>
         </row>
       </sheetData>
@@ -3605,1837 +3217,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>252.2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>15870.190913199998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>584.07899999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2035.424</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>2146</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>226551.95815200001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>12239</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>34</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>154.69999999999999</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>31321.2152981</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1077.7</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2396.4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4396</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3141807.6866959999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>112267</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>37500</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>127.35</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>14912.684999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>441.1</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>781.30000000000007</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="KPIs"/>
-      <sheetName val="CoC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.04</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>10356.130046052</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1019.9</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>59.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>40.49</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>22544.952903140002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>652.29999999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>935.09999999999991</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financials"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>58.65</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>88163.993584049997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>19318.056</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>10827.793</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>338.01</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>20461.91295813</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2250.8000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1238.3</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>76.739999999999995</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>89555.579999999987</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>6221.5751200000004</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>898.55169000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>23.62</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>6150.6480000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1877.4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>778.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>20.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>7942.6458629000008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1466.4690000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>4155.6499999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="J3">
-            <v>52.82</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>164591.95229051998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>10960</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>33.710999999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>6199.6570538160004</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>229.227</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>1140.2079999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>25.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>9484.0043700000006</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>2517</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>1491</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financials"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>60.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>9118.7085583999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1467.8490000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>628.88699999999994</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>86.1</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5854.2555035999994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>203.84100000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>396.62300000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>8953.7999999999993</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>112.633</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1754.22</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>21.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>8574.6616225199996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>848.8</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1039.2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17550</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>32570.869500000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1577</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2262</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>8.7799999999999994</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>42144</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>6390</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>1540</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41240</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>459995.53764</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>45360.78</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>52633.11</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="Coc"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>99.2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>5094.5152000000007</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>130.35400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1230.885</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>159.05000000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>179090.30000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>6230</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>2869</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>27.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>102081.60000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>4793</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>12059</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>0.93779999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4808.1005999999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>531</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>656</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>86.42</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>9891.3739399999995</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>292.61099999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>16.02</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>37954.121342400002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>17557.536999999997</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>8.01</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>36725.331993300002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>8082.48891</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>20208.361519999999</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>65.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5874.7799535000004</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>695.93000000000006</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>24.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3545.2105000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>290</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>572</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>3.75</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>37653.589800000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5665.9049999999997</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>995.54700000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="WACC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>95.69</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4527.9551099999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>784.57600000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>55.02</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2880.3823910400001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>790.7940000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>471.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>85081.629528000005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9760</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>22957</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>76.37</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>3497.9518935199999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>158.19999999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2258.7999999999997</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2816.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>697412.87774050003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>138918</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5959</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>11.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4310.384</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>452</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>545</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>165.1</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>5044.7333572999996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>95.319000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>78.680000000000007</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4372.5807311200006</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>107.482</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1366.51</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>132.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>130841.4975</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>3309.02</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>7400.7630000000008</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>161.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2990.6024601600002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>211.91</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>36.299999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2505.286971</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>343.12599999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>295.77</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>7.47</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3181.39830747</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>464.64800000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>989.73099999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>14.35</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2756.6605860499999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>160.19499999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5481,405 +3263,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>263.45</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270582.07176934998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1259.98</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>3707.71</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>54.91</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4407.5666168399994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>249</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1351</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>33.92</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>2464.3691366400003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>111.31400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>293.49</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>19.670000000000002</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2341.6752811900001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>129</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1671</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>9.6300000000000008</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2436.6190977000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>231.22499999999997</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>348.65300000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>828.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>201333.06192080001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>440.44</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>269.23</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5.82</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2055.0937514400002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>214.85400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2186.0569999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.42</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>1491.5652650000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>412.92599999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>498.12</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>38.119999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1935.4971035199997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>325.44000000000005</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>24.73</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1761.5194085300002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>256.60000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5934,407 +3318,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>27.07</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1188.01315849</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>104.68600000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>224.17499999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>59.85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>939.70682505000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>7.0270000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>57.816000000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>14.56</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1413.6025904000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>346.9</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>415.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.53</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>736.21656488999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>245.11399999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>9.6039999999999992</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>16.75</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>872.38125524999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>189.63499999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>623.71199999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main "/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="F2">
-            <v>4.3620000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="F4">
-            <v>519.44946792000007</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>391</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>688.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>0.98</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>97.21301296</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>17.213000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>291.31400000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17.79</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270.90115659000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>45.523000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>70.016000000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2540</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>64964.434459999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>33044</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>13470</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1638</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>206.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>621.70000000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6374,7 +3358,91 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="H3">
+            <v>176.36</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>56659.177199999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4061.1729999999998</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>1516.972</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>156.36000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>17275.07043756</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1807.202</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6388,23 +3456,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="J2">
-            <v>180.8</v>
+          <cell r="I2">
+            <v>141.80000000000001</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="J4">
-            <v>14437.908028799999</v>
+          <cell r="I4">
+            <v>25319.697396000003</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>1689.94</v>
+          <cell r="I5">
+            <v>1617</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>1484.2170000000001</v>
+          <cell r="I6">
+            <v>2641</v>
           </cell>
         </row>
       </sheetData>
@@ -6414,7 +3482,61 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Brands"/>
+      <sheetName val="Macro"/>
+      <sheetName val="Model"/>
+      <sheetName val="Quart"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="CoC"/>
+      <sheetName val="TradingComps"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>284.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>34917.850457599998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>4313</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>12562</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6424,39 +3546,117 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="Quarter"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>101.6</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>265357.92597599997</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>32144</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>24040</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="M2">
+            <v>115.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="M4">
+            <v>16366.831656300001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="M5">
+            <v>2086.7460000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>233</v>
+            <v>185.55</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>106951.39810799999</v>
+            <v>297628.32315000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>3544</v>
+            <v>20908</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>10839</v>
+            <v>20675</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6498,7 +3698,419 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="WACC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>40.880000000000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>12552.5670144</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1261.6759999999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>1732.366</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5221.55</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1856195.55198455</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5"/>
+        </row>
+        <row r="6">
+          <cell r="I6"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarter"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>55.15</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>14919.336445949999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1341.982</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>980.13599999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>252.2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>15870.190913199998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>584.07899999999995</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2035.424</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>154.69999999999999</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>31321.2152981</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1077.7</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2396.4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4396</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3141807.6866959999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>112267</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>37500</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>127.35</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>14912.684999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>441.1</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>781.30000000000007</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="KPIs"/>
+      <sheetName val="CoC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41.04</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>10356.130046052</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1019.9</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>59.5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>40.49</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>22544.952903140002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>652.29999999999995</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>935.09999999999991</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financials"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>58.65</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>88163.993584049997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>19318.056</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>10827.793</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6538,7 +4150,407 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>338.01</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>20461.91295813</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2250.8000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1238.3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>76.739999999999995</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>89555.579999999987</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>6221.5751200000004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>898.55169000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>23.62</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>6150.6480000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1877.4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>778.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>20.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>7942.6458629000008</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1466.4690000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4155.6499999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>33.710999999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>6199.6570538160004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>229.227</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>1140.2079999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>25.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>9484.0043700000006</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>2517</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>1491</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financials"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>60.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>9118.7085583999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1467.8490000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>628.88699999999994</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>86.1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5854.2555035999994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>203.84100000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>396.62300000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>8953.7999999999993</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>112.633</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1754.22</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>21.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>8574.6616225199996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>848.8</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1039.2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6572,7 +4584,1995 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>17550</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>32570.869500000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1577</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2262</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>8.7799999999999994</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>42144</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>6390</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>1540</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41240</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>459995.53764</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>45360.78</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>52633.11</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="Coc"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Data"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>99.2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>5094.5152000000007</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>130.35400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1230.885</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>27.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>102081.60000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>4793</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>12059</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>0.93779999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4808.1005999999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>531</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>656</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>86.42</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>9891.3739399999995</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>292.61099999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>16.02</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>37954.121342400002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>17557.536999999997</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>8.01</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>36725.331993300002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>8082.48891</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>20208.361519999999</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>65.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5874.7799535000004</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>695.93000000000006</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="I4">
+            <v>549</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>273230.13006</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>8794</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>20343</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>24.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3545.2105000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>290</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>572</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>3.75</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>37653.589800000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5665.9049999999997</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>995.54700000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>95.69</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4527.9551099999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>784.57600000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>55.02</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2880.3823910400001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>790.7940000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>76.37</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>3497.9518935199999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>158.19999999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2258.7999999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2816.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>697412.87774050003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>138918</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5959</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>11.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4310.384</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>452</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>545</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>165.1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5044.7333572999996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>95.319000000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>78.680000000000007</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4372.5807311200006</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>107.482</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1366.51</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>132.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>130841.4975</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>3309.02</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>7400.7630000000008</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>2146</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>226551.95815200001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>12239</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>34</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>161.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2990.6024601600002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>211.91</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>36.299999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2505.286971</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>343.12599999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>295.77</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>7.47</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3181.39830747</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>464.64800000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>989.73099999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>14.35</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2756.6605860499999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>160.19499999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>263.45</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270582.07176934998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1259.98</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>3707.71</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>54.91</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4407.5666168399994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>249</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1351</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>33.92</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>2464.3691366400003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>111.31400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>293.49</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>19.670000000000002</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2341.6752811900001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>129</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1671</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>9.6300000000000008</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2436.6190977000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>231.22499999999997</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>348.65300000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>828.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>201333.06192080001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>440.44</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>269.23</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="J3">
+            <v>52.82</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>164591.95229051998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>10960</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5.82</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2055.0937514400002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>214.85400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2186.0569999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41.42</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>1491.5652650000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>412.92599999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>498.12</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>38.119999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1935.4971035199997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>325.44000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>24.73</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1761.5194085300002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>256.60000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>27.07</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1188.01315849</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>104.68600000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>224.17499999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>59.85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>939.70682505000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>7.0270000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>57.816000000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>14.56</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1413.6025904000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>346.9</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>415.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4.53</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>736.21656488999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>245.11399999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>9.6039999999999992</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>16.75</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>872.38125524999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>189.63499999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>623.71199999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main "/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="F2">
+            <v>2.4350000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4">
+            <v>290.48290130999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>318.89999999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>503.6</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>159.05000000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>179090.30000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>6230</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>2869</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>0.98</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>97.21301296</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>17.213000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>291.31400000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>17.79</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270.90115659000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>45.523000000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>70.016000000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2540</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>64964.434459999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>33044</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>13470</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1638</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>206.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>621.70000000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>180.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>14437.908028799999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1689.94</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>1484.2170000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6587,28 +6587,28 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Model"/>
+      <sheetName val="Financial"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="3">
-          <cell r="H3">
-            <v>176.36</v>
+        <row r="2">
+          <cell r="I2">
+            <v>471.6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>85081.629528000005</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>56659.177199999998</v>
+          <cell r="I5">
+            <v>9760</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>4061.1729999999998</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1516.972</v>
+          <cell r="I6">
+            <v>22957</v>
           </cell>
         </row>
       </sheetData>
@@ -7154,15 +7154,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1880037.5180990517</v>
+        <v>1879753.5995564552</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>-65.795324800000117</v>
+        <v>-205.17132480000015</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1879971.7227742509</v>
+        <v>1879548.4282316547</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7224,15 +7224,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23823.858152356326</v>
+        <v>23820.264246753839</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>-0.85448473766233923</v>
+        <v>-2.6645626597402616</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24415.217178886374</v>
+        <v>24409.719847164346</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7330,15 +7330,15 @@
         <v>20</v>
       </c>
       <c r="E6" s="25">
-        <f>+[1]Main!$I$4</f>
+        <f>+[5]Main!$I$4</f>
         <v>549</v>
       </c>
       <c r="F6" s="18">
-        <f>+[1]Main!$I$6*FX!C3</f>
+        <f>+[5]Main!$I$6*FX!C3</f>
         <v>284159.33526239998</v>
       </c>
       <c r="G6" s="18">
-        <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
+        <f>(+[5]Main!$I$8-[5]Main!$I$7)*FX!C3</f>
         <v>12010.960000000001</v>
       </c>
       <c r="H6" s="18">
@@ -7433,15 +7433,15 @@
         <v>20</v>
       </c>
       <c r="E7" s="30">
-        <f>+[2]Main!$K$2</f>
+        <f>+[6]Main!$K$2</f>
         <v>2146</v>
       </c>
       <c r="F7" s="18">
-        <f>+[2]Main!$K$4*FX!C3</f>
+        <f>+[6]Main!$K$4*FX!C3</f>
         <v>235614.03647808</v>
       </c>
       <c r="G7" s="18">
-        <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
+        <f>+([6]Main!$K$6-[6]Main!$K$5)*FX!C3</f>
         <v>-12693.2</v>
       </c>
       <c r="H7" s="18">
@@ -7536,15 +7536,15 @@
         <v>100</v>
       </c>
       <c r="E8" s="25">
-        <f>+[3]Main!$J$3</f>
+        <f>+[7]Main!$J$3</f>
         <v>52.82</v>
       </c>
       <c r="F8" s="18">
-        <f>+[3]Main!$J$5*FX!C3</f>
+        <f>+[7]Main!$J$5*FX!C3</f>
         <v>171175.63038214078</v>
       </c>
       <c r="G8" s="18">
-        <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
+        <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C3</f>
         <v>-11396.32</v>
       </c>
       <c r="H8" s="18">
@@ -7636,15 +7636,15 @@
         <v>21</v>
       </c>
       <c r="E9" s="25">
-        <f>+[4]Main!$I$3</f>
+        <f>+[8]Main!$I$3</f>
         <v>159.05000000000001</v>
       </c>
       <c r="F9" s="18">
-        <f>+[4]Main!$I$5</f>
+        <f>+[8]Main!$I$5</f>
         <v>179090.30000000002</v>
       </c>
       <c r="G9" s="18">
-        <f>+[4]Main!$I$7-[4]Main!$I$6</f>
+        <f>+[8]Main!$I$7-[8]Main!$I$6</f>
         <v>-3361</v>
       </c>
       <c r="H9" s="18">
@@ -7731,15 +7731,15 @@
         <v>20</v>
       </c>
       <c r="E10" s="25">
-        <f>+[5]Main!$I$2</f>
+        <f>+[9]Main!$I$2</f>
         <v>471.6</v>
       </c>
       <c r="F10" s="18">
-        <f>+[5]Main!$I$4*FX!C3</f>
+        <f>+[9]Main!$I$4*FX!C3</f>
         <v>88484.89470912001</v>
       </c>
       <c r="G10" s="18">
-        <f>+([5]Main!$I$6-[5]Main!$I$5)*FX!C3</f>
+        <f>+([9]Main!$I$6-[9]Main!$I$5)*FX!C3</f>
         <v>13724.880000000001</v>
       </c>
       <c r="H10" s="18">
@@ -7806,15 +7806,15 @@
         <v>21</v>
       </c>
       <c r="E11" s="25">
-        <f>+[6]Main!$I$3</f>
+        <f>+[10]Main!$I$3</f>
         <v>58.85</v>
       </c>
       <c r="F11" s="18">
-        <f>+[6]Main!$I$5</f>
+        <f>+[10]Main!$I$5</f>
         <v>87068.574999999997</v>
       </c>
       <c r="G11" s="18">
-        <f>+[6]Main!$I$7-[6]Main!$I$6</f>
+        <f>+[10]Main!$I$7-[10]Main!$I$6</f>
         <v>-330</v>
       </c>
       <c r="H11" s="18">
@@ -7903,15 +7903,15 @@
         <v>124</v>
       </c>
       <c r="E12" s="30">
-        <f>+[7]Main!$J$3</f>
+        <f>+[11]Main!$J$3</f>
         <v>62750</v>
       </c>
       <c r="F12" s="18">
-        <f>+[7]Main!$J$5*FX!C5</f>
+        <f>+[11]Main!$J$5*FX!C5</f>
         <v>121295.419182</v>
       </c>
       <c r="G12" s="18">
-        <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
+        <f>+([11]Main!$J$7-[11]Main!$J$6)*FX!C5</f>
         <v>-10509.2505</v>
       </c>
       <c r="H12" s="18">
@@ -7932,7 +7932,7 @@
         <v>0.08</v>
       </c>
       <c r="M12" s="18">
-        <f>+SUM([7]Model!$G$20:$I$20,[7]Model!$C$20)*FX!C5</f>
+        <f>+SUM([11]Model!$G$20:$I$20,[11]Model!$C$20)*FX!C5</f>
         <v>3765.1320000000001</v>
       </c>
       <c r="N12" s="18">
@@ -7991,15 +7991,15 @@
         <v>21</v>
       </c>
       <c r="E13" s="25">
-        <f>+[8]Main!$K$2</f>
+        <f>+[12]Main!$K$2</f>
         <v>187.97</v>
       </c>
       <c r="F13" s="18">
-        <f>+[8]Main!$K$4</f>
+        <f>+[12]Main!$K$4</f>
         <v>75466.759510000004</v>
       </c>
       <c r="G13" s="18">
-        <f>+[8]Main!$K$6-[8]Main!$K$5</f>
+        <f>+[12]Main!$K$6-[12]Main!$K$5</f>
         <v>2776.4369999999999</v>
       </c>
       <c r="H13" s="18">
@@ -8070,15 +8070,15 @@
         <v>21</v>
       </c>
       <c r="E14" s="25">
-        <f>+[9]Main!$H$3</f>
+        <f>+[13]Main!$H$3</f>
         <v>176.36</v>
       </c>
       <c r="F14" s="18">
-        <f>+[9]Main!$H$5</f>
+        <f>+[13]Main!$H$5</f>
         <v>56659.177199999998</v>
       </c>
       <c r="G14" s="18">
-        <f>+[9]Main!$H$7-[9]Main!$H$6</f>
+        <f>+[13]Main!$H$7-[13]Main!$H$6</f>
         <v>-2544.201</v>
       </c>
       <c r="H14" s="18">
@@ -8145,15 +8145,15 @@
         <v>107</v>
       </c>
       <c r="E15" s="25">
-        <f>+[10]Main!$I$2</f>
+        <f>+[14]Main!$I$2</f>
         <v>156.36000000000001</v>
       </c>
       <c r="F15" s="18">
-        <f>+[10]Main!$I$4</f>
+        <f>+[14]Main!$I$4</f>
         <v>17275.07043756</v>
       </c>
       <c r="G15" s="18">
-        <f>+[10]Main!$I$6-[10]Main!$I$5</f>
+        <f>+[14]Main!$I$6-[14]Main!$I$5</f>
         <v>-1807.202</v>
       </c>
       <c r="H15" s="18">
@@ -8218,15 +8218,15 @@
         <v>82</v>
       </c>
       <c r="E16" s="25">
-        <f>+[11]Main!$I$2</f>
+        <f>+[15]Main!$I$2</f>
         <v>141.80000000000001</v>
       </c>
       <c r="F16" s="18">
-        <f>+[11]Main!$I$4*FX!C3</f>
+        <f>+[15]Main!$I$4*FX!C3</f>
         <v>26332.485291840003</v>
       </c>
       <c r="G16" s="18">
-        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
+        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C3</f>
         <v>1064.96</v>
       </c>
       <c r="H16" s="18">
@@ -8296,15 +8296,15 @@
         <v>20</v>
       </c>
       <c r="E17" s="25">
-        <f>+[12]Main!$H$2</f>
+        <f>+[16]Main!$H$2</f>
         <v>284.8</v>
       </c>
       <c r="F17" s="18">
-        <f>+[12]Main!$H$4*FX!C3</f>
+        <f>+[16]Main!$H$4*FX!C3</f>
         <v>36314.564475904001</v>
       </c>
       <c r="G17" s="18">
-        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
+        <f>+([16]Main!$H$6-[16]Main!$H$5)*FX!C3</f>
         <v>8578.9600000000009</v>
       </c>
       <c r="H17" s="18">
@@ -8396,15 +8396,15 @@
         <v>454</v>
       </c>
       <c r="E18" s="25">
-        <f>+[13]Main!$H$2</f>
+        <f>+[17]Main!$H$2</f>
         <v>101.6</v>
       </c>
       <c r="F18" s="18">
-        <f>+[13]Main!$H$5*FX!C9</f>
+        <f>+[17]Main!$H$5*FX!C9</f>
         <v>37150.109636640002</v>
       </c>
       <c r="G18" s="18">
-        <f>+([13]Main!$H$7-[13]Main!$H$6)*FX!C9</f>
+        <f>+([17]Main!$H$7-[17]Main!$H$6)*FX!C9</f>
         <v>-1134.5600000000002</v>
       </c>
       <c r="H18" s="18">
@@ -8475,15 +8475,15 @@
         <v>21</v>
       </c>
       <c r="E19" s="25">
-        <f>+[14]Main!$M$2</f>
+        <f>+[18]Main!$M$2</f>
         <v>115.3</v>
       </c>
       <c r="F19" s="18">
-        <f>+[14]Main!$M$4</f>
+        <f>+[18]Main!$M$4</f>
         <v>16366.831656300001</v>
       </c>
       <c r="G19" s="18">
-        <f>+[14]Main!$M$6-[14]Main!$M$5</f>
+        <f>+[18]Main!$M$6-[18]Main!$M$5</f>
         <v>-2086.7460000000001</v>
       </c>
       <c r="H19" s="18">
@@ -8559,15 +8559,15 @@
         <v>109</v>
       </c>
       <c r="E20" s="25">
-        <f>+[15]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>185.55</v>
       </c>
       <c r="F20" s="18">
-        <f>+[15]Main!$I$4*FX!C4</f>
+        <f>+[19]Main!$I$4*FX!C4</f>
         <v>28274.690699250001</v>
       </c>
       <c r="G20" s="18">
-        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C4</f>
+        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C4</f>
         <v>-22.135000000000002</v>
       </c>
       <c r="H20" s="18">
@@ -8627,15 +8627,15 @@
         <v>165</v>
       </c>
       <c r="E21" s="25">
-        <f>+[16]Main!$H$2</f>
+        <f>+[20]Main!$H$2</f>
         <v>40.880000000000003</v>
       </c>
       <c r="F21" s="18">
-        <f>+[16]Main!$H$5*FX!C3</f>
+        <f>+[20]Main!$H$5*FX!C3</f>
         <v>13054.669694976001</v>
       </c>
       <c r="G21" s="18">
-        <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
+        <f>(+[20]Main!$H$7-[20]Main!$H$6)*FX!C3</f>
         <v>489.51760000000007</v>
       </c>
       <c r="H21" s="18">
@@ -8690,15 +8690,15 @@
         <v>185</v>
       </c>
       <c r="E22" s="25">
-        <f>+[17]Main!$I$2</f>
+        <f>+[21]Main!$I$2</f>
         <v>5221.55</v>
       </c>
       <c r="F22" s="18">
-        <f>+[17]Main!$I$4*FX!C12</f>
+        <f>+[21]Main!$I$4*FX!C12</f>
         <v>20418.151071830049</v>
       </c>
       <c r="G22" s="18">
-        <f>+([17]Main!$I$6-[17]Main!$I$5)*FX!C12</f>
+        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C12</f>
         <v>0</v>
       </c>
       <c r="H22" s="18">
@@ -8747,15 +8747,15 @@
         <v>165</v>
       </c>
       <c r="E23" s="25">
-        <f>+[18]Main!$H$2</f>
+        <f>+[22]Main!$H$2</f>
         <v>55.15</v>
       </c>
       <c r="F23" s="18">
-        <f>+[18]Main!$H$4*FX!C3</f>
+        <f>+[22]Main!$H$4*FX!C3</f>
         <v>15516.109903787999</v>
       </c>
       <c r="G23" s="18">
-        <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C3</f>
+        <f>+([22]Main!$H$6-[22]Main!$H$5)*FX!C3</f>
         <v>-376.31984</v>
       </c>
       <c r="H23" s="18">
@@ -8810,15 +8810,15 @@
         <v>21</v>
       </c>
       <c r="E24" s="25">
-        <f>+[19]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>252.2</v>
       </c>
       <c r="F24" s="18">
-        <f>+[19]Main!$I$4</f>
+        <f>+[23]Main!$I$4</f>
         <v>15870.190913199998</v>
       </c>
       <c r="G24" s="18">
-        <f>+[19]Main!$I$6-[19]Main!$I$5</f>
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>1451.345</v>
       </c>
       <c r="H24" s="18">
@@ -8873,15 +8873,15 @@
         <v>21</v>
       </c>
       <c r="E25" s="25">
-        <f>+[20]Main!$J$2</f>
+        <f>+[24]Main!$J$2</f>
         <v>154.69999999999999</v>
       </c>
       <c r="F25" s="18">
-        <f>+[20]Main!$J$4</f>
+        <f>+[24]Main!$J$4</f>
         <v>31321.2152981</v>
       </c>
       <c r="G25" s="18">
-        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
+        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
         <v>1318.7</v>
       </c>
       <c r="H25" s="18">
@@ -8936,15 +8936,15 @@
         <v>124</v>
       </c>
       <c r="E26" s="25">
-        <f>+[21]Main!$I$2</f>
+        <f>+[25]Main!$I$2</f>
         <v>4396</v>
       </c>
       <c r="F26" s="18">
-        <f>+[21]Main!$I$4*FX!C5</f>
+        <f>+[25]Main!$I$4*FX!C5</f>
         <v>19793.3884261848</v>
       </c>
       <c r="G26" s="18">
-        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C5</f>
+        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C5</f>
         <v>-471.03210000000001</v>
       </c>
       <c r="H26" s="18">
@@ -8999,15 +8999,15 @@
         <v>219</v>
       </c>
       <c r="E27" s="25">
-        <f>+[22]Main!$I$2</f>
+        <f>+[26]Main!$I$2</f>
         <v>127.35</v>
       </c>
       <c r="F27" s="18">
-        <f>+[22]Main!$I$4*FX!C8</f>
+        <f>+[26]Main!$I$4*FX!C8</f>
         <v>18491.7294</v>
       </c>
       <c r="G27" s="18">
-        <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C8</f>
+        <f>+([26]Main!$I$6-[26]Main!$I$5)*FX!C8</f>
         <v>421.84800000000007</v>
       </c>
       <c r="H27" s="18">
@@ -9062,15 +9062,15 @@
         <v>166</v>
       </c>
       <c r="E28" s="25">
-        <f>+[23]Main!$H$2</f>
+        <f>+[27]Main!$H$2</f>
         <v>41.04</v>
       </c>
       <c r="F28" s="18">
-        <f>+[23]Main!$H$5*FX!C7</f>
+        <f>+[27]Main!$H$5*FX!C7</f>
         <v>11598.86565157824</v>
       </c>
       <c r="G28" s="18">
-        <f>+([23]Main!$H$7-[23]Main!$H$6)*FX!C7</f>
+        <f>+([27]Main!$H$7-[27]Main!$H$6)*FX!C7</f>
         <v>-1075.6480000000001</v>
       </c>
       <c r="H28" s="18">
@@ -9125,15 +9125,15 @@
         <v>214</v>
       </c>
       <c r="E29" s="25">
-        <f>+[24]Main!$J$2</f>
+        <f>+[28]Main!$J$2</f>
         <v>40.49</v>
       </c>
       <c r="F29" s="18">
-        <f>+[24]Main!$J$4</f>
+        <f>+[28]Main!$J$4</f>
         <v>22544.952903140002</v>
       </c>
       <c r="G29" s="18">
-        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
+        <f>+[28]Main!$J$6-[28]Main!$J$5</f>
         <v>282.79999999999995</v>
       </c>
       <c r="H29" s="18">
@@ -9188,15 +9188,15 @@
         <v>454</v>
       </c>
       <c r="E30" s="25">
-        <f>+[25]Main!$J$2</f>
+        <f>+[29]Main!$J$2</f>
         <v>58.65</v>
       </c>
       <c r="F30" s="18">
-        <f>+[25]Main!$J$4*FX!C9</f>
+        <f>+[29]Main!$J$4*FX!C9</f>
         <v>12342.959101767001</v>
       </c>
       <c r="G30" s="18">
-        <f>+([25]Main!$J$6-[25]Main!$J$5)*FX!C9</f>
+        <f>+([29]Main!$J$6-[29]Main!$J$5)*FX!C9</f>
         <v>-1188.6368200000002</v>
       </c>
       <c r="H30" s="18">
@@ -9251,15 +9251,15 @@
         <v>21</v>
       </c>
       <c r="E31" s="25">
-        <f>+[26]Main!$H$2</f>
+        <f>+[30]Main!$H$2</f>
         <v>338.01</v>
       </c>
       <c r="F31" s="18">
-        <f>+[26]Main!$H$4</f>
+        <f>+[30]Main!$H$4</f>
         <v>20461.91295813</v>
       </c>
       <c r="G31" s="18">
-        <f>+[26]Main!$H$6-[26]Main!$H$5</f>
+        <f>+[30]Main!$H$6-[30]Main!$H$5</f>
         <v>-1012.5000000000002</v>
       </c>
       <c r="H31" s="18">
@@ -9345,15 +9345,15 @@
         <v>454</v>
       </c>
       <c r="E32" s="25">
-        <f>+[27]Main!$K$2</f>
+        <f>+[31]Main!$K$2</f>
         <v>76.739999999999995</v>
       </c>
       <c r="F32" s="18">
-        <f>+[27]Main!$K$4*FX!C9</f>
+        <f>+[31]Main!$K$4*FX!C9</f>
         <v>12537.781199999999</v>
       </c>
       <c r="G32" s="18">
-        <f>+([27]Main!$K$6-[27]Main!$K$5)*FX!C9</f>
+        <f>+([31]Main!$K$6-[31]Main!$K$5)*FX!C9</f>
         <v>-745.22328020000009</v>
       </c>
       <c r="H32" s="18">
@@ -9408,15 +9408,15 @@
         <v>82</v>
       </c>
       <c r="E33" s="25">
-        <f>+[28]Main!$I$2</f>
+        <f>+[32]Main!$I$2</f>
         <v>23.62</v>
       </c>
       <c r="F33" s="18">
-        <f>+[28]Main!$I$4*FX!C3</f>
+        <f>+[32]Main!$I$4*FX!C3</f>
         <v>6396.6739200000002</v>
       </c>
       <c r="G33" s="18">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
+        <f>+([32]Main!$I$6-[32]Main!$I$5)*FX!C3</f>
         <v>-1142.7520000000002</v>
       </c>
       <c r="H33" s="18">
@@ -9471,15 +9471,15 @@
         <v>21</v>
       </c>
       <c r="E34" s="25">
-        <f>+[29]Main!$H$2</f>
+        <f>+[33]Main!$H$2</f>
         <v>20.3</v>
       </c>
       <c r="F34" s="18">
-        <f>+[29]Main!$H$4</f>
+        <f>+[33]Main!$H$4</f>
         <v>7942.6458629000008</v>
       </c>
       <c r="G34" s="18">
-        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
+        <f>+[33]Main!$H$6-[33]Main!$H$5</f>
         <v>2689.1809999999996</v>
       </c>
       <c r="H34" s="18">
@@ -9534,15 +9534,15 @@
         <v>82</v>
       </c>
       <c r="E35" s="25">
-        <f>+[30]Main!$I$3</f>
+        <f>+[34]Main!$I$3</f>
         <v>33.710999999999999</v>
       </c>
       <c r="F35" s="18">
-        <f>+[30]Main!$I$5*FX!C3</f>
+        <f>+[34]Main!$I$5*FX!C3</f>
         <v>6447.6433359686407</v>
       </c>
       <c r="G35" s="18">
-        <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
+        <f>+([34]Main!$I$7-[34]Main!$I$6)*FX!C3</f>
         <v>947.42023999999992</v>
       </c>
       <c r="H35" s="18">
@@ -9597,15 +9597,15 @@
         <v>21</v>
       </c>
       <c r="E36" s="25">
-        <f>+[31]Main!$J$2</f>
+        <f>+[35]Main!$J$2</f>
         <v>25.5</v>
       </c>
       <c r="F36" s="18">
-        <f>+[31]Main!$J$4</f>
+        <f>+[35]Main!$J$4</f>
         <v>9484.0043700000006</v>
       </c>
       <c r="G36" s="18">
-        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
+        <f>+([35]Main!$J$6-[35]Main!$J$5)</f>
         <v>-1026</v>
       </c>
       <c r="H36" s="18">
@@ -9672,15 +9672,15 @@
         <v>21</v>
       </c>
       <c r="E37" s="25">
-        <f>+[32]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>60.4</v>
       </c>
       <c r="F37" s="18">
-        <f>+[32]Main!$I$4</f>
+        <f>+[36]Main!$I$4</f>
         <v>9118.7085583999997</v>
       </c>
       <c r="G37" s="18">
-        <f>+[32]Main!$I$6-[32]Main!$I$5</f>
+        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
         <v>-838.96200000000022</v>
       </c>
       <c r="H37" s="18">
@@ -9735,15 +9735,15 @@
         <v>165</v>
       </c>
       <c r="E38" s="25">
-        <f>+[33]Main!$J$2</f>
+        <f>+[37]Main!$J$2</f>
         <v>86.1</v>
       </c>
       <c r="F38" s="18">
-        <f>+[33]Main!$J$4*FX!C3</f>
+        <f>+[37]Main!$J$4*FX!C3</f>
         <v>6088.4257237439997</v>
       </c>
       <c r="G38" s="18">
-        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
+        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C3</f>
         <v>200.49328000000006</v>
       </c>
       <c r="H38" s="18">
@@ -9798,15 +9798,15 @@
         <v>107</v>
       </c>
       <c r="E39" s="25">
-        <f>+[34]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>60</v>
       </c>
       <c r="F39" s="18">
-        <f>+[34]Main!$I$4</f>
+        <f>+[38]Main!$I$4</f>
         <v>8953.7999999999993</v>
       </c>
       <c r="G39" s="18">
-        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
+        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
         <v>1641.587</v>
       </c>
       <c r="H39" s="18">
@@ -9861,15 +9861,15 @@
         <v>21</v>
       </c>
       <c r="E40" s="25">
-        <f>+[35]Main!$I$2</f>
+        <f>+[39]Main!$I$2</f>
         <v>21.96</v>
       </c>
       <c r="F40" s="18">
-        <f>+[35]Main!$I$4</f>
+        <f>+[39]Main!$I$4</f>
         <v>8574.6616225199996</v>
       </c>
       <c r="G40" s="18">
-        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
+        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
         <v>190.40000000000009</v>
       </c>
       <c r="H40" s="18">
@@ -9936,15 +9936,15 @@
         <v>294</v>
       </c>
       <c r="E41" s="25">
-        <f>+[36]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>17550</v>
       </c>
       <c r="F41" s="18">
-        <f>+[36]Main!$I$4*FX!C11</f>
+        <f>+[40]Main!$I$4*FX!C11</f>
         <v>8142.7173750000002</v>
       </c>
       <c r="G41" s="18">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
+        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C11</f>
         <v>171.25</v>
       </c>
       <c r="H41" s="18">
@@ -9995,15 +9995,15 @@
         <v>454</v>
       </c>
       <c r="E42" s="25">
-        <f>+[37]Main!$J$2</f>
+        <f>+[41]Main!$J$2</f>
         <v>8.7799999999999994</v>
       </c>
       <c r="F42" s="18">
-        <f>+[37]Main!$J$4*FX!C9</f>
+        <f>+[41]Main!$J$4*FX!C9</f>
         <v>5900.1600000000008</v>
       </c>
       <c r="G42" s="18">
-        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C9</f>
+        <f>+([41]Main!$J$6-[41]Main!$J$5)*FX!C9</f>
         <v>-679.00000000000011</v>
       </c>
       <c r="H42" s="18">
@@ -10054,15 +10054,15 @@
         <v>185</v>
       </c>
       <c r="E43" s="25">
-        <f>+[38]Main!$H$2</f>
+        <f>+[42]Main!$H$2</f>
         <v>41240</v>
       </c>
       <c r="F43" s="18">
-        <f>+[38]Main!$H$4*FX!C12</f>
+        <f>+[42]Main!$H$4*FX!C12</f>
         <v>5059.9509140399996</v>
       </c>
       <c r="G43" s="18">
-        <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
+        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C12</f>
         <v>79.99563000000002</v>
       </c>
       <c r="H43" s="18">
@@ -10113,15 +10113,15 @@
         <v>21</v>
       </c>
       <c r="E44" s="25">
-        <f>+[39]Main!$H$2</f>
+        <f>+[43]Main!$H$2</f>
         <v>99.2</v>
       </c>
       <c r="F44" s="18">
-        <f>+[39]Main!$H$4</f>
+        <f>+[43]Main!$H$4</f>
         <v>5094.5152000000007</v>
       </c>
       <c r="G44" s="18">
-        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
+        <f>+[43]Main!$H$6-[43]Main!$H$5</f>
         <v>1100.5309999999999</v>
       </c>
       <c r="H44" s="18">
@@ -10176,15 +10176,15 @@
         <v>325</v>
       </c>
       <c r="E45" s="25">
-        <f>+[40]Main!$I$2</f>
+        <f>+[44]Main!$I$2</f>
         <v>27.8</v>
       </c>
       <c r="F45" s="18">
-        <f>+[40]Main!$I$4*FX!C14</f>
+        <f>+[44]Main!$I$4*FX!C14</f>
         <v>5512.4063999999998</v>
       </c>
       <c r="G45" s="18">
-        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C14</f>
+        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C14</f>
         <v>392.36399999999998</v>
       </c>
       <c r="H45" s="18">
@@ -10239,15 +10239,15 @@
         <v>219</v>
       </c>
       <c r="E46" s="25">
-        <f>+[41]Main!$I$2</f>
+        <f>+[45]Main!$I$2</f>
         <v>0.93779999999999997</v>
       </c>
       <c r="F46" s="18">
-        <f>+[41]Main!$I$4*FX!C8</f>
+        <f>+[45]Main!$I$4*FX!C8</f>
         <v>5962.0447439999998</v>
       </c>
       <c r="G46" s="18">
-        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
+        <f>+([45]Main!$I$6-[45]Main!$I$5)*FX!C8</f>
         <v>155</v>
       </c>
       <c r="H46" s="18">
@@ -10302,15 +10302,15 @@
         <v>107</v>
       </c>
       <c r="E47" s="25">
-        <f>+[42]Main!$H$2</f>
+        <f>+[46]Main!$H$2</f>
         <v>86.42</v>
       </c>
       <c r="F47" s="18">
-        <f>+[42]Main!$H$4*FX!C13</f>
+        <f>+[46]Main!$H$4*FX!C13</f>
         <v>6825.0480185999995</v>
       </c>
       <c r="G47" s="18">
-        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
+        <f>+([46]Main!$H$6-[46]Main!$H$5)*FX!C13</f>
         <v>-201.90158999999997</v>
       </c>
       <c r="H47" s="18">
@@ -10361,15 +10361,15 @@
         <v>454</v>
       </c>
       <c r="E48" s="25">
-        <f>+[43]Main!$H$2</f>
+        <f>+[47]Main!$H$2</f>
         <v>16.02</v>
       </c>
       <c r="F48" s="18">
-        <f>+[43]Main!$H$5*FX!C9</f>
+        <f>+[47]Main!$H$5*FX!C9</f>
         <v>5313.5769879360005</v>
       </c>
       <c r="G48" s="18">
-        <f>+([43]Main!$H$7-[43]Main!$H$6)*FX!C9</f>
+        <f>+([47]Main!$H$7-[47]Main!$H$6)*FX!C9</f>
         <v>-2458.0551799999998</v>
       </c>
       <c r="H48" s="18">
@@ -10422,15 +10422,15 @@
         <v>454</v>
       </c>
       <c r="E49" s="25">
-        <f>+[44]Main!$I$2</f>
+        <f>+[48]Main!$I$2</f>
         <v>8.01</v>
       </c>
       <c r="F49" s="18">
-        <f>+[44]Main!$I$4*FX!C9</f>
+        <f>+[48]Main!$I$4*FX!C9</f>
         <v>5141.5464790620008</v>
       </c>
       <c r="G49" s="18">
-        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C9</f>
+        <f>+([48]Main!$I$6-[48]Main!$I$5)*FX!C9</f>
         <v>1697.6221653999999</v>
       </c>
       <c r="H49" s="18">
@@ -10479,15 +10479,15 @@
         <v>21</v>
       </c>
       <c r="E50" s="25">
-        <f>+[45]Main!$J$2</f>
+        <f>+[49]Main!$J$2</f>
         <v>65.5</v>
       </c>
       <c r="F50" s="18">
-        <f>+[45]Main!$J$4</f>
+        <f>+[49]Main!$J$4</f>
         <v>5874.7799535000004</v>
       </c>
       <c r="G50" s="18">
-        <f>+[45]Main!$J$6-[45]Main!$J$5</f>
+        <f>+[49]Main!$J$6-[49]Main!$J$5</f>
         <v>-695.93000000000006</v>
       </c>
       <c r="H50" s="18">
@@ -10538,15 +10538,15 @@
         <v>82</v>
       </c>
       <c r="E51" s="25">
-        <f>+[46]Main!$I$2</f>
+        <f>+[50]Main!$I$2</f>
         <v>24.05</v>
       </c>
       <c r="F51" s="18">
-        <f>+[46]Main!$I$4*FX!C3</f>
+        <f>+[50]Main!$I$4*FX!C3</f>
         <v>3687.0189200000004</v>
       </c>
       <c r="G51" s="18">
-        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
+        <f>+([50]Main!$I$6-[50]Main!$I$5)*FX!C3</f>
         <v>293.28000000000003</v>
       </c>
       <c r="H51" s="18">
@@ -10601,15 +10601,15 @@
         <v>454</v>
       </c>
       <c r="E52" s="25">
-        <f>+[47]Main!$I$2</f>
+        <f>+[51]Main!$I$2</f>
         <v>3.75</v>
       </c>
       <c r="F52" s="18">
-        <f>+[47]Main!$I$5*FX!C9</f>
+        <f>+[51]Main!$I$5*FX!C9</f>
         <v>5271.5025720000003</v>
       </c>
       <c r="G52" s="18">
-        <f>+([47]Main!$I$7-[47]Main!$I$6)*FX!C9</f>
+        <f>+([51]Main!$I$7-[51]Main!$I$6)*FX!C9</f>
         <v>-653.85012000000006</v>
       </c>
       <c r="H52" s="18">
@@ -10664,15 +10664,15 @@
         <v>21</v>
       </c>
       <c r="E53" s="25">
-        <f>+[48]Main!$I$2</f>
+        <f>+[52]Main!$I$2</f>
         <v>95.69</v>
       </c>
       <c r="F53" s="18">
-        <f>+[48]Main!$I$4</f>
+        <f>+[52]Main!$I$4</f>
         <v>4527.9551099999999</v>
       </c>
       <c r="G53" s="18">
-        <f>+[48]Main!$I$6-[48]Main!$I$5</f>
+        <f>+[52]Main!$I$6-[52]Main!$I$5</f>
         <v>-784.57600000000002</v>
       </c>
       <c r="H53" s="18">
@@ -10739,15 +10739,15 @@
         <v>21</v>
       </c>
       <c r="E54" s="25">
-        <f>+[49]Main!$I$2</f>
+        <f>+[53]Main!$I$2</f>
         <v>55.02</v>
       </c>
       <c r="F54" s="18">
-        <f>+[49]Main!$I$4</f>
+        <f>+[53]Main!$I$4</f>
         <v>2880.3823910400001</v>
       </c>
       <c r="G54" s="18">
-        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
+        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
         <v>-790.7940000000001</v>
       </c>
       <c r="H54" s="18">
@@ -10802,15 +10802,15 @@
         <v>21</v>
       </c>
       <c r="E55" s="25">
-        <f>+[50]Main!$J$2</f>
+        <f>+[54]Main!$J$2</f>
         <v>76.37</v>
       </c>
       <c r="F55" s="18">
-        <f>+[50]Main!$J$4</f>
+        <f>+[54]Main!$J$4</f>
         <v>3497.9518935199999</v>
       </c>
       <c r="G55" s="18">
-        <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
+        <f>+([54]Main!$J$6-[54]Main!$J$5)</f>
         <v>2100.6</v>
       </c>
       <c r="H55" s="18">
@@ -10865,15 +10865,15 @@
         <v>124</v>
       </c>
       <c r="E56" s="25">
-        <f>+[51]Main!$I$2</f>
+        <f>+[55]Main!$I$2</f>
         <v>2816.5</v>
       </c>
       <c r="F56" s="18">
-        <f>+[51]Main!$I$4*FX!C5</f>
+        <f>+[55]Main!$I$4*FX!C5</f>
         <v>4393.7011297651507</v>
       </c>
       <c r="G56" s="18">
-        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
+        <f>+([55]Main!$I$6-[55]Main!$I$5)*FX!C5</f>
         <v>-837.64170000000001</v>
       </c>
       <c r="H56" s="18">
@@ -10928,15 +10928,15 @@
         <v>219</v>
       </c>
       <c r="E57" s="25">
-        <f>+[52]Main!$I$2</f>
+        <f>+[56]Main!$I$2</f>
         <v>11.96</v>
       </c>
       <c r="F57" s="18">
-        <f>+[52]Main!$I$4*FX!C3</f>
+        <f>+[56]Main!$I$4*FX!C3</f>
         <v>4482.79936</v>
       </c>
       <c r="G57" s="18">
-        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
+        <f>+([56]Main!$I$6-[56]Main!$I$5)*FX!C3</f>
         <v>96.72</v>
       </c>
       <c r="H57" s="18">
@@ -10987,15 +10987,15 @@
         <v>21</v>
       </c>
       <c r="E58" s="25">
-        <f>+[53]Main!$I$2</f>
+        <f>+[57]Main!$I$2</f>
         <v>165.1</v>
       </c>
       <c r="F58" s="18">
-        <f>+[53]Main!$I$4</f>
+        <f>+[57]Main!$I$4</f>
         <v>5044.7333572999996</v>
       </c>
       <c r="G58" s="18">
-        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
+        <f>+[57]Main!$I$6-[57]Main!$I$5</f>
         <v>-95.319000000000003</v>
       </c>
       <c r="H58" s="18">
@@ -11050,15 +11050,15 @@
         <v>21</v>
       </c>
       <c r="E59" s="25">
-        <f>+[54]Main!$I$2</f>
+        <f>+[58]Main!$I$2</f>
         <v>78.680000000000007</v>
       </c>
       <c r="F59" s="18">
-        <f>+[54]Main!$I$4</f>
+        <f>+[58]Main!$I$4</f>
         <v>4372.5807311200006</v>
       </c>
       <c r="G59" s="18">
-        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
+        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
         <v>1259.028</v>
       </c>
       <c r="H59" s="18">
@@ -11160,15 +11160,15 @@
         <v>433</v>
       </c>
       <c r="E61" s="25">
-        <f>+[55]Main!$J$2</f>
+        <f>+[59]Main!$J$2</f>
         <v>132.5</v>
       </c>
       <c r="F61" s="18">
-        <f>+[55]Main!$J$4*FX!C15</f>
+        <f>+[59]Main!$J$4*FX!C15</f>
         <v>3925.244925</v>
       </c>
       <c r="G61" s="18">
-        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
+        <f>+([59]Main!$J$6-[59]Main!$J$5)*FX!C15</f>
         <v>122.75229000000002</v>
       </c>
       <c r="H61" s="18">
@@ -11217,15 +11217,15 @@
         <v>21</v>
       </c>
       <c r="E62" s="25">
-        <f>+[56]Main!$J$2</f>
+        <f>+[60]Main!$J$2</f>
         <v>161.28</v>
       </c>
       <c r="F62" s="18">
-        <f>+[56]Main!$J$4</f>
+        <f>+[60]Main!$J$4</f>
         <v>2990.6024601600002</v>
       </c>
       <c r="G62" s="18">
-        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
+        <f>+[60]Main!$J$6-[60]Main!$J$5</f>
         <v>-211.91</v>
       </c>
       <c r="H62" s="18">
@@ -11276,15 +11276,15 @@
         <v>82</v>
       </c>
       <c r="E63" s="25">
-        <f>+[57]Main!$J$2</f>
+        <f>+[61]Main!$J$2</f>
         <v>36.299999999999997</v>
       </c>
       <c r="F63" s="18">
-        <f>+[57]Main!$J$4*FX!C3</f>
+        <f>+[61]Main!$J$4*FX!C3</f>
         <v>2605.4984498399999</v>
       </c>
       <c r="G63" s="18">
-        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
+        <f>+([61]Main!$J$6-[61]Main!$J$5)*FX!C3</f>
         <v>-49.250239999999998</v>
       </c>
       <c r="H63" s="18">
@@ -11335,15 +11335,15 @@
         <v>21</v>
       </c>
       <c r="E64" s="25">
-        <f>+[58]Main!$I$2</f>
+        <f>+[62]Main!$I$2</f>
         <v>7.47</v>
       </c>
       <c r="F64" s="18">
-        <f>+[58]Main!$I$4</f>
+        <f>+[62]Main!$I$4</f>
         <v>3181.39830747</v>
       </c>
       <c r="G64" s="18">
-        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
+        <f>+[62]Main!$I$6-[62]Main!$I$5</f>
         <v>525.08299999999997</v>
       </c>
       <c r="H64" s="18">
@@ -11394,15 +11394,15 @@
         <v>21</v>
       </c>
       <c r="E65" s="25">
-        <f>+[59]Main!$I$2</f>
+        <f>+[63]Main!$I$2</f>
         <v>14.35</v>
       </c>
       <c r="F65" s="18">
-        <f>+[59]Main!$I$4</f>
+        <f>+[63]Main!$I$4</f>
         <v>2756.6605860499999</v>
       </c>
       <c r="G65" s="18">
-        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
+        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
         <v>-160.19499999999999</v>
       </c>
       <c r="H65" s="18">
@@ -11453,15 +11453,15 @@
         <v>185</v>
       </c>
       <c r="E66" s="25">
-        <f>+[60]Main!$I$2</f>
+        <f>+[64]Main!$I$2</f>
         <v>263.45</v>
       </c>
       <c r="F66" s="18">
-        <f>+[60]Main!$I$4*FX!C12</f>
+        <f>+[64]Main!$I$4*FX!C12</f>
         <v>2976.4027894628493</v>
       </c>
       <c r="G66" s="18">
-        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
+        <f>+([64]Main!$I$6-[64]Main!$I$5)*FX!C12</f>
         <v>26.92503</v>
       </c>
       <c r="H66" s="18">
@@ -11510,15 +11510,15 @@
         <v>21</v>
       </c>
       <c r="E67" s="25">
-        <f>+[61]Main!$I$2</f>
+        <f>+[65]Main!$I$2</f>
         <v>54.91</v>
       </c>
       <c r="F67" s="18">
-        <f>+[61]Main!$I$4</f>
+        <f>+[65]Main!$I$4</f>
         <v>4407.5666168399994</v>
       </c>
       <c r="G67" s="18">
-        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
+        <f>+[65]Main!$I$6-[65]Main!$I$5</f>
         <v>1102</v>
       </c>
       <c r="H67" s="18">
@@ -11573,15 +11573,15 @@
         <v>21</v>
       </c>
       <c r="E68" s="25">
-        <f>+[62]Main!$H$2</f>
+        <f>+[66]Main!$H$2</f>
         <v>33.92</v>
       </c>
       <c r="F68" s="18">
-        <f>+[62]Main!$H$4</f>
+        <f>+[66]Main!$H$4</f>
         <v>2464.3691366400003</v>
       </c>
       <c r="G68" s="18">
-        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
+        <f>+[66]Main!$H$6-[66]Main!$H$5</f>
         <v>182.17599999999999</v>
       </c>
       <c r="H68" s="18">
@@ -11632,15 +11632,15 @@
         <v>219</v>
       </c>
       <c r="E69" s="25">
-        <f>+[63]Main!$I$2</f>
+        <f>+[67]Main!$I$2</f>
         <v>19.670000000000002</v>
       </c>
       <c r="F69" s="18">
-        <f>+[63]Main!$I$4</f>
+        <f>+[67]Main!$I$4</f>
         <v>2341.6752811900001</v>
       </c>
       <c r="G69" s="18">
-        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
+        <f>+[67]Main!$I$6-[67]Main!$I$5</f>
         <v>1542</v>
       </c>
       <c r="H69" s="18">
@@ -11695,15 +11695,15 @@
         <v>165</v>
       </c>
       <c r="E70" s="25">
-        <f>+[64]Main!$J$2</f>
+        <f>+[68]Main!$J$2</f>
         <v>9.6300000000000008</v>
       </c>
       <c r="F70" s="18">
-        <f>+[64]Main!$J$4*FX!C3</f>
+        <f>+[68]Main!$J$4*FX!C3</f>
         <v>2534.083861608</v>
       </c>
       <c r="G70" s="18">
-        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
+        <f>+([68]Main!$J$6-[68]Main!$J$5)*FX!C3</f>
         <v>122.12512000000007</v>
       </c>
       <c r="H70" s="18">
@@ -11754,15 +11754,15 @@
         <v>185</v>
       </c>
       <c r="E71" s="25">
-        <f>+[65]Main!$J$2</f>
+        <f>+[69]Main!$J$2</f>
         <v>828.4</v>
       </c>
       <c r="F71" s="18">
-        <f>+[65]Main!$J$4*FX!C12</f>
+        <f>+[69]Main!$J$4*FX!C12</f>
         <v>2214.6636811287999</v>
       </c>
       <c r="G71" s="18">
-        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
+        <f>+([69]Main!$J$6-[69]Main!$J$5)*FX!C12</f>
         <v>-1.8833099999999996</v>
       </c>
       <c r="H71" s="18">
@@ -12264,15 +12264,15 @@
         <v>21</v>
       </c>
       <c r="E83" s="25">
-        <f>+[66]Main!$I$2</f>
+        <f>+[70]Main!$I$2</f>
         <v>5.82</v>
       </c>
       <c r="F83" s="18">
-        <f>+[66]Main!$I$4</f>
+        <f>+[70]Main!$I$4</f>
         <v>2055.0937514400002</v>
       </c>
       <c r="G83" s="18">
-        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
+        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
         <v>1971.2029999999997</v>
       </c>
       <c r="H83" s="18">
@@ -12532,15 +12532,15 @@
         <v>21</v>
       </c>
       <c r="E89" s="25">
-        <f>+[67]Main!$H$2</f>
+        <f>+[71]Main!$H$2</f>
         <v>41.42</v>
       </c>
       <c r="F89" s="18">
-        <f>+[67]Main!$H$4</f>
+        <f>+[71]Main!$H$4</f>
         <v>1491.5652650000002</v>
       </c>
       <c r="G89" s="18">
-        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
+        <f>+[71]Main!$H$6-[71]Main!$H$5</f>
         <v>85.194000000000017</v>
       </c>
       <c r="H89" s="18">
@@ -12589,15 +12589,15 @@
         <v>21</v>
       </c>
       <c r="E90" s="25">
-        <f>+[68]Main!$I$2</f>
+        <f>+[72]Main!$I$2</f>
         <v>38.119999999999997</v>
       </c>
       <c r="F90" s="18">
-        <f>+[68]Main!$I$4</f>
+        <f>+[72]Main!$I$4</f>
         <v>1935.4971035199997</v>
       </c>
       <c r="G90" s="18">
-        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
+        <f>+[72]Main!$I$6-[72]Main!$I$5</f>
         <v>-325.44000000000005</v>
       </c>
       <c r="H90" s="18">
@@ -12646,15 +12646,15 @@
         <v>21</v>
       </c>
       <c r="E91" s="25">
-        <f>+[69]Main!$I$2</f>
+        <f>+[73]Main!$I$2</f>
         <v>24.73</v>
       </c>
       <c r="F91" s="18">
-        <f>+[69]Main!$I$4</f>
+        <f>+[73]Main!$I$4</f>
         <v>1761.5194085300002</v>
       </c>
       <c r="G91" s="18">
-        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
+        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
         <v>-256.60000000000002</v>
       </c>
       <c r="H91" s="18">
@@ -12836,15 +12836,15 @@
         <v>21</v>
       </c>
       <c r="E95" s="25">
-        <f>+[70]Main!$I$2</f>
+        <f>+[74]Main!$I$2</f>
         <v>27.07</v>
       </c>
       <c r="F95" s="18">
-        <f>+[70]Main!$I$4</f>
+        <f>+[74]Main!$I$4</f>
         <v>1188.01315849</v>
       </c>
       <c r="G95" s="18">
-        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
+        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
         <v>119.48899999999998</v>
       </c>
       <c r="H95" s="18">
@@ -12893,15 +12893,15 @@
         <v>21</v>
       </c>
       <c r="E96" s="25">
-        <f>+[71]Main!$I$2</f>
+        <f>+[75]Main!$I$2</f>
         <v>59.85</v>
       </c>
       <c r="F96" s="18">
-        <f>+[71]Main!$I$4</f>
+        <f>+[75]Main!$I$4</f>
         <v>939.70682505000002</v>
       </c>
       <c r="G96" s="18">
-        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
+        <f>+[75]Main!$I$6-[75]Main!$I$5</f>
         <v>50.789000000000001</v>
       </c>
       <c r="H96" s="18">
@@ -12950,15 +12950,15 @@
         <v>107</v>
       </c>
       <c r="E97" s="25">
-        <f>+[72]Main!$J$2</f>
+        <f>+[76]Main!$J$2</f>
         <v>14.56</v>
       </c>
       <c r="F97" s="18">
-        <f>+[72]Main!$J$4*FX!C13</f>
+        <f>+[76]Main!$J$4*FX!C13</f>
         <v>975.38578737599994</v>
       </c>
       <c r="G97" s="18">
-        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
+        <f>+([76]Main!$J$6-[76]Main!$J$5)*FX!C13</f>
         <v>47.058000000000028</v>
       </c>
       <c r="H97" s="18">
@@ -13095,15 +13095,15 @@
         <v>21</v>
       </c>
       <c r="E100" s="25">
-        <f>+[73]Main!$I$2</f>
+        <f>+[77]Main!$I$2</f>
         <v>4.53</v>
       </c>
       <c r="F100" s="18">
-        <f>+[73]Main!$I$4</f>
+        <f>+[77]Main!$I$4</f>
         <v>736.21656488999997</v>
       </c>
       <c r="G100" s="18">
-        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
+        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
         <v>-235.51</v>
       </c>
       <c r="H100" s="18">
@@ -13152,15 +13152,15 @@
         <v>21</v>
       </c>
       <c r="E101" s="25">
-        <f>+[74]Main!$I$2</f>
+        <f>+[78]Main!$I$2</f>
         <v>16.75</v>
       </c>
       <c r="F101" s="18">
-        <f>+[74]Main!$I$4</f>
+        <f>+[78]Main!$I$4</f>
         <v>872.38125524999998</v>
       </c>
       <c r="G101" s="18">
-        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
+        <f>+[78]Main!$I$6-[78]Main!$I$5</f>
         <v>434.077</v>
       </c>
       <c r="H101" s="18">
@@ -13811,22 +13811,24 @@
         <v>219</v>
       </c>
       <c r="E116" s="25">
-        <f>+'[75]Main '!$F$2</f>
-        <v>4.3620000000000001</v>
+        <f>+'[79]Main '!$F$2</f>
+        <v>2.4350000000000001</v>
       </c>
       <c r="F116" s="18">
-        <f>+'[75]Main '!$F$4*FX!C8</f>
-        <v>644.11734022080009</v>
+        <f>+'[79]Main '!$F$4*FX!C8</f>
+        <v>360.19879762439996</v>
       </c>
       <c r="G116" s="18">
-        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
-        <v>368.40400000000005</v>
+        <f>+('[79]Main '!$F$6-'[79]Main '!$F$5)*FX!C8</f>
+        <v>229.02800000000005</v>
       </c>
       <c r="H116" s="18">
         <f>+F116+G116</f>
-        <v>1012.5213402208001</v>
-      </c>
-      <c r="I116" s="17"/>
+        <v>589.22679762439998</v>
+      </c>
+      <c r="I116" s="17" t="s">
+        <v>422</v>
+      </c>
       <c r="J116" s="3"/>
       <c r="K116" s="25"/>
       <c r="L116" s="22"/>
@@ -14124,15 +14126,15 @@
         <v>21</v>
       </c>
       <c r="E123" s="25">
-        <f>+[76]Main!$H$2</f>
+        <f>+[80]Main!$H$2</f>
         <v>0.98</v>
       </c>
       <c r="F123" s="18">
-        <f>+[76]Main!$H$4</f>
+        <f>+[80]Main!$H$4</f>
         <v>97.21301296</v>
       </c>
       <c r="G123" s="18">
-        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
+        <f>+[80]Main!$H$6-[80]Main!$H$5</f>
         <v>274.101</v>
       </c>
       <c r="H123" s="18">
@@ -14224,15 +14226,15 @@
         <v>21</v>
       </c>
       <c r="E125" s="25">
-        <f>+[77]Main!$I$2</f>
+        <f>+[81]Main!$I$2</f>
         <v>17.79</v>
       </c>
       <c r="F125" s="18">
-        <f>+[77]Main!$I$4</f>
+        <f>+[81]Main!$I$4</f>
         <v>270.90115659000003</v>
       </c>
       <c r="G125" s="18">
-        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
+        <f>+[81]Main!$I$6-[81]Main!$I$5</f>
         <v>24.493000000000002</v>
       </c>
       <c r="H125" s="18">
@@ -15485,15 +15487,15 @@
         <v>124</v>
       </c>
       <c r="E154" s="25">
-        <f>+[78]Main!$I$2</f>
+        <f>+[82]Main!$I$2</f>
         <v>2540</v>
       </c>
       <c r="F154" s="18">
-        <f>+[78]Main!$I$4*FX!C5</f>
+        <f>+[82]Main!$I$4*FX!C5</f>
         <v>409.27593709799999</v>
       </c>
       <c r="G154" s="18">
-        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
+        <f>+([82]Main!$I$6-[82]Main!$I$5)*FX!C5</f>
         <v>-123.31619999999999</v>
       </c>
       <c r="H154" s="18">
@@ -15542,15 +15544,15 @@
         <v>21</v>
       </c>
       <c r="E155" s="25">
-        <f>+[79]Main!$J$2</f>
+        <f>+[83]Main!$J$2</f>
         <v>20</v>
       </c>
       <c r="F155" s="18">
-        <f>+[79]Main!$J$4</f>
+        <f>+[83]Main!$J$4</f>
         <v>1638</v>
       </c>
       <c r="G155" s="18">
-        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
+        <f>+[83]Main!$J$6-[83]Main!$J$5</f>
         <v>415.40000000000003</v>
       </c>
       <c r="H155" s="18">
@@ -21270,15 +21272,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="46">
-        <f>+[80]Main!$J$2</f>
+        <f>+[84]Main!$J$2</f>
         <v>180.8</v>
       </c>
       <c r="F20" s="57">
-        <f>+[80]Main!$J$4</f>
+        <f>+[84]Main!$J$4</f>
         <v>14437.908028799999</v>
       </c>
       <c r="G20" s="57">
-        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
+        <f>+[84]Main!$J$6-[84]Main!$J$5</f>
         <v>-205.72299999999996</v>
       </c>
       <c r="H20" s="57">
@@ -39990,15 +39992,15 @@
         <v>20</v>
       </c>
       <c r="E4" s="59">
-        <f>+[81]Main!$I$2</f>
+        <f>+[1]Main!$I$2</f>
         <v>233</v>
       </c>
       <c r="F4" s="57">
-        <f>+[81]Main!$I$4*FX!C3</f>
+        <f>+[1]Main!$I$4*FX!C3</f>
         <v>111229.45403231999</v>
       </c>
       <c r="G4" s="57">
-        <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
+        <f>+([1]Main!$I$6-[1]Main!$I$5)*FX!C3</f>
         <v>7586.8</v>
       </c>
       <c r="H4" s="57">
@@ -40056,15 +40058,15 @@
         <v>85</v>
       </c>
       <c r="E5" s="59">
-        <f>+[82]Main!$J$2</f>
+        <f>+[2]Main!$J$2</f>
         <v>138.30000000000001</v>
       </c>
       <c r="F5" s="57">
-        <f>+[82]Main!$J$5*FX!C7</f>
+        <f>+[2]Main!$J$5*FX!C7</f>
         <v>96477.902976000012</v>
       </c>
       <c r="G5" s="57">
-        <f>+([82]Main!$J$7-[82]Main!$J$6)*FX!C7</f>
+        <f>+([2]Main!$J$7-[2]Main!$J$6)*FX!C7</f>
         <v>-1444.8000000000002</v>
       </c>
       <c r="H5" s="57">
@@ -40122,15 +40124,15 @@
         <v>21</v>
       </c>
       <c r="E6" s="59">
-        <f>+[83]Main!$K$2</f>
+        <f>+[3]Main!$K$2</f>
         <v>111.2</v>
       </c>
       <c r="F6" s="57">
-        <f>+[83]Main!$K$4</f>
+        <f>+[3]Main!$K$4</f>
         <v>40224.047181599999</v>
       </c>
       <c r="G6" s="57">
-        <f>+([83]Main!$K$6-[83]Main!$K$5)</f>
+        <f>+([3]Main!$K$6-[3]Main!$K$5)</f>
         <v>4240</v>
       </c>
       <c r="H6" s="57">
@@ -40188,15 +40190,15 @@
         <v>85</v>
       </c>
       <c r="E7" s="59">
-        <f>+[84]Main!$I$3</f>
+        <f>+[4]Main!$I$3</f>
         <v>177.95</v>
       </c>
       <c r="F7" s="57">
-        <f>+[84]Main!$I$5*FX!C7</f>
+        <f>+[4]Main!$I$5*FX!C7</f>
         <v>10344.705947284801</v>
       </c>
       <c r="G7" s="57">
-        <f>+([84]Main!$I$7-[84]Main!$I$6)*FX!C7</f>
+        <f>+([4]Main!$I$7-[4]Main!$I$6)*FX!C7</f>
         <v>-1336.16</v>
       </c>
       <c r="H7" s="57">

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183BF855-A79E-4E1D-997C-9C79F806F5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0765C58A-6532-4F86-A0D3-B6F49DCB31C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="869">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2754,6 +2754,18 @@
   </si>
   <si>
     <t>Thierry</t>
+  </si>
+  <si>
+    <t>American Exchange Group</t>
+  </si>
+  <si>
+    <t>American Exchane Group</t>
+  </si>
+  <si>
+    <t>Allbirds</t>
+  </si>
+  <si>
+    <t>Brands: Ed Hardy, Allbirds etc.</t>
   </si>
 </sst>
 </file>
@@ -2767,13 +2779,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2964,22 +2982,100 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2993,168 +3089,97 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3184,34 +3209,38 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
       <sheetName val="Model"/>
-      <sheetName val="Quarter"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>233</v>
-          </cell>
-        </row>
         <row r="4">
           <cell r="I4">
-            <v>106951.39810799999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>3544</v>
+            <v>549</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>10839</v>
+            <v>273230.13006</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>8794</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>20343</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3229,28 +3258,452 @@
       <sheetName val="Model"/>
       <sheetName val="Ratios"/>
       <sheetName val="DCF"/>
-      <sheetName val="CoC"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>58.85</v>
+        <row r="2">
+          <cell r="I2">
+            <v>156.36000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>17275.07043756</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>87068.574999999997</v>
+            <v>1807.202</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>8345</v>
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.80000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>25319.697396000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1617</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2641</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Brands"/>
+      <sheetName val="Macro"/>
+      <sheetName val="Model"/>
+      <sheetName val="Quart"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="CoC"/>
+      <sheetName val="TradingComps"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>284.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>34917.850457599998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>4313</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>12562</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>80.55</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>208286.331768</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>36456</v>
           </cell>
         </row>
         <row r="7">
-          <cell r="I7">
-            <v>8015</v>
+          <cell r="H7">
+            <v>23302</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="M2">
+            <v>115.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="M4">
+            <v>16366.831656300001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="M5">
+            <v>2086.7460000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>170.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>272336.26679999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>18733</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>20675</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="WACC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>40.880000000000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>12552.5670144</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1261.6759999999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>1732.366</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5221.55</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1856195.55198455</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5"/>
+        </row>
+        <row r="6">
+          <cell r="I6"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarter"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>55.15</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>14919.336445949999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1341.982</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>980.13599999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>252.2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>15870.190913199998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>584.07899999999995</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2035.424</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>2146</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>226551.95815200001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>12239</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>34</v>
           </cell>
         </row>
       </sheetData>
@@ -3263,7 +3716,2195 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>154.69999999999999</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>31321.2152981</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1077.7</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2396.4</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4396</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3141807.6866959999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>112267</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>37500</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>127.35</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>14912.684999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>441.1</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>781.30000000000007</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="KPIs"/>
+      <sheetName val="CoC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41.04</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>10356.130046052</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1019.9</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>59.5</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>40.49</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>22544.952903140002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>652.29999999999995</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>935.09999999999991</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>47.12</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>62332.018625043194</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>25437.420999999998</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>14701.28</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>338.01</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>20461.91295813</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2250.8000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1238.3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>76.739999999999995</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>89555.579999999987</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>6221.5751200000004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>898.55169000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>23.62</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>6150.6480000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1877.4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>778.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>20.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>7942.6458629000008</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1466.4690000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4155.6499999999996</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="J3">
+            <v>52.82</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>164591.95229051998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>10960</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>33.710999999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>6199.6570538160004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>229.227</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>1140.2079999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>25.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>9484.0043700000006</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>2517</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>1491</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financials"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>60.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>9118.7085583999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1467.8490000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>628.88699999999994</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>86.1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5854.2555035999994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>203.84100000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>396.62300000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>60</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>8953.7999999999993</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>112.633</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1754.22</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>21.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>8574.6616225199996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>848.8</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1039.2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>17550</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>32570.869500000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1577</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2262</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>8.7799999999999994</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>42144</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>6390</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>1540</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41240</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>459995.53764</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>45360.78</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>52633.11</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="Coc"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Data"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>99.2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>5094.5152000000007</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>130.35400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1230.885</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>159.05000000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>179090.30000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>6230</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>2869</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>27.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>102081.60000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>4793</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>12059</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>0.93779999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4808.1005999999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>531</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>656</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>86.42</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>9891.3739399999995</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>292.61099999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>16.02</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>37954.121342400002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>17557.536999999997</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>8.01</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>36725.331993300002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>8082.48891</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>20208.361519999999</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>65.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>5874.7799535000004</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>695.93000000000006</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>24.05</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3545.2105000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>290</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>572</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>3.75</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>37653.589800000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5665.9049999999997</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>995.54700000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="WACC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>95.69</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4527.9551099999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>784.57600000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>55.02</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2880.3823910400001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>790.7940000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>471.6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>85081.629528000005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9760</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>22957</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>76.37</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>3497.9518935199999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>158.19999999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2258.7999999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2816.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>697412.87774050003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>138918</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5959</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>11.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4310.384</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>452</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>545</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>165.1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5044.7333572999996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>95.319000000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>78.680000000000007</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4372.5807311200006</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>107.482</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1366.51</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>132.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>130841.4975</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>3309.02</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>7400.7630000000008</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>161.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2990.6024601600002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>211.91</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>36.299999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2505.286971</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>343.12599999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>295.77</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>7.47</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3181.39830747</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>464.64800000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>989.73099999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>14.35</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2756.6605860499999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>160.19499999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+      <sheetName val="CoC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>48.01</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>71078.804999999993</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>8057</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>8029</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>263.45</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270582.07176934998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1259.98</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>3707.71</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>54.91</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4407.5666168399994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>249</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1351</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>33.92</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>2464.3691366400003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>111.31400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>293.49</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>19.670000000000002</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2341.6752811900001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>129</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1671</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>9.6300000000000008</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2436.6190977000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>231.22499999999997</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>348.65300000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>828.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>201333.06192080001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>440.44</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>269.23</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5.82</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2055.0937514400002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>214.85400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2186.0569999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41.42</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>1491.5652650000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>412.92599999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>498.12</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>38.119999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1935.4971035199997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>325.44000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>24.73</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1761.5194085300002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>256.60000000000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3318,7 +5959,407 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>27.07</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1188.01315849</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>104.68600000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>224.17499999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>59.85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>939.70682505000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>7.0270000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>57.816000000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>14.56</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1413.6025904000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>346.9</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>415.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4.53</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>736.21656488999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>245.11399999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>9.6039999999999992</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>16.75</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>872.38125524999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>189.63499999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>623.71199999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main "/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="F2">
+            <v>2.4350000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4">
+            <v>290.48290130999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>318.89999999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>503.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>0.98</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>97.21301296</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>17.213000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>291.31400000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>17.79</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270.90115659000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>45.523000000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>70.016000000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2540</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>64964.434459999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>33044</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>13470</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1638</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>206.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>621.70000000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3333,116 +6374,32 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>187.97</v>
+            <v>170</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>75466.759510000004</v>
+            <v>68068</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>200.84200000000001</v>
+            <v>183.20400000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>2977.279</v>
+            <v>2656.7910000000002</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="H3">
-            <v>176.36</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>56659.177199999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>4061.1729999999998</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1516.972</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>156.36000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>17275.07043756</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1807.202</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3456,23 +6413,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="I2">
-            <v>141.80000000000001</v>
+          <cell r="J2">
+            <v>180.8</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="I4">
-            <v>25319.697396000003</v>
+          <cell r="J4">
+            <v>14437.908028799999</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="I5">
-            <v>1617</v>
+          <cell r="J5">
+            <v>1689.94</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="I6">
-            <v>2641</v>
+          <cell r="J6">
+            <v>1484.2170000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -3482,61 +6439,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Brands"/>
-      <sheetName val="Macro"/>
-      <sheetName val="Model"/>
-      <sheetName val="Quart"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="CoC"/>
-      <sheetName val="TradingComps"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>284.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>34917.850457599998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>4313</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>12562</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3546,117 +6449,39 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Quarter"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="H2">
-            <v>101.6</v>
+          <cell r="I2">
+            <v>233</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>106951.39810799999</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>265357.92597599997</v>
+          <cell r="I5">
+            <v>3544</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>32144</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>24040</v>
+          <cell r="I6">
+            <v>10839</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="M2">
-            <v>115.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="M4">
-            <v>16366.831656300001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="M5">
-            <v>2086.7460000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="M6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>185.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>297628.32315000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>20908</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>20675</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3698,419 +6523,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-      <sheetName val="WACC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>40.880000000000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>12552.5670144</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1261.6759999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1732.366</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5221.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1856195.55198455</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5"/>
-        </row>
-        <row r="6">
-          <cell r="I6"/>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarter"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>55.15</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>14919.336445949999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1341.982</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>980.13599999999997</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>252.2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>15870.190913199998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>584.07899999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2035.424</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>154.69999999999999</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>31321.2152981</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1077.7</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2396.4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4396</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3141807.6866959999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>112267</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>37500</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>127.35</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>14912.684999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>441.1</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>781.30000000000007</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="KPIs"/>
-      <sheetName val="CoC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.04</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>10356.130046052</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1019.9</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>59.5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>40.49</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>22544.952903140002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>652.29999999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>935.09999999999991</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financials"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>58.65</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>88163.993584049997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>19318.056</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>10827.793</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4150,407 +6563,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>338.01</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>20461.91295813</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2250.8000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1238.3</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>76.739999999999995</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>89555.579999999987</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>6221.5751200000004</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>898.55169000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>23.62</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>6150.6480000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1877.4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>778.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>20.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>7942.6458629000008</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1466.4690000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>4155.6499999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>33.710999999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>6199.6570538160004</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>229.227</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>1140.2079999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>25.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>9484.0043700000006</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>2517</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>1491</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financials"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>60.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>9118.7085583999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1467.8490000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>628.88699999999994</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>86.1</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5854.2555035999994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>203.84100000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>396.62300000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>8953.7999999999993</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>112.633</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1754.22</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>21.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>8574.6616225199996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>848.8</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1039.2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4590,7 +6603,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4603,2016 +6616,28 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17550</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>32570.869500000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1577</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2262</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>8.7799999999999994</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>42144</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>6390</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>1540</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41240</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>459995.53764</v>
+        <row r="3">
+          <cell r="H3">
+            <v>216.48</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>45360.78</v>
+            <v>69783.79898159999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>52633.11</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="Coc"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>99.2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>5094.5152000000007</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>130.35400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1230.885</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>27.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>102081.60000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>4793</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>12059</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>0.93779999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4808.1005999999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>531</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>656</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>86.42</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>9891.3739399999995</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>292.61099999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>16.02</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>37954.121342400002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>17557.536999999997</v>
+            <v>4594.3919999999998</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>8.01</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>36725.331993300002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>8082.48891</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>20208.361519999999</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>65.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>5874.7799535000004</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>695.93000000000006</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="I4">
-            <v>549</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>273230.13006</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>8794</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="I8">
-            <v>20343</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>24.05</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3545.2105000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>290</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>572</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>3.75</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>37653.589800000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5665.9049999999997</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>995.54700000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="WACC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>95.69</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4527.9551099999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>784.57600000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>55.02</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2880.3823910400001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>790.7940000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>76.37</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>3497.9518935199999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>158.19999999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2258.7999999999997</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2816.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>697412.87774050003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>138918</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5959</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>11.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4310.384</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>452</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>545</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>165.1</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>5044.7333572999996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>95.319000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>78.680000000000007</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4372.5807311200006</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>107.482</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1366.51</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>132.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>130841.4975</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>3309.02</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>7400.7630000000008</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>2146</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>226551.95815200001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>12239</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>34</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>161.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2990.6024601600002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>211.91</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>36.299999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2505.286971</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>343.12599999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>295.77</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>7.47</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3181.39830747</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>464.64800000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>989.73099999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>14.35</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2756.6605860499999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>160.19499999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>263.45</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270582.07176934998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1259.98</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>3707.71</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>54.91</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4407.5666168399994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>249</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1351</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>33.92</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>2464.3691366400003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>111.31400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>293.49</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>19.670000000000002</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2341.6752811900001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>129</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1671</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>9.6300000000000008</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2436.6190977000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>231.22499999999997</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>348.65300000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>828.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>201333.06192080001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>440.44</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>269.23</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="J3">
-            <v>52.82</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>164591.95229051998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>10960</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5.82</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2055.0937514400002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>214.85400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2186.0569999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.42</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>1491.5652650000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>412.92599999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>498.12</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>38.119999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1935.4971035199997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>325.44000000000005</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>24.73</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1761.5194085300002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>256.60000000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>27.07</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1188.01315849</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>104.68600000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>224.17499999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>59.85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>939.70682505000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>7.0270000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>57.816000000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>14.56</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1413.6025904000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>346.9</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>415.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.53</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>736.21656488999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>245.11399999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>9.6039999999999992</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>16.75</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>872.38125524999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>189.63499999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>623.71199999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main "/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="F2">
-            <v>2.4350000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="F4">
-            <v>290.48290130999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>318.89999999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>503.6</v>
+            <v>1517.606</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>159.05000000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>179090.30000000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>6230</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>2869</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>0.98</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>97.21301296</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>17.213000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>291.31400000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17.79</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270.90115659000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>45.523000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>70.016000000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2540</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>64964.434459999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>33044</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>13470</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1638</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>206.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>621.70000000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>180.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>14437.908028799999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1689.94</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>1484.2170000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>471.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>85081.629528000005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9760</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>22957</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7154,15 +7179,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1879753.5995564552</v>
+        <v>1855480.446791424</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>-205.17132480000015</v>
+        <v>-1553.4042447999996</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1879548.4282316547</v>
+        <v>1853927.0425466236</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7224,15 +7249,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23820.264246753839</v>
+        <v>23513.009148462304</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>-2.6645626597402616</v>
+        <v>-20.174081101298697</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24409.719847164346</v>
+        <v>24076.974578527581</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7330,15 +7355,15 @@
         <v>20</v>
       </c>
       <c r="E6" s="25">
-        <f>+[5]Main!$I$4</f>
+        <f>+[1]Main!$I$4</f>
         <v>549</v>
       </c>
       <c r="F6" s="18">
-        <f>+[5]Main!$I$6*FX!C3</f>
+        <f>+[1]Main!$I$6*FX!C3</f>
         <v>284159.33526239998</v>
       </c>
       <c r="G6" s="18">
-        <f>(+[5]Main!$I$8-[5]Main!$I$7)*FX!C3</f>
+        <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
         <v>12010.960000000001</v>
       </c>
       <c r="H6" s="18">
@@ -7433,15 +7458,15 @@
         <v>20</v>
       </c>
       <c r="E7" s="30">
-        <f>+[6]Main!$K$2</f>
+        <f>+[2]Main!$K$2</f>
         <v>2146</v>
       </c>
       <c r="F7" s="18">
-        <f>+[6]Main!$K$4*FX!C3</f>
+        <f>+[2]Main!$K$4*FX!C3</f>
         <v>235614.03647808</v>
       </c>
       <c r="G7" s="18">
-        <f>+([6]Main!$K$6-[6]Main!$K$5)*FX!C3</f>
+        <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
         <v>-12693.2</v>
       </c>
       <c r="H7" s="18">
@@ -7536,15 +7561,15 @@
         <v>100</v>
       </c>
       <c r="E8" s="25">
-        <f>+[7]Main!$J$3</f>
+        <f>+[3]Main!$J$3</f>
         <v>52.82</v>
       </c>
       <c r="F8" s="18">
-        <f>+[7]Main!$J$5*FX!C3</f>
+        <f>+[3]Main!$J$5*FX!C3</f>
         <v>171175.63038214078</v>
       </c>
       <c r="G8" s="18">
-        <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C3</f>
+        <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
         <v>-11396.32</v>
       </c>
       <c r="H8" s="18">
@@ -7636,15 +7661,15 @@
         <v>21</v>
       </c>
       <c r="E9" s="25">
-        <f>+[8]Main!$I$3</f>
+        <f>+[4]Main!$I$3</f>
         <v>159.05000000000001</v>
       </c>
       <c r="F9" s="18">
-        <f>+[8]Main!$I$5</f>
+        <f>+[4]Main!$I$5</f>
         <v>179090.30000000002</v>
       </c>
       <c r="G9" s="18">
-        <f>+[8]Main!$I$7-[8]Main!$I$6</f>
+        <f>+[4]Main!$I$7-[4]Main!$I$6</f>
         <v>-3361</v>
       </c>
       <c r="H9" s="18">
@@ -7731,15 +7756,15 @@
         <v>20</v>
       </c>
       <c r="E10" s="25">
-        <f>+[9]Main!$I$2</f>
+        <f>+[5]Main!$I$2</f>
         <v>471.6</v>
       </c>
       <c r="F10" s="18">
-        <f>+[9]Main!$I$4*FX!C3</f>
+        <f>+[5]Main!$I$4*FX!C3</f>
         <v>88484.89470912001</v>
       </c>
       <c r="G10" s="18">
-        <f>+([9]Main!$I$6-[9]Main!$I$5)*FX!C3</f>
+        <f>+([5]Main!$I$6-[5]Main!$I$5)*FX!C3</f>
         <v>13724.880000000001</v>
       </c>
       <c r="H10" s="18">
@@ -7806,26 +7831,26 @@
         <v>21</v>
       </c>
       <c r="E11" s="25">
-        <f>+[10]Main!$I$3</f>
-        <v>58.85</v>
+        <f>+[6]Main!$I$3</f>
+        <v>48.01</v>
       </c>
       <c r="F11" s="18">
-        <f>+[10]Main!$I$5</f>
-        <v>87068.574999999997</v>
+        <f>+[6]Main!$I$5</f>
+        <v>71078.804999999993</v>
       </c>
       <c r="G11" s="18">
-        <f>+[10]Main!$I$7-[10]Main!$I$6</f>
-        <v>-330</v>
+        <f>+[6]Main!$I$7-[6]Main!$I$6</f>
+        <v>-28</v>
       </c>
       <c r="H11" s="18">
         <f t="shared" si="1"/>
-        <v>86738.574999999997</v>
+        <v>71050.804999999993</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="J11" s="27">
-        <v>46100</v>
+        <v>46198</v>
       </c>
       <c r="K11" s="18">
         <v>51362</v>
@@ -7903,15 +7928,15 @@
         <v>124</v>
       </c>
       <c r="E12" s="30">
-        <f>+[11]Main!$J$3</f>
+        <f>+[7]Main!$J$3</f>
         <v>62750</v>
       </c>
       <c r="F12" s="18">
-        <f>+[11]Main!$J$5*FX!C5</f>
+        <f>+[7]Main!$J$5*FX!C5</f>
         <v>121295.419182</v>
       </c>
       <c r="G12" s="18">
-        <f>+([11]Main!$J$7-[11]Main!$J$6)*FX!C5</f>
+        <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
         <v>-10509.2505</v>
       </c>
       <c r="H12" s="18">
@@ -7932,7 +7957,7 @@
         <v>0.08</v>
       </c>
       <c r="M12" s="18">
-        <f>+SUM([11]Model!$G$20:$I$20,[11]Model!$C$20)*FX!C5</f>
+        <f>+SUM([7]Model!$G$20:$I$20,[7]Model!$C$20)*FX!C5</f>
         <v>3765.1320000000001</v>
       </c>
       <c r="N12" s="18">
@@ -7991,26 +8016,26 @@
         <v>21</v>
       </c>
       <c r="E13" s="25">
-        <f>+[12]Main!$K$2</f>
-        <v>187.97</v>
+        <f>+[8]Main!$K$2</f>
+        <v>170</v>
       </c>
       <c r="F13" s="18">
-        <f>+[12]Main!$K$4</f>
-        <v>75466.759510000004</v>
+        <f>+[8]Main!$K$4</f>
+        <v>68068</v>
       </c>
       <c r="G13" s="18">
-        <f>+[12]Main!$K$6-[12]Main!$K$5</f>
-        <v>2776.4369999999999</v>
+        <f>+[8]Main!$K$6-[8]Main!$K$5</f>
+        <v>2473.587</v>
       </c>
       <c r="H13" s="18">
         <f t="shared" si="1"/>
-        <v>78243.196510000009</v>
+        <v>70541.587</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="J13" s="27">
-        <v>46106</v>
+        <v>46219</v>
       </c>
       <c r="K13" s="18">
         <v>8815.7999999999993</v>
@@ -8070,26 +8095,26 @@
         <v>21</v>
       </c>
       <c r="E14" s="25">
-        <f>+[13]Main!$H$3</f>
-        <v>176.36</v>
+        <f>+[9]Main!$H$3</f>
+        <v>216.48</v>
       </c>
       <c r="F14" s="18">
-        <f>+[13]Main!$H$5</f>
-        <v>56659.177199999998</v>
+        <f>+[9]Main!$H$5</f>
+        <v>69783.79898159999</v>
       </c>
       <c r="G14" s="18">
-        <f>+[13]Main!$H$7-[13]Main!$H$6</f>
-        <v>-2544.201</v>
+        <f>+[9]Main!$H$7-[9]Main!$H$6</f>
+        <v>-3076.7860000000001</v>
       </c>
       <c r="H14" s="18">
         <f t="shared" si="1"/>
-        <v>54114.976199999997</v>
+        <v>66707.012981599983</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>821</v>
+        <v>830</v>
       </c>
       <c r="J14" s="27">
-        <v>46086</v>
+        <v>46163</v>
       </c>
       <c r="K14" s="18">
         <v>20376.900000000001</v>
@@ -8145,15 +8170,15 @@
         <v>107</v>
       </c>
       <c r="E15" s="25">
-        <f>+[14]Main!$I$2</f>
+        <f>+[10]Main!$I$2</f>
         <v>156.36000000000001</v>
       </c>
       <c r="F15" s="18">
-        <f>+[14]Main!$I$4</f>
+        <f>+[10]Main!$I$4</f>
         <v>17275.07043756</v>
       </c>
       <c r="G15" s="18">
-        <f>+[14]Main!$I$6-[14]Main!$I$5</f>
+        <f>+[10]Main!$I$6-[10]Main!$I$5</f>
         <v>-1807.202</v>
       </c>
       <c r="H15" s="18">
@@ -8163,7 +8188,9 @@
       <c r="I15" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="J15" s="27"/>
+      <c r="J15" s="27">
+        <v>46177</v>
+      </c>
       <c r="K15" s="18">
         <v>9619.2999999999993</v>
       </c>
@@ -8218,15 +8245,15 @@
         <v>82</v>
       </c>
       <c r="E16" s="25">
-        <f>+[15]Main!$I$2</f>
+        <f>+[11]Main!$I$2</f>
         <v>141.80000000000001</v>
       </c>
       <c r="F16" s="18">
-        <f>+[15]Main!$I$4*FX!C3</f>
+        <f>+[11]Main!$I$4*FX!C3</f>
         <v>26332.485291840003</v>
       </c>
       <c r="G16" s="18">
-        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C3</f>
+        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
         <v>1064.96</v>
       </c>
       <c r="H16" s="18">
@@ -8296,15 +8323,15 @@
         <v>20</v>
       </c>
       <c r="E17" s="25">
-        <f>+[16]Main!$H$2</f>
+        <f>+[12]Main!$H$2</f>
         <v>284.8</v>
       </c>
       <c r="F17" s="18">
-        <f>+[16]Main!$H$4*FX!C3</f>
+        <f>+[12]Main!$H$4*FX!C3</f>
         <v>36314.564475904001</v>
       </c>
       <c r="G17" s="18">
-        <f>+([16]Main!$H$6-[16]Main!$H$5)*FX!C3</f>
+        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
         <v>8578.9600000000009</v>
       </c>
       <c r="H17" s="18">
@@ -8396,26 +8423,26 @@
         <v>454</v>
       </c>
       <c r="E18" s="25">
-        <f>+[17]Main!$H$2</f>
-        <v>101.6</v>
+        <f>+[13]Main!$H$2</f>
+        <v>80.55</v>
       </c>
       <c r="F18" s="18">
-        <f>+[17]Main!$H$5*FX!C9</f>
-        <v>37150.109636640002</v>
+        <f>+[13]Main!$H$5*FX!C9</f>
+        <v>29160.086447520003</v>
       </c>
       <c r="G18" s="18">
-        <f>+([17]Main!$H$7-[17]Main!$H$6)*FX!C9</f>
-        <v>-1134.5600000000002</v>
+        <f>+([13]Main!$H$7-[13]Main!$H$6)*FX!C9</f>
+        <v>-1841.5600000000002</v>
       </c>
       <c r="H18" s="18">
         <f t="shared" si="1"/>
-        <v>36015.549636640004</v>
+        <v>27318.526447520002</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>149</v>
+        <v>422</v>
       </c>
       <c r="J18" s="31">
-        <v>46099</v>
+        <v>46260</v>
       </c>
       <c r="K18" s="18">
         <f>70826*FX!C9</f>
@@ -8475,15 +8502,15 @@
         <v>21</v>
       </c>
       <c r="E19" s="25">
-        <f>+[18]Main!$M$2</f>
+        <f>+[14]Main!$M$2</f>
         <v>115.3</v>
       </c>
       <c r="F19" s="18">
-        <f>+[18]Main!$M$4</f>
+        <f>+[14]Main!$M$4</f>
         <v>16366.831656300001</v>
       </c>
       <c r="G19" s="18">
-        <f>+[18]Main!$M$6-[18]Main!$M$5</f>
+        <f>+[14]Main!$M$6-[14]Main!$M$5</f>
         <v>-2086.7460000000001</v>
       </c>
       <c r="H19" s="18">
@@ -8559,26 +8586,26 @@
         <v>109</v>
       </c>
       <c r="E20" s="25">
-        <f>+[19]Main!$I$2</f>
-        <v>185.55</v>
+        <f>+[15]Main!$I$2</f>
+        <v>170.3</v>
       </c>
       <c r="F20" s="18">
-        <f>+[19]Main!$I$4*FX!C4</f>
-        <v>28274.690699250001</v>
+        <f>+[15]Main!$I$4*FX!C4</f>
+        <v>25871.945346</v>
       </c>
       <c r="G20" s="18">
-        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C4</f>
-        <v>-22.135000000000002</v>
+        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C4</f>
+        <v>184.49</v>
       </c>
       <c r="H20" s="18">
         <f t="shared" si="1"/>
-        <v>28252.555699250002</v>
+        <v>26056.435346000002</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J20" s="27">
-        <v>46107</v>
+        <v>46198</v>
       </c>
       <c r="K20" s="18">
         <f>234478*FX!C4</f>
@@ -8627,15 +8654,15 @@
         <v>165</v>
       </c>
       <c r="E21" s="25">
-        <f>+[20]Main!$H$2</f>
+        <f>+[16]Main!$H$2</f>
         <v>40.880000000000003</v>
       </c>
       <c r="F21" s="18">
-        <f>+[20]Main!$H$5*FX!C3</f>
+        <f>+[16]Main!$H$5*FX!C3</f>
         <v>13054.669694976001</v>
       </c>
       <c r="G21" s="18">
-        <f>(+[20]Main!$H$7-[20]Main!$H$6)*FX!C3</f>
+        <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
         <v>489.51760000000007</v>
       </c>
       <c r="H21" s="18">
@@ -8690,15 +8717,15 @@
         <v>185</v>
       </c>
       <c r="E22" s="25">
-        <f>+[21]Main!$I$2</f>
+        <f>+[17]Main!$I$2</f>
         <v>5221.55</v>
       </c>
       <c r="F22" s="18">
-        <f>+[21]Main!$I$4*FX!C12</f>
+        <f>+[17]Main!$I$4*FX!C12</f>
         <v>20418.151071830049</v>
       </c>
       <c r="G22" s="18">
-        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C12</f>
+        <f>+([17]Main!$I$6-[17]Main!$I$5)*FX!C12</f>
         <v>0</v>
       </c>
       <c r="H22" s="18">
@@ -8747,15 +8774,15 @@
         <v>165</v>
       </c>
       <c r="E23" s="25">
-        <f>+[22]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>55.15</v>
       </c>
       <c r="F23" s="18">
-        <f>+[22]Main!$H$4*FX!C3</f>
+        <f>+[18]Main!$H$4*FX!C3</f>
         <v>15516.109903787999</v>
       </c>
       <c r="G23" s="18">
-        <f>+([22]Main!$H$6-[22]Main!$H$5)*FX!C3</f>
+        <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C3</f>
         <v>-376.31984</v>
       </c>
       <c r="H23" s="18">
@@ -8810,15 +8837,15 @@
         <v>21</v>
       </c>
       <c r="E24" s="25">
-        <f>+[23]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>252.2</v>
       </c>
       <c r="F24" s="18">
-        <f>+[23]Main!$I$4</f>
+        <f>+[19]Main!$I$4</f>
         <v>15870.190913199998</v>
       </c>
       <c r="G24" s="18">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <f>+[19]Main!$I$6-[19]Main!$I$5</f>
         <v>1451.345</v>
       </c>
       <c r="H24" s="18">
@@ -8873,15 +8900,15 @@
         <v>21</v>
       </c>
       <c r="E25" s="25">
-        <f>+[24]Main!$J$2</f>
+        <f>+[20]Main!$J$2</f>
         <v>154.69999999999999</v>
       </c>
       <c r="F25" s="18">
-        <f>+[24]Main!$J$4</f>
+        <f>+[20]Main!$J$4</f>
         <v>31321.2152981</v>
       </c>
       <c r="G25" s="18">
-        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
+        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
         <v>1318.7</v>
       </c>
       <c r="H25" s="18">
@@ -8936,15 +8963,15 @@
         <v>124</v>
       </c>
       <c r="E26" s="25">
-        <f>+[25]Main!$I$2</f>
+        <f>+[21]Main!$I$2</f>
         <v>4396</v>
       </c>
       <c r="F26" s="18">
-        <f>+[25]Main!$I$4*FX!C5</f>
+        <f>+[21]Main!$I$4*FX!C5</f>
         <v>19793.3884261848</v>
       </c>
       <c r="G26" s="18">
-        <f>+([25]Main!$I$6-[25]Main!$I$5)*FX!C5</f>
+        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C5</f>
         <v>-471.03210000000001</v>
       </c>
       <c r="H26" s="18">
@@ -8999,15 +9026,15 @@
         <v>219</v>
       </c>
       <c r="E27" s="25">
-        <f>+[26]Main!$I$2</f>
+        <f>+[22]Main!$I$2</f>
         <v>127.35</v>
       </c>
       <c r="F27" s="18">
-        <f>+[26]Main!$I$4*FX!C8</f>
+        <f>+[22]Main!$I$4*FX!C8</f>
         <v>18491.7294</v>
       </c>
       <c r="G27" s="18">
-        <f>+([26]Main!$I$6-[26]Main!$I$5)*FX!C8</f>
+        <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C8</f>
         <v>421.84800000000007</v>
       </c>
       <c r="H27" s="18">
@@ -9062,15 +9089,15 @@
         <v>166</v>
       </c>
       <c r="E28" s="25">
-        <f>+[27]Main!$H$2</f>
+        <f>+[23]Main!$H$2</f>
         <v>41.04</v>
       </c>
       <c r="F28" s="18">
-        <f>+[27]Main!$H$5*FX!C7</f>
+        <f>+[23]Main!$H$5*FX!C7</f>
         <v>11598.86565157824</v>
       </c>
       <c r="G28" s="18">
-        <f>+([27]Main!$H$7-[27]Main!$H$6)*FX!C7</f>
+        <f>+([23]Main!$H$7-[23]Main!$H$6)*FX!C7</f>
         <v>-1075.6480000000001</v>
       </c>
       <c r="H28" s="18">
@@ -9125,15 +9152,15 @@
         <v>214</v>
       </c>
       <c r="E29" s="25">
-        <f>+[28]Main!$J$2</f>
+        <f>+[24]Main!$J$2</f>
         <v>40.49</v>
       </c>
       <c r="F29" s="18">
-        <f>+[28]Main!$J$4</f>
+        <f>+[24]Main!$J$4</f>
         <v>22544.952903140002</v>
       </c>
       <c r="G29" s="18">
-        <f>+[28]Main!$J$6-[28]Main!$J$5</f>
+        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
         <v>282.79999999999995</v>
       </c>
       <c r="H29" s="18">
@@ -9188,26 +9215,26 @@
         <v>454</v>
       </c>
       <c r="E30" s="25">
-        <f>+[29]Main!$J$2</f>
-        <v>58.65</v>
+        <f>+[25]Main!$J$2</f>
+        <v>47.12</v>
       </c>
       <c r="F30" s="18">
-        <f>+[29]Main!$J$4*FX!C9</f>
-        <v>12342.959101767001</v>
+        <f>+[25]Main!$J$5*FX!C9</f>
+        <v>8726.4826075060482</v>
       </c>
       <c r="G30" s="18">
-        <f>+([29]Main!$J$6-[29]Main!$J$5)*FX!C9</f>
-        <v>-1188.6368200000002</v>
+        <f>+([25]Main!$J$7-[25]Main!$J$6)*FX!C9</f>
+        <v>-1503.0597399999999</v>
       </c>
       <c r="H30" s="18">
         <f t="shared" si="1"/>
-        <v>11154.322281767001</v>
+        <v>7223.4228675060485</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J30" s="31">
-        <v>45741</v>
+        <v>46260</v>
       </c>
       <c r="K30" s="25"/>
       <c r="L30" s="22"/>
@@ -9251,15 +9278,15 @@
         <v>21</v>
       </c>
       <c r="E31" s="25">
-        <f>+[30]Main!$H$2</f>
+        <f>+[26]Main!$H$2</f>
         <v>338.01</v>
       </c>
       <c r="F31" s="18">
-        <f>+[30]Main!$H$4</f>
+        <f>+[26]Main!$H$4</f>
         <v>20461.91295813</v>
       </c>
       <c r="G31" s="18">
-        <f>+[30]Main!$H$6-[30]Main!$H$5</f>
+        <f>+[26]Main!$H$6-[26]Main!$H$5</f>
         <v>-1012.5000000000002</v>
       </c>
       <c r="H31" s="18">
@@ -9345,15 +9372,15 @@
         <v>454</v>
       </c>
       <c r="E32" s="25">
-        <f>+[31]Main!$K$2</f>
+        <f>+[27]Main!$K$2</f>
         <v>76.739999999999995</v>
       </c>
       <c r="F32" s="18">
-        <f>+[31]Main!$K$4*FX!C9</f>
+        <f>+[27]Main!$K$4*FX!C9</f>
         <v>12537.781199999999</v>
       </c>
       <c r="G32" s="18">
-        <f>+([31]Main!$K$6-[31]Main!$K$5)*FX!C9</f>
+        <f>+([27]Main!$K$6-[27]Main!$K$5)*FX!C9</f>
         <v>-745.22328020000009</v>
       </c>
       <c r="H32" s="18">
@@ -9408,15 +9435,15 @@
         <v>82</v>
       </c>
       <c r="E33" s="25">
-        <f>+[32]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>23.62</v>
       </c>
       <c r="F33" s="18">
-        <f>+[32]Main!$I$4*FX!C3</f>
+        <f>+[28]Main!$I$4*FX!C3</f>
         <v>6396.6739200000002</v>
       </c>
       <c r="G33" s="18">
-        <f>+([32]Main!$I$6-[32]Main!$I$5)*FX!C3</f>
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
         <v>-1142.7520000000002</v>
       </c>
       <c r="H33" s="18">
@@ -9471,15 +9498,15 @@
         <v>21</v>
       </c>
       <c r="E34" s="25">
-        <f>+[33]Main!$H$2</f>
+        <f>+[29]Main!$H$2</f>
         <v>20.3</v>
       </c>
       <c r="F34" s="18">
-        <f>+[33]Main!$H$4</f>
+        <f>+[29]Main!$H$4</f>
         <v>7942.6458629000008</v>
       </c>
       <c r="G34" s="18">
-        <f>+[33]Main!$H$6-[33]Main!$H$5</f>
+        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
         <v>2689.1809999999996</v>
       </c>
       <c r="H34" s="18">
@@ -9534,15 +9561,15 @@
         <v>82</v>
       </c>
       <c r="E35" s="25">
-        <f>+[34]Main!$I$3</f>
+        <f>+[30]Main!$I$3</f>
         <v>33.710999999999999</v>
       </c>
       <c r="F35" s="18">
-        <f>+[34]Main!$I$5*FX!C3</f>
+        <f>+[30]Main!$I$5*FX!C3</f>
         <v>6447.6433359686407</v>
       </c>
       <c r="G35" s="18">
-        <f>+([34]Main!$I$7-[34]Main!$I$6)*FX!C3</f>
+        <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
         <v>947.42023999999992</v>
       </c>
       <c r="H35" s="18">
@@ -9597,15 +9624,15 @@
         <v>21</v>
       </c>
       <c r="E36" s="25">
-        <f>+[35]Main!$J$2</f>
+        <f>+[31]Main!$J$2</f>
         <v>25.5</v>
       </c>
       <c r="F36" s="18">
-        <f>+[35]Main!$J$4</f>
+        <f>+[31]Main!$J$4</f>
         <v>9484.0043700000006</v>
       </c>
       <c r="G36" s="18">
-        <f>+([35]Main!$J$6-[35]Main!$J$5)</f>
+        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
         <v>-1026</v>
       </c>
       <c r="H36" s="18">
@@ -9672,15 +9699,15 @@
         <v>21</v>
       </c>
       <c r="E37" s="25">
-        <f>+[36]Main!$I$2</f>
+        <f>+[32]Main!$I$2</f>
         <v>60.4</v>
       </c>
       <c r="F37" s="18">
-        <f>+[36]Main!$I$4</f>
+        <f>+[32]Main!$I$4</f>
         <v>9118.7085583999997</v>
       </c>
       <c r="G37" s="18">
-        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
+        <f>+[32]Main!$I$6-[32]Main!$I$5</f>
         <v>-838.96200000000022</v>
       </c>
       <c r="H37" s="18">
@@ -9735,15 +9762,15 @@
         <v>165</v>
       </c>
       <c r="E38" s="25">
-        <f>+[37]Main!$J$2</f>
+        <f>+[33]Main!$J$2</f>
         <v>86.1</v>
       </c>
       <c r="F38" s="18">
-        <f>+[37]Main!$J$4*FX!C3</f>
+        <f>+[33]Main!$J$4*FX!C3</f>
         <v>6088.4257237439997</v>
       </c>
       <c r="G38" s="18">
-        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C3</f>
+        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
         <v>200.49328000000006</v>
       </c>
       <c r="H38" s="18">
@@ -9798,15 +9825,15 @@
         <v>107</v>
       </c>
       <c r="E39" s="25">
-        <f>+[38]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>60</v>
       </c>
       <c r="F39" s="18">
-        <f>+[38]Main!$I$4</f>
+        <f>+[34]Main!$I$4</f>
         <v>8953.7999999999993</v>
       </c>
       <c r="G39" s="18">
-        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
+        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
         <v>1641.587</v>
       </c>
       <c r="H39" s="18">
@@ -9861,15 +9888,15 @@
         <v>21</v>
       </c>
       <c r="E40" s="25">
-        <f>+[39]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>21.96</v>
       </c>
       <c r="F40" s="18">
-        <f>+[39]Main!$I$4</f>
+        <f>+[35]Main!$I$4</f>
         <v>8574.6616225199996</v>
       </c>
       <c r="G40" s="18">
-        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
+        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
         <v>190.40000000000009</v>
       </c>
       <c r="H40" s="18">
@@ -9936,15 +9963,15 @@
         <v>294</v>
       </c>
       <c r="E41" s="25">
-        <f>+[40]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>17550</v>
       </c>
       <c r="F41" s="18">
-        <f>+[40]Main!$I$4*FX!C11</f>
+        <f>+[36]Main!$I$4*FX!C11</f>
         <v>8142.7173750000002</v>
       </c>
       <c r="G41" s="18">
-        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C11</f>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
         <v>171.25</v>
       </c>
       <c r="H41" s="18">
@@ -9995,15 +10022,15 @@
         <v>454</v>
       </c>
       <c r="E42" s="25">
-        <f>+[41]Main!$J$2</f>
+        <f>+[37]Main!$J$2</f>
         <v>8.7799999999999994</v>
       </c>
       <c r="F42" s="18">
-        <f>+[41]Main!$J$4*FX!C9</f>
+        <f>+[37]Main!$J$4*FX!C9</f>
         <v>5900.1600000000008</v>
       </c>
       <c r="G42" s="18">
-        <f>+([41]Main!$J$6-[41]Main!$J$5)*FX!C9</f>
+        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C9</f>
         <v>-679.00000000000011</v>
       </c>
       <c r="H42" s="18">
@@ -10054,15 +10081,15 @@
         <v>185</v>
       </c>
       <c r="E43" s="25">
-        <f>+[42]Main!$H$2</f>
+        <f>+[38]Main!$H$2</f>
         <v>41240</v>
       </c>
       <c r="F43" s="18">
-        <f>+[42]Main!$H$4*FX!C12</f>
+        <f>+[38]Main!$H$4*FX!C12</f>
         <v>5059.9509140399996</v>
       </c>
       <c r="G43" s="18">
-        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C12</f>
+        <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
         <v>79.99563000000002</v>
       </c>
       <c r="H43" s="18">
@@ -10113,15 +10140,15 @@
         <v>21</v>
       </c>
       <c r="E44" s="25">
-        <f>+[43]Main!$H$2</f>
+        <f>+[39]Main!$H$2</f>
         <v>99.2</v>
       </c>
       <c r="F44" s="18">
-        <f>+[43]Main!$H$4</f>
+        <f>+[39]Main!$H$4</f>
         <v>5094.5152000000007</v>
       </c>
       <c r="G44" s="18">
-        <f>+[43]Main!$H$6-[43]Main!$H$5</f>
+        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
         <v>1100.5309999999999</v>
       </c>
       <c r="H44" s="18">
@@ -10176,15 +10203,15 @@
         <v>325</v>
       </c>
       <c r="E45" s="25">
-        <f>+[44]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>27.8</v>
       </c>
       <c r="F45" s="18">
-        <f>+[44]Main!$I$4*FX!C14</f>
+        <f>+[40]Main!$I$4*FX!C14</f>
         <v>5512.4063999999998</v>
       </c>
       <c r="G45" s="18">
-        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C14</f>
+        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C14</f>
         <v>392.36399999999998</v>
       </c>
       <c r="H45" s="18">
@@ -10239,15 +10266,15 @@
         <v>219</v>
       </c>
       <c r="E46" s="25">
-        <f>+[45]Main!$I$2</f>
+        <f>+[41]Main!$I$2</f>
         <v>0.93779999999999997</v>
       </c>
       <c r="F46" s="18">
-        <f>+[45]Main!$I$4*FX!C8</f>
+        <f>+[41]Main!$I$4*FX!C8</f>
         <v>5962.0447439999998</v>
       </c>
       <c r="G46" s="18">
-        <f>+([45]Main!$I$6-[45]Main!$I$5)*FX!C8</f>
+        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
         <v>155</v>
       </c>
       <c r="H46" s="18">
@@ -10302,15 +10329,15 @@
         <v>107</v>
       </c>
       <c r="E47" s="25">
-        <f>+[46]Main!$H$2</f>
+        <f>+[42]Main!$H$2</f>
         <v>86.42</v>
       </c>
       <c r="F47" s="18">
-        <f>+[46]Main!$H$4*FX!C13</f>
+        <f>+[42]Main!$H$4*FX!C13</f>
         <v>6825.0480185999995</v>
       </c>
       <c r="G47" s="18">
-        <f>+([46]Main!$H$6-[46]Main!$H$5)*FX!C13</f>
+        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
         <v>-201.90158999999997</v>
       </c>
       <c r="H47" s="18">
@@ -10361,15 +10388,15 @@
         <v>454</v>
       </c>
       <c r="E48" s="25">
-        <f>+[47]Main!$H$2</f>
+        <f>+[43]Main!$H$2</f>
         <v>16.02</v>
       </c>
       <c r="F48" s="18">
-        <f>+[47]Main!$H$5*FX!C9</f>
+        <f>+[43]Main!$H$5*FX!C9</f>
         <v>5313.5769879360005</v>
       </c>
       <c r="G48" s="18">
-        <f>+([47]Main!$H$7-[47]Main!$H$6)*FX!C9</f>
+        <f>+([43]Main!$H$7-[43]Main!$H$6)*FX!C9</f>
         <v>-2458.0551799999998</v>
       </c>
       <c r="H48" s="18">
@@ -10422,15 +10449,15 @@
         <v>454</v>
       </c>
       <c r="E49" s="25">
-        <f>+[48]Main!$I$2</f>
+        <f>+[44]Main!$I$2</f>
         <v>8.01</v>
       </c>
       <c r="F49" s="18">
-        <f>+[48]Main!$I$4*FX!C9</f>
+        <f>+[44]Main!$I$4*FX!C9</f>
         <v>5141.5464790620008</v>
       </c>
       <c r="G49" s="18">
-        <f>+([48]Main!$I$6-[48]Main!$I$5)*FX!C9</f>
+        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C9</f>
         <v>1697.6221653999999</v>
       </c>
       <c r="H49" s="18">
@@ -10479,15 +10506,15 @@
         <v>21</v>
       </c>
       <c r="E50" s="25">
-        <f>+[49]Main!$J$2</f>
+        <f>+[45]Main!$J$2</f>
         <v>65.5</v>
       </c>
       <c r="F50" s="18">
-        <f>+[49]Main!$J$4</f>
+        <f>+[45]Main!$J$4</f>
         <v>5874.7799535000004</v>
       </c>
       <c r="G50" s="18">
-        <f>+[49]Main!$J$6-[49]Main!$J$5</f>
+        <f>+[45]Main!$J$6-[45]Main!$J$5</f>
         <v>-695.93000000000006</v>
       </c>
       <c r="H50" s="18">
@@ -10538,15 +10565,15 @@
         <v>82</v>
       </c>
       <c r="E51" s="25">
-        <f>+[50]Main!$I$2</f>
+        <f>+[46]Main!$I$2</f>
         <v>24.05</v>
       </c>
       <c r="F51" s="18">
-        <f>+[50]Main!$I$4*FX!C3</f>
+        <f>+[46]Main!$I$4*FX!C3</f>
         <v>3687.0189200000004</v>
       </c>
       <c r="G51" s="18">
-        <f>+([50]Main!$I$6-[50]Main!$I$5)*FX!C3</f>
+        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
         <v>293.28000000000003</v>
       </c>
       <c r="H51" s="18">
@@ -10601,15 +10628,15 @@
         <v>454</v>
       </c>
       <c r="E52" s="25">
-        <f>+[51]Main!$I$2</f>
+        <f>+[47]Main!$I$2</f>
         <v>3.75</v>
       </c>
       <c r="F52" s="18">
-        <f>+[51]Main!$I$5*FX!C9</f>
+        <f>+[47]Main!$I$5*FX!C9</f>
         <v>5271.5025720000003</v>
       </c>
       <c r="G52" s="18">
-        <f>+([51]Main!$I$7-[51]Main!$I$6)*FX!C9</f>
+        <f>+([47]Main!$I$7-[47]Main!$I$6)*FX!C9</f>
         <v>-653.85012000000006</v>
       </c>
       <c r="H52" s="18">
@@ -10664,15 +10691,15 @@
         <v>21</v>
       </c>
       <c r="E53" s="25">
-        <f>+[52]Main!$I$2</f>
+        <f>+[48]Main!$I$2</f>
         <v>95.69</v>
       </c>
       <c r="F53" s="18">
-        <f>+[52]Main!$I$4</f>
+        <f>+[48]Main!$I$4</f>
         <v>4527.9551099999999</v>
       </c>
       <c r="G53" s="18">
-        <f>+[52]Main!$I$6-[52]Main!$I$5</f>
+        <f>+[48]Main!$I$6-[48]Main!$I$5</f>
         <v>-784.57600000000002</v>
       </c>
       <c r="H53" s="18">
@@ -10739,15 +10766,15 @@
         <v>21</v>
       </c>
       <c r="E54" s="25">
-        <f>+[53]Main!$I$2</f>
+        <f>+[49]Main!$I$2</f>
         <v>55.02</v>
       </c>
       <c r="F54" s="18">
-        <f>+[53]Main!$I$4</f>
+        <f>+[49]Main!$I$4</f>
         <v>2880.3823910400001</v>
       </c>
       <c r="G54" s="18">
-        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
+        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
         <v>-790.7940000000001</v>
       </c>
       <c r="H54" s="18">
@@ -10802,15 +10829,15 @@
         <v>21</v>
       </c>
       <c r="E55" s="25">
-        <f>+[54]Main!$J$2</f>
+        <f>+[50]Main!$J$2</f>
         <v>76.37</v>
       </c>
       <c r="F55" s="18">
-        <f>+[54]Main!$J$4</f>
+        <f>+[50]Main!$J$4</f>
         <v>3497.9518935199999</v>
       </c>
       <c r="G55" s="18">
-        <f>+([54]Main!$J$6-[54]Main!$J$5)</f>
+        <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
         <v>2100.6</v>
       </c>
       <c r="H55" s="18">
@@ -10865,15 +10892,15 @@
         <v>124</v>
       </c>
       <c r="E56" s="25">
-        <f>+[55]Main!$I$2</f>
+        <f>+[51]Main!$I$2</f>
         <v>2816.5</v>
       </c>
       <c r="F56" s="18">
-        <f>+[55]Main!$I$4*FX!C5</f>
+        <f>+[51]Main!$I$4*FX!C5</f>
         <v>4393.7011297651507</v>
       </c>
       <c r="G56" s="18">
-        <f>+([55]Main!$I$6-[55]Main!$I$5)*FX!C5</f>
+        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
         <v>-837.64170000000001</v>
       </c>
       <c r="H56" s="18">
@@ -10928,15 +10955,15 @@
         <v>219</v>
       </c>
       <c r="E57" s="25">
-        <f>+[56]Main!$I$2</f>
+        <f>+[52]Main!$I$2</f>
         <v>11.96</v>
       </c>
       <c r="F57" s="18">
-        <f>+[56]Main!$I$4*FX!C3</f>
+        <f>+[52]Main!$I$4*FX!C3</f>
         <v>4482.79936</v>
       </c>
       <c r="G57" s="18">
-        <f>+([56]Main!$I$6-[56]Main!$I$5)*FX!C3</f>
+        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
         <v>96.72</v>
       </c>
       <c r="H57" s="18">
@@ -10987,15 +11014,15 @@
         <v>21</v>
       </c>
       <c r="E58" s="25">
-        <f>+[57]Main!$I$2</f>
+        <f>+[53]Main!$I$2</f>
         <v>165.1</v>
       </c>
       <c r="F58" s="18">
-        <f>+[57]Main!$I$4</f>
+        <f>+[53]Main!$I$4</f>
         <v>5044.7333572999996</v>
       </c>
       <c r="G58" s="18">
-        <f>+[57]Main!$I$6-[57]Main!$I$5</f>
+        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
         <v>-95.319000000000003</v>
       </c>
       <c r="H58" s="18">
@@ -11050,15 +11077,15 @@
         <v>21</v>
       </c>
       <c r="E59" s="25">
-        <f>+[58]Main!$I$2</f>
+        <f>+[54]Main!$I$2</f>
         <v>78.680000000000007</v>
       </c>
       <c r="F59" s="18">
-        <f>+[58]Main!$I$4</f>
+        <f>+[54]Main!$I$4</f>
         <v>4372.5807311200006</v>
       </c>
       <c r="G59" s="18">
-        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
+        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
         <v>1259.028</v>
       </c>
       <c r="H59" s="18">
@@ -11160,15 +11187,15 @@
         <v>433</v>
       </c>
       <c r="E61" s="25">
-        <f>+[59]Main!$J$2</f>
+        <f>+[55]Main!$J$2</f>
         <v>132.5</v>
       </c>
       <c r="F61" s="18">
-        <f>+[59]Main!$J$4*FX!C15</f>
+        <f>+[55]Main!$J$4*FX!C15</f>
         <v>3925.244925</v>
       </c>
       <c r="G61" s="18">
-        <f>+([59]Main!$J$6-[59]Main!$J$5)*FX!C15</f>
+        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
         <v>122.75229000000002</v>
       </c>
       <c r="H61" s="18">
@@ -11217,15 +11244,15 @@
         <v>21</v>
       </c>
       <c r="E62" s="25">
-        <f>+[60]Main!$J$2</f>
+        <f>+[56]Main!$J$2</f>
         <v>161.28</v>
       </c>
       <c r="F62" s="18">
-        <f>+[60]Main!$J$4</f>
+        <f>+[56]Main!$J$4</f>
         <v>2990.6024601600002</v>
       </c>
       <c r="G62" s="18">
-        <f>+[60]Main!$J$6-[60]Main!$J$5</f>
+        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
         <v>-211.91</v>
       </c>
       <c r="H62" s="18">
@@ -11276,15 +11303,15 @@
         <v>82</v>
       </c>
       <c r="E63" s="25">
-        <f>+[61]Main!$J$2</f>
+        <f>+[57]Main!$J$2</f>
         <v>36.299999999999997</v>
       </c>
       <c r="F63" s="18">
-        <f>+[61]Main!$J$4*FX!C3</f>
+        <f>+[57]Main!$J$4*FX!C3</f>
         <v>2605.4984498399999</v>
       </c>
       <c r="G63" s="18">
-        <f>+([61]Main!$J$6-[61]Main!$J$5)*FX!C3</f>
+        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
         <v>-49.250239999999998</v>
       </c>
       <c r="H63" s="18">
@@ -11335,15 +11362,15 @@
         <v>21</v>
       </c>
       <c r="E64" s="25">
-        <f>+[62]Main!$I$2</f>
+        <f>+[58]Main!$I$2</f>
         <v>7.47</v>
       </c>
       <c r="F64" s="18">
-        <f>+[62]Main!$I$4</f>
+        <f>+[58]Main!$I$4</f>
         <v>3181.39830747</v>
       </c>
       <c r="G64" s="18">
-        <f>+[62]Main!$I$6-[62]Main!$I$5</f>
+        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
         <v>525.08299999999997</v>
       </c>
       <c r="H64" s="18">
@@ -11394,15 +11421,15 @@
         <v>21</v>
       </c>
       <c r="E65" s="25">
-        <f>+[63]Main!$I$2</f>
+        <f>+[59]Main!$I$2</f>
         <v>14.35</v>
       </c>
       <c r="F65" s="18">
-        <f>+[63]Main!$I$4</f>
+        <f>+[59]Main!$I$4</f>
         <v>2756.6605860499999</v>
       </c>
       <c r="G65" s="18">
-        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
+        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
         <v>-160.19499999999999</v>
       </c>
       <c r="H65" s="18">
@@ -11453,15 +11480,15 @@
         <v>185</v>
       </c>
       <c r="E66" s="25">
-        <f>+[64]Main!$I$2</f>
+        <f>+[60]Main!$I$2</f>
         <v>263.45</v>
       </c>
       <c r="F66" s="18">
-        <f>+[64]Main!$I$4*FX!C12</f>
+        <f>+[60]Main!$I$4*FX!C12</f>
         <v>2976.4027894628493</v>
       </c>
       <c r="G66" s="18">
-        <f>+([64]Main!$I$6-[64]Main!$I$5)*FX!C12</f>
+        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
         <v>26.92503</v>
       </c>
       <c r="H66" s="18">
@@ -11510,15 +11537,15 @@
         <v>21</v>
       </c>
       <c r="E67" s="25">
-        <f>+[65]Main!$I$2</f>
+        <f>+[61]Main!$I$2</f>
         <v>54.91</v>
       </c>
       <c r="F67" s="18">
-        <f>+[65]Main!$I$4</f>
+        <f>+[61]Main!$I$4</f>
         <v>4407.5666168399994</v>
       </c>
       <c r="G67" s="18">
-        <f>+[65]Main!$I$6-[65]Main!$I$5</f>
+        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
         <v>1102</v>
       </c>
       <c r="H67" s="18">
@@ -11573,15 +11600,15 @@
         <v>21</v>
       </c>
       <c r="E68" s="25">
-        <f>+[66]Main!$H$2</f>
+        <f>+[62]Main!$H$2</f>
         <v>33.92</v>
       </c>
       <c r="F68" s="18">
-        <f>+[66]Main!$H$4</f>
+        <f>+[62]Main!$H$4</f>
         <v>2464.3691366400003</v>
       </c>
       <c r="G68" s="18">
-        <f>+[66]Main!$H$6-[66]Main!$H$5</f>
+        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
         <v>182.17599999999999</v>
       </c>
       <c r="H68" s="18">
@@ -11632,15 +11659,15 @@
         <v>219</v>
       </c>
       <c r="E69" s="25">
-        <f>+[67]Main!$I$2</f>
+        <f>+[63]Main!$I$2</f>
         <v>19.670000000000002</v>
       </c>
       <c r="F69" s="18">
-        <f>+[67]Main!$I$4</f>
+        <f>+[63]Main!$I$4</f>
         <v>2341.6752811900001</v>
       </c>
       <c r="G69" s="18">
-        <f>+[67]Main!$I$6-[67]Main!$I$5</f>
+        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
         <v>1542</v>
       </c>
       <c r="H69" s="18">
@@ -11695,15 +11722,15 @@
         <v>165</v>
       </c>
       <c r="E70" s="25">
-        <f>+[68]Main!$J$2</f>
+        <f>+[64]Main!$J$2</f>
         <v>9.6300000000000008</v>
       </c>
       <c r="F70" s="18">
-        <f>+[68]Main!$J$4*FX!C3</f>
+        <f>+[64]Main!$J$4*FX!C3</f>
         <v>2534.083861608</v>
       </c>
       <c r="G70" s="18">
-        <f>+([68]Main!$J$6-[68]Main!$J$5)*FX!C3</f>
+        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
         <v>122.12512000000007</v>
       </c>
       <c r="H70" s="18">
@@ -11754,15 +11781,15 @@
         <v>185</v>
       </c>
       <c r="E71" s="25">
-        <f>+[69]Main!$J$2</f>
+        <f>+[65]Main!$J$2</f>
         <v>828.4</v>
       </c>
       <c r="F71" s="18">
-        <f>+[69]Main!$J$4*FX!C12</f>
+        <f>+[65]Main!$J$4*FX!C12</f>
         <v>2214.6636811287999</v>
       </c>
       <c r="G71" s="18">
-        <f>+([69]Main!$J$6-[69]Main!$J$5)*FX!C12</f>
+        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
         <v>-1.8833099999999996</v>
       </c>
       <c r="H71" s="18">
@@ -12264,15 +12291,15 @@
         <v>21</v>
       </c>
       <c r="E83" s="25">
-        <f>+[70]Main!$I$2</f>
+        <f>+[66]Main!$I$2</f>
         <v>5.82</v>
       </c>
       <c r="F83" s="18">
-        <f>+[70]Main!$I$4</f>
+        <f>+[66]Main!$I$4</f>
         <v>2055.0937514400002</v>
       </c>
       <c r="G83" s="18">
-        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
+        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
         <v>1971.2029999999997</v>
       </c>
       <c r="H83" s="18">
@@ -12532,15 +12559,15 @@
         <v>21</v>
       </c>
       <c r="E89" s="25">
-        <f>+[71]Main!$H$2</f>
+        <f>+[67]Main!$H$2</f>
         <v>41.42</v>
       </c>
       <c r="F89" s="18">
-        <f>+[71]Main!$H$4</f>
+        <f>+[67]Main!$H$4</f>
         <v>1491.5652650000002</v>
       </c>
       <c r="G89" s="18">
-        <f>+[71]Main!$H$6-[71]Main!$H$5</f>
+        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
         <v>85.194000000000017</v>
       </c>
       <c r="H89" s="18">
@@ -12589,15 +12616,15 @@
         <v>21</v>
       </c>
       <c r="E90" s="25">
-        <f>+[72]Main!$I$2</f>
+        <f>+[68]Main!$I$2</f>
         <v>38.119999999999997</v>
       </c>
       <c r="F90" s="18">
-        <f>+[72]Main!$I$4</f>
+        <f>+[68]Main!$I$4</f>
         <v>1935.4971035199997</v>
       </c>
       <c r="G90" s="18">
-        <f>+[72]Main!$I$6-[72]Main!$I$5</f>
+        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
         <v>-325.44000000000005</v>
       </c>
       <c r="H90" s="18">
@@ -12646,15 +12673,15 @@
         <v>21</v>
       </c>
       <c r="E91" s="25">
-        <f>+[73]Main!$I$2</f>
+        <f>+[69]Main!$I$2</f>
         <v>24.73</v>
       </c>
       <c r="F91" s="18">
-        <f>+[73]Main!$I$4</f>
+        <f>+[69]Main!$I$4</f>
         <v>1761.5194085300002</v>
       </c>
       <c r="G91" s="18">
-        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
+        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
         <v>-256.60000000000002</v>
       </c>
       <c r="H91" s="18">
@@ -12836,15 +12863,15 @@
         <v>21</v>
       </c>
       <c r="E95" s="25">
-        <f>+[74]Main!$I$2</f>
+        <f>+[70]Main!$I$2</f>
         <v>27.07</v>
       </c>
       <c r="F95" s="18">
-        <f>+[74]Main!$I$4</f>
+        <f>+[70]Main!$I$4</f>
         <v>1188.01315849</v>
       </c>
       <c r="G95" s="18">
-        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
+        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
         <v>119.48899999999998</v>
       </c>
       <c r="H95" s="18">
@@ -12893,15 +12920,15 @@
         <v>21</v>
       </c>
       <c r="E96" s="25">
-        <f>+[75]Main!$I$2</f>
+        <f>+[71]Main!$I$2</f>
         <v>59.85</v>
       </c>
       <c r="F96" s="18">
-        <f>+[75]Main!$I$4</f>
+        <f>+[71]Main!$I$4</f>
         <v>939.70682505000002</v>
       </c>
       <c r="G96" s="18">
-        <f>+[75]Main!$I$6-[75]Main!$I$5</f>
+        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
         <v>50.789000000000001</v>
       </c>
       <c r="H96" s="18">
@@ -12950,15 +12977,15 @@
         <v>107</v>
       </c>
       <c r="E97" s="25">
-        <f>+[76]Main!$J$2</f>
+        <f>+[72]Main!$J$2</f>
         <v>14.56</v>
       </c>
       <c r="F97" s="18">
-        <f>+[76]Main!$J$4*FX!C13</f>
+        <f>+[72]Main!$J$4*FX!C13</f>
         <v>975.38578737599994</v>
       </c>
       <c r="G97" s="18">
-        <f>+([76]Main!$J$6-[76]Main!$J$5)*FX!C13</f>
+        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
         <v>47.058000000000028</v>
       </c>
       <c r="H97" s="18">
@@ -13095,15 +13122,15 @@
         <v>21</v>
       </c>
       <c r="E100" s="25">
-        <f>+[77]Main!$I$2</f>
+        <f>+[73]Main!$I$2</f>
         <v>4.53</v>
       </c>
       <c r="F100" s="18">
-        <f>+[77]Main!$I$4</f>
+        <f>+[73]Main!$I$4</f>
         <v>736.21656488999997</v>
       </c>
       <c r="G100" s="18">
-        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
+        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
         <v>-235.51</v>
       </c>
       <c r="H100" s="18">
@@ -13152,15 +13179,15 @@
         <v>21</v>
       </c>
       <c r="E101" s="25">
-        <f>+[78]Main!$I$2</f>
+        <f>+[74]Main!$I$2</f>
         <v>16.75</v>
       </c>
       <c r="F101" s="18">
-        <f>+[78]Main!$I$4</f>
+        <f>+[74]Main!$I$4</f>
         <v>872.38125524999998</v>
       </c>
       <c r="G101" s="18">
-        <f>+[78]Main!$I$6-[78]Main!$I$5</f>
+        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
         <v>434.077</v>
       </c>
       <c r="H101" s="18">
@@ -13811,15 +13838,15 @@
         <v>219</v>
       </c>
       <c r="E116" s="25">
-        <f>+'[79]Main '!$F$2</f>
+        <f>+'[75]Main '!$F$2</f>
         <v>2.4350000000000001</v>
       </c>
       <c r="F116" s="18">
-        <f>+'[79]Main '!$F$4*FX!C8</f>
+        <f>+'[75]Main '!$F$4*FX!C8</f>
         <v>360.19879762439996</v>
       </c>
       <c r="G116" s="18">
-        <f>+('[79]Main '!$F$6-'[79]Main '!$F$5)*FX!C8</f>
+        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
         <v>229.02800000000005</v>
       </c>
       <c r="H116" s="18">
@@ -14126,15 +14153,15 @@
         <v>21</v>
       </c>
       <c r="E123" s="25">
-        <f>+[80]Main!$H$2</f>
+        <f>+[76]Main!$H$2</f>
         <v>0.98</v>
       </c>
       <c r="F123" s="18">
-        <f>+[80]Main!$H$4</f>
+        <f>+[76]Main!$H$4</f>
         <v>97.21301296</v>
       </c>
       <c r="G123" s="18">
-        <f>+[80]Main!$H$6-[80]Main!$H$5</f>
+        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
         <v>274.101</v>
       </c>
       <c r="H123" s="18">
@@ -14226,15 +14253,15 @@
         <v>21</v>
       </c>
       <c r="E125" s="25">
-        <f>+[81]Main!$I$2</f>
+        <f>+[77]Main!$I$2</f>
         <v>17.79</v>
       </c>
       <c r="F125" s="18">
-        <f>+[81]Main!$I$4</f>
+        <f>+[77]Main!$I$4</f>
         <v>270.90115659000003</v>
       </c>
       <c r="G125" s="18">
-        <f>+[81]Main!$I$6-[81]Main!$I$5</f>
+        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
         <v>24.493000000000002</v>
       </c>
       <c r="H125" s="18">
@@ -15487,15 +15514,15 @@
         <v>124</v>
       </c>
       <c r="E154" s="25">
-        <f>+[82]Main!$I$2</f>
+        <f>+[78]Main!$I$2</f>
         <v>2540</v>
       </c>
       <c r="F154" s="18">
-        <f>+[82]Main!$I$4*FX!C5</f>
+        <f>+[78]Main!$I$4*FX!C5</f>
         <v>409.27593709799999</v>
       </c>
       <c r="G154" s="18">
-        <f>+([82]Main!$I$6-[82]Main!$I$5)*FX!C5</f>
+        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
         <v>-123.31619999999999</v>
       </c>
       <c r="H154" s="18">
@@ -15544,15 +15571,15 @@
         <v>21</v>
       </c>
       <c r="E155" s="25">
-        <f>+[83]Main!$J$2</f>
+        <f>+[79]Main!$J$2</f>
         <v>20</v>
       </c>
       <c r="F155" s="18">
-        <f>+[83]Main!$J$4</f>
+        <f>+[79]Main!$J$4</f>
         <v>1638</v>
       </c>
       <c r="G155" s="18">
-        <f>+[83]Main!$J$6-[83]Main!$J$5</f>
+        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
         <v>415.40000000000003</v>
       </c>
       <c r="H155" s="18">
@@ -18081,12 +18108,22 @@
     </row>
     <row r="10" spans="1:32">
       <c r="A10" s="46"/>
-      <c r="B10" s="46"/>
+      <c r="B10" s="98" t="s">
+        <v>867</v>
+      </c>
       <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
+      <c r="D10" s="98" t="s">
+        <v>866</v>
+      </c>
+      <c r="E10" s="77">
+        <v>46112</v>
+      </c>
+      <c r="F10" s="99" t="s">
+        <v>474</v>
+      </c>
+      <c r="G10" s="46">
+        <v>39</v>
+      </c>
       <c r="H10" s="46"/>
       <c r="I10" s="46"/>
       <c r="J10" s="46"/>
@@ -19771,11 +19808,11 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0FC56C3-8711-45A1-8A34-862C4185F0B3}">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
@@ -20081,10 +20118,12 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="46"/>
-      <c r="B15" s="46" t="s">
-        <v>686</v>
-      </c>
-      <c r="C15" s="58"/>
+      <c r="B15" s="98" t="s">
+        <v>865</v>
+      </c>
+      <c r="C15" s="100" t="s">
+        <v>868</v>
+      </c>
       <c r="D15" s="46"/>
       <c r="E15" s="59"/>
       <c r="F15" s="57"/>
@@ -20103,7 +20142,7 @@
     <row r="16" spans="1:17">
       <c r="A16" s="46"/>
       <c r="B16" s="46" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C16" s="58"/>
       <c r="D16" s="46"/>
@@ -20124,7 +20163,7 @@
     <row r="17" spans="1:17">
       <c r="A17" s="46"/>
       <c r="B17" s="46" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="C17" s="58"/>
       <c r="D17" s="46"/>
@@ -20144,16 +20183,12 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="46"/>
-      <c r="B18" s="95" t="s">
-        <v>850</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>803</v>
-      </c>
+      <c r="B18" s="46" t="s">
+        <v>695</v>
+      </c>
+      <c r="C18" s="58"/>
       <c r="D18" s="46"/>
-      <c r="E18" s="59" t="s">
-        <v>804</v>
-      </c>
+      <c r="E18" s="59"/>
       <c r="F18" s="57"/>
       <c r="G18" s="57"/>
       <c r="H18" s="57"/>
@@ -20169,10 +20204,16 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="46"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="58"/>
+      <c r="B19" s="95" t="s">
+        <v>850</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>803</v>
+      </c>
       <c r="D19" s="46"/>
-      <c r="E19" s="59"/>
+      <c r="E19" s="59" t="s">
+        <v>804</v>
+      </c>
       <c r="F19" s="57"/>
       <c r="G19" s="57"/>
       <c r="H19" s="57"/>
@@ -20188,9 +20229,7 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="46"/>
-      <c r="B20" s="81" t="s">
-        <v>822</v>
-      </c>
+      <c r="B20" s="46"/>
       <c r="C20" s="58"/>
       <c r="D20" s="46"/>
       <c r="E20" s="59"/>
@@ -20210,11 +20249,9 @@
     <row r="21" spans="1:17">
       <c r="A21" s="46"/>
       <c r="B21" s="81" t="s">
-        <v>823</v>
-      </c>
-      <c r="C21" s="81" t="s">
-        <v>824</v>
-      </c>
+        <v>822</v>
+      </c>
+      <c r="C21" s="58"/>
       <c r="D21" s="46"/>
       <c r="E21" s="59"/>
       <c r="F21" s="57"/>
@@ -20232,8 +20269,12 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="46"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="58"/>
+      <c r="B22" s="81" t="s">
+        <v>823</v>
+      </c>
+      <c r="C22" s="81" t="s">
+        <v>824</v>
+      </c>
       <c r="D22" s="46"/>
       <c r="E22" s="59"/>
       <c r="F22" s="57"/>
@@ -20252,7 +20293,7 @@
     <row r="23" spans="1:17">
       <c r="A23" s="46"/>
       <c r="B23" s="46"/>
-      <c r="C23" s="72"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="46"/>
       <c r="E23" s="59"/>
       <c r="F23" s="57"/>
@@ -20267,6 +20308,25 @@
       <c r="O23" s="46"/>
       <c r="P23" s="46"/>
       <c r="Q23" s="46"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="46"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21272,15 +21332,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="46">
-        <f>+[84]Main!$J$2</f>
+        <f>+[80]Main!$J$2</f>
         <v>180.8</v>
       </c>
       <c r="F20" s="57">
-        <f>+[84]Main!$J$4</f>
+        <f>+[80]Main!$J$4</f>
         <v>14437.908028799999</v>
       </c>
       <c r="G20" s="57">
-        <f>+[84]Main!$J$6-[84]Main!$J$5</f>
+        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
         <v>-205.72299999999996</v>
       </c>
       <c r="H20" s="57">
@@ -39992,15 +40052,15 @@
         <v>20</v>
       </c>
       <c r="E4" s="59">
-        <f>+[1]Main!$I$2</f>
+        <f>+[81]Main!$I$2</f>
         <v>233</v>
       </c>
       <c r="F4" s="57">
-        <f>+[1]Main!$I$4*FX!C3</f>
+        <f>+[81]Main!$I$4*FX!C3</f>
         <v>111229.45403231999</v>
       </c>
       <c r="G4" s="57">
-        <f>+([1]Main!$I$6-[1]Main!$I$5)*FX!C3</f>
+        <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
         <v>7586.8</v>
       </c>
       <c r="H4" s="57">
@@ -40058,15 +40118,15 @@
         <v>85</v>
       </c>
       <c r="E5" s="59">
-        <f>+[2]Main!$J$2</f>
+        <f>+[82]Main!$J$2</f>
         <v>138.30000000000001</v>
       </c>
       <c r="F5" s="57">
-        <f>+[2]Main!$J$5*FX!C7</f>
+        <f>+[82]Main!$J$5*FX!C7</f>
         <v>96477.902976000012</v>
       </c>
       <c r="G5" s="57">
-        <f>+([2]Main!$J$7-[2]Main!$J$6)*FX!C7</f>
+        <f>+([82]Main!$J$7-[82]Main!$J$6)*FX!C7</f>
         <v>-1444.8000000000002</v>
       </c>
       <c r="H5" s="57">
@@ -40124,15 +40184,15 @@
         <v>21</v>
       </c>
       <c r="E6" s="59">
-        <f>+[3]Main!$K$2</f>
+        <f>+[83]Main!$K$2</f>
         <v>111.2</v>
       </c>
       <c r="F6" s="57">
-        <f>+[3]Main!$K$4</f>
+        <f>+[83]Main!$K$4</f>
         <v>40224.047181599999</v>
       </c>
       <c r="G6" s="57">
-        <f>+([3]Main!$K$6-[3]Main!$K$5)</f>
+        <f>+([83]Main!$K$6-[83]Main!$K$5)</f>
         <v>4240</v>
       </c>
       <c r="H6" s="57">
@@ -40190,15 +40250,15 @@
         <v>85</v>
       </c>
       <c r="E7" s="59">
-        <f>+[4]Main!$I$3</f>
+        <f>+[84]Main!$I$3</f>
         <v>177.95</v>
       </c>
       <c r="F7" s="57">
-        <f>+[4]Main!$I$5*FX!C7</f>
+        <f>+[84]Main!$I$5*FX!C7</f>
         <v>10344.705947284801</v>
       </c>
       <c r="G7" s="57">
-        <f>+([4]Main!$I$7-[4]Main!$I$6)*FX!C7</f>
+        <f>+([84]Main!$I$7-[84]Main!$I$6)*FX!C7</f>
         <v>-1336.16</v>
       </c>
       <c r="H7" s="57">

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0765C58A-6532-4F86-A0D3-B6F49DCB31C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166E7314-9234-4A57-A52A-2F91E543F35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -3218,12 +3218,12 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="I4">
-            <v>549</v>
+            <v>499.3</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>273230.13006</v>
+            <v>248495.08914200001</v>
           </cell>
         </row>
         <row r="7">
@@ -3305,26 +3305,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>141.80000000000001</v>
+            <v>147.4</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>25319.697396000003</v>
+            <v>26118.171109800001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1617</v>
+            <v>873</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>2641</v>
+            <v>2997</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3352,12 +3352,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>284.8</v>
+            <v>256.14999999999998</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>34917.850457599998</v>
+            <v>31405.222593799997</v>
           </cell>
         </row>
         <row r="5">
@@ -3371,14 +3371,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3418,7 +3418,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3523,12 +3523,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>40.880000000000003</v>
+            <v>34.700000000000003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>12552.5670144</v>
+            <v>10654.943136000002</v>
           </cell>
         </row>
         <row r="6">
@@ -3542,11 +3542,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3604,12 +3604,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>55.15</v>
+            <v>53.46</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>14919.336445949999</v>
+            <v>14462.152790580001</v>
           </cell>
         </row>
         <row r="5">
@@ -3688,12 +3688,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>2146</v>
+            <v>1751</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>226551.95815200001</v>
+            <v>184852.040412</v>
           </cell>
         </row>
         <row r="5">
@@ -3956,7 +3956,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4341,26 +4341,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>60</v>
+            <v>63.14</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>8953.7999999999993</v>
+            <v>11754.016119999998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>112.633</v>
+            <v>237.05500000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1754.22</v>
+            <v>4715.1000000000004</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4381,22 +4381,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>21.96</v>
+            <v>22.76</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>8574.6616225199996</v>
+            <v>8753.410672760001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>848.8</v>
+            <v>812</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1039.2</v>
+            <v>1049.4000000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -4545,30 +4545,30 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>99.2</v>
+            <v>102.6</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>5094.5152000000007</v>
+            <v>5098.1578847999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>130.35400000000001</v>
+            <v>130.881</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1230.885</v>
+            <v>1335.8209999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4871,26 +4871,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>24.05</v>
+            <v>25.98</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3545.2105000000001</v>
+            <v>3825.0353999999998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>290</v>
+            <v>326.2</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>572</v>
+            <v>1683.8</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5919,22 +5919,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>62750</v>
+            <v>75540</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>19253241.140000001</v>
+            <v>23177866.739159998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1983578</v>
+            <v>1040505</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>315443</v>
+            <v>255356</v>
           </cell>
         </row>
       </sheetData>
@@ -6393,7 +6393,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6637,7 +6637,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7179,15 +7179,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1855480.446791424</v>
+        <v>1809115.1366617314</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>-1553.4042447999996</v>
+        <v>9259.8985552000031</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1853927.0425466236</v>
+        <v>1818375.0352169308</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7249,15 +7249,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23513.009148462304</v>
+        <v>22926.106488592777</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>-20.174081101298697</v>
+        <v>120.25842279480524</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>24076.974578527581</v>
+        <v>23615.260197622476</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -7356,11 +7356,11 @@
       </c>
       <c r="E6" s="25">
         <f>+[1]Main!$I$4</f>
-        <v>549</v>
+        <v>499.3</v>
       </c>
       <c r="F6" s="18">
         <f>+[1]Main!$I$6*FX!C3</f>
-        <v>284159.33526239998</v>
+        <v>258434.89270768003</v>
       </c>
       <c r="G6" s="18">
         <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
@@ -7368,13 +7368,13 @@
       </c>
       <c r="H6" s="18">
         <f>F6+G6</f>
-        <v>296170.2952624</v>
+        <v>270445.85270768002</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J6" s="27">
-        <v>46125</v>
+        <v>46231</v>
       </c>
       <c r="K6" s="18">
         <f>80807*FX!C3</f>
@@ -7459,11 +7459,11 @@
       </c>
       <c r="E7" s="30">
         <f>+[2]Main!$K$2</f>
-        <v>2146</v>
+        <v>1751</v>
       </c>
       <c r="F7" s="18">
         <f>+[2]Main!$K$4*FX!C3</f>
-        <v>235614.03647808</v>
+        <v>192246.12202848002</v>
       </c>
       <c r="G7" s="18">
         <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
@@ -7471,13 +7471,13 @@
       </c>
       <c r="H7" s="18">
         <f>F7+G7</f>
-        <v>222920.83647807999</v>
+        <v>179552.92202848001</v>
       </c>
       <c r="I7" s="26" t="s">
         <v>338</v>
       </c>
       <c r="J7" s="27">
-        <v>46127</v>
+        <v>46232</v>
       </c>
       <c r="K7" s="18">
         <f>16002*FX!C3</f>
@@ -7929,25 +7929,25 @@
       </c>
       <c r="E12" s="30">
         <f>+[7]Main!$J$3</f>
-        <v>62750</v>
+        <v>75540</v>
       </c>
       <c r="F12" s="18">
         <f>+[7]Main!$J$5*FX!C5</f>
-        <v>121295.419182</v>
+        <v>146020.56045670799</v>
       </c>
       <c r="G12" s="18">
         <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
-        <v>-10509.2505</v>
+        <v>-4946.4386999999997</v>
       </c>
       <c r="H12" s="18">
         <f t="shared" si="1"/>
-        <v>110786.168682</v>
+        <v>141074.12175670799</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>715</v>
+        <v>798</v>
       </c>
       <c r="J12" s="27">
-        <v>46121</v>
+        <v>46212</v>
       </c>
       <c r="K12" s="18">
         <f>2301122*FX!C5</f>
@@ -8246,25 +8246,25 @@
       </c>
       <c r="E16" s="25">
         <f>+[11]Main!$I$2</f>
-        <v>141.80000000000001</v>
+        <v>147.4</v>
       </c>
       <c r="F16" s="18">
         <f>+[11]Main!$I$4*FX!C3</f>
-        <v>26332.485291840003</v>
+        <v>27162.897954192002</v>
       </c>
       <c r="G16" s="18">
         <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
-        <v>1064.96</v>
+        <v>2208.96</v>
       </c>
       <c r="H16" s="18">
         <f>F16+G16</f>
-        <v>27397.445291840002</v>
+        <v>29371.857954192001</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J16" s="27">
-        <v>46141</v>
+        <v>46233</v>
       </c>
       <c r="K16" s="18">
         <f>21427*FX!C3</f>
@@ -8324,11 +8324,11 @@
       </c>
       <c r="E17" s="25">
         <f>+[12]Main!$H$2</f>
-        <v>284.8</v>
+        <v>256.14999999999998</v>
       </c>
       <c r="F17" s="18">
         <f>+[12]Main!$H$4*FX!C3</f>
-        <v>36314.564475904001</v>
+        <v>32661.431497551999</v>
       </c>
       <c r="G17" s="18">
         <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
@@ -8336,13 +8336,13 @@
       </c>
       <c r="H17" s="18">
         <f t="shared" si="1"/>
-        <v>44893.524475904</v>
+        <v>41240.391497552002</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J17" s="27">
-        <v>46133</v>
+        <v>46231</v>
       </c>
       <c r="K17" s="18">
         <f>17194*FX!C3</f>
@@ -8655,11 +8655,11 @@
       </c>
       <c r="E21" s="25">
         <f>+[16]Main!$H$2</f>
-        <v>40.880000000000003</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="F21" s="18">
         <f>+[16]Main!$H$5*FX!C3</f>
-        <v>13054.669694976001</v>
+        <v>11081.140861440002</v>
       </c>
       <c r="G21" s="18">
         <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
@@ -8667,13 +8667,13 @@
       </c>
       <c r="H21" s="18">
         <f t="shared" si="1"/>
-        <v>13544.187294976</v>
+        <v>11570.658461440002</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J21" s="27">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="22"/>
@@ -8775,11 +8775,11 @@
       </c>
       <c r="E23" s="25">
         <f>+[18]Main!$H$2</f>
-        <v>55.15</v>
+        <v>53.46</v>
       </c>
       <c r="F23" s="18">
         <f>+[18]Main!$H$4*FX!C3</f>
-        <v>15516.109903787999</v>
+        <v>15040.638902203202</v>
       </c>
       <c r="G23" s="18">
         <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C3</f>
@@ -8787,10 +8787,10 @@
       </c>
       <c r="H23" s="18">
         <f t="shared" si="1"/>
-        <v>15139.790063787999</v>
+        <v>14664.319062203202</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J23" s="27">
         <v>46225</v>
@@ -9826,25 +9826,25 @@
       </c>
       <c r="E39" s="25">
         <f>+[34]Main!$I$2</f>
-        <v>60</v>
+        <v>63.14</v>
       </c>
       <c r="F39" s="18">
         <f>+[34]Main!$I$4</f>
-        <v>8953.7999999999993</v>
+        <v>11754.016119999998</v>
       </c>
       <c r="G39" s="18">
         <f>+[34]Main!$I$6-[34]Main!$I$5</f>
-        <v>1641.587</v>
+        <v>4478.0450000000001</v>
       </c>
       <c r="H39" s="18">
         <f>F39+G39</f>
-        <v>10595.386999999999</v>
+        <v>16232.061119999998</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="J39" s="27">
-        <v>46076</v>
+        <v>46233</v>
       </c>
       <c r="K39" s="18"/>
       <c r="L39" s="22"/>
@@ -9889,22 +9889,22 @@
       </c>
       <c r="E40" s="25">
         <f>+[35]Main!$I$2</f>
-        <v>21.96</v>
+        <v>22.76</v>
       </c>
       <c r="F40" s="18">
         <f>+[35]Main!$I$4</f>
-        <v>8574.6616225199996</v>
+        <v>8753.410672760001</v>
       </c>
       <c r="G40" s="18">
         <f>+[35]Main!$I$6-[35]Main!$I$5</f>
-        <v>190.40000000000009</v>
+        <v>237.40000000000009</v>
       </c>
       <c r="H40" s="18">
         <f>F40+G40</f>
-        <v>8765.0616225199992</v>
+        <v>8990.8106727600007</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J40" s="27">
         <v>46118</v>
@@ -10141,25 +10141,25 @@
       </c>
       <c r="E44" s="25">
         <f>+[39]Main!$H$2</f>
-        <v>99.2</v>
+        <v>102.6</v>
       </c>
       <c r="F44" s="18">
         <f>+[39]Main!$H$4</f>
-        <v>5094.5152000000007</v>
+        <v>5098.1578847999999</v>
       </c>
       <c r="G44" s="18">
         <f>+[39]Main!$H$6-[39]Main!$H$5</f>
-        <v>1100.5309999999999</v>
+        <v>1204.9399999999998</v>
       </c>
       <c r="H44" s="18">
         <f>F44+G44</f>
-        <v>6195.0462000000007</v>
+        <v>6303.0978847999995</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J44" s="27">
-        <v>46149</v>
+        <v>46240</v>
       </c>
       <c r="K44" s="18"/>
       <c r="L44" s="22"/>
@@ -10566,25 +10566,25 @@
       </c>
       <c r="E51" s="25">
         <f>+[46]Main!$I$2</f>
-        <v>24.05</v>
+        <v>25.98</v>
       </c>
       <c r="F51" s="18">
         <f>+[46]Main!$I$4*FX!C3</f>
-        <v>3687.0189200000004</v>
+        <v>3978.0368159999998</v>
       </c>
       <c r="G51" s="18">
         <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
-        <v>293.28000000000003</v>
+        <v>1411.904</v>
       </c>
       <c r="H51" s="18">
         <f t="shared" si="3"/>
-        <v>3980.2989200000006</v>
+        <v>5389.9408160000003</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J51" s="27">
-        <v>46142</v>
+        <v>46233</v>
       </c>
       <c r="K51" s="18"/>
       <c r="L51" s="22"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166E7314-9234-4A57-A52A-2F91E543F35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A126220-B161-4B86-97C4-0797BC0BAD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3324,7 +3324,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3371,14 +3371,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3542,11 +3542,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3645,12 +3645,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>252.2</v>
+            <v>304.51</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>15870.190913199998</v>
+            <v>19088.948091260001</v>
           </cell>
         </row>
         <row r="5">
@@ -3731,22 +3731,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>154.69999999999999</v>
+            <v>134.28</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>31321.2152981</v>
+            <v>27130.56419592</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>1077.7</v>
+            <v>1046.5220999999999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>2396.4</v>
+            <v>2377.1</v>
           </cell>
         </row>
       </sheetData>
@@ -4057,26 +4057,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>23.62</v>
+            <v>19.87</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>6150.6480000000001</v>
+            <v>5174.1480000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1877.4</v>
+            <v>1259.7</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>778.6</v>
+            <v>715.7</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4360,7 +4360,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4381,12 +4381,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>22.76</v>
+            <v>22.68</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>8753.410672760001</v>
+            <v>8722.6429726799997</v>
           </cell>
         </row>
         <row r="5">
@@ -4564,11 +4564,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4890,7 +4890,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7179,15 +7179,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1809115.1366617314</v>
+        <v>1807096.9150375314</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>9259.8985552000031</v>
+        <v>9848.7684552000028</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1818375.0352169308</v>
+        <v>1816945.6834927304</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7249,15 +7249,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22926.106488592777</v>
+        <v>22900.559379425689</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>120.25842279480524</v>
+        <v>127.90608383376627</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>23615.260197622476</v>
+        <v>23596.697188217277</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -8838,11 +8838,11 @@
       </c>
       <c r="E24" s="25">
         <f>+[19]Main!$I$2</f>
-        <v>252.2</v>
+        <v>304.51</v>
       </c>
       <c r="F24" s="18">
         <f>+[19]Main!$I$4</f>
-        <v>15870.190913199998</v>
+        <v>19088.948091260001</v>
       </c>
       <c r="G24" s="18">
         <f>+[19]Main!$I$6-[19]Main!$I$5</f>
@@ -8850,13 +8850,13 @@
       </c>
       <c r="H24" s="18">
         <f>F24+G24</f>
-        <v>17321.535913199998</v>
+        <v>20540.293091260002</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>149</v>
+        <v>422</v>
       </c>
       <c r="J24" s="27">
-        <v>46086</v>
+        <v>46170</v>
       </c>
       <c r="K24" s="25"/>
       <c r="L24" s="22"/>
@@ -8901,25 +8901,25 @@
       </c>
       <c r="E25" s="25">
         <f>+[20]Main!$J$2</f>
-        <v>154.69999999999999</v>
+        <v>134.28</v>
       </c>
       <c r="F25" s="18">
         <f>+[20]Main!$J$4</f>
-        <v>31321.2152981</v>
+        <v>27130.56419592</v>
       </c>
       <c r="G25" s="18">
         <f>+[20]Main!$J$6-[20]Main!$J$5</f>
-        <v>1318.7</v>
+        <v>1330.5779</v>
       </c>
       <c r="H25" s="18">
         <f t="shared" si="1"/>
-        <v>32639.915298100001</v>
+        <v>28461.14209592</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="J25" s="27">
-        <v>46149</v>
+        <v>46247</v>
       </c>
       <c r="K25" s="25"/>
       <c r="L25" s="22"/>
@@ -9436,26 +9436,24 @@
       </c>
       <c r="E33" s="25">
         <f>+[28]Main!$I$2</f>
-        <v>23.62</v>
+        <v>19.87</v>
       </c>
       <c r="F33" s="18">
         <f>+[28]Main!$I$4*FX!C3</f>
-        <v>6396.6739200000002</v>
+        <v>5381.1139200000007</v>
       </c>
       <c r="G33" s="18">
         <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
-        <v>-1142.7520000000002</v>
+        <v>-565.76</v>
       </c>
       <c r="H33" s="18">
         <f>F33+G33</f>
-        <v>5253.9219199999998</v>
+        <v>4815.3539200000005</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>422</v>
-      </c>
-      <c r="J33" s="27">
-        <v>46148</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="J33" s="27"/>
       <c r="K33" s="25"/>
       <c r="L33" s="22"/>
       <c r="M33" s="25"/>
@@ -9889,11 +9887,11 @@
       </c>
       <c r="E40" s="25">
         <f>+[35]Main!$I$2</f>
-        <v>22.76</v>
+        <v>22.68</v>
       </c>
       <c r="F40" s="18">
         <f>+[35]Main!$I$4</f>
-        <v>8753.410672760001</v>
+        <v>8722.6429726799997</v>
       </c>
       <c r="G40" s="18">
         <f>+[35]Main!$I$6-[35]Main!$I$5</f>
@@ -9901,13 +9899,13 @@
       </c>
       <c r="H40" s="18">
         <f>F40+G40</f>
-        <v>8990.8106727600007</v>
+        <v>8960.0429726799994</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>829</v>
       </c>
       <c r="J40" s="27">
-        <v>46118</v>
+        <v>46212</v>
       </c>
       <c r="K40" s="18">
         <v>6179</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A126220-B161-4B86-97C4-0797BC0BAD4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EACF5A-BDBC-4BF4-97DC-EB5E6FB9FEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="872">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2766,6 +2766,15 @@
   </si>
   <si>
     <t>Brands: Ed Hardy, Allbirds etc.</t>
+  </si>
+  <si>
+    <t>Marc Jacob</t>
+  </si>
+  <si>
+    <t>WHP Global: (joint venture with G-III Apparel Group)</t>
+  </si>
+  <si>
+    <t>FQ425</t>
   </si>
 </sst>
 </file>
@@ -2779,13 +2788,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2982,22 +2997,100 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3011,175 +3104,101 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3771,22 +3790,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>4396</v>
+            <v>4496</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3141807.6866959999</v>
+            <v>3186338.7905119997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>112267</v>
+            <v>119389</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>37500</v>
+            <v>75000</v>
           </cell>
         </row>
       </sheetData>
@@ -3854,22 +3873,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>41.04</v>
+            <v>36.42</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>10356.130046052</v>
+            <v>9190.3083888210003</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1019.9</v>
+            <v>1020.4</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>59.5</v>
+            <v>58</v>
           </cell>
         </row>
       </sheetData>
@@ -4076,7 +4095,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4181,22 +4200,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>33.710999999999999</v>
+            <v>29.172000000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>6199.6570538160004</v>
+            <v>5364.9074656319999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>229.227</v>
+            <v>201.46700000000001</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>1140.2079999999999</v>
+            <v>1148.6680000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -4997,17 +5016,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>55.02</v>
+            <v>58.06</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2880.3823910400001</v>
+            <v>2969.2344415800003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>790.7940000000001</v>
+            <v>535.35400000000004</v>
           </cell>
         </row>
         <row r="6">
@@ -5077,26 +5096,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>76.37</v>
+            <v>80.760000000000005</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>3497.9518935199999</v>
+            <v>3699.7390012800006</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>158.19999999999999</v>
+            <v>701.6</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>2258.7999999999997</v>
+            <v>2291.4</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5155,22 +5174,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>11.96</v>
+            <v>10.93</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4310.384</v>
+            <v>3916.2190000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>452</v>
+            <v>671</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>545</v>
+            <v>568</v>
           </cell>
         </row>
       </sheetData>
@@ -5355,22 +5374,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>36.299999999999997</v>
+            <v>35.700000000000003</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2505.286971</v>
+            <v>2463.8772690000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>343.12599999999998</v>
+            <v>314</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>295.77</v>
+            <v>297</v>
           </cell>
         </row>
       </sheetData>
@@ -5395,26 +5414,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>7.47</v>
+            <v>4.97</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3181.39830747</v>
+            <v>2117.1355100000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>464.64800000000002</v>
+            <v>309.16800000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>989.73099999999999</v>
+            <v>1190.444</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5679,26 +5698,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>9.6300000000000008</v>
+            <v>10.61</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2436.6190977000001</v>
+            <v>2684.5824118999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>231.22499999999997</v>
+            <v>297.553</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>348.65300000000002</v>
+            <v>246.18899999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6054,26 +6073,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>14.56</v>
+            <v>13.57</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1413.6025904000001</v>
+            <v>1318.1272015899999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>346.9</v>
+            <v>408.2</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>415.1</v>
+            <v>410.59999999999997</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7179,15 +7198,15 @@
       </c>
       <c r="F4" s="18">
         <f>SUM(F6:F153)</f>
-        <v>1807096.9150375314</v>
+        <v>1804168.9836630011</v>
       </c>
       <c r="G4" s="18">
         <f>SUM(G6:G153)</f>
-        <v>9848.7684552000028</v>
+        <v>9783.1962152000033</v>
       </c>
       <c r="H4" s="18">
         <f>SUM(H6:H153)</f>
-        <v>1816945.6834927304</v>
+        <v>1813952.1798782004</v>
       </c>
       <c r="I4" s="83" t="s">
         <v>422</v>
@@ -7249,15 +7268,15 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22900.559379425689</v>
+        <v>22863.496956963281</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
-        <v>127.90608383376627</v>
+        <v>127.05449630129874</v>
       </c>
       <c r="H5" s="87">
         <f>AVERAGE(H6:H153)</f>
-        <v>23596.697188217277</v>
+        <v>23557.820517898708</v>
       </c>
       <c r="I5" s="88" t="s">
         <v>422</v>
@@ -8964,25 +8983,25 @@
       </c>
       <c r="E26" s="25">
         <f>+[21]Main!$I$2</f>
-        <v>4396</v>
+        <v>4496</v>
       </c>
       <c r="F26" s="18">
         <f>+[21]Main!$I$4*FX!C5</f>
-        <v>19793.3884261848</v>
+        <v>20073.934380225597</v>
       </c>
       <c r="G26" s="18">
         <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C5</f>
-        <v>-471.03210000000001</v>
+        <v>-279.65070000000003</v>
       </c>
       <c r="H26" s="18">
         <f>F26+G26</f>
-        <v>19322.356326184799</v>
+        <v>19794.283680225599</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J26" s="27">
-        <v>46155</v>
+        <v>46247</v>
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="22"/>
@@ -9090,25 +9109,25 @@
       </c>
       <c r="E28" s="25">
         <f>+[23]Main!$H$2</f>
-        <v>41.04</v>
+        <v>36.42</v>
       </c>
       <c r="F28" s="18">
         <f>+[23]Main!$H$5*FX!C7</f>
-        <v>11598.86565157824</v>
+        <v>10293.145395479522</v>
       </c>
       <c r="G28" s="18">
         <f>+([23]Main!$H$7-[23]Main!$H$6)*FX!C7</f>
-        <v>-1075.6480000000001</v>
+        <v>-1077.8880000000001</v>
       </c>
       <c r="H28" s="18">
         <f>F28+G28</f>
-        <v>10523.217651578241</v>
+        <v>9215.2573954795207</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>422</v>
+        <v>829</v>
       </c>
       <c r="J28" s="27">
-        <v>46154</v>
+        <v>46245</v>
       </c>
       <c r="K28" s="25"/>
       <c r="L28" s="22"/>
@@ -9560,25 +9579,25 @@
       </c>
       <c r="E35" s="25">
         <f>+[30]Main!$I$3</f>
-        <v>33.710999999999999</v>
+        <v>29.172000000000001</v>
       </c>
       <c r="F35" s="18">
         <f>+[30]Main!$I$5*FX!C3</f>
-        <v>6447.6433359686407</v>
+        <v>5579.5037642572797</v>
       </c>
       <c r="G35" s="18">
         <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
-        <v>947.42023999999992</v>
+        <v>985.08904000000018</v>
       </c>
       <c r="H35" s="18">
         <f t="shared" si="1"/>
-        <v>7395.0635759686411</v>
+        <v>6564.5928042572796</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="J35" s="27">
-        <v>46157</v>
+        <v>46247</v>
       </c>
       <c r="K35" s="18"/>
       <c r="L35" s="22"/>
@@ -9779,7 +9798,7 @@
         <v>422</v>
       </c>
       <c r="J38" s="27">
-        <v>46093</v>
+        <v>46210</v>
       </c>
       <c r="K38" s="18"/>
       <c r="L38" s="22"/>
@@ -10765,25 +10784,25 @@
       </c>
       <c r="E54" s="25">
         <f>+[49]Main!$I$2</f>
-        <v>55.02</v>
+        <v>58.06</v>
       </c>
       <c r="F54" s="18">
         <f>+[49]Main!$I$4</f>
-        <v>2880.3823910400001</v>
+        <v>2969.2344415800003</v>
       </c>
       <c r="G54" s="18">
         <f>+[49]Main!$I$6-[49]Main!$I$5</f>
-        <v>-790.7940000000001</v>
+        <v>-535.35400000000004</v>
       </c>
       <c r="H54" s="18">
         <f t="shared" si="3"/>
-        <v>2089.5883910399998</v>
+        <v>2433.8804415800005</v>
       </c>
       <c r="I54" s="17" t="s">
         <v>422</v>
       </c>
       <c r="J54" s="27">
-        <v>46142</v>
+        <v>46233</v>
       </c>
       <c r="K54" s="18"/>
       <c r="L54" s="22"/>
@@ -10828,25 +10847,25 @@
       </c>
       <c r="E55" s="25">
         <f>+[50]Main!$J$2</f>
-        <v>76.37</v>
+        <v>80.760000000000005</v>
       </c>
       <c r="F55" s="18">
         <f>+[50]Main!$J$4</f>
-        <v>3497.9518935199999</v>
+        <v>3699.7390012800006</v>
       </c>
       <c r="G55" s="18">
         <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
-        <v>2100.6</v>
+        <v>1589.8000000000002</v>
       </c>
       <c r="H55" s="18">
         <f>F55+G55</f>
-        <v>5598.5518935199998</v>
+        <v>5289.5390012800008</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>814</v>
+        <v>422</v>
       </c>
       <c r="J55" s="27">
-        <v>46108</v>
+        <v>46177</v>
       </c>
       <c r="K55" s="18"/>
       <c r="L55" s="22"/>
@@ -10954,26 +10973,24 @@
       </c>
       <c r="E57" s="25">
         <f>+[52]Main!$I$2</f>
-        <v>11.96</v>
+        <v>10.93</v>
       </c>
       <c r="F57" s="18">
         <f>+[52]Main!$I$4*FX!C3</f>
-        <v>4482.79936</v>
+        <v>4072.8677600000001</v>
       </c>
       <c r="G57" s="18">
         <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
-        <v>96.72</v>
+        <v>-107.12</v>
       </c>
       <c r="H57" s="18">
         <f>+F57+G57</f>
-        <v>4579.5193600000002</v>
+        <v>3965.7477600000002</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="J57" s="27">
-        <v>46156</v>
-      </c>
+        <v>830</v>
+      </c>
+      <c r="J57" s="27"/>
       <c r="K57" s="18"/>
       <c r="L57" s="22"/>
       <c r="M57" s="18"/>
@@ -11302,26 +11319,24 @@
       </c>
       <c r="E63" s="25">
         <f>+[57]Main!$J$2</f>
-        <v>36.299999999999997</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="F63" s="18">
         <f>+[57]Main!$J$4*FX!C3</f>
-        <v>2605.4984498399999</v>
+        <v>2562.4323597600001</v>
       </c>
       <c r="G63" s="18">
         <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
-        <v>-49.250239999999998</v>
+        <v>-17.68</v>
       </c>
       <c r="H63" s="18">
         <f>+F63+G63</f>
-        <v>2556.2482098400001</v>
+        <v>2544.7523597600002</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>422</v>
-      </c>
-      <c r="J63" s="27">
-        <v>46147</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="J63" s="27"/>
       <c r="K63" s="18"/>
       <c r="L63" s="22"/>
       <c r="M63" s="18"/>
@@ -11361,25 +11376,25 @@
       </c>
       <c r="E64" s="25">
         <f>+[58]Main!$I$2</f>
-        <v>7.47</v>
+        <v>4.97</v>
       </c>
       <c r="F64" s="18">
         <f>+[58]Main!$I$4</f>
-        <v>3181.39830747</v>
+        <v>2117.1355100000001</v>
       </c>
       <c r="G64" s="18">
         <f>+[58]Main!$I$6-[58]Main!$I$5</f>
-        <v>525.08299999999997</v>
+        <v>881.27599999999995</v>
       </c>
       <c r="H64" s="18">
         <f>+F64+G64</f>
-        <v>3706.48130747</v>
+        <v>2998.4115099999999</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="J64" s="27">
-        <v>46156</v>
+        <v>46241</v>
       </c>
       <c r="K64" s="18"/>
       <c r="L64" s="22"/>
@@ -11721,25 +11736,25 @@
       </c>
       <c r="E70" s="25">
         <f>+[64]Main!$J$2</f>
-        <v>9.6300000000000008</v>
+        <v>10.61</v>
       </c>
       <c r="F70" s="18">
         <f>+[64]Main!$J$4*FX!C3</f>
-        <v>2534.083861608</v>
+        <v>2791.9657083759998</v>
       </c>
       <c r="G70" s="18">
         <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
-        <v>122.12512000000007</v>
+        <v>-53.418560000000006</v>
       </c>
       <c r="H70" s="18">
         <f>+F70+G70</f>
-        <v>2656.2089816080002</v>
+        <v>2738.5471483759998</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>149</v>
+        <v>422</v>
       </c>
       <c r="J70" s="27">
-        <v>45953</v>
+        <v>46226</v>
       </c>
       <c r="K70" s="18"/>
       <c r="L70" s="22"/>
@@ -12976,25 +12991,25 @@
       </c>
       <c r="E97" s="25">
         <f>+[72]Main!$J$2</f>
-        <v>14.56</v>
+        <v>13.57</v>
       </c>
       <c r="F97" s="18">
         <f>+[72]Main!$J$4*FX!C13</f>
-        <v>975.38578737599994</v>
+        <v>909.50776909709987</v>
       </c>
       <c r="G97" s="18">
         <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
-        <v>47.058000000000028</v>
+        <v>1.6559999999999842</v>
       </c>
       <c r="H97" s="18">
         <f>+F97+G97</f>
-        <v>1022.4437873759999</v>
+        <v>911.16376909709982</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>820</v>
+        <v>871</v>
       </c>
       <c r="J97" s="27">
-        <v>46162</v>
+        <v>46233</v>
       </c>
       <c r="K97" s="18"/>
       <c r="L97" s="22"/>
@@ -18150,12 +18165,24 @@
     </row>
     <row r="11" spans="1:32">
       <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
+      <c r="B11" s="101" t="s">
+        <v>869</v>
+      </c>
+      <c r="C11" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="101" t="s">
+        <v>870</v>
+      </c>
+      <c r="E11" s="77">
+        <v>46156</v>
+      </c>
+      <c r="F11" s="102" t="s">
+        <v>474</v>
+      </c>
+      <c r="G11" s="46">
+        <v>850</v>
+      </c>
       <c r="H11" s="46"/>
       <c r="I11" s="46"/>
       <c r="J11" s="46"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EACF5A-BDBC-4BF4-97DC-EB5E6FB9FEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B648EF0-D012-490E-97A5-54D7FA3C3316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2788,13 +2788,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2997,22 +3003,100 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3026,177 +3110,102 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -5115,7 +5124,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5433,7 +5442,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5717,7 +5726,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6092,7 +6101,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6353,26 +6362,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>20</v>
+            <v>15.35</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1638</v>
+            <v>1258.5394543499999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>206.3</v>
+            <v>119.6</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>621.70000000000005</v>
+            <v>546.9</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6433,26 +6442,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>180.8</v>
+            <v>215.35</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>14437.908028799999</v>
+            <v>19175.813831250001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>1689.94</v>
+            <v>1353.2260000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1484.2170000000001</v>
+            <v>1905.299</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6474,12 +6483,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>233</v>
+            <v>173.25</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>106951.39810799999</v>
+            <v>79525.020267</v>
           </cell>
         </row>
         <row r="5">
@@ -6493,8 +6502,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6557,26 +6566,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>111.2</v>
+            <v>80.58</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>40224.047181599999</v>
+            <v>29153.4342507</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>3082</v>
+            <v>3126</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>7322</v>
+            <v>7312</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7268,7 +7277,7 @@
       </c>
       <c r="F5" s="87">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22863.496956963281</v>
+        <v>22858.69365891708</v>
       </c>
       <c r="G5" s="87">
         <f>AVERAGE(G6:G153)</f>
@@ -15585,19 +15594,19 @@
       </c>
       <c r="E155" s="25">
         <f>+[79]Main!$J$2</f>
-        <v>20</v>
+        <v>15.35</v>
       </c>
       <c r="F155" s="18">
         <f>+[79]Main!$J$4</f>
-        <v>1638</v>
+        <v>1258.5394543499999</v>
       </c>
       <c r="G155" s="18">
         <f>+[79]Main!$J$6-[79]Main!$J$5</f>
-        <v>415.40000000000003</v>
+        <v>427.29999999999995</v>
       </c>
       <c r="H155" s="18">
         <f>+F155+G155</f>
-        <v>2053.4</v>
+        <v>1685.8394543499999</v>
       </c>
       <c r="I155" s="17" t="s">
         <v>422</v>
@@ -21358,22 +21367,22 @@
       </c>
       <c r="E20" s="46">
         <f>+[80]Main!$J$2</f>
-        <v>180.8</v>
+        <v>215.35</v>
       </c>
       <c r="F20" s="57">
         <f>+[80]Main!$J$4</f>
-        <v>14437.908028799999</v>
+        <v>19175.813831250001</v>
       </c>
       <c r="G20" s="57">
         <f>+[80]Main!$J$6-[80]Main!$J$5</f>
-        <v>-205.72299999999996</v>
+        <v>552.07299999999987</v>
       </c>
       <c r="H20" s="57">
         <f>+F20+G20</f>
-        <v>14232.185028799999</v>
-      </c>
-      <c r="I20" s="47" t="s">
-        <v>338</v>
+        <v>19727.886831250002</v>
+      </c>
+      <c r="I20" s="103" t="s">
+        <v>422</v>
       </c>
       <c r="J20" s="46"/>
       <c r="K20" s="46"/>
@@ -40078,11 +40087,11 @@
       </c>
       <c r="E4" s="59">
         <f>+[81]Main!$I$2</f>
-        <v>233</v>
+        <v>173.25</v>
       </c>
       <c r="F4" s="57">
         <f>+[81]Main!$I$4*FX!C3</f>
-        <v>111229.45403231999</v>
+        <v>82706.021077680009</v>
       </c>
       <c r="G4" s="57">
         <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
@@ -40090,13 +40099,13 @@
       </c>
       <c r="H4" s="57">
         <f>+F4+G4</f>
-        <v>118816.25403231999</v>
+        <v>90292.821077680012</v>
       </c>
       <c r="I4" s="93" t="s">
         <v>422</v>
       </c>
       <c r="J4" s="61">
-        <v>46134</v>
+        <v>46231</v>
       </c>
       <c r="K4" s="59"/>
       <c r="L4" s="62"/>
@@ -40210,26 +40219,24 @@
       </c>
       <c r="E6" s="59">
         <f>+[83]Main!$K$2</f>
-        <v>111.2</v>
+        <v>80.58</v>
       </c>
       <c r="F6" s="57">
         <f>+[83]Main!$K$4</f>
-        <v>40224.047181599999</v>
+        <v>29153.4342507</v>
       </c>
       <c r="G6" s="57">
         <f>+([83]Main!$K$6-[83]Main!$K$5)</f>
-        <v>4240</v>
+        <v>4186</v>
       </c>
       <c r="H6" s="57">
         <f t="shared" si="0"/>
-        <v>44464.047181599999</v>
-      </c>
-      <c r="I6" s="93" t="s">
-        <v>808</v>
-      </c>
-      <c r="J6" s="61">
-        <v>46143</v>
-      </c>
+        <v>33339.434250699996</v>
+      </c>
+      <c r="I6" s="103" t="s">
+        <v>821</v>
+      </c>
+      <c r="J6" s="61"/>
       <c r="K6" s="59"/>
       <c r="L6" s="62"/>
       <c r="M6" s="59"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6841EE4C-3C90-4DFB-8362-587B51B8545D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14EED8F-FD96-4771-BD1C-EB2DB98750A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="780" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="899">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2790,6 +2790,72 @@
   </si>
   <si>
     <t>Q127</t>
+  </si>
+  <si>
+    <t>Atelier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Werksatt eines Couturiers -&gt; Modelle entworfen und handgefetigt </t>
+  </si>
+  <si>
+    <t>Chabre Syndicale de la Haute Coutre</t>
+  </si>
+  <si>
+    <t>Verband der Pariser Haute-Couture Häuser (seit 1868)</t>
+  </si>
+  <si>
+    <t>Look</t>
+  </si>
+  <si>
+    <t>Einzlenes Outfit innerhalb einer Kollektion</t>
+  </si>
+  <si>
+    <t>Capsule Collection</t>
+  </si>
+  <si>
+    <t>kleine, zeitlich limitierte Kollektion</t>
+  </si>
+  <si>
+    <t>Kurze Kollektionszyklen und niedrigen Preispunkten</t>
+  </si>
+  <si>
+    <t>Silhouette</t>
+  </si>
+  <si>
+    <t>Gesamte äußere Kontur eines Kleidungsstücks</t>
+  </si>
+  <si>
+    <t>Toile</t>
+  </si>
+  <si>
+    <t>Probemodell um Passform und Konstruktion zu testen</t>
+  </si>
+  <si>
+    <t>Trunk Show</t>
+  </si>
+  <si>
+    <t>Exklusive Präsentation einer Kollektion in einem Einzelhandelgeschäft</t>
+  </si>
+  <si>
+    <t>Greige</t>
+  </si>
+  <si>
+    <t>Ungefärbtes Rohmaterial</t>
+  </si>
+  <si>
+    <t>Courturier</t>
+  </si>
+  <si>
+    <t>Inhaber/Leitender Designer eines Haute-Couture Hauses</t>
+  </si>
+  <si>
+    <t>Maison</t>
+  </si>
+  <si>
+    <t>Tradionreiches Modehaus</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -2803,13 +2869,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3012,21 +3084,99 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3040,183 +3190,106 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
@@ -3299,12 +3372,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>156.36000000000001</v>
+            <v>127.35</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>17275.07043756</v>
+            <v>14069.968151849998</v>
           </cell>
         </row>
         <row r="5">
@@ -4152,7 +4225,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4646,9 +4719,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4886,7 +4959,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4990,17 +5063,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>95.69</v>
+            <v>83.06</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>4527.9551099999999</v>
+            <v>3735.1251400000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>784.57600000000002</v>
+            <v>619.22400000000005</v>
           </cell>
         </row>
         <row r="6">
@@ -5009,10 +5082,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5675,26 +5748,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>19.670000000000002</v>
+            <v>18.14</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2341.6752811900001</v>
+            <v>2154.9996926600002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>129</v>
+            <v>135</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1671</v>
+            <v>357</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6552,8 +6625,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6673,7 +6746,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7215,15 +7288,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1804913.2447462713</v>
+        <v>1800728.636902031</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>10241.959215200002</v>
+        <v>9087.3112152000031</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1815155.2039614709</v>
+        <v>1809815.9481172308</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7285,15 +7358,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22868.114685287586</v>
+        <v>22815.144965740241</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>133.01245734025977</v>
+        <v>118.01702876883121</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23573.444207291828</v>
+        <v>23504.103222301699</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -8205,11 +8278,11 @@
       </c>
       <c r="E15" s="24">
         <f>+[10]Main!$I$2</f>
-        <v>156.36000000000001</v>
+        <v>127.35</v>
       </c>
       <c r="F15" s="17">
         <f>+[10]Main!$I$4</f>
-        <v>17275.07043756</v>
+        <v>14069.968151849998</v>
       </c>
       <c r="G15" s="17">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
@@ -8217,7 +8290,7 @@
       </c>
       <c r="H15" s="17">
         <f>F15+G15</f>
-        <v>15467.868437560001</v>
+        <v>12262.766151849999</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>422</v>
@@ -10722,26 +10795,24 @@
       </c>
       <c r="E53" s="24">
         <f>+[48]Main!$I$2</f>
-        <v>95.69</v>
+        <v>83.06</v>
       </c>
       <c r="F53" s="17">
         <f>+[48]Main!$I$4</f>
-        <v>4527.9551099999999</v>
+        <v>3735.1251400000001</v>
       </c>
       <c r="G53" s="17">
         <f>+[48]Main!$I$6-[48]Main!$I$5</f>
-        <v>-784.57600000000002</v>
+        <v>-619.22400000000005</v>
       </c>
       <c r="H53" s="17">
         <f>F53+G53</f>
-        <v>3743.3791099999999</v>
+        <v>3115.9011399999999</v>
       </c>
       <c r="I53" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="J53" s="26">
-        <v>46169</v>
-      </c>
+        <v>828</v>
+      </c>
+      <c r="J53" s="26"/>
       <c r="K53" s="17">
         <v>4280.7</v>
       </c>
@@ -11686,25 +11757,25 @@
       </c>
       <c r="E69" s="24">
         <f>+[63]Main!$I$2</f>
-        <v>19.670000000000002</v>
+        <v>18.14</v>
       </c>
       <c r="F69" s="17">
         <f>+[63]Main!$I$4</f>
-        <v>2341.6752811900001</v>
+        <v>2154.9996926600002</v>
       </c>
       <c r="G69" s="17">
         <f>+[63]Main!$I$6-[63]Main!$I$5</f>
-        <v>1542</v>
+        <v>222</v>
       </c>
       <c r="H69" s="17">
         <f>+F69+G69</f>
-        <v>3883.6752811900001</v>
+        <v>2376.9996926600002</v>
       </c>
       <c r="I69" s="16" t="s">
-        <v>380</v>
+        <v>827</v>
       </c>
       <c r="J69" s="26">
-        <v>45805</v>
+        <v>46239</v>
       </c>
       <c r="K69" s="17"/>
       <c r="L69" s="21"/>
@@ -50682,11 +50753,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4991721E-8381-4599-A817-7308E9F2867F}">
-  <dimension ref="B3:K13"/>
+  <dimension ref="B3:K26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -50866,7 +50937,103 @@
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="103" t="s">
+        <v>877</v>
+      </c>
+      <c r="C14" s="103" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="103" t="s">
+        <v>879</v>
+      </c>
+      <c r="C15" s="103" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="103" t="s">
+        <v>881</v>
+      </c>
+      <c r="C16" s="103" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="103" t="s">
+        <v>883</v>
+      </c>
+      <c r="C17" s="103" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="103" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="103" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="103" t="s">
+        <v>886</v>
+      </c>
+      <c r="C19" s="103" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="103" t="s">
+        <v>888</v>
+      </c>
+      <c r="C20" s="103" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="103" t="s">
+        <v>890</v>
+      </c>
+      <c r="C21" s="103" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="103" t="s">
+        <v>892</v>
+      </c>
+      <c r="C22" s="103" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="103" t="s">
+        <v>894</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="103" t="s">
+        <v>896</v>
+      </c>
+      <c r="C24" s="103" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="44" t="s">
+        <v>898</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B26" r:id="rId1" xr:uid="{2497FE43-AD89-4E81-A1FB-4BB8A8E28BD7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14EED8F-FD96-4771-BD1C-EB2DB98750A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6242176-F75D-4675-AAC8-609DA6BF69AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="780" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2869,13 +2869,19 @@
     <numFmt numFmtId="167" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3084,21 +3090,99 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3112,184 +3196,109 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="14" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
@@ -4330,26 +4339,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>25.5</v>
+            <v>21.27</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>9484.0043700000006</v>
+            <v>7806.09</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>2517</v>
+            <v>2561</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1491</v>
+            <v>1492</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5082,10 +5091,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5767,7 +5776,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6523,26 +6532,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>215.35</v>
+            <v>225.4</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>19175.813831250001</v>
+            <v>19955.789000000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>1353.2260000000001</v>
+            <v>998.22799999999995</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1905.299</v>
+            <v>1905.81</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7288,15 +7297,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1800728.636902031</v>
+        <v>1799050.7225320311</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>9087.3112152000031</v>
+        <v>9044.3112152000031</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1809815.9481172308</v>
+        <v>1808095.0337472309</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7358,15 +7367,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22815.144965740241</v>
+        <v>22793.905543335179</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>118.01702876883121</v>
+        <v>117.45858721038965</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23504.103222301699</v>
+        <v>23481.753685028973</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -9730,25 +9739,25 @@
       </c>
       <c r="E36" s="24">
         <f>+[31]Main!$J$2</f>
-        <v>25.5</v>
+        <v>21.27</v>
       </c>
       <c r="F36" s="17">
         <f>+[31]Main!$J$4</f>
-        <v>9484.0043700000006</v>
+        <v>7806.09</v>
       </c>
       <c r="G36" s="17">
         <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
-        <v>-1026</v>
+        <v>-1069</v>
       </c>
       <c r="H36" s="17">
         <f>+G36+F36</f>
-        <v>8458.0043700000006</v>
+        <v>6737.09</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>422</v>
+        <v>828</v>
       </c>
       <c r="J36" s="26">
-        <v>46170</v>
+        <v>46261</v>
       </c>
       <c r="K36" s="17">
         <v>14889</v>
@@ -20425,24 +20434,26 @@
       </c>
       <c r="E20" s="45">
         <f>+[80]Main!$J$2</f>
-        <v>215.35</v>
+        <v>225.4</v>
       </c>
       <c r="F20" s="56">
         <f>+[80]Main!$J$4</f>
-        <v>19175.813831250001</v>
+        <v>19955.789000000001</v>
       </c>
       <c r="G20" s="56">
         <f>+[80]Main!$J$6-[80]Main!$J$5</f>
-        <v>552.07299999999987</v>
+        <v>907.58199999999999</v>
       </c>
       <c r="H20" s="56">
         <f>+F20+G20</f>
-        <v>19727.886831250002</v>
-      </c>
-      <c r="I20" s="96" t="s">
-        <v>422</v>
-      </c>
-      <c r="J20" s="45"/>
+        <v>20863.370999999999</v>
+      </c>
+      <c r="I20" s="104" t="s">
+        <v>828</v>
+      </c>
+      <c r="J20" s="60">
+        <v>46261</v>
+      </c>
       <c r="K20" s="45"/>
       <c r="L20" s="45"/>
       <c r="M20" s="45"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr updateLinks="always"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6242176-F75D-4675-AAC8-609DA6BF69AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4ABFB7B-4E81-4451-85A0-6F9329426EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="900">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2856,6 +2856,9 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>VSXY</t>
   </si>
 </sst>
 </file>
@@ -3327,44 +3330,78 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
       <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>225.4</v>
+          </cell>
+        </row>
         <row r="4">
-          <cell r="I4">
-            <v>499.3</v>
+          <cell r="J4">
+            <v>19955.789000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>998.22799999999995</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="I6">
-            <v>248495.08914200001</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>8794</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="I8">
-            <v>20343</v>
+          <cell r="J6">
+            <v>1905.81</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="H3">
+            <v>232.02</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>74236.423139999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4130.9799999999996</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>1018.1869999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3381,17 +3418,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>127.35</v>
+            <v>114.34</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>14069.968151849998</v>
+            <v>12398.796003380001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1807.202</v>
+            <v>1514.729</v>
           </cell>
         </row>
         <row r="6">
@@ -3400,15 +3437,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3448,7 +3485,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3502,7 +3539,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3542,7 +3579,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3582,7 +3619,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3622,7 +3659,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3670,7 +3707,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3706,7 +3743,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3748,7 +3785,53 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="I4">
+            <v>499.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>248495.08914200001</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>8794</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>20343</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3788,7 +3871,373 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>134.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>27130.56419592</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1046.5220999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2377.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4496</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3186338.7905119997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>119389</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>75000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>127.35</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>14912.684999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>441.1</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>781.30000000000007</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="KPIs"/>
+      <sheetName val="CoC"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>36.42</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>9190.3083888210003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1020.4</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>58</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>35.26</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>19918.456120539999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>683.7</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>144.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>47.12</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>62332.018625043194</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>25437.420999999998</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>14701.28</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>376.91</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>22473.766070860001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2065</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1238.9000000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>76.739999999999995</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>89555.579999999987</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>6221.5751200000004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>898.55169000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>19.87</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5174.1480000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1259.7</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>715.7</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3834,373 +4283,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>134.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>27130.56419592</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>1046.5220999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2377.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4496</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3186338.7905119997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>119389</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>75000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>127.35</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>14912.684999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>441.1</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>781.30000000000007</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="KPIs"/>
-      <sheetName val="CoC"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>36.42</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>9190.3083888210003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1020.4</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>58</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>35.26</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>19918.456120539999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>683.7</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>144.9</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>47.12</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>62332.018625043194</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>25437.420999999998</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>14701.28</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>376.91</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>22473.766070860001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2065</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1238.9000000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>76.739999999999995</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>89555.579999999987</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>6221.5751200000004</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>898.55169000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>19.87</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>5174.1480000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1259.7</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>715.7</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4234,57 +4317,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="J3">
-            <v>52.82</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>164591.95229051998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>10960</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4324,7 +4363,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4358,13 +4397,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4404,7 +4443,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4444,7 +4483,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4484,7 +4523,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4524,7 +4563,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4564,7 +4603,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4604,7 +4643,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4644,7 +4683,51 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="J3">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>171386.35277500001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>10797</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4692,51 +4775,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>159.16999999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>178270.4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5580</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>2870</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4776,7 +4815,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4816,7 +4855,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4856,7 +4895,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4896,7 +4935,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4934,7 +4973,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4974,7 +5013,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5014,7 +5053,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5054,7 +5093,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5100,7 +5139,51 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>159.16999999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>178270.4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5580</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>2870</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5140,7 +5223,365 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>77.790000000000006</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>3586.7484766800003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>592.5</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2282.3000000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2816.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>697412.87774050003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>138918</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5959</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>10.93</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3916.2190000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>671</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>568</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>165.1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5044.7333572999996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>95.319000000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>78.680000000000007</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>4372.5807311200006</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>107.482</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1366.51</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>132.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>130841.4975</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>3309.02</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>7400.7630000000008</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>161.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2990.6024601600002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>211.91</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>35.700000000000003</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2463.8772690000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>314</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>297</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4.97</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2117.1355100000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>309.16800000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1190.444</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5180,365 +5621,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>80.760000000000005</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>3699.7390012800006</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>701.6</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2291.4</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2816.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>697412.87774050003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>138918</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5959</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>10.93</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3916.2190000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>671</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>568</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>165.1</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>5044.7333572999996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>95.319000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>78.680000000000007</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4372.5807311200006</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>107.482</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1366.51</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>132.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>130841.4975</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>3309.02</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>7400.7630000000008</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>161.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2990.6024601600002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>211.91</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>35.700000000000003</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2463.8772690000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>314</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>297</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.97</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2117.1355100000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>309.16800000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1190.444</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5578,7 +5661,365 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>263.45</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270582.07176934998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1259.98</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>3707.71</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>74.900000000000006</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5953.9305021000009</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>207</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>990</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>44.03</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>3217.9517470800001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>77.156000000000006</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>286.49700000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>18.14</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2154.9996926600002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>357</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>10.61</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2684.5824118999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>297.553</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>246.18899999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>828.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>201333.06192080001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>440.44</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>269.23</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5.82</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2055.0937514400002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>214.85400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2186.0569999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41.42</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>1491.5652650000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>412.92599999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>498.12</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>38.119999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1935.4971035199997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>325.44000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5624,365 +6065,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>263.45</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270582.07176934998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1259.98</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>3707.71</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>54.91</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>4407.5666168399994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>249</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1351</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>33.92</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>2464.3691366400003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>111.31400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>293.49</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>18.14</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2154.9996926600002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>135</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>357</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>10.61</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2684.5824118999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>297.553</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>246.18899999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>828.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>201333.06192080001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>440.44</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>269.23</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5.82</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2055.0937514400002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>214.85400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2186.0569999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.42</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>1491.5652650000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>412.92599999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>498.12</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>38.119999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1935.4971035199997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>325.44000000000005</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6022,7 +6105,367 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>27.07</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1188.01315849</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>104.68600000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>224.17499999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>59.85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>939.70682505000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>7.0270000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>57.816000000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>13.57</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1318.1272015899999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>408.2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>410.59999999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4.53</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>736.21656488999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>245.11399999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>9.6039999999999992</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>16.75</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>872.38125524999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>189.63499999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>623.71199999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main "/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="F2">
+            <v>2.4350000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4">
+            <v>290.48290130999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>318.89999999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>503.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>0.98</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>97.21301296</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>17.213000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>291.31400000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>17.79</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270.90115659000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>45.523000000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>70.016000000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2540</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>64964.434459999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>33044</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>13470</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6077,367 +6520,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>27.07</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1188.01315849</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>104.68600000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>224.17499999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>59.85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>939.70682505000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>7.0270000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>57.816000000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>13.57</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1318.1272015899999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>408.2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>410.59999999999997</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.53</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>736.21656488999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>245.11399999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>9.6039999999999992</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>16.75</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>872.38125524999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>189.63499999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>623.71199999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main "/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="F2">
-            <v>2.4350000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="F4">
-            <v>290.48290130999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>318.89999999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>503.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>0.98</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>97.21301296</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>17.213000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>291.31400000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17.79</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270.90115659000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>45.523000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>70.016000000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2540</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>64964.434459999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>33044</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>13470</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6472,86 +6555,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>170</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>68068</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>183.20400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>2656.7910000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>225.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>19955.789000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>998.22799999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>1905.81</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6734,24 +6737,24 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="3">
-          <cell r="H3">
-            <v>232.02</v>
+        <row r="2">
+          <cell r="K2">
+            <v>170</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>68068</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>74236.423139999999</v>
+          <cell r="K5">
+            <v>183.20400000000001</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>4130.9799999999996</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1018.1869999999999</v>
+          <cell r="K6">
+            <v>2656.7910000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -7297,15 +7300,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1799050.7225320311</v>
+        <v>1806632.6828585202</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>9044.3112152000031</v>
+        <v>9312.3892152000008</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1808095.0337472309</v>
+        <v>1815945.0720737199</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7367,15 +7370,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22793.905543335179</v>
+        <v>22889.879724683142</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>117.45858721038965</v>
+        <v>120.94011967792208</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23481.753685028973</v>
+        <v>23583.702234723634</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -7473,15 +7476,15 @@
         <v>20</v>
       </c>
       <c r="E6" s="24">
-        <f>+[1]Main!$I$4</f>
+        <f>+[2]Main!$I$4</f>
         <v>499.3</v>
       </c>
       <c r="F6" s="17">
-        <f>+[1]Main!$I$6*FX!C3</f>
+        <f>+[2]Main!$I$6*FX!C3</f>
         <v>258434.89270768003</v>
       </c>
       <c r="G6" s="17">
-        <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
+        <f>(+[2]Main!$I$8-[2]Main!$I$7)*FX!C3</f>
         <v>12010.960000000001</v>
       </c>
       <c r="H6" s="17">
@@ -7576,15 +7579,15 @@
         <v>20</v>
       </c>
       <c r="E7" s="29">
-        <f>+[2]Main!$K$2</f>
+        <f>+[3]Main!$K$2</f>
         <v>1751</v>
       </c>
       <c r="F7" s="17">
-        <f>+[2]Main!$K$4*FX!C3</f>
+        <f>+[3]Main!$K$4*FX!C3</f>
         <v>192246.12202848002</v>
       </c>
       <c r="G7" s="17">
-        <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
+        <f>+([3]Main!$K$6-[3]Main!$K$5)*FX!C3</f>
         <v>-12693.2</v>
       </c>
       <c r="H7" s="17">
@@ -7679,26 +7682,26 @@
         <v>100</v>
       </c>
       <c r="E8" s="24">
-        <f>+[3]Main!$J$3</f>
-        <v>52.82</v>
+        <f>+[4]Main!$J$3</f>
+        <v>55</v>
       </c>
       <c r="F8" s="17">
-        <f>+[3]Main!$J$5*FX!C3</f>
-        <v>171175.63038214078</v>
+        <f>+[4]Main!$J$5*FX!C3</f>
+        <v>178241.80688600001</v>
       </c>
       <c r="G8" s="17">
-        <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
-        <v>-11396.32</v>
+        <f>+([4]Main!$J$7-[4]Main!$J$6)*FX!C3</f>
+        <v>-11228.880000000001</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" ref="H8:H35" si="1">F8+G8</f>
-        <v>159779.31038214077</v>
+        <v>167012.926886</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>422</v>
+        <v>828</v>
       </c>
       <c r="J8" s="26">
-        <v>46183</v>
+        <v>46274</v>
       </c>
       <c r="K8" s="17">
         <f>35947*FX!C3</f>
@@ -7779,15 +7782,15 @@
         <v>21</v>
       </c>
       <c r="E9" s="24">
-        <f>+[4]Main!$I$3</f>
+        <f>+[5]Main!$I$3</f>
         <v>159.16999999999999</v>
       </c>
       <c r="F9" s="17">
-        <f>+[4]Main!$I$5</f>
+        <f>+[5]Main!$I$5</f>
         <v>178270.4</v>
       </c>
       <c r="G9" s="17">
-        <f>+[4]Main!$I$7-[4]Main!$I$6</f>
+        <f>+[5]Main!$I$7-[5]Main!$I$6</f>
         <v>-2710</v>
       </c>
       <c r="H9" s="17">
@@ -7797,7 +7800,9 @@
       <c r="I9" s="25" t="s">
         <v>875</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="26">
+        <v>46253</v>
+      </c>
       <c r="K9" s="24">
         <v>54217</v>
       </c>
@@ -7872,15 +7877,15 @@
         <v>20</v>
       </c>
       <c r="E10" s="24">
-        <f>+[5]Main!$I$2</f>
+        <f>+[6]Main!$I$2</f>
         <v>471.6</v>
       </c>
       <c r="F10" s="17">
-        <f>+[5]Main!$I$4*FX!C3</f>
+        <f>+[6]Main!$I$4*FX!C3</f>
         <v>88484.89470912001</v>
       </c>
       <c r="G10" s="17">
-        <f>+([5]Main!$I$6-[5]Main!$I$5)*FX!C3</f>
+        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C3</f>
         <v>13724.880000000001</v>
       </c>
       <c r="H10" s="17">
@@ -7947,15 +7952,15 @@
         <v>21</v>
       </c>
       <c r="E11" s="24">
-        <f>+[6]Main!$I$3</f>
+        <f>+[7]Main!$I$3</f>
         <v>48.01</v>
       </c>
       <c r="F11" s="17">
-        <f>+[6]Main!$I$5</f>
+        <f>+[7]Main!$I$5</f>
         <v>71078.804999999993</v>
       </c>
       <c r="G11" s="17">
-        <f>+[6]Main!$I$7-[6]Main!$I$6</f>
+        <f>+[7]Main!$I$7-[7]Main!$I$6</f>
         <v>-28</v>
       </c>
       <c r="H11" s="17">
@@ -8044,15 +8049,15 @@
         <v>124</v>
       </c>
       <c r="E12" s="29">
-        <f>+[7]Main!$J$3</f>
+        <f>+[8]Main!$J$3</f>
         <v>75540</v>
       </c>
       <c r="F12" s="17">
-        <f>+[7]Main!$J$5*FX!C5</f>
+        <f>+[8]Main!$J$5*FX!C5</f>
         <v>146020.56045670799</v>
       </c>
       <c r="G12" s="17">
-        <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
+        <f>+([8]Main!$J$7-[8]Main!$J$6)*FX!C5</f>
         <v>-4946.4386999999997</v>
       </c>
       <c r="H12" s="17">
@@ -8073,7 +8078,7 @@
         <v>0.08</v>
       </c>
       <c r="M12" s="17">
-        <f>+SUM([7]Model!$G$20:$I$20,[7]Model!$C$20)*FX!C5</f>
+        <f>+SUM([8]Model!$G$20:$I$20,[8]Model!$C$20)*FX!C5</f>
         <v>3765.1320000000001</v>
       </c>
       <c r="N12" s="17">
@@ -8132,15 +8137,15 @@
         <v>21</v>
       </c>
       <c r="E13" s="24">
-        <f>+[8]Main!$K$2</f>
+        <f>+[9]Main!$K$2</f>
         <v>170</v>
       </c>
       <c r="F13" s="17">
-        <f>+[8]Main!$K$4</f>
+        <f>+[9]Main!$K$4</f>
         <v>68068</v>
       </c>
       <c r="G13" s="17">
-        <f>+[8]Main!$K$6-[8]Main!$K$5</f>
+        <f>+[9]Main!$K$6-[9]Main!$K$5</f>
         <v>2473.587</v>
       </c>
       <c r="H13" s="17">
@@ -8211,15 +8216,15 @@
         <v>21</v>
       </c>
       <c r="E14" s="24">
-        <f>+[9]Main!$H$3</f>
+        <f>+[10]Main!$H$3</f>
         <v>232.02</v>
       </c>
       <c r="F14" s="17">
-        <f>+[9]Main!$H$5</f>
+        <f>+[10]Main!$H$5</f>
         <v>74236.423139999999</v>
       </c>
       <c r="G14" s="17">
-        <f>+[9]Main!$H$7-[9]Main!$H$6</f>
+        <f>+[10]Main!$H$7-[10]Main!$H$6</f>
         <v>-3112.7929999999997</v>
       </c>
       <c r="H14" s="17">
@@ -8286,20 +8291,20 @@
         <v>107</v>
       </c>
       <c r="E15" s="24">
-        <f>+[10]Main!$I$2</f>
-        <v>127.35</v>
+        <f>+[11]Main!$I$2</f>
+        <v>114.34</v>
       </c>
       <c r="F15" s="17">
-        <f>+[10]Main!$I$4</f>
-        <v>14069.968151849998</v>
+        <f>+[11]Main!$I$4</f>
+        <v>12398.796003380001</v>
       </c>
       <c r="G15" s="17">
-        <f>+[10]Main!$I$6-[10]Main!$I$5</f>
-        <v>-1807.202</v>
+        <f>+[11]Main!$I$6-[11]Main!$I$5</f>
+        <v>-1514.729</v>
       </c>
       <c r="H15" s="17">
         <f>F15+G15</f>
-        <v>12262.766151849999</v>
+        <v>10884.067003380002</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>422</v>
@@ -8361,15 +8366,15 @@
         <v>82</v>
       </c>
       <c r="E16" s="24">
-        <f>+[11]Main!$I$2</f>
+        <f>+[12]Main!$I$2</f>
         <v>147.4</v>
       </c>
       <c r="F16" s="17">
-        <f>+[11]Main!$I$4*FX!C3</f>
+        <f>+[12]Main!$I$4*FX!C3</f>
         <v>27162.897954192002</v>
       </c>
       <c r="G16" s="17">
-        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
+        <f>+([12]Main!$I$6-[12]Main!$I$5)*FX!C3</f>
         <v>2208.96</v>
       </c>
       <c r="H16" s="17">
@@ -8380,7 +8385,7 @@
         <v>828</v>
       </c>
       <c r="J16" s="26">
-        <v>46233</v>
+        <v>46268</v>
       </c>
       <c r="K16" s="17">
         <f>21427*FX!C3</f>
@@ -8439,15 +8444,15 @@
         <v>20</v>
       </c>
       <c r="E17" s="24">
-        <f>+[12]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>256.14999999999998</v>
       </c>
       <c r="F17" s="17">
-        <f>+[12]Main!$H$4*FX!C3</f>
+        <f>+[13]Main!$H$4*FX!C3</f>
         <v>32661.431497551999</v>
       </c>
       <c r="G17" s="17">
-        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
+        <f>+([13]Main!$H$6-[13]Main!$H$5)*FX!C3</f>
         <v>8578.9600000000009</v>
       </c>
       <c r="H17" s="17">
@@ -8539,15 +8544,15 @@
         <v>454</v>
       </c>
       <c r="E18" s="24">
-        <f>+[13]Main!$H$2</f>
+        <f>+[14]Main!$H$2</f>
         <v>80.55</v>
       </c>
       <c r="F18" s="17">
-        <f>+[13]Main!$H$5*FX!C9</f>
+        <f>+[14]Main!$H$5*FX!C9</f>
         <v>29160.086447520003</v>
       </c>
       <c r="G18" s="17">
-        <f>+([13]Main!$H$7-[13]Main!$H$6)*FX!C9</f>
+        <f>+([14]Main!$H$7-[14]Main!$H$6)*FX!C9</f>
         <v>-1841.5600000000002</v>
       </c>
       <c r="H18" s="17">
@@ -8618,15 +8623,15 @@
         <v>21</v>
       </c>
       <c r="E19" s="24">
-        <f>+[14]Main!$M$2</f>
+        <f>+[15]Main!$M$2</f>
         <v>107</v>
       </c>
       <c r="F19" s="17">
-        <f>+[14]Main!$M$4</f>
+        <f>+[15]Main!$M$4</f>
         <v>14860.262398999999</v>
       </c>
       <c r="G19" s="17">
-        <f>+[14]Main!$M$6-[14]Main!$M$5</f>
+        <f>+[15]Main!$M$6-[15]Main!$M$5</f>
         <v>-1907.249</v>
       </c>
       <c r="H19" s="17">
@@ -8702,15 +8707,15 @@
         <v>109</v>
       </c>
       <c r="E20" s="24">
-        <f>+[15]Main!$I$2</f>
+        <f>+[16]Main!$I$2</f>
         <v>170.3</v>
       </c>
       <c r="F20" s="17">
-        <f>+[15]Main!$I$4*FX!C4</f>
+        <f>+[16]Main!$I$4*FX!C4</f>
         <v>25871.945346</v>
       </c>
       <c r="G20" s="17">
-        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C4</f>
+        <f>+([16]Main!$I$6-[16]Main!$I$5)*FX!C4</f>
         <v>184.49</v>
       </c>
       <c r="H20" s="17">
@@ -8770,15 +8775,15 @@
         <v>165</v>
       </c>
       <c r="E21" s="24">
-        <f>+[16]Main!$H$2</f>
+        <f>+[17]Main!$H$2</f>
         <v>34.700000000000003</v>
       </c>
       <c r="F21" s="17">
-        <f>+[16]Main!$H$5*FX!C3</f>
+        <f>+[17]Main!$H$5*FX!C3</f>
         <v>11081.140861440002</v>
       </c>
       <c r="G21" s="17">
-        <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
+        <f>(+[17]Main!$H$7-[17]Main!$H$6)*FX!C3</f>
         <v>489.51760000000007</v>
       </c>
       <c r="H21" s="17">
@@ -8833,15 +8838,15 @@
         <v>185</v>
       </c>
       <c r="E22" s="24">
-        <f>+[17]Main!$I$2</f>
+        <f>+[18]Main!$I$2</f>
         <v>5221.55</v>
       </c>
       <c r="F22" s="17">
-        <f>+[17]Main!$I$4*FX!C12</f>
+        <f>+[18]Main!$I$4*FX!C12</f>
         <v>20418.151071830049</v>
       </c>
       <c r="G22" s="17">
-        <f>+([17]Main!$I$6-[17]Main!$I$5)*FX!C12</f>
+        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C12</f>
         <v>0</v>
       </c>
       <c r="H22" s="17">
@@ -8890,15 +8895,15 @@
         <v>165</v>
       </c>
       <c r="E23" s="24">
-        <f>+[18]Main!$H$2</f>
+        <f>+[19]Main!$H$2</f>
         <v>53.46</v>
       </c>
       <c r="F23" s="17">
-        <f>+[18]Main!$H$4*FX!C3</f>
+        <f>+[19]Main!$H$4*FX!C3</f>
         <v>15040.638902203202</v>
       </c>
       <c r="G23" s="17">
-        <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C3</f>
+        <f>+([19]Main!$H$6-[19]Main!$H$5)*FX!C3</f>
         <v>-376.31984</v>
       </c>
       <c r="H23" s="17">
@@ -8953,15 +8958,15 @@
         <v>21</v>
       </c>
       <c r="E24" s="24">
-        <f>+[19]Main!$I$2</f>
+        <f>+[20]Main!$I$2</f>
         <v>304.51</v>
       </c>
       <c r="F24" s="17">
-        <f>+[19]Main!$I$4</f>
+        <f>+[20]Main!$I$4</f>
         <v>19088.948091260001</v>
       </c>
       <c r="G24" s="17">
-        <f>+[19]Main!$I$6-[19]Main!$I$5</f>
+        <f>+[20]Main!$I$6-[20]Main!$I$5</f>
         <v>1451.345</v>
       </c>
       <c r="H24" s="17">
@@ -9016,15 +9021,15 @@
         <v>21</v>
       </c>
       <c r="E25" s="24">
-        <f>+[20]Main!$J$2</f>
+        <f>+[21]Main!$J$2</f>
         <v>134.28</v>
       </c>
       <c r="F25" s="17">
-        <f>+[20]Main!$J$4</f>
+        <f>+[21]Main!$J$4</f>
         <v>27130.56419592</v>
       </c>
       <c r="G25" s="17">
-        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
+        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
         <v>1330.5779</v>
       </c>
       <c r="H25" s="17">
@@ -9079,15 +9084,15 @@
         <v>124</v>
       </c>
       <c r="E26" s="24">
-        <f>+[21]Main!$I$2</f>
+        <f>+[22]Main!$I$2</f>
         <v>4496</v>
       </c>
       <c r="F26" s="17">
-        <f>+[21]Main!$I$4*FX!C5</f>
+        <f>+[22]Main!$I$4*FX!C5</f>
         <v>20073.934380225597</v>
       </c>
       <c r="G26" s="17">
-        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C5</f>
+        <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C5</f>
         <v>-279.65070000000003</v>
       </c>
       <c r="H26" s="17">
@@ -9142,15 +9147,15 @@
         <v>219</v>
       </c>
       <c r="E27" s="24">
-        <f>+[22]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>127.35</v>
       </c>
       <c r="F27" s="17">
-        <f>+[22]Main!$I$4*FX!C8</f>
+        <f>+[23]Main!$I$4*FX!C8</f>
         <v>18491.7294</v>
       </c>
       <c r="G27" s="17">
-        <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C8</f>
+        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C8</f>
         <v>421.84800000000007</v>
       </c>
       <c r="H27" s="17">
@@ -9205,15 +9210,15 @@
         <v>166</v>
       </c>
       <c r="E28" s="24">
-        <f>+[23]Main!$H$2</f>
+        <f>+[24]Main!$H$2</f>
         <v>36.42</v>
       </c>
       <c r="F28" s="17">
-        <f>+[23]Main!$H$5*FX!C7</f>
+        <f>+[24]Main!$H$5*FX!C7</f>
         <v>10293.145395479522</v>
       </c>
       <c r="G28" s="17">
-        <f>+([23]Main!$H$7-[23]Main!$H$6)*FX!C7</f>
+        <f>+([24]Main!$H$7-[24]Main!$H$6)*FX!C7</f>
         <v>-1077.8880000000001</v>
       </c>
       <c r="H28" s="17">
@@ -9268,15 +9273,15 @@
         <v>214</v>
       </c>
       <c r="E29" s="24">
-        <f>+[24]Main!$J$2</f>
+        <f>+[25]Main!$J$2</f>
         <v>35.26</v>
       </c>
       <c r="F29" s="17">
-        <f>+[24]Main!$J$4</f>
+        <f>+[25]Main!$J$4</f>
         <v>19918.456120539999</v>
       </c>
       <c r="G29" s="17">
-        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
+        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
         <v>-538.80000000000007</v>
       </c>
       <c r="H29" s="17">
@@ -9331,15 +9336,15 @@
         <v>454</v>
       </c>
       <c r="E30" s="24">
-        <f>+[25]Main!$J$2</f>
+        <f>+[26]Main!$J$2</f>
         <v>47.12</v>
       </c>
       <c r="F30" s="17">
-        <f>+[25]Main!$J$5*FX!C9</f>
+        <f>+[26]Main!$J$5*FX!C9</f>
         <v>8726.4826075060482</v>
       </c>
       <c r="G30" s="17">
-        <f>+([25]Main!$J$7-[25]Main!$J$6)*FX!C9</f>
+        <f>+([26]Main!$J$7-[26]Main!$J$6)*FX!C9</f>
         <v>-1503.0597399999999</v>
       </c>
       <c r="H30" s="17">
@@ -9394,15 +9399,15 @@
         <v>21</v>
       </c>
       <c r="E31" s="24">
-        <f>+[26]Main!$H$2</f>
+        <f>+[27]Main!$H$2</f>
         <v>376.91</v>
       </c>
       <c r="F31" s="17">
-        <f>+[26]Main!$H$4</f>
+        <f>+[27]Main!$H$4</f>
         <v>22473.766070860001</v>
       </c>
       <c r="G31" s="17">
-        <f>+[26]Main!$H$6-[26]Main!$H$5</f>
+        <f>+[27]Main!$H$6-[27]Main!$H$5</f>
         <v>-826.09999999999991</v>
       </c>
       <c r="H31" s="17">
@@ -9488,15 +9493,15 @@
         <v>454</v>
       </c>
       <c r="E32" s="24">
-        <f>+[27]Main!$K$2</f>
+        <f>+[28]Main!$K$2</f>
         <v>76.739999999999995</v>
       </c>
       <c r="F32" s="17">
-        <f>+[27]Main!$K$4*FX!C9</f>
+        <f>+[28]Main!$K$4*FX!C9</f>
         <v>12537.781199999999</v>
       </c>
       <c r="G32" s="17">
-        <f>+([27]Main!$K$6-[27]Main!$K$5)*FX!C9</f>
+        <f>+([28]Main!$K$6-[28]Main!$K$5)*FX!C9</f>
         <v>-745.22328020000009</v>
       </c>
       <c r="H32" s="17">
@@ -9551,15 +9556,15 @@
         <v>82</v>
       </c>
       <c r="E33" s="24">
-        <f>+[28]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>19.87</v>
       </c>
       <c r="F33" s="17">
-        <f>+[28]Main!$I$4*FX!C3</f>
+        <f>+[29]Main!$I$4*FX!C3</f>
         <v>5381.1139200000007</v>
       </c>
       <c r="G33" s="17">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
+        <f>+([29]Main!$I$6-[29]Main!$I$5)*FX!C3</f>
         <v>-565.76</v>
       </c>
       <c r="H33" s="17">
@@ -9612,15 +9617,15 @@
         <v>21</v>
       </c>
       <c r="E34" s="24">
-        <f>+[29]Main!$H$2</f>
+        <f>+[30]Main!$H$2</f>
         <v>16.72</v>
       </c>
       <c r="F34" s="17">
-        <f>+[29]Main!$H$4</f>
+        <f>+[30]Main!$H$4</f>
         <v>6550.3894675999991</v>
       </c>
       <c r="G34" s="17">
-        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
+        <f>+[30]Main!$H$6-[30]Main!$H$5</f>
         <v>2706.0659999999998</v>
       </c>
       <c r="H34" s="17">
@@ -9675,15 +9680,15 @@
         <v>82</v>
       </c>
       <c r="E35" s="24">
-        <f>+[30]Main!$I$3</f>
+        <f>+[31]Main!$I$3</f>
         <v>29.172000000000001</v>
       </c>
       <c r="F35" s="17">
-        <f>+[30]Main!$I$5*FX!C3</f>
+        <f>+[31]Main!$I$5*FX!C3</f>
         <v>5579.5037642572797</v>
       </c>
       <c r="G35" s="17">
-        <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
+        <f>+([31]Main!$I$7-[31]Main!$I$6)*FX!C3</f>
         <v>985.08904000000018</v>
       </c>
       <c r="H35" s="17">
@@ -9738,15 +9743,15 @@
         <v>21</v>
       </c>
       <c r="E36" s="24">
-        <f>+[31]Main!$J$2</f>
+        <f>+[32]Main!$J$2</f>
         <v>21.27</v>
       </c>
       <c r="F36" s="17">
-        <f>+[31]Main!$J$4</f>
+        <f>+[32]Main!$J$4</f>
         <v>7806.09</v>
       </c>
       <c r="G36" s="17">
-        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
+        <f>+([32]Main!$J$6-[32]Main!$J$5)</f>
         <v>-1069</v>
       </c>
       <c r="H36" s="17">
@@ -9813,15 +9818,15 @@
         <v>21</v>
       </c>
       <c r="E37" s="24">
-        <f>+[32]Main!$I$2</f>
+        <f>+[33]Main!$I$2</f>
         <v>60.4</v>
       </c>
       <c r="F37" s="17">
-        <f>+[32]Main!$I$4</f>
+        <f>+[33]Main!$I$4</f>
         <v>9118.7085583999997</v>
       </c>
       <c r="G37" s="17">
-        <f>+[32]Main!$I$6-[32]Main!$I$5</f>
+        <f>+[33]Main!$I$6-[33]Main!$I$5</f>
         <v>-838.96200000000022</v>
       </c>
       <c r="H37" s="17">
@@ -9876,15 +9881,15 @@
         <v>165</v>
       </c>
       <c r="E38" s="24">
-        <f>+[33]Main!$J$2</f>
+        <f>+[34]Main!$J$2</f>
         <v>86.1</v>
       </c>
       <c r="F38" s="17">
-        <f>+[33]Main!$J$4*FX!C3</f>
+        <f>+[34]Main!$J$4*FX!C3</f>
         <v>6088.4257237439997</v>
       </c>
       <c r="G38" s="17">
-        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
+        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C3</f>
         <v>200.49328000000006</v>
       </c>
       <c r="H38" s="17">
@@ -9939,15 +9944,15 @@
         <v>107</v>
       </c>
       <c r="E39" s="24">
-        <f>+[34]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>63.14</v>
       </c>
       <c r="F39" s="17">
-        <f>+[34]Main!$I$4</f>
+        <f>+[35]Main!$I$4</f>
         <v>11754.016119999998</v>
       </c>
       <c r="G39" s="17">
-        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
+        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
         <v>4478.0450000000001</v>
       </c>
       <c r="H39" s="17">
@@ -10002,15 +10007,15 @@
         <v>21</v>
       </c>
       <c r="E40" s="24">
-        <f>+[35]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>22.68</v>
       </c>
       <c r="F40" s="17">
-        <f>+[35]Main!$I$4</f>
+        <f>+[36]Main!$I$4</f>
         <v>8722.6429726799997</v>
       </c>
       <c r="G40" s="17">
-        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
+        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
         <v>237.40000000000009</v>
       </c>
       <c r="H40" s="17">
@@ -10077,15 +10082,15 @@
         <v>294</v>
       </c>
       <c r="E41" s="24">
-        <f>+[36]Main!$I$2</f>
+        <f>+[37]Main!$I$2</f>
         <v>17550</v>
       </c>
       <c r="F41" s="17">
-        <f>+[36]Main!$I$4*FX!C11</f>
+        <f>+[37]Main!$I$4*FX!C11</f>
         <v>8142.7173750000002</v>
       </c>
       <c r="G41" s="17">
-        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
+        <f>+([37]Main!$I$6-[37]Main!$I$5)*FX!C11</f>
         <v>171.25</v>
       </c>
       <c r="H41" s="17">
@@ -10136,15 +10141,15 @@
         <v>454</v>
       </c>
       <c r="E42" s="24">
-        <f>+[37]Main!$J$2</f>
+        <f>+[38]Main!$J$2</f>
         <v>8.7799999999999994</v>
       </c>
       <c r="F42" s="17">
-        <f>+[37]Main!$J$4*FX!C9</f>
+        <f>+[38]Main!$J$4*FX!C9</f>
         <v>5900.1600000000008</v>
       </c>
       <c r="G42" s="17">
-        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C9</f>
+        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C9</f>
         <v>-679.00000000000011</v>
       </c>
       <c r="H42" s="17">
@@ -10195,15 +10200,15 @@
         <v>185</v>
       </c>
       <c r="E43" s="24">
-        <f>+[38]Main!$H$2</f>
+        <f>+[39]Main!$H$2</f>
         <v>41240</v>
       </c>
       <c r="F43" s="17">
-        <f>+[38]Main!$H$4*FX!C12</f>
+        <f>+[39]Main!$H$4*FX!C12</f>
         <v>5059.9509140399996</v>
       </c>
       <c r="G43" s="17">
-        <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
+        <f>+([39]Main!$H$6-[39]Main!$H$5)*FX!C12</f>
         <v>79.99563000000002</v>
       </c>
       <c r="H43" s="17">
@@ -10254,15 +10259,15 @@
         <v>21</v>
       </c>
       <c r="E44" s="24">
-        <f>+[39]Main!$H$2</f>
+        <f>+[40]Main!$H$2</f>
         <v>102.6</v>
       </c>
       <c r="F44" s="17">
-        <f>+[39]Main!$H$4</f>
+        <f>+[40]Main!$H$4</f>
         <v>5098.1578847999999</v>
       </c>
       <c r="G44" s="17">
-        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
+        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
         <v>1204.9399999999998</v>
       </c>
       <c r="H44" s="17">
@@ -10317,15 +10322,15 @@
         <v>325</v>
       </c>
       <c r="E45" s="24">
-        <f>+[40]Main!$I$2</f>
+        <f>+[41]Main!$I$2</f>
         <v>27.8</v>
       </c>
       <c r="F45" s="17">
-        <f>+[40]Main!$I$4*FX!C14</f>
+        <f>+[41]Main!$I$4*FX!C14</f>
         <v>5512.4063999999998</v>
       </c>
       <c r="G45" s="17">
-        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C14</f>
+        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C14</f>
         <v>392.36399999999998</v>
       </c>
       <c r="H45" s="17">
@@ -10380,15 +10385,15 @@
         <v>219</v>
       </c>
       <c r="E46" s="24">
-        <f>+[41]Main!$I$2</f>
+        <f>+[42]Main!$I$2</f>
         <v>0.93779999999999997</v>
       </c>
       <c r="F46" s="17">
-        <f>+[41]Main!$I$4*FX!C8</f>
+        <f>+[42]Main!$I$4*FX!C8</f>
         <v>5962.0447439999998</v>
       </c>
       <c r="G46" s="17">
-        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
+        <f>+([42]Main!$I$6-[42]Main!$I$5)*FX!C8</f>
         <v>155</v>
       </c>
       <c r="H46" s="17">
@@ -10443,15 +10448,15 @@
         <v>107</v>
       </c>
       <c r="E47" s="24">
-        <f>+[42]Main!$H$2</f>
+        <f>+[43]Main!$H$2</f>
         <v>86.42</v>
       </c>
       <c r="F47" s="17">
-        <f>+[42]Main!$H$4*FX!C13</f>
+        <f>+[43]Main!$H$4*FX!C13</f>
         <v>6825.0480185999995</v>
       </c>
       <c r="G47" s="17">
-        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
+        <f>+([43]Main!$H$6-[43]Main!$H$5)*FX!C13</f>
         <v>-201.90158999999997</v>
       </c>
       <c r="H47" s="17">
@@ -10502,15 +10507,15 @@
         <v>454</v>
       </c>
       <c r="E48" s="24">
-        <f>+[43]Main!$H$2</f>
+        <f>+[44]Main!$H$2</f>
         <v>16.02</v>
       </c>
       <c r="F48" s="17">
-        <f>+[43]Main!$H$5*FX!C9</f>
+        <f>+[44]Main!$H$5*FX!C9</f>
         <v>5313.5769879360005</v>
       </c>
       <c r="G48" s="17">
-        <f>+([43]Main!$H$7-[43]Main!$H$6)*FX!C9</f>
+        <f>+([44]Main!$H$7-[44]Main!$H$6)*FX!C9</f>
         <v>-2458.0551799999998</v>
       </c>
       <c r="H48" s="17">
@@ -10563,15 +10568,15 @@
         <v>454</v>
       </c>
       <c r="E49" s="24">
-        <f>+[44]Main!$I$2</f>
+        <f>+[45]Main!$I$2</f>
         <v>8.01</v>
       </c>
       <c r="F49" s="17">
-        <f>+[44]Main!$I$4*FX!C9</f>
+        <f>+[45]Main!$I$4*FX!C9</f>
         <v>5141.5464790620008</v>
       </c>
       <c r="G49" s="17">
-        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C9</f>
+        <f>+([45]Main!$I$6-[45]Main!$I$5)*FX!C9</f>
         <v>1697.6221653999999</v>
       </c>
       <c r="H49" s="17">
@@ -10620,15 +10625,15 @@
         <v>21</v>
       </c>
       <c r="E50" s="24">
-        <f>+[45]Main!$J$2</f>
+        <f>+[46]Main!$J$2</f>
         <v>74.28</v>
       </c>
       <c r="F50" s="17">
-        <f>+[45]Main!$J$4</f>
+        <f>+[46]Main!$J$4</f>
         <v>6499.7862008400007</v>
       </c>
       <c r="G50" s="17">
-        <f>+[45]Main!$J$6-[45]Main!$J$5</f>
+        <f>+[46]Main!$J$6-[46]Main!$J$5</f>
         <v>-413.34199999999998</v>
       </c>
       <c r="H50" s="17">
@@ -10677,15 +10682,15 @@
         <v>82</v>
       </c>
       <c r="E51" s="24">
-        <f>+[46]Main!$I$2</f>
+        <f>+[47]Main!$I$2</f>
         <v>25.98</v>
       </c>
       <c r="F51" s="17">
-        <f>+[46]Main!$I$4*FX!C3</f>
+        <f>+[47]Main!$I$4*FX!C3</f>
         <v>3978.0368159999998</v>
       </c>
       <c r="G51" s="17">
-        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
+        <f>+([47]Main!$I$6-[47]Main!$I$5)*FX!C3</f>
         <v>1411.904</v>
       </c>
       <c r="H51" s="17">
@@ -10740,15 +10745,15 @@
         <v>454</v>
       </c>
       <c r="E52" s="24">
-        <f>+[47]Main!$I$2</f>
+        <f>+[48]Main!$I$2</f>
         <v>3.75</v>
       </c>
       <c r="F52" s="17">
-        <f>+[47]Main!$I$5*FX!C9</f>
+        <f>+[48]Main!$I$5*FX!C9</f>
         <v>5271.5025720000003</v>
       </c>
       <c r="G52" s="17">
-        <f>+([47]Main!$I$7-[47]Main!$I$6)*FX!C9</f>
+        <f>+([48]Main!$I$7-[48]Main!$I$6)*FX!C9</f>
         <v>-653.85012000000006</v>
       </c>
       <c r="H52" s="17">
@@ -10803,15 +10808,15 @@
         <v>21</v>
       </c>
       <c r="E53" s="24">
-        <f>+[48]Main!$I$2</f>
+        <f>+[49]Main!$I$2</f>
         <v>83.06</v>
       </c>
       <c r="F53" s="17">
-        <f>+[48]Main!$I$4</f>
+        <f>+[49]Main!$I$4</f>
         <v>3735.1251400000001</v>
       </c>
       <c r="G53" s="17">
-        <f>+[48]Main!$I$6-[48]Main!$I$5</f>
+        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
         <v>-619.22400000000005</v>
       </c>
       <c r="H53" s="17">
@@ -10876,15 +10881,15 @@
         <v>21</v>
       </c>
       <c r="E54" s="24">
-        <f>+[49]Main!$I$2</f>
+        <f>+[50]Main!$I$2</f>
         <v>58.06</v>
       </c>
       <c r="F54" s="17">
-        <f>+[49]Main!$I$4</f>
+        <f>+[50]Main!$I$4</f>
         <v>2969.2344415800003</v>
       </c>
       <c r="G54" s="17">
-        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
+        <f>+[50]Main!$I$6-[50]Main!$I$5</f>
         <v>-535.35400000000004</v>
       </c>
       <c r="H54" s="17">
@@ -10939,26 +10944,26 @@
         <v>21</v>
       </c>
       <c r="E55" s="24">
-        <f>+[50]Main!$J$2</f>
-        <v>80.760000000000005</v>
+        <f>+[51]Main!$J$2</f>
+        <v>77.790000000000006</v>
       </c>
       <c r="F55" s="17">
-        <f>+[50]Main!$J$4</f>
-        <v>3699.7390012800006</v>
+        <f>+[51]Main!$J$4</f>
+        <v>3586.7484766800003</v>
       </c>
       <c r="G55" s="17">
-        <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
-        <v>1589.8000000000002</v>
+        <f>+([51]Main!$J$6-[51]Main!$J$5)</f>
+        <v>1689.8000000000002</v>
       </c>
       <c r="H55" s="17">
         <f>F55+G55</f>
-        <v>5289.5390012800008</v>
+        <v>5276.54847668</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>422</v>
+        <v>828</v>
       </c>
       <c r="J55" s="26">
-        <v>46177</v>
+        <v>46261</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="21"/>
@@ -11002,15 +11007,15 @@
         <v>124</v>
       </c>
       <c r="E56" s="24">
-        <f>+[51]Main!$I$2</f>
+        <f>+[52]Main!$I$2</f>
         <v>2816.5</v>
       </c>
       <c r="F56" s="17">
-        <f>+[51]Main!$I$4*FX!C5</f>
+        <f>+[52]Main!$I$4*FX!C5</f>
         <v>4393.7011297651507</v>
       </c>
       <c r="G56" s="17">
-        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
+        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C5</f>
         <v>-837.64170000000001</v>
       </c>
       <c r="H56" s="17">
@@ -11065,15 +11070,15 @@
         <v>219</v>
       </c>
       <c r="E57" s="24">
-        <f>+[52]Main!$I$2</f>
+        <f>+[53]Main!$I$2</f>
         <v>10.93</v>
       </c>
       <c r="F57" s="17">
-        <f>+[52]Main!$I$4*FX!C3</f>
+        <f>+[53]Main!$I$4*FX!C3</f>
         <v>4072.8677600000001</v>
       </c>
       <c r="G57" s="17">
-        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
+        <f>+([53]Main!$I$6-[53]Main!$I$5)*FX!C3</f>
         <v>-107.12</v>
       </c>
       <c r="H57" s="17">
@@ -11122,15 +11127,15 @@
         <v>21</v>
       </c>
       <c r="E58" s="24">
-        <f>+[53]Main!$I$2</f>
+        <f>+[54]Main!$I$2</f>
         <v>165.1</v>
       </c>
       <c r="F58" s="17">
-        <f>+[53]Main!$I$4</f>
+        <f>+[54]Main!$I$4</f>
         <v>5044.7333572999996</v>
       </c>
       <c r="G58" s="17">
-        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
+        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
         <v>-95.319000000000003</v>
       </c>
       <c r="H58" s="17">
@@ -11185,15 +11190,15 @@
         <v>21</v>
       </c>
       <c r="E59" s="24">
-        <f>+[54]Main!$I$2</f>
+        <f>+[55]Main!$I$2</f>
         <v>78.680000000000007</v>
       </c>
       <c r="F59" s="17">
-        <f>+[54]Main!$I$4</f>
+        <f>+[55]Main!$I$4</f>
         <v>4372.5807311200006</v>
       </c>
       <c r="G59" s="17">
-        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
+        <f>+[55]Main!$I$6-[55]Main!$I$5</f>
         <v>1259.028</v>
       </c>
       <c r="H59" s="17">
@@ -11295,15 +11300,15 @@
         <v>433</v>
       </c>
       <c r="E61" s="24">
-        <f>+[55]Main!$J$2</f>
+        <f>+[56]Main!$J$2</f>
         <v>132.5</v>
       </c>
       <c r="F61" s="17">
-        <f>+[55]Main!$J$4*FX!C15</f>
+        <f>+[56]Main!$J$4*FX!C15</f>
         <v>3925.244925</v>
       </c>
       <c r="G61" s="17">
-        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
+        <f>+([56]Main!$J$6-[56]Main!$J$5)*FX!C15</f>
         <v>122.75229000000002</v>
       </c>
       <c r="H61" s="17">
@@ -11352,15 +11357,15 @@
         <v>21</v>
       </c>
       <c r="E62" s="24">
-        <f>+[56]Main!$J$2</f>
+        <f>+[57]Main!$J$2</f>
         <v>161.28</v>
       </c>
       <c r="F62" s="17">
-        <f>+[56]Main!$J$4</f>
+        <f>+[57]Main!$J$4</f>
         <v>2990.6024601600002</v>
       </c>
       <c r="G62" s="17">
-        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
+        <f>+[57]Main!$J$6-[57]Main!$J$5</f>
         <v>-211.91</v>
       </c>
       <c r="H62" s="17">
@@ -11411,15 +11416,15 @@
         <v>82</v>
       </c>
       <c r="E63" s="24">
-        <f>+[57]Main!$J$2</f>
+        <f>+[58]Main!$J$2</f>
         <v>35.700000000000003</v>
       </c>
       <c r="F63" s="17">
-        <f>+[57]Main!$J$4*FX!C3</f>
+        <f>+[58]Main!$J$4*FX!C3</f>
         <v>2562.4323597600001</v>
       </c>
       <c r="G63" s="17">
-        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
+        <f>+([58]Main!$J$6-[58]Main!$J$5)*FX!C3</f>
         <v>-17.68</v>
       </c>
       <c r="H63" s="17">
@@ -11468,15 +11473,15 @@
         <v>21</v>
       </c>
       <c r="E64" s="24">
-        <f>+[58]Main!$I$2</f>
+        <f>+[59]Main!$I$2</f>
         <v>4.97</v>
       </c>
       <c r="F64" s="17">
-        <f>+[58]Main!$I$4</f>
+        <f>+[59]Main!$I$4</f>
         <v>2117.1355100000001</v>
       </c>
       <c r="G64" s="17">
-        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
+        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
         <v>881.27599999999995</v>
       </c>
       <c r="H64" s="17">
@@ -11527,15 +11532,15 @@
         <v>21</v>
       </c>
       <c r="E65" s="24">
-        <f>+[59]Main!$I$2</f>
+        <f>+[60]Main!$I$2</f>
         <v>14.35</v>
       </c>
       <c r="F65" s="17">
-        <f>+[59]Main!$I$4</f>
+        <f>+[60]Main!$I$4</f>
         <v>2756.6605860499999</v>
       </c>
       <c r="G65" s="17">
-        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
+        <f>+[60]Main!$I$6-[60]Main!$I$5</f>
         <v>-160.19499999999999</v>
       </c>
       <c r="H65" s="17">
@@ -11586,15 +11591,15 @@
         <v>185</v>
       </c>
       <c r="E66" s="24">
-        <f>+[60]Main!$I$2</f>
+        <f>+[61]Main!$I$2</f>
         <v>263.45</v>
       </c>
       <c r="F66" s="17">
-        <f>+[60]Main!$I$4*FX!C12</f>
+        <f>+[61]Main!$I$4*FX!C12</f>
         <v>2976.4027894628493</v>
       </c>
       <c r="G66" s="17">
-        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
+        <f>+([61]Main!$I$6-[61]Main!$I$5)*FX!C12</f>
         <v>26.92503</v>
       </c>
       <c r="H66" s="17">
@@ -11633,36 +11638,36 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="B67" s="23" t="s">
+      <c r="B67" s="44" t="s">
         <v>161</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>394</v>
+        <v>899</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E67" s="24">
-        <f>+[61]Main!$I$2</f>
-        <v>54.91</v>
+        <f>+[62]Main!$I$2</f>
+        <v>74.900000000000006</v>
       </c>
       <c r="F67" s="17">
-        <f>+[61]Main!$I$4</f>
-        <v>4407.5666168399994</v>
+        <f>+[62]Main!$I$4</f>
+        <v>5953.9305021000009</v>
       </c>
       <c r="G67" s="17">
-        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
-        <v>1102</v>
+        <f>+[62]Main!$I$6-[62]Main!$I$5</f>
+        <v>783</v>
       </c>
       <c r="H67" s="17">
         <f>F67+G67</f>
-        <v>5509.5666168399994</v>
+        <v>6736.9305021000009</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="J67" s="26">
-        <v>46085</v>
+        <v>46261</v>
       </c>
       <c r="K67" s="24"/>
       <c r="L67" s="21"/>
@@ -11706,26 +11711,26 @@
         <v>21</v>
       </c>
       <c r="E68" s="24">
-        <f>+[62]Main!$H$2</f>
-        <v>33.92</v>
+        <f>+[63]Main!$H$2</f>
+        <v>44.03</v>
       </c>
       <c r="F68" s="17">
-        <f>+[62]Main!$H$4</f>
-        <v>2464.3691366400003</v>
+        <f>+[63]Main!$H$4</f>
+        <v>3217.9517470800001</v>
       </c>
       <c r="G68" s="17">
-        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
-        <v>182.17599999999999</v>
+        <f>+[63]Main!$H$6-[63]Main!$H$5</f>
+        <v>209.34100000000001</v>
       </c>
       <c r="H68" s="17">
         <f>+F68+G68</f>
-        <v>2646.5451366400002</v>
+        <v>3427.29274708</v>
       </c>
       <c r="I68" s="16" t="s">
-        <v>149</v>
+        <v>828</v>
       </c>
       <c r="J68" s="26">
-        <v>45967</v>
+        <v>46232</v>
       </c>
       <c r="K68" s="17"/>
       <c r="L68" s="21"/>
@@ -11765,15 +11770,15 @@
         <v>219</v>
       </c>
       <c r="E69" s="24">
-        <f>+[63]Main!$I$2</f>
+        <f>+[64]Main!$I$2</f>
         <v>18.14</v>
       </c>
       <c r="F69" s="17">
-        <f>+[63]Main!$I$4</f>
+        <f>+[64]Main!$I$4</f>
         <v>2154.9996926600002</v>
       </c>
       <c r="G69" s="17">
-        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
+        <f>+[64]Main!$I$6-[64]Main!$I$5</f>
         <v>222</v>
       </c>
       <c r="H69" s="17">
@@ -11828,15 +11833,15 @@
         <v>165</v>
       </c>
       <c r="E70" s="24">
-        <f>+[64]Main!$J$2</f>
+        <f>+[65]Main!$J$2</f>
         <v>10.61</v>
       </c>
       <c r="F70" s="17">
-        <f>+[64]Main!$J$4*FX!C3</f>
+        <f>+[65]Main!$J$4*FX!C3</f>
         <v>2791.9657083759998</v>
       </c>
       <c r="G70" s="17">
-        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
+        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C3</f>
         <v>-53.418560000000006</v>
       </c>
       <c r="H70" s="17">
@@ -11887,15 +11892,15 @@
         <v>185</v>
       </c>
       <c r="E71" s="24">
-        <f>+[65]Main!$J$2</f>
+        <f>+[66]Main!$J$2</f>
         <v>828.4</v>
       </c>
       <c r="F71" s="17">
-        <f>+[65]Main!$J$4*FX!C12</f>
+        <f>+[66]Main!$J$4*FX!C12</f>
         <v>2214.6636811287999</v>
       </c>
       <c r="G71" s="17">
-        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
+        <f>+([66]Main!$J$6-[66]Main!$J$5)*FX!C12</f>
         <v>-1.8833099999999996</v>
       </c>
       <c r="H71" s="17">
@@ -12397,15 +12402,15 @@
         <v>21</v>
       </c>
       <c r="E83" s="24">
-        <f>+[66]Main!$I$2</f>
+        <f>+[67]Main!$I$2</f>
         <v>5.82</v>
       </c>
       <c r="F83" s="17">
-        <f>+[66]Main!$I$4</f>
+        <f>+[67]Main!$I$4</f>
         <v>2055.0937514400002</v>
       </c>
       <c r="G83" s="17">
-        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
+        <f>+[67]Main!$I$6-[67]Main!$I$5</f>
         <v>1971.2029999999997</v>
       </c>
       <c r="H83" s="17">
@@ -12665,15 +12670,15 @@
         <v>21</v>
       </c>
       <c r="E89" s="24">
-        <f>+[67]Main!$H$2</f>
+        <f>+[68]Main!$H$2</f>
         <v>41.42</v>
       </c>
       <c r="F89" s="17">
-        <f>+[67]Main!$H$4</f>
+        <f>+[68]Main!$H$4</f>
         <v>1491.5652650000002</v>
       </c>
       <c r="G89" s="17">
-        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
+        <f>+[68]Main!$H$6-[68]Main!$H$5</f>
         <v>85.194000000000017</v>
       </c>
       <c r="H89" s="17">
@@ -12722,15 +12727,15 @@
         <v>21</v>
       </c>
       <c r="E90" s="24">
-        <f>+[68]Main!$I$2</f>
+        <f>+[69]Main!$I$2</f>
         <v>38.119999999999997</v>
       </c>
       <c r="F90" s="17">
-        <f>+[68]Main!$I$4</f>
+        <f>+[69]Main!$I$4</f>
         <v>1935.4971035199997</v>
       </c>
       <c r="G90" s="17">
-        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
+        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
         <v>-325.44000000000005</v>
       </c>
       <c r="H90" s="17">
@@ -12779,15 +12784,15 @@
         <v>21</v>
       </c>
       <c r="E91" s="24">
-        <f>+[69]Main!$I$2</f>
+        <f>+[70]Main!$I$2</f>
         <v>24.73</v>
       </c>
       <c r="F91" s="17">
-        <f>+[69]Main!$I$4</f>
+        <f>+[70]Main!$I$4</f>
         <v>1761.5194085300002</v>
       </c>
       <c r="G91" s="17">
-        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
+        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
         <v>-256.60000000000002</v>
       </c>
       <c r="H91" s="17">
@@ -12969,15 +12974,15 @@
         <v>21</v>
       </c>
       <c r="E95" s="24">
-        <f>+[70]Main!$I$2</f>
+        <f>+[71]Main!$I$2</f>
         <v>27.07</v>
       </c>
       <c r="F95" s="17">
-        <f>+[70]Main!$I$4</f>
+        <f>+[71]Main!$I$4</f>
         <v>1188.01315849</v>
       </c>
       <c r="G95" s="17">
-        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
+        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
         <v>119.48899999999998</v>
       </c>
       <c r="H95" s="17">
@@ -13026,15 +13031,15 @@
         <v>21</v>
       </c>
       <c r="E96" s="24">
-        <f>+[71]Main!$I$2</f>
+        <f>+[72]Main!$I$2</f>
         <v>59.85</v>
       </c>
       <c r="F96" s="17">
-        <f>+[71]Main!$I$4</f>
+        <f>+[72]Main!$I$4</f>
         <v>939.70682505000002</v>
       </c>
       <c r="G96" s="17">
-        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
+        <f>+[72]Main!$I$6-[72]Main!$I$5</f>
         <v>50.789000000000001</v>
       </c>
       <c r="H96" s="17">
@@ -13083,15 +13088,15 @@
         <v>107</v>
       </c>
       <c r="E97" s="24">
-        <f>+[72]Main!$J$2</f>
+        <f>+[73]Main!$J$2</f>
         <v>13.57</v>
       </c>
       <c r="F97" s="17">
-        <f>+[72]Main!$J$4*FX!C13</f>
+        <f>+[73]Main!$J$4*FX!C13</f>
         <v>909.50776909709987</v>
       </c>
       <c r="G97" s="17">
-        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
+        <f>+([73]Main!$J$6-[73]Main!$J$5)*FX!C13</f>
         <v>1.6559999999999842</v>
       </c>
       <c r="H97" s="17">
@@ -13228,15 +13233,15 @@
         <v>21</v>
       </c>
       <c r="E100" s="24">
-        <f>+[73]Main!$I$2</f>
+        <f>+[74]Main!$I$2</f>
         <v>4.53</v>
       </c>
       <c r="F100" s="17">
-        <f>+[73]Main!$I$4</f>
+        <f>+[74]Main!$I$4</f>
         <v>736.21656488999997</v>
       </c>
       <c r="G100" s="17">
-        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
+        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
         <v>-235.51</v>
       </c>
       <c r="H100" s="17">
@@ -13285,15 +13290,15 @@
         <v>21</v>
       </c>
       <c r="E101" s="24">
-        <f>+[74]Main!$I$2</f>
+        <f>+[75]Main!$I$2</f>
         <v>16.75</v>
       </c>
       <c r="F101" s="17">
-        <f>+[74]Main!$I$4</f>
+        <f>+[75]Main!$I$4</f>
         <v>872.38125524999998</v>
       </c>
       <c r="G101" s="17">
-        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
+        <f>+[75]Main!$I$6-[75]Main!$I$5</f>
         <v>434.077</v>
       </c>
       <c r="H101" s="17">
@@ -13944,15 +13949,15 @@
         <v>219</v>
       </c>
       <c r="E116" s="24">
-        <f>+'[75]Main '!$F$2</f>
+        <f>+'[76]Main '!$F$2</f>
         <v>2.4350000000000001</v>
       </c>
       <c r="F116" s="17">
-        <f>+'[75]Main '!$F$4*FX!C8</f>
+        <f>+'[76]Main '!$F$4*FX!C8</f>
         <v>360.19879762439996</v>
       </c>
       <c r="G116" s="17">
-        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
+        <f>+('[76]Main '!$F$6-'[76]Main '!$F$5)*FX!C8</f>
         <v>229.02800000000005</v>
       </c>
       <c r="H116" s="17">
@@ -14259,15 +14264,15 @@
         <v>21</v>
       </c>
       <c r="E123" s="24">
-        <f>+[76]Main!$H$2</f>
+        <f>+[77]Main!$H$2</f>
         <v>0.98</v>
       </c>
       <c r="F123" s="17">
-        <f>+[76]Main!$H$4</f>
+        <f>+[77]Main!$H$4</f>
         <v>97.21301296</v>
       </c>
       <c r="G123" s="17">
-        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
+        <f>+[77]Main!$H$6-[77]Main!$H$5</f>
         <v>274.101</v>
       </c>
       <c r="H123" s="17">
@@ -14359,15 +14364,15 @@
         <v>21</v>
       </c>
       <c r="E125" s="24">
-        <f>+[77]Main!$I$2</f>
+        <f>+[78]Main!$I$2</f>
         <v>17.79</v>
       </c>
       <c r="F125" s="17">
-        <f>+[77]Main!$I$4</f>
+        <f>+[78]Main!$I$4</f>
         <v>270.90115659000003</v>
       </c>
       <c r="G125" s="17">
-        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
+        <f>+[78]Main!$I$6-[78]Main!$I$5</f>
         <v>24.493000000000002</v>
       </c>
       <c r="H125" s="17">
@@ -15620,15 +15625,15 @@
         <v>124</v>
       </c>
       <c r="E154" s="24">
-        <f>+[78]Main!$I$2</f>
+        <f>+[79]Main!$I$2</f>
         <v>2540</v>
       </c>
       <c r="F154" s="17">
-        <f>+[78]Main!$I$4*FX!C5</f>
+        <f>+[79]Main!$I$4*FX!C5</f>
         <v>409.27593709799999</v>
       </c>
       <c r="G154" s="17">
-        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
+        <f>+([79]Main!$I$6-[79]Main!$I$5)*FX!C5</f>
         <v>-123.31619999999999</v>
       </c>
       <c r="H154" s="17">
@@ -15677,15 +15682,15 @@
         <v>21</v>
       </c>
       <c r="E155" s="24">
-        <f>+[79]Main!$J$2</f>
+        <f>+[80]Main!$J$2</f>
         <v>15.35</v>
       </c>
       <c r="F155" s="17">
-        <f>+[79]Main!$J$4</f>
+        <f>+[80]Main!$J$4</f>
         <v>1258.5394543499999</v>
       </c>
       <c r="G155" s="17">
-        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
+        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
         <v>427.29999999999995</v>
       </c>
       <c r="H155" s="17">
@@ -20433,15 +20438,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="45">
-        <f>+[80]Main!$J$2</f>
+        <f>+[1]Main!$J$2</f>
         <v>225.4</v>
       </c>
       <c r="F20" s="56">
-        <f>+[80]Main!$J$4</f>
+        <f>+[1]Main!$J$4</f>
         <v>19955.789000000001</v>
       </c>
       <c r="G20" s="56">
-        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
+        <f>+[1]Main!$J$6-[1]Main!$J$5</f>
         <v>907.58199999999999</v>
       </c>
       <c r="H20" s="56">

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4ABFB7B-4E81-4451-85A0-6F9329426EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB70E10C-0078-4252-83B3-38C764A26DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="4680" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3330,78 +3330,44 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Quarters"/>
       <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>225.4</v>
-          </cell>
-        </row>
         <row r="4">
-          <cell r="J4">
-            <v>19955.789000000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>998.22799999999995</v>
+          <cell r="I4">
+            <v>499.3</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>1905.81</v>
+          <cell r="I6">
+            <v>248495.08914200001</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>8794</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>20343</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="H3">
-            <v>232.02</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>74236.423139999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>4130.9799999999996</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1018.1869999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3437,15 +3403,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3485,7 +3451,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3539,7 +3505,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3579,7 +3545,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3619,7 +3585,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3634,17 +3600,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>170.3</v>
+            <v>166.25</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>272336.26679999998</v>
+            <v>265601.16625000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>18733</v>
+            <v>18697</v>
           </cell>
         </row>
         <row r="6">
@@ -3653,13 +3619,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3707,7 +3673,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3743,7 +3709,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3785,53 +3751,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="I4">
-            <v>499.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>248495.08914200001</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>8794</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="I8">
-            <v>20343</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3871,7 +3791,53 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Quarters"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>1751</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>184852.040412</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>12239</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>34</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3911,7 +3877,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3951,7 +3917,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3991,7 +3957,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4037,7 +4003,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4077,7 +4043,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4117,7 +4083,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4159,7 +4125,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4197,7 +4163,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4237,53 +4203,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Quarters"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>1751</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>184852.040412</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>12239</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>34</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4317,13 +4237,57 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="J3">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>171386.35277500001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>10797</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4363,7 +4327,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4403,7 +4367,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4443,7 +4407,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4483,7 +4447,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4523,7 +4487,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4563,7 +4527,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4603,7 +4567,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4643,7 +4607,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4683,51 +4647,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="J3">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>171386.35277500001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>10797</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4775,7 +4695,51 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+      <sheetName val="DCF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>159.16999999999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>178270.4</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5580</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>2870</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4815,7 +4779,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4855,7 +4819,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4895,7 +4859,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4935,7 +4899,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4973,7 +4937,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5013,7 +4977,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5053,7 +5017,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5093,7 +5057,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5139,51 +5103,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-      <sheetName val="DCF"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>159.16999999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>178270.4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5580</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>2870</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5223,7 +5143,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financial"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>471.6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>85081.629528000005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9760</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>22957</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5257,13 +5217,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5301,7 +5261,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5341,7 +5301,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5381,7 +5341,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5421,7 +5381,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5461,7 +5421,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5501,7 +5461,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5541,7 +5501,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5581,47 +5541,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financial"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>471.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>85081.629528000005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9760</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>22957</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -5661,365 +5581,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>263.45</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270582.07176934998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1259.98</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>3707.71</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>74.900000000000006</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>5953.9305021000009</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>207</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>990</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>44.03</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>3217.9517470800001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>77.156000000000006</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>286.49700000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>18.14</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2154.9996926600002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>135</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>357</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>10.61</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>2684.5824118999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>297.553</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>246.18899999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>828.4</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>201333.06192080001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>440.44</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>269.23</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5.82</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2055.0937514400002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>214.85400000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2186.0569999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.42</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>1491.5652650000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>412.92599999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>498.12</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>38.119999999999997</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1935.4971035199997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>325.44000000000005</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6065,7 +5627,365 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>263.45</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270582.07176934998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1259.98</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>3707.71</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>74.900000000000006</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5953.9305021000009</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>207</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>990</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>44.03</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>3217.9517470800001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>77.156000000000006</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>286.49700000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>18.14</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2154.9996926600002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>357</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>10.61</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>2684.5824118999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>297.553</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>246.18899999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>828.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>201333.06192080001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>440.44</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>269.23</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5.82</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2055.0937514400002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>214.85400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2186.0569999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41.42</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>1491.5652650000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>412.92599999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>498.12</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>38.119999999999997</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1935.4971035199997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>325.44000000000005</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6105,367 +6025,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>27.07</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1188.01315849</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>104.68600000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>224.17499999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>59.85</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>939.70682505000002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>7.0270000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>57.816000000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>13.57</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>1318.1272015899999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>408.2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>410.59999999999997</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>4.53</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>736.21656488999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>245.11399999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>9.6039999999999992</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>16.75</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>872.38125524999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>189.63499999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>623.71199999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main "/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="F2">
-            <v>2.4350000000000001</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="F4">
-            <v>290.48290130999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="F5">
-            <v>318.89999999999998</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="F6">
-            <v>503.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>0.98</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>97.21301296</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>17.213000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>291.31400000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>17.79</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>270.90115659000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>45.523000000000003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>70.016000000000005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2540</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>64964.434459999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>33044</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>13470</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6520,7 +6080,367 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>27.07</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1188.01315849</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>104.68600000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>224.17499999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>59.85</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>939.70682505000002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>7.0270000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>57.816000000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>13.57</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>1318.1272015899999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>408.2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>410.59999999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4.53</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>736.21656488999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>245.11399999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>9.6039999999999992</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>16.75</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>872.38125524999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>189.63499999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>623.71199999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main "/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="F2">
+            <v>2.4350000000000001</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4">
+            <v>290.48290130999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5">
+            <v>318.89999999999998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>503.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>0.98</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>97.21301296</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>17.213000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>291.31400000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>17.79</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>270.90115659000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>45.523000000000003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>70.016000000000005</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2540</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>64964.434459999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>33044</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>13470</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -6551,6 +6471,86 @@
         <row r="6">
           <cell r="J6">
             <v>546.9</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>170</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>68068</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>183.20400000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>2656.7910000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>225.4</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>19955.789000000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>998.22799999999995</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>1905.81</v>
           </cell>
         </row>
       </sheetData>
@@ -6737,24 +6737,24 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>170</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>68068</v>
+        <row r="3">
+          <cell r="H3">
+            <v>232.02</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>183.20400000000001</v>
+          <cell r="H5">
+            <v>74236.423139999999</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>2656.7910000000002</v>
+          <cell r="H6">
+            <v>4130.9799999999996</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>1018.1869999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -7300,15 +7300,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1806632.6828585202</v>
+        <v>1805992.8483062703</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>9312.3892152000008</v>
+        <v>9315.8092152000008</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1815945.0720737199</v>
+        <v>1815308.65752147</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7370,15 +7370,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22889.879724683142</v>
+        <v>22881.780553135675</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>120.94011967792208</v>
+        <v>120.98453526233767</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23583.702234723634</v>
+        <v>23575.437110668441</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -7476,15 +7476,15 @@
         <v>20</v>
       </c>
       <c r="E6" s="24">
-        <f>+[2]Main!$I$4</f>
+        <f>+[1]Main!$I$4</f>
         <v>499.3</v>
       </c>
       <c r="F6" s="17">
-        <f>+[2]Main!$I$6*FX!C3</f>
+        <f>+[1]Main!$I$6*FX!C3</f>
         <v>258434.89270768003</v>
       </c>
       <c r="G6" s="17">
-        <f>(+[2]Main!$I$8-[2]Main!$I$7)*FX!C3</f>
+        <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
         <v>12010.960000000001</v>
       </c>
       <c r="H6" s="17">
@@ -7579,15 +7579,15 @@
         <v>20</v>
       </c>
       <c r="E7" s="29">
-        <f>+[3]Main!$K$2</f>
+        <f>+[2]Main!$K$2</f>
         <v>1751</v>
       </c>
       <c r="F7" s="17">
-        <f>+[3]Main!$K$4*FX!C3</f>
+        <f>+[2]Main!$K$4*FX!C3</f>
         <v>192246.12202848002</v>
       </c>
       <c r="G7" s="17">
-        <f>+([3]Main!$K$6-[3]Main!$K$5)*FX!C3</f>
+        <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
         <v>-12693.2</v>
       </c>
       <c r="H7" s="17">
@@ -7682,15 +7682,15 @@
         <v>100</v>
       </c>
       <c r="E8" s="24">
-        <f>+[4]Main!$J$3</f>
+        <f>+[3]Main!$J$3</f>
         <v>55</v>
       </c>
       <c r="F8" s="17">
-        <f>+[4]Main!$J$5*FX!C3</f>
+        <f>+[3]Main!$J$5*FX!C3</f>
         <v>178241.80688600001</v>
       </c>
       <c r="G8" s="17">
-        <f>+([4]Main!$J$7-[4]Main!$J$6)*FX!C3</f>
+        <f>+([3]Main!$J$7-[3]Main!$J$6)*FX!C3</f>
         <v>-11228.880000000001</v>
       </c>
       <c r="H8" s="17">
@@ -7782,15 +7782,15 @@
         <v>21</v>
       </c>
       <c r="E9" s="24">
-        <f>+[5]Main!$I$3</f>
+        <f>+[4]Main!$I$3</f>
         <v>159.16999999999999</v>
       </c>
       <c r="F9" s="17">
-        <f>+[5]Main!$I$5</f>
+        <f>+[4]Main!$I$5</f>
         <v>178270.4</v>
       </c>
       <c r="G9" s="17">
-        <f>+[5]Main!$I$7-[5]Main!$I$6</f>
+        <f>+[4]Main!$I$7-[4]Main!$I$6</f>
         <v>-2710</v>
       </c>
       <c r="H9" s="17">
@@ -7877,15 +7877,15 @@
         <v>20</v>
       </c>
       <c r="E10" s="24">
-        <f>+[6]Main!$I$2</f>
+        <f>+[5]Main!$I$2</f>
         <v>471.6</v>
       </c>
       <c r="F10" s="17">
-        <f>+[6]Main!$I$4*FX!C3</f>
+        <f>+[5]Main!$I$4*FX!C3</f>
         <v>88484.89470912001</v>
       </c>
       <c r="G10" s="17">
-        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C3</f>
+        <f>+([5]Main!$I$6-[5]Main!$I$5)*FX!C3</f>
         <v>13724.880000000001</v>
       </c>
       <c r="H10" s="17">
@@ -7952,15 +7952,15 @@
         <v>21</v>
       </c>
       <c r="E11" s="24">
-        <f>+[7]Main!$I$3</f>
+        <f>+[6]Main!$I$3</f>
         <v>48.01</v>
       </c>
       <c r="F11" s="17">
-        <f>+[7]Main!$I$5</f>
+        <f>+[6]Main!$I$5</f>
         <v>71078.804999999993</v>
       </c>
       <c r="G11" s="17">
-        <f>+[7]Main!$I$7-[7]Main!$I$6</f>
+        <f>+[6]Main!$I$7-[6]Main!$I$6</f>
         <v>-28</v>
       </c>
       <c r="H11" s="17">
@@ -8049,15 +8049,15 @@
         <v>124</v>
       </c>
       <c r="E12" s="29">
-        <f>+[8]Main!$J$3</f>
+        <f>+[7]Main!$J$3</f>
         <v>75540</v>
       </c>
       <c r="F12" s="17">
-        <f>+[8]Main!$J$5*FX!C5</f>
+        <f>+[7]Main!$J$5*FX!C5</f>
         <v>146020.56045670799</v>
       </c>
       <c r="G12" s="17">
-        <f>+([8]Main!$J$7-[8]Main!$J$6)*FX!C5</f>
+        <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
         <v>-4946.4386999999997</v>
       </c>
       <c r="H12" s="17">
@@ -8078,7 +8078,7 @@
         <v>0.08</v>
       </c>
       <c r="M12" s="17">
-        <f>+SUM([8]Model!$G$20:$I$20,[8]Model!$C$20)*FX!C5</f>
+        <f>+SUM([7]Model!$G$20:$I$20,[7]Model!$C$20)*FX!C5</f>
         <v>3765.1320000000001</v>
       </c>
       <c r="N12" s="17">
@@ -8137,15 +8137,15 @@
         <v>21</v>
       </c>
       <c r="E13" s="24">
-        <f>+[9]Main!$K$2</f>
+        <f>+[8]Main!$K$2</f>
         <v>170</v>
       </c>
       <c r="F13" s="17">
-        <f>+[9]Main!$K$4</f>
+        <f>+[8]Main!$K$4</f>
         <v>68068</v>
       </c>
       <c r="G13" s="17">
-        <f>+[9]Main!$K$6-[9]Main!$K$5</f>
+        <f>+[8]Main!$K$6-[8]Main!$K$5</f>
         <v>2473.587</v>
       </c>
       <c r="H13" s="17">
@@ -8216,15 +8216,15 @@
         <v>21</v>
       </c>
       <c r="E14" s="24">
-        <f>+[10]Main!$H$3</f>
+        <f>+[9]Main!$H$3</f>
         <v>232.02</v>
       </c>
       <c r="F14" s="17">
-        <f>+[10]Main!$H$5</f>
+        <f>+[9]Main!$H$5</f>
         <v>74236.423139999999</v>
       </c>
       <c r="G14" s="17">
-        <f>+[10]Main!$H$7-[10]Main!$H$6</f>
+        <f>+[9]Main!$H$7-[9]Main!$H$6</f>
         <v>-3112.7929999999997</v>
       </c>
       <c r="H14" s="17">
@@ -8291,15 +8291,15 @@
         <v>107</v>
       </c>
       <c r="E15" s="24">
-        <f>+[11]Main!$I$2</f>
+        <f>+[10]Main!$I$2</f>
         <v>114.34</v>
       </c>
       <c r="F15" s="17">
-        <f>+[11]Main!$I$4</f>
+        <f>+[10]Main!$I$4</f>
         <v>12398.796003380001</v>
       </c>
       <c r="G15" s="17">
-        <f>+[11]Main!$I$6-[11]Main!$I$5</f>
+        <f>+[10]Main!$I$6-[10]Main!$I$5</f>
         <v>-1514.729</v>
       </c>
       <c r="H15" s="17">
@@ -8366,15 +8366,15 @@
         <v>82</v>
       </c>
       <c r="E16" s="24">
-        <f>+[12]Main!$I$2</f>
+        <f>+[11]Main!$I$2</f>
         <v>147.4</v>
       </c>
       <c r="F16" s="17">
-        <f>+[12]Main!$I$4*FX!C3</f>
+        <f>+[11]Main!$I$4*FX!C3</f>
         <v>27162.897954192002</v>
       </c>
       <c r="G16" s="17">
-        <f>+([12]Main!$I$6-[12]Main!$I$5)*FX!C3</f>
+        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
         <v>2208.96</v>
       </c>
       <c r="H16" s="17">
@@ -8444,15 +8444,15 @@
         <v>20</v>
       </c>
       <c r="E17" s="24">
-        <f>+[13]Main!$H$2</f>
+        <f>+[12]Main!$H$2</f>
         <v>256.14999999999998</v>
       </c>
       <c r="F17" s="17">
-        <f>+[13]Main!$H$4*FX!C3</f>
+        <f>+[12]Main!$H$4*FX!C3</f>
         <v>32661.431497551999</v>
       </c>
       <c r="G17" s="17">
-        <f>+([13]Main!$H$6-[13]Main!$H$5)*FX!C3</f>
+        <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
         <v>8578.9600000000009</v>
       </c>
       <c r="H17" s="17">
@@ -8544,15 +8544,15 @@
         <v>454</v>
       </c>
       <c r="E18" s="24">
-        <f>+[14]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>80.55</v>
       </c>
       <c r="F18" s="17">
-        <f>+[14]Main!$H$5*FX!C9</f>
+        <f>+[13]Main!$H$5*FX!C9</f>
         <v>29160.086447520003</v>
       </c>
       <c r="G18" s="17">
-        <f>+([14]Main!$H$7-[14]Main!$H$6)*FX!C9</f>
+        <f>+([13]Main!$H$7-[13]Main!$H$6)*FX!C9</f>
         <v>-1841.5600000000002</v>
       </c>
       <c r="H18" s="17">
@@ -8623,15 +8623,15 @@
         <v>21</v>
       </c>
       <c r="E19" s="24">
-        <f>+[15]Main!$M$2</f>
+        <f>+[14]Main!$M$2</f>
         <v>107</v>
       </c>
       <c r="F19" s="17">
-        <f>+[15]Main!$M$4</f>
+        <f>+[14]Main!$M$4</f>
         <v>14860.262398999999</v>
       </c>
       <c r="G19" s="17">
-        <f>+[15]Main!$M$6-[15]Main!$M$5</f>
+        <f>+[14]Main!$M$6-[14]Main!$M$5</f>
         <v>-1907.249</v>
       </c>
       <c r="H19" s="17">
@@ -8707,27 +8707,25 @@
         <v>109</v>
       </c>
       <c r="E20" s="24">
-        <f>+[16]Main!$I$2</f>
-        <v>170.3</v>
+        <f>+[15]Main!$I$2</f>
+        <v>166.25</v>
       </c>
       <c r="F20" s="17">
-        <f>+[16]Main!$I$4*FX!C4</f>
-        <v>25871.945346</v>
+        <f>+[15]Main!$I$4*FX!C4</f>
+        <v>25232.110793750002</v>
       </c>
       <c r="G20" s="17">
-        <f>+([16]Main!$I$6-[16]Main!$I$5)*FX!C4</f>
-        <v>184.49</v>
+        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C4</f>
+        <v>187.91</v>
       </c>
       <c r="H20" s="17">
         <f t="shared" si="1"/>
-        <v>26056.435346000002</v>
+        <v>25420.020793750002</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>828</v>
-      </c>
-      <c r="J20" s="26">
-        <v>46198</v>
-      </c>
+        <v>807</v>
+      </c>
+      <c r="J20" s="26"/>
       <c r="K20" s="17">
         <f>234478*FX!C4</f>
         <v>22275.41</v>
@@ -8775,15 +8773,15 @@
         <v>165</v>
       </c>
       <c r="E21" s="24">
-        <f>+[17]Main!$H$2</f>
+        <f>+[16]Main!$H$2</f>
         <v>34.700000000000003</v>
       </c>
       <c r="F21" s="17">
-        <f>+[17]Main!$H$5*FX!C3</f>
+        <f>+[16]Main!$H$5*FX!C3</f>
         <v>11081.140861440002</v>
       </c>
       <c r="G21" s="17">
-        <f>(+[17]Main!$H$7-[17]Main!$H$6)*FX!C3</f>
+        <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
         <v>489.51760000000007</v>
       </c>
       <c r="H21" s="17">
@@ -8838,15 +8836,15 @@
         <v>185</v>
       </c>
       <c r="E22" s="24">
-        <f>+[18]Main!$I$2</f>
+        <f>+[17]Main!$I$2</f>
         <v>5221.55</v>
       </c>
       <c r="F22" s="17">
-        <f>+[18]Main!$I$4*FX!C12</f>
+        <f>+[17]Main!$I$4*FX!C12</f>
         <v>20418.151071830049</v>
       </c>
       <c r="G22" s="17">
-        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C12</f>
+        <f>+([17]Main!$I$6-[17]Main!$I$5)*FX!C12</f>
         <v>0</v>
       </c>
       <c r="H22" s="17">
@@ -8895,15 +8893,15 @@
         <v>165</v>
       </c>
       <c r="E23" s="24">
-        <f>+[19]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>53.46</v>
       </c>
       <c r="F23" s="17">
-        <f>+[19]Main!$H$4*FX!C3</f>
+        <f>+[18]Main!$H$4*FX!C3</f>
         <v>15040.638902203202</v>
       </c>
       <c r="G23" s="17">
-        <f>+([19]Main!$H$6-[19]Main!$H$5)*FX!C3</f>
+        <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C3</f>
         <v>-376.31984</v>
       </c>
       <c r="H23" s="17">
@@ -8958,15 +8956,15 @@
         <v>21</v>
       </c>
       <c r="E24" s="24">
-        <f>+[20]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>304.51</v>
       </c>
       <c r="F24" s="17">
-        <f>+[20]Main!$I$4</f>
+        <f>+[19]Main!$I$4</f>
         <v>19088.948091260001</v>
       </c>
       <c r="G24" s="17">
-        <f>+[20]Main!$I$6-[20]Main!$I$5</f>
+        <f>+[19]Main!$I$6-[19]Main!$I$5</f>
         <v>1451.345</v>
       </c>
       <c r="H24" s="17">
@@ -9021,15 +9019,15 @@
         <v>21</v>
       </c>
       <c r="E25" s="24">
-        <f>+[21]Main!$J$2</f>
+        <f>+[20]Main!$J$2</f>
         <v>134.28</v>
       </c>
       <c r="F25" s="17">
-        <f>+[21]Main!$J$4</f>
+        <f>+[20]Main!$J$4</f>
         <v>27130.56419592</v>
       </c>
       <c r="G25" s="17">
-        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
+        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
         <v>1330.5779</v>
       </c>
       <c r="H25" s="17">
@@ -9084,15 +9082,15 @@
         <v>124</v>
       </c>
       <c r="E26" s="24">
-        <f>+[22]Main!$I$2</f>
+        <f>+[21]Main!$I$2</f>
         <v>4496</v>
       </c>
       <c r="F26" s="17">
-        <f>+[22]Main!$I$4*FX!C5</f>
+        <f>+[21]Main!$I$4*FX!C5</f>
         <v>20073.934380225597</v>
       </c>
       <c r="G26" s="17">
-        <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C5</f>
+        <f>+([21]Main!$I$6-[21]Main!$I$5)*FX!C5</f>
         <v>-279.65070000000003</v>
       </c>
       <c r="H26" s="17">
@@ -9147,15 +9145,15 @@
         <v>219</v>
       </c>
       <c r="E27" s="24">
-        <f>+[23]Main!$I$2</f>
+        <f>+[22]Main!$I$2</f>
         <v>127.35</v>
       </c>
       <c r="F27" s="17">
-        <f>+[23]Main!$I$4*FX!C8</f>
+        <f>+[22]Main!$I$4*FX!C8</f>
         <v>18491.7294</v>
       </c>
       <c r="G27" s="17">
-        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C8</f>
+        <f>+([22]Main!$I$6-[22]Main!$I$5)*FX!C8</f>
         <v>421.84800000000007</v>
       </c>
       <c r="H27" s="17">
@@ -9210,15 +9208,15 @@
         <v>166</v>
       </c>
       <c r="E28" s="24">
-        <f>+[24]Main!$H$2</f>
+        <f>+[23]Main!$H$2</f>
         <v>36.42</v>
       </c>
       <c r="F28" s="17">
-        <f>+[24]Main!$H$5*FX!C7</f>
+        <f>+[23]Main!$H$5*FX!C7</f>
         <v>10293.145395479522</v>
       </c>
       <c r="G28" s="17">
-        <f>+([24]Main!$H$7-[24]Main!$H$6)*FX!C7</f>
+        <f>+([23]Main!$H$7-[23]Main!$H$6)*FX!C7</f>
         <v>-1077.8880000000001</v>
       </c>
       <c r="H28" s="17">
@@ -9273,15 +9271,15 @@
         <v>214</v>
       </c>
       <c r="E29" s="24">
-        <f>+[25]Main!$J$2</f>
+        <f>+[24]Main!$J$2</f>
         <v>35.26</v>
       </c>
       <c r="F29" s="17">
-        <f>+[25]Main!$J$4</f>
+        <f>+[24]Main!$J$4</f>
         <v>19918.456120539999</v>
       </c>
       <c r="G29" s="17">
-        <f>+[25]Main!$J$6-[25]Main!$J$5</f>
+        <f>+[24]Main!$J$6-[24]Main!$J$5</f>
         <v>-538.80000000000007</v>
       </c>
       <c r="H29" s="17">
@@ -9336,15 +9334,15 @@
         <v>454</v>
       </c>
       <c r="E30" s="24">
-        <f>+[26]Main!$J$2</f>
+        <f>+[25]Main!$J$2</f>
         <v>47.12</v>
       </c>
       <c r="F30" s="17">
-        <f>+[26]Main!$J$5*FX!C9</f>
+        <f>+[25]Main!$J$5*FX!C9</f>
         <v>8726.4826075060482</v>
       </c>
       <c r="G30" s="17">
-        <f>+([26]Main!$J$7-[26]Main!$J$6)*FX!C9</f>
+        <f>+([25]Main!$J$7-[25]Main!$J$6)*FX!C9</f>
         <v>-1503.0597399999999</v>
       </c>
       <c r="H30" s="17">
@@ -9399,15 +9397,15 @@
         <v>21</v>
       </c>
       <c r="E31" s="24">
-        <f>+[27]Main!$H$2</f>
+        <f>+[26]Main!$H$2</f>
         <v>376.91</v>
       </c>
       <c r="F31" s="17">
-        <f>+[27]Main!$H$4</f>
+        <f>+[26]Main!$H$4</f>
         <v>22473.766070860001</v>
       </c>
       <c r="G31" s="17">
-        <f>+[27]Main!$H$6-[27]Main!$H$5</f>
+        <f>+[26]Main!$H$6-[26]Main!$H$5</f>
         <v>-826.09999999999991</v>
       </c>
       <c r="H31" s="17">
@@ -9493,15 +9491,15 @@
         <v>454</v>
       </c>
       <c r="E32" s="24">
-        <f>+[28]Main!$K$2</f>
+        <f>+[27]Main!$K$2</f>
         <v>76.739999999999995</v>
       </c>
       <c r="F32" s="17">
-        <f>+[28]Main!$K$4*FX!C9</f>
+        <f>+[27]Main!$K$4*FX!C9</f>
         <v>12537.781199999999</v>
       </c>
       <c r="G32" s="17">
-        <f>+([28]Main!$K$6-[28]Main!$K$5)*FX!C9</f>
+        <f>+([27]Main!$K$6-[27]Main!$K$5)*FX!C9</f>
         <v>-745.22328020000009</v>
       </c>
       <c r="H32" s="17">
@@ -9556,15 +9554,15 @@
         <v>82</v>
       </c>
       <c r="E33" s="24">
-        <f>+[29]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>19.87</v>
       </c>
       <c r="F33" s="17">
-        <f>+[29]Main!$I$4*FX!C3</f>
+        <f>+[28]Main!$I$4*FX!C3</f>
         <v>5381.1139200000007</v>
       </c>
       <c r="G33" s="17">
-        <f>+([29]Main!$I$6-[29]Main!$I$5)*FX!C3</f>
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
         <v>-565.76</v>
       </c>
       <c r="H33" s="17">
@@ -9617,15 +9615,15 @@
         <v>21</v>
       </c>
       <c r="E34" s="24">
-        <f>+[30]Main!$H$2</f>
+        <f>+[29]Main!$H$2</f>
         <v>16.72</v>
       </c>
       <c r="F34" s="17">
-        <f>+[30]Main!$H$4</f>
+        <f>+[29]Main!$H$4</f>
         <v>6550.3894675999991</v>
       </c>
       <c r="G34" s="17">
-        <f>+[30]Main!$H$6-[30]Main!$H$5</f>
+        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
         <v>2706.0659999999998</v>
       </c>
       <c r="H34" s="17">
@@ -9680,15 +9678,15 @@
         <v>82</v>
       </c>
       <c r="E35" s="24">
-        <f>+[31]Main!$I$3</f>
+        <f>+[30]Main!$I$3</f>
         <v>29.172000000000001</v>
       </c>
       <c r="F35" s="17">
-        <f>+[31]Main!$I$5*FX!C3</f>
+        <f>+[30]Main!$I$5*FX!C3</f>
         <v>5579.5037642572797</v>
       </c>
       <c r="G35" s="17">
-        <f>+([31]Main!$I$7-[31]Main!$I$6)*FX!C3</f>
+        <f>+([30]Main!$I$7-[30]Main!$I$6)*FX!C3</f>
         <v>985.08904000000018</v>
       </c>
       <c r="H35" s="17">
@@ -9743,15 +9741,15 @@
         <v>21</v>
       </c>
       <c r="E36" s="24">
-        <f>+[32]Main!$J$2</f>
+        <f>+[31]Main!$J$2</f>
         <v>21.27</v>
       </c>
       <c r="F36" s="17">
-        <f>+[32]Main!$J$4</f>
+        <f>+[31]Main!$J$4</f>
         <v>7806.09</v>
       </c>
       <c r="G36" s="17">
-        <f>+([32]Main!$J$6-[32]Main!$J$5)</f>
+        <f>+([31]Main!$J$6-[31]Main!$J$5)</f>
         <v>-1069</v>
       </c>
       <c r="H36" s="17">
@@ -9818,15 +9816,15 @@
         <v>21</v>
       </c>
       <c r="E37" s="24">
-        <f>+[33]Main!$I$2</f>
+        <f>+[32]Main!$I$2</f>
         <v>60.4</v>
       </c>
       <c r="F37" s="17">
-        <f>+[33]Main!$I$4</f>
+        <f>+[32]Main!$I$4</f>
         <v>9118.7085583999997</v>
       </c>
       <c r="G37" s="17">
-        <f>+[33]Main!$I$6-[33]Main!$I$5</f>
+        <f>+[32]Main!$I$6-[32]Main!$I$5</f>
         <v>-838.96200000000022</v>
       </c>
       <c r="H37" s="17">
@@ -9881,15 +9879,15 @@
         <v>165</v>
       </c>
       <c r="E38" s="24">
-        <f>+[34]Main!$J$2</f>
+        <f>+[33]Main!$J$2</f>
         <v>86.1</v>
       </c>
       <c r="F38" s="17">
-        <f>+[34]Main!$J$4*FX!C3</f>
+        <f>+[33]Main!$J$4*FX!C3</f>
         <v>6088.4257237439997</v>
       </c>
       <c r="G38" s="17">
-        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C3</f>
+        <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
         <v>200.49328000000006</v>
       </c>
       <c r="H38" s="17">
@@ -9944,15 +9942,15 @@
         <v>107</v>
       </c>
       <c r="E39" s="24">
-        <f>+[35]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>63.14</v>
       </c>
       <c r="F39" s="17">
-        <f>+[35]Main!$I$4</f>
+        <f>+[34]Main!$I$4</f>
         <v>11754.016119999998</v>
       </c>
       <c r="G39" s="17">
-        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
+        <f>+[34]Main!$I$6-[34]Main!$I$5</f>
         <v>4478.0450000000001</v>
       </c>
       <c r="H39" s="17">
@@ -10007,15 +10005,15 @@
         <v>21</v>
       </c>
       <c r="E40" s="24">
-        <f>+[36]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>22.68</v>
       </c>
       <c r="F40" s="17">
-        <f>+[36]Main!$I$4</f>
+        <f>+[35]Main!$I$4</f>
         <v>8722.6429726799997</v>
       </c>
       <c r="G40" s="17">
-        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
+        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
         <v>237.40000000000009</v>
       </c>
       <c r="H40" s="17">
@@ -10082,15 +10080,15 @@
         <v>294</v>
       </c>
       <c r="E41" s="24">
-        <f>+[37]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>17550</v>
       </c>
       <c r="F41" s="17">
-        <f>+[37]Main!$I$4*FX!C11</f>
+        <f>+[36]Main!$I$4*FX!C11</f>
         <v>8142.7173750000002</v>
       </c>
       <c r="G41" s="17">
-        <f>+([37]Main!$I$6-[37]Main!$I$5)*FX!C11</f>
+        <f>+([36]Main!$I$6-[36]Main!$I$5)*FX!C11</f>
         <v>171.25</v>
       </c>
       <c r="H41" s="17">
@@ -10141,15 +10139,15 @@
         <v>454</v>
       </c>
       <c r="E42" s="24">
-        <f>+[38]Main!$J$2</f>
+        <f>+[37]Main!$J$2</f>
         <v>8.7799999999999994</v>
       </c>
       <c r="F42" s="17">
-        <f>+[38]Main!$J$4*FX!C9</f>
+        <f>+[37]Main!$J$4*FX!C9</f>
         <v>5900.1600000000008</v>
       </c>
       <c r="G42" s="17">
-        <f>+([38]Main!$J$6-[38]Main!$J$5)*FX!C9</f>
+        <f>+([37]Main!$J$6-[37]Main!$J$5)*FX!C9</f>
         <v>-679.00000000000011</v>
       </c>
       <c r="H42" s="17">
@@ -10200,15 +10198,15 @@
         <v>185</v>
       </c>
       <c r="E43" s="24">
-        <f>+[39]Main!$H$2</f>
+        <f>+[38]Main!$H$2</f>
         <v>41240</v>
       </c>
       <c r="F43" s="17">
-        <f>+[39]Main!$H$4*FX!C12</f>
+        <f>+[38]Main!$H$4*FX!C12</f>
         <v>5059.9509140399996</v>
       </c>
       <c r="G43" s="17">
-        <f>+([39]Main!$H$6-[39]Main!$H$5)*FX!C12</f>
+        <f>+([38]Main!$H$6-[38]Main!$H$5)*FX!C12</f>
         <v>79.99563000000002</v>
       </c>
       <c r="H43" s="17">
@@ -10259,15 +10257,15 @@
         <v>21</v>
       </c>
       <c r="E44" s="24">
-        <f>+[40]Main!$H$2</f>
+        <f>+[39]Main!$H$2</f>
         <v>102.6</v>
       </c>
       <c r="F44" s="17">
-        <f>+[40]Main!$H$4</f>
+        <f>+[39]Main!$H$4</f>
         <v>5098.1578847999999</v>
       </c>
       <c r="G44" s="17">
-        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
+        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
         <v>1204.9399999999998</v>
       </c>
       <c r="H44" s="17">
@@ -10322,15 +10320,15 @@
         <v>325</v>
       </c>
       <c r="E45" s="24">
-        <f>+[41]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>27.8</v>
       </c>
       <c r="F45" s="17">
-        <f>+[41]Main!$I$4*FX!C14</f>
+        <f>+[40]Main!$I$4*FX!C14</f>
         <v>5512.4063999999998</v>
       </c>
       <c r="G45" s="17">
-        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C14</f>
+        <f>+([40]Main!$I$6-[40]Main!$I$5)*FX!C14</f>
         <v>392.36399999999998</v>
       </c>
       <c r="H45" s="17">
@@ -10385,15 +10383,15 @@
         <v>219</v>
       </c>
       <c r="E46" s="24">
-        <f>+[42]Main!$I$2</f>
+        <f>+[41]Main!$I$2</f>
         <v>0.93779999999999997</v>
       </c>
       <c r="F46" s="17">
-        <f>+[42]Main!$I$4*FX!C8</f>
+        <f>+[41]Main!$I$4*FX!C8</f>
         <v>5962.0447439999998</v>
       </c>
       <c r="G46" s="17">
-        <f>+([42]Main!$I$6-[42]Main!$I$5)*FX!C8</f>
+        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C8</f>
         <v>155</v>
       </c>
       <c r="H46" s="17">
@@ -10448,15 +10446,15 @@
         <v>107</v>
       </c>
       <c r="E47" s="24">
-        <f>+[43]Main!$H$2</f>
+        <f>+[42]Main!$H$2</f>
         <v>86.42</v>
       </c>
       <c r="F47" s="17">
-        <f>+[43]Main!$H$4*FX!C13</f>
+        <f>+[42]Main!$H$4*FX!C13</f>
         <v>6825.0480185999995</v>
       </c>
       <c r="G47" s="17">
-        <f>+([43]Main!$H$6-[43]Main!$H$5)*FX!C13</f>
+        <f>+([42]Main!$H$6-[42]Main!$H$5)*FX!C13</f>
         <v>-201.90158999999997</v>
       </c>
       <c r="H47" s="17">
@@ -10507,15 +10505,15 @@
         <v>454</v>
       </c>
       <c r="E48" s="24">
-        <f>+[44]Main!$H$2</f>
+        <f>+[43]Main!$H$2</f>
         <v>16.02</v>
       </c>
       <c r="F48" s="17">
-        <f>+[44]Main!$H$5*FX!C9</f>
+        <f>+[43]Main!$H$5*FX!C9</f>
         <v>5313.5769879360005</v>
       </c>
       <c r="G48" s="17">
-        <f>+([44]Main!$H$7-[44]Main!$H$6)*FX!C9</f>
+        <f>+([43]Main!$H$7-[43]Main!$H$6)*FX!C9</f>
         <v>-2458.0551799999998</v>
       </c>
       <c r="H48" s="17">
@@ -10568,15 +10566,15 @@
         <v>454</v>
       </c>
       <c r="E49" s="24">
-        <f>+[45]Main!$I$2</f>
+        <f>+[44]Main!$I$2</f>
         <v>8.01</v>
       </c>
       <c r="F49" s="17">
-        <f>+[45]Main!$I$4*FX!C9</f>
+        <f>+[44]Main!$I$4*FX!C9</f>
         <v>5141.5464790620008</v>
       </c>
       <c r="G49" s="17">
-        <f>+([45]Main!$I$6-[45]Main!$I$5)*FX!C9</f>
+        <f>+([44]Main!$I$6-[44]Main!$I$5)*FX!C9</f>
         <v>1697.6221653999999</v>
       </c>
       <c r="H49" s="17">
@@ -10625,15 +10623,15 @@
         <v>21</v>
       </c>
       <c r="E50" s="24">
-        <f>+[46]Main!$J$2</f>
+        <f>+[45]Main!$J$2</f>
         <v>74.28</v>
       </c>
       <c r="F50" s="17">
-        <f>+[46]Main!$J$4</f>
+        <f>+[45]Main!$J$4</f>
         <v>6499.7862008400007</v>
       </c>
       <c r="G50" s="17">
-        <f>+[46]Main!$J$6-[46]Main!$J$5</f>
+        <f>+[45]Main!$J$6-[45]Main!$J$5</f>
         <v>-413.34199999999998</v>
       </c>
       <c r="H50" s="17">
@@ -10682,15 +10680,15 @@
         <v>82</v>
       </c>
       <c r="E51" s="24">
-        <f>+[47]Main!$I$2</f>
+        <f>+[46]Main!$I$2</f>
         <v>25.98</v>
       </c>
       <c r="F51" s="17">
-        <f>+[47]Main!$I$4*FX!C3</f>
+        <f>+[46]Main!$I$4*FX!C3</f>
         <v>3978.0368159999998</v>
       </c>
       <c r="G51" s="17">
-        <f>+([47]Main!$I$6-[47]Main!$I$5)*FX!C3</f>
+        <f>+([46]Main!$I$6-[46]Main!$I$5)*FX!C3</f>
         <v>1411.904</v>
       </c>
       <c r="H51" s="17">
@@ -10745,15 +10743,15 @@
         <v>454</v>
       </c>
       <c r="E52" s="24">
-        <f>+[48]Main!$I$2</f>
+        <f>+[47]Main!$I$2</f>
         <v>3.75</v>
       </c>
       <c r="F52" s="17">
-        <f>+[48]Main!$I$5*FX!C9</f>
+        <f>+[47]Main!$I$5*FX!C9</f>
         <v>5271.5025720000003</v>
       </c>
       <c r="G52" s="17">
-        <f>+([48]Main!$I$7-[48]Main!$I$6)*FX!C9</f>
+        <f>+([47]Main!$I$7-[47]Main!$I$6)*FX!C9</f>
         <v>-653.85012000000006</v>
       </c>
       <c r="H52" s="17">
@@ -10808,15 +10806,15 @@
         <v>21</v>
       </c>
       <c r="E53" s="24">
-        <f>+[49]Main!$I$2</f>
+        <f>+[48]Main!$I$2</f>
         <v>83.06</v>
       </c>
       <c r="F53" s="17">
-        <f>+[49]Main!$I$4</f>
+        <f>+[48]Main!$I$4</f>
         <v>3735.1251400000001</v>
       </c>
       <c r="G53" s="17">
-        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
+        <f>+[48]Main!$I$6-[48]Main!$I$5</f>
         <v>-619.22400000000005</v>
       </c>
       <c r="H53" s="17">
@@ -10881,15 +10879,15 @@
         <v>21</v>
       </c>
       <c r="E54" s="24">
-        <f>+[50]Main!$I$2</f>
+        <f>+[49]Main!$I$2</f>
         <v>58.06</v>
       </c>
       <c r="F54" s="17">
-        <f>+[50]Main!$I$4</f>
+        <f>+[49]Main!$I$4</f>
         <v>2969.2344415800003</v>
       </c>
       <c r="G54" s="17">
-        <f>+[50]Main!$I$6-[50]Main!$I$5</f>
+        <f>+[49]Main!$I$6-[49]Main!$I$5</f>
         <v>-535.35400000000004</v>
       </c>
       <c r="H54" s="17">
@@ -10944,15 +10942,15 @@
         <v>21</v>
       </c>
       <c r="E55" s="24">
-        <f>+[51]Main!$J$2</f>
+        <f>+[50]Main!$J$2</f>
         <v>77.790000000000006</v>
       </c>
       <c r="F55" s="17">
-        <f>+[51]Main!$J$4</f>
+        <f>+[50]Main!$J$4</f>
         <v>3586.7484766800003</v>
       </c>
       <c r="G55" s="17">
-        <f>+([51]Main!$J$6-[51]Main!$J$5)</f>
+        <f>+([50]Main!$J$6-[50]Main!$J$5)</f>
         <v>1689.8000000000002</v>
       </c>
       <c r="H55" s="17">
@@ -11007,15 +11005,15 @@
         <v>124</v>
       </c>
       <c r="E56" s="24">
-        <f>+[52]Main!$I$2</f>
+        <f>+[51]Main!$I$2</f>
         <v>2816.5</v>
       </c>
       <c r="F56" s="17">
-        <f>+[52]Main!$I$4*FX!C5</f>
+        <f>+[51]Main!$I$4*FX!C5</f>
         <v>4393.7011297651507</v>
       </c>
       <c r="G56" s="17">
-        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C5</f>
+        <f>+([51]Main!$I$6-[51]Main!$I$5)*FX!C5</f>
         <v>-837.64170000000001</v>
       </c>
       <c r="H56" s="17">
@@ -11070,15 +11068,15 @@
         <v>219</v>
       </c>
       <c r="E57" s="24">
-        <f>+[53]Main!$I$2</f>
+        <f>+[52]Main!$I$2</f>
         <v>10.93</v>
       </c>
       <c r="F57" s="17">
-        <f>+[53]Main!$I$4*FX!C3</f>
+        <f>+[52]Main!$I$4*FX!C3</f>
         <v>4072.8677600000001</v>
       </c>
       <c r="G57" s="17">
-        <f>+([53]Main!$I$6-[53]Main!$I$5)*FX!C3</f>
+        <f>+([52]Main!$I$6-[52]Main!$I$5)*FX!C3</f>
         <v>-107.12</v>
       </c>
       <c r="H57" s="17">
@@ -11127,15 +11125,15 @@
         <v>21</v>
       </c>
       <c r="E58" s="24">
-        <f>+[54]Main!$I$2</f>
+        <f>+[53]Main!$I$2</f>
         <v>165.1</v>
       </c>
       <c r="F58" s="17">
-        <f>+[54]Main!$I$4</f>
+        <f>+[53]Main!$I$4</f>
         <v>5044.7333572999996</v>
       </c>
       <c r="G58" s="17">
-        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
+        <f>+[53]Main!$I$6-[53]Main!$I$5</f>
         <v>-95.319000000000003</v>
       </c>
       <c r="H58" s="17">
@@ -11190,15 +11188,15 @@
         <v>21</v>
       </c>
       <c r="E59" s="24">
-        <f>+[55]Main!$I$2</f>
+        <f>+[54]Main!$I$2</f>
         <v>78.680000000000007</v>
       </c>
       <c r="F59" s="17">
-        <f>+[55]Main!$I$4</f>
+        <f>+[54]Main!$I$4</f>
         <v>4372.5807311200006</v>
       </c>
       <c r="G59" s="17">
-        <f>+[55]Main!$I$6-[55]Main!$I$5</f>
+        <f>+[54]Main!$I$6-[54]Main!$I$5</f>
         <v>1259.028</v>
       </c>
       <c r="H59" s="17">
@@ -11300,15 +11298,15 @@
         <v>433</v>
       </c>
       <c r="E61" s="24">
-        <f>+[56]Main!$J$2</f>
+        <f>+[55]Main!$J$2</f>
         <v>132.5</v>
       </c>
       <c r="F61" s="17">
-        <f>+[56]Main!$J$4*FX!C15</f>
+        <f>+[55]Main!$J$4*FX!C15</f>
         <v>3925.244925</v>
       </c>
       <c r="G61" s="17">
-        <f>+([56]Main!$J$6-[56]Main!$J$5)*FX!C15</f>
+        <f>+([55]Main!$J$6-[55]Main!$J$5)*FX!C15</f>
         <v>122.75229000000002</v>
       </c>
       <c r="H61" s="17">
@@ -11357,15 +11355,15 @@
         <v>21</v>
       </c>
       <c r="E62" s="24">
-        <f>+[57]Main!$J$2</f>
+        <f>+[56]Main!$J$2</f>
         <v>161.28</v>
       </c>
       <c r="F62" s="17">
-        <f>+[57]Main!$J$4</f>
+        <f>+[56]Main!$J$4</f>
         <v>2990.6024601600002</v>
       </c>
       <c r="G62" s="17">
-        <f>+[57]Main!$J$6-[57]Main!$J$5</f>
+        <f>+[56]Main!$J$6-[56]Main!$J$5</f>
         <v>-211.91</v>
       </c>
       <c r="H62" s="17">
@@ -11416,15 +11414,15 @@
         <v>82</v>
       </c>
       <c r="E63" s="24">
-        <f>+[58]Main!$J$2</f>
+        <f>+[57]Main!$J$2</f>
         <v>35.700000000000003</v>
       </c>
       <c r="F63" s="17">
-        <f>+[58]Main!$J$4*FX!C3</f>
+        <f>+[57]Main!$J$4*FX!C3</f>
         <v>2562.4323597600001</v>
       </c>
       <c r="G63" s="17">
-        <f>+([58]Main!$J$6-[58]Main!$J$5)*FX!C3</f>
+        <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
         <v>-17.68</v>
       </c>
       <c r="H63" s="17">
@@ -11473,15 +11471,15 @@
         <v>21</v>
       </c>
       <c r="E64" s="24">
-        <f>+[59]Main!$I$2</f>
+        <f>+[58]Main!$I$2</f>
         <v>4.97</v>
       </c>
       <c r="F64" s="17">
-        <f>+[59]Main!$I$4</f>
+        <f>+[58]Main!$I$4</f>
         <v>2117.1355100000001</v>
       </c>
       <c r="G64" s="17">
-        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
+        <f>+[58]Main!$I$6-[58]Main!$I$5</f>
         <v>881.27599999999995</v>
       </c>
       <c r="H64" s="17">
@@ -11532,15 +11530,15 @@
         <v>21</v>
       </c>
       <c r="E65" s="24">
-        <f>+[60]Main!$I$2</f>
+        <f>+[59]Main!$I$2</f>
         <v>14.35</v>
       </c>
       <c r="F65" s="17">
-        <f>+[60]Main!$I$4</f>
+        <f>+[59]Main!$I$4</f>
         <v>2756.6605860499999</v>
       </c>
       <c r="G65" s="17">
-        <f>+[60]Main!$I$6-[60]Main!$I$5</f>
+        <f>+[59]Main!$I$6-[59]Main!$I$5</f>
         <v>-160.19499999999999</v>
       </c>
       <c r="H65" s="17">
@@ -11591,15 +11589,15 @@
         <v>185</v>
       </c>
       <c r="E66" s="24">
-        <f>+[61]Main!$I$2</f>
+        <f>+[60]Main!$I$2</f>
         <v>263.45</v>
       </c>
       <c r="F66" s="17">
-        <f>+[61]Main!$I$4*FX!C12</f>
+        <f>+[60]Main!$I$4*FX!C12</f>
         <v>2976.4027894628493</v>
       </c>
       <c r="G66" s="17">
-        <f>+([61]Main!$I$6-[61]Main!$I$5)*FX!C12</f>
+        <f>+([60]Main!$I$6-[60]Main!$I$5)*FX!C12</f>
         <v>26.92503</v>
       </c>
       <c r="H66" s="17">
@@ -11648,15 +11646,15 @@
         <v>21</v>
       </c>
       <c r="E67" s="24">
-        <f>+[62]Main!$I$2</f>
+        <f>+[61]Main!$I$2</f>
         <v>74.900000000000006</v>
       </c>
       <c r="F67" s="17">
-        <f>+[62]Main!$I$4</f>
+        <f>+[61]Main!$I$4</f>
         <v>5953.9305021000009</v>
       </c>
       <c r="G67" s="17">
-        <f>+[62]Main!$I$6-[62]Main!$I$5</f>
+        <f>+[61]Main!$I$6-[61]Main!$I$5</f>
         <v>783</v>
       </c>
       <c r="H67" s="17">
@@ -11711,15 +11709,15 @@
         <v>21</v>
       </c>
       <c r="E68" s="24">
-        <f>+[63]Main!$H$2</f>
+        <f>+[62]Main!$H$2</f>
         <v>44.03</v>
       </c>
       <c r="F68" s="17">
-        <f>+[63]Main!$H$4</f>
+        <f>+[62]Main!$H$4</f>
         <v>3217.9517470800001</v>
       </c>
       <c r="G68" s="17">
-        <f>+[63]Main!$H$6-[63]Main!$H$5</f>
+        <f>+[62]Main!$H$6-[62]Main!$H$5</f>
         <v>209.34100000000001</v>
       </c>
       <c r="H68" s="17">
@@ -11770,15 +11768,15 @@
         <v>219</v>
       </c>
       <c r="E69" s="24">
-        <f>+[64]Main!$I$2</f>
+        <f>+[63]Main!$I$2</f>
         <v>18.14</v>
       </c>
       <c r="F69" s="17">
-        <f>+[64]Main!$I$4</f>
+        <f>+[63]Main!$I$4</f>
         <v>2154.9996926600002</v>
       </c>
       <c r="G69" s="17">
-        <f>+[64]Main!$I$6-[64]Main!$I$5</f>
+        <f>+[63]Main!$I$6-[63]Main!$I$5</f>
         <v>222</v>
       </c>
       <c r="H69" s="17">
@@ -11833,15 +11831,15 @@
         <v>165</v>
       </c>
       <c r="E70" s="24">
-        <f>+[65]Main!$J$2</f>
+        <f>+[64]Main!$J$2</f>
         <v>10.61</v>
       </c>
       <c r="F70" s="17">
-        <f>+[65]Main!$J$4*FX!C3</f>
+        <f>+[64]Main!$J$4*FX!C3</f>
         <v>2791.9657083759998</v>
       </c>
       <c r="G70" s="17">
-        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C3</f>
+        <f>+([64]Main!$J$6-[64]Main!$J$5)*FX!C3</f>
         <v>-53.418560000000006</v>
       </c>
       <c r="H70" s="17">
@@ -11892,15 +11890,15 @@
         <v>185</v>
       </c>
       <c r="E71" s="24">
-        <f>+[66]Main!$J$2</f>
+        <f>+[65]Main!$J$2</f>
         <v>828.4</v>
       </c>
       <c r="F71" s="17">
-        <f>+[66]Main!$J$4*FX!C12</f>
+        <f>+[65]Main!$J$4*FX!C12</f>
         <v>2214.6636811287999</v>
       </c>
       <c r="G71" s="17">
-        <f>+([66]Main!$J$6-[66]Main!$J$5)*FX!C12</f>
+        <f>+([65]Main!$J$6-[65]Main!$J$5)*FX!C12</f>
         <v>-1.8833099999999996</v>
       </c>
       <c r="H71" s="17">
@@ -12402,15 +12400,15 @@
         <v>21</v>
       </c>
       <c r="E83" s="24">
-        <f>+[67]Main!$I$2</f>
+        <f>+[66]Main!$I$2</f>
         <v>5.82</v>
       </c>
       <c r="F83" s="17">
-        <f>+[67]Main!$I$4</f>
+        <f>+[66]Main!$I$4</f>
         <v>2055.0937514400002</v>
       </c>
       <c r="G83" s="17">
-        <f>+[67]Main!$I$6-[67]Main!$I$5</f>
+        <f>+[66]Main!$I$6-[66]Main!$I$5</f>
         <v>1971.2029999999997</v>
       </c>
       <c r="H83" s="17">
@@ -12670,15 +12668,15 @@
         <v>21</v>
       </c>
       <c r="E89" s="24">
-        <f>+[68]Main!$H$2</f>
+        <f>+[67]Main!$H$2</f>
         <v>41.42</v>
       </c>
       <c r="F89" s="17">
-        <f>+[68]Main!$H$4</f>
+        <f>+[67]Main!$H$4</f>
         <v>1491.5652650000002</v>
       </c>
       <c r="G89" s="17">
-        <f>+[68]Main!$H$6-[68]Main!$H$5</f>
+        <f>+[67]Main!$H$6-[67]Main!$H$5</f>
         <v>85.194000000000017</v>
       </c>
       <c r="H89" s="17">
@@ -12727,15 +12725,15 @@
         <v>21</v>
       </c>
       <c r="E90" s="24">
-        <f>+[69]Main!$I$2</f>
+        <f>+[68]Main!$I$2</f>
         <v>38.119999999999997</v>
       </c>
       <c r="F90" s="17">
-        <f>+[69]Main!$I$4</f>
+        <f>+[68]Main!$I$4</f>
         <v>1935.4971035199997</v>
       </c>
       <c r="G90" s="17">
-        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
+        <f>+[68]Main!$I$6-[68]Main!$I$5</f>
         <v>-325.44000000000005</v>
       </c>
       <c r="H90" s="17">
@@ -12784,15 +12782,15 @@
         <v>21</v>
       </c>
       <c r="E91" s="24">
-        <f>+[70]Main!$I$2</f>
+        <f>+[69]Main!$I$2</f>
         <v>24.73</v>
       </c>
       <c r="F91" s="17">
-        <f>+[70]Main!$I$4</f>
+        <f>+[69]Main!$I$4</f>
         <v>1761.5194085300002</v>
       </c>
       <c r="G91" s="17">
-        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
+        <f>+[69]Main!$I$6-[69]Main!$I$5</f>
         <v>-256.60000000000002</v>
       </c>
       <c r="H91" s="17">
@@ -12974,15 +12972,15 @@
         <v>21</v>
       </c>
       <c r="E95" s="24">
-        <f>+[71]Main!$I$2</f>
+        <f>+[70]Main!$I$2</f>
         <v>27.07</v>
       </c>
       <c r="F95" s="17">
-        <f>+[71]Main!$I$4</f>
+        <f>+[70]Main!$I$4</f>
         <v>1188.01315849</v>
       </c>
       <c r="G95" s="17">
-        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
+        <f>+[70]Main!$I$6-[70]Main!$I$5</f>
         <v>119.48899999999998</v>
       </c>
       <c r="H95" s="17">
@@ -13031,15 +13029,15 @@
         <v>21</v>
       </c>
       <c r="E96" s="24">
-        <f>+[72]Main!$I$2</f>
+        <f>+[71]Main!$I$2</f>
         <v>59.85</v>
       </c>
       <c r="F96" s="17">
-        <f>+[72]Main!$I$4</f>
+        <f>+[71]Main!$I$4</f>
         <v>939.70682505000002</v>
       </c>
       <c r="G96" s="17">
-        <f>+[72]Main!$I$6-[72]Main!$I$5</f>
+        <f>+[71]Main!$I$6-[71]Main!$I$5</f>
         <v>50.789000000000001</v>
       </c>
       <c r="H96" s="17">
@@ -13088,15 +13086,15 @@
         <v>107</v>
       </c>
       <c r="E97" s="24">
-        <f>+[73]Main!$J$2</f>
+        <f>+[72]Main!$J$2</f>
         <v>13.57</v>
       </c>
       <c r="F97" s="17">
-        <f>+[73]Main!$J$4*FX!C13</f>
+        <f>+[72]Main!$J$4*FX!C13</f>
         <v>909.50776909709987</v>
       </c>
       <c r="G97" s="17">
-        <f>+([73]Main!$J$6-[73]Main!$J$5)*FX!C13</f>
+        <f>+([72]Main!$J$6-[72]Main!$J$5)*FX!C13</f>
         <v>1.6559999999999842</v>
       </c>
       <c r="H97" s="17">
@@ -13233,15 +13231,15 @@
         <v>21</v>
       </c>
       <c r="E100" s="24">
-        <f>+[74]Main!$I$2</f>
+        <f>+[73]Main!$I$2</f>
         <v>4.53</v>
       </c>
       <c r="F100" s="17">
-        <f>+[74]Main!$I$4</f>
+        <f>+[73]Main!$I$4</f>
         <v>736.21656488999997</v>
       </c>
       <c r="G100" s="17">
-        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
+        <f>+[73]Main!$I$6-[73]Main!$I$5</f>
         <v>-235.51</v>
       </c>
       <c r="H100" s="17">
@@ -13290,15 +13288,15 @@
         <v>21</v>
       </c>
       <c r="E101" s="24">
-        <f>+[75]Main!$I$2</f>
+        <f>+[74]Main!$I$2</f>
         <v>16.75</v>
       </c>
       <c r="F101" s="17">
-        <f>+[75]Main!$I$4</f>
+        <f>+[74]Main!$I$4</f>
         <v>872.38125524999998</v>
       </c>
       <c r="G101" s="17">
-        <f>+[75]Main!$I$6-[75]Main!$I$5</f>
+        <f>+[74]Main!$I$6-[74]Main!$I$5</f>
         <v>434.077</v>
       </c>
       <c r="H101" s="17">
@@ -13949,15 +13947,15 @@
         <v>219</v>
       </c>
       <c r="E116" s="24">
-        <f>+'[76]Main '!$F$2</f>
+        <f>+'[75]Main '!$F$2</f>
         <v>2.4350000000000001</v>
       </c>
       <c r="F116" s="17">
-        <f>+'[76]Main '!$F$4*FX!C8</f>
+        <f>+'[75]Main '!$F$4*FX!C8</f>
         <v>360.19879762439996</v>
       </c>
       <c r="G116" s="17">
-        <f>+('[76]Main '!$F$6-'[76]Main '!$F$5)*FX!C8</f>
+        <f>+('[75]Main '!$F$6-'[75]Main '!$F$5)*FX!C8</f>
         <v>229.02800000000005</v>
       </c>
       <c r="H116" s="17">
@@ -14264,15 +14262,15 @@
         <v>21</v>
       </c>
       <c r="E123" s="24">
-        <f>+[77]Main!$H$2</f>
+        <f>+[76]Main!$H$2</f>
         <v>0.98</v>
       </c>
       <c r="F123" s="17">
-        <f>+[77]Main!$H$4</f>
+        <f>+[76]Main!$H$4</f>
         <v>97.21301296</v>
       </c>
       <c r="G123" s="17">
-        <f>+[77]Main!$H$6-[77]Main!$H$5</f>
+        <f>+[76]Main!$H$6-[76]Main!$H$5</f>
         <v>274.101</v>
       </c>
       <c r="H123" s="17">
@@ -14364,15 +14362,15 @@
         <v>21</v>
       </c>
       <c r="E125" s="24">
-        <f>+[78]Main!$I$2</f>
+        <f>+[77]Main!$I$2</f>
         <v>17.79</v>
       </c>
       <c r="F125" s="17">
-        <f>+[78]Main!$I$4</f>
+        <f>+[77]Main!$I$4</f>
         <v>270.90115659000003</v>
       </c>
       <c r="G125" s="17">
-        <f>+[78]Main!$I$6-[78]Main!$I$5</f>
+        <f>+[77]Main!$I$6-[77]Main!$I$5</f>
         <v>24.493000000000002</v>
       </c>
       <c r="H125" s="17">
@@ -15625,15 +15623,15 @@
         <v>124</v>
       </c>
       <c r="E154" s="24">
-        <f>+[79]Main!$I$2</f>
+        <f>+[78]Main!$I$2</f>
         <v>2540</v>
       </c>
       <c r="F154" s="17">
-        <f>+[79]Main!$I$4*FX!C5</f>
+        <f>+[78]Main!$I$4*FX!C5</f>
         <v>409.27593709799999</v>
       </c>
       <c r="G154" s="17">
-        <f>+([79]Main!$I$6-[79]Main!$I$5)*FX!C5</f>
+        <f>+([78]Main!$I$6-[78]Main!$I$5)*FX!C5</f>
         <v>-123.31619999999999</v>
       </c>
       <c r="H154" s="17">
@@ -15682,15 +15680,15 @@
         <v>21</v>
       </c>
       <c r="E155" s="24">
-        <f>+[80]Main!$J$2</f>
+        <f>+[79]Main!$J$2</f>
         <v>15.35</v>
       </c>
       <c r="F155" s="17">
-        <f>+[80]Main!$J$4</f>
+        <f>+[79]Main!$J$4</f>
         <v>1258.5394543499999</v>
       </c>
       <c r="G155" s="17">
-        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
+        <f>+[79]Main!$J$6-[79]Main!$J$5</f>
         <v>427.29999999999995</v>
       </c>
       <c r="H155" s="17">
@@ -20438,15 +20436,15 @@
         <v>21</v>
       </c>
       <c r="E20" s="45">
-        <f>+[1]Main!$J$2</f>
+        <f>+[80]Main!$J$2</f>
         <v>225.4</v>
       </c>
       <c r="F20" s="56">
-        <f>+[1]Main!$J$4</f>
+        <f>+[80]Main!$J$4</f>
         <v>19955.789000000001</v>
       </c>
       <c r="G20" s="56">
-        <f>+[1]Main!$J$6-[1]Main!$J$5</f>
+        <f>+[80]Main!$J$6-[80]Main!$J$5</f>
         <v>907.58199999999999</v>
       </c>
       <c r="H20" s="56">

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB70E10C-0078-4252-83B3-38C764A26DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6FD525-6E01-454D-8079-EF4D02C3F74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4680" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="899">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2550,9 +2550,6 @@
   </si>
   <si>
     <t>Former influencial people</t>
-  </si>
-  <si>
-    <t>FQ226</t>
   </si>
   <si>
     <t>https://investors.guess.com/news-releases/news-release-details/guess-co-founders-maurice-and-paul-marciano-and-ceo-carlos</t>
@@ -3096,7 +3093,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3271,34 +3268,35 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3619,7 +3617,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4502,22 +4500,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>22.68</v>
+            <v>24.26</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>8722.6429726799997</v>
+            <v>8463.1146341200019</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>812</v>
+            <v>977.8</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1049.4000000000001</v>
+            <v>1043</v>
           </cell>
         </row>
       </sheetData>
@@ -5599,22 +5597,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>48.01</v>
+            <v>44.05</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>71078.804999999993</v>
+            <v>65348.117867149995</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>8057</v>
+            <v>9027</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>8029</v>
+            <v>7942</v>
           </cell>
         </row>
       </sheetData>
@@ -6040,22 +6038,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>75540</v>
+            <v>82110</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>23177866.739159998</v>
+            <v>25194231.538980003</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>1040505</v>
+            <v>1132.078</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>255356</v>
+            <v>232915</v>
           </cell>
         </row>
       </sheetData>
@@ -6495,12 +6493,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>170</v>
+            <v>202.53</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>68068</v>
+            <v>81093.012000000002</v>
           </cell>
         </row>
         <row r="5">
@@ -6637,8 +6635,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7218,10 +7216,10 @@
         <v>95</v>
       </c>
       <c r="M3" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="N3" s="10" t="s">
         <v>810</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>811</v>
       </c>
       <c r="O3" s="10" t="s">
         <v>89</v>
@@ -7296,25 +7294,25 @@
         <v>31</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1805992.8483062703</v>
+        <v>1825730.7430737263</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>9315.8092152000008</v>
+        <v>14493.280323800005</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1815308.65752147</v>
+        <v>1840224.023397526</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="K4" s="17">
         <f>SUM(K6:K153)</f>
@@ -7359,32 +7357,32 @@
         <v>88</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D5" s="82" t="str" cm="1">
         <f t="array" ref="D5">_xlfn.LET(_xlpm.rng,D6:D182,INDEX(_xlpm.rng,MATCH(MAX(COUNTIF(_xlpm.rng,_xlpm.rng)),COUNTIF(_xlpm.rng,_xlpm.rng),0)))</f>
         <v>US</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22881.780553135675</v>
+        <v>23131.627322343978</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>120.98453526233767</v>
+        <v>188.22441978961047</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23575.437110668441</v>
+        <v>23899.013290876963</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
       </c>
       <c r="J5" s="80" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="K5" s="83">
         <f>AVERAGE(K6:K153)</f>
@@ -7492,7 +7490,7 @@
         <v>270445.85270768002</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J6" s="26">
         <v>46231</v>
@@ -7698,7 +7696,7 @@
         <v>167012.926886</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J8" s="26">
         <v>46274</v>
@@ -7798,7 +7796,7 @@
         <v>175560.4</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="J9" s="26">
         <v>46253</v>
@@ -7953,25 +7951,25 @@
       </c>
       <c r="E11" s="24">
         <f>+[6]Main!$I$3</f>
-        <v>48.01</v>
+        <v>44.05</v>
       </c>
       <c r="F11" s="17">
         <f>+[6]Main!$I$5</f>
-        <v>71078.804999999993</v>
+        <v>65348.117867149995</v>
       </c>
       <c r="G11" s="17">
         <f>+[6]Main!$I$7-[6]Main!$I$6</f>
-        <v>-28</v>
+        <v>-1085</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>71050.804999999993</v>
+        <v>64263.117867149995</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="J11" s="26">
-        <v>46198</v>
+        <v>46294</v>
       </c>
       <c r="K11" s="17">
         <v>51362</v>
@@ -8050,25 +8048,25 @@
       </c>
       <c r="E12" s="29">
         <f>+[7]Main!$J$3</f>
-        <v>75540</v>
+        <v>82110</v>
       </c>
       <c r="F12" s="17">
         <f>+[7]Main!$J$5*FX!C5</f>
-        <v>146020.56045670799</v>
+        <v>158723.65869557403</v>
       </c>
       <c r="G12" s="17">
         <f>+([7]Main!$J$7-[7]Main!$J$6)*FX!C5</f>
-        <v>-4946.4386999999997</v>
+        <v>1460.2324085999999</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" si="1"/>
-        <v>141074.12175670799</v>
+        <v>160183.89110417402</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>797</v>
+        <v>818</v>
       </c>
       <c r="J12" s="26">
-        <v>46212</v>
+        <v>46303</v>
       </c>
       <c r="K12" s="17">
         <f>2301122*FX!C5</f>
@@ -8138,11 +8136,11 @@
       </c>
       <c r="E13" s="24">
         <f>+[8]Main!$K$2</f>
-        <v>170</v>
+        <v>202.53</v>
       </c>
       <c r="F13" s="17">
         <f>+[8]Main!$K$4</f>
-        <v>68068</v>
+        <v>81093.012000000002</v>
       </c>
       <c r="G13" s="17">
         <f>+[8]Main!$K$6-[8]Main!$K$5</f>
@@ -8150,10 +8148,10 @@
       </c>
       <c r="H13" s="17">
         <f t="shared" si="1"/>
-        <v>70541.587</v>
+        <v>83566.599000000002</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J13" s="26">
         <v>46219</v>
@@ -8232,7 +8230,7 @@
         <v>71123.630139999994</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J14" s="26">
         <v>46254</v>
@@ -8382,7 +8380,7 @@
         <v>29371.857954192001</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J16" s="26">
         <v>46268</v>
@@ -8460,7 +8458,7 @@
         <v>41240.391497552002</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J17" s="26">
         <v>46231</v>
@@ -8639,7 +8637,7 @@
         <v>12953.013398999999</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J19" s="26">
         <v>46226</v>
@@ -8723,7 +8721,7 @@
         <v>25420.020793750002</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J20" s="26"/>
       <c r="K20" s="17">
@@ -8789,7 +8787,7 @@
         <v>11570.658461440002</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J21" s="26">
         <v>46203</v>
@@ -8909,7 +8907,7 @@
         <v>14664.319062203202</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J23" s="26">
         <v>46225</v>
@@ -9035,7 +9033,7 @@
         <v>28461.14209592</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J25" s="26">
         <v>46247</v>
@@ -9098,7 +9096,7 @@
         <v>19794.283680225599</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J26" s="26">
         <v>46247</v>
@@ -9224,7 +9222,7 @@
         <v>9215.2573954795207</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J28" s="26">
         <v>46245</v>
@@ -9287,7 +9285,7 @@
         <v>19379.656120539999</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J29" s="26">
         <v>46252</v>
@@ -9413,7 +9411,7 @@
         <v>21647.666070860003</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J31" s="26">
         <v>46240</v>
@@ -9570,7 +9568,7 @@
         <v>4815.3539200000005</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J33" s="26"/>
       <c r="K33" s="24"/>
@@ -9631,7 +9629,7 @@
         <v>9256.4554675999989</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J34" s="26">
         <v>46232</v>
@@ -9694,7 +9692,7 @@
         <v>6564.5928042572796</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J35" s="26">
         <v>46247</v>
@@ -9757,7 +9755,7 @@
         <v>6737.09</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J36" s="26">
         <v>46261</v>
@@ -9835,7 +9833,7 @@
         <v>337</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="K37" s="17"/>
       <c r="L37" s="21"/>
@@ -9958,7 +9956,7 @@
         <v>16232.061119999998</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J39" s="26">
         <v>46233</v>
@@ -10006,25 +10004,25 @@
       </c>
       <c r="E40" s="24">
         <f>+[35]Main!$I$2</f>
-        <v>22.68</v>
+        <v>24.26</v>
       </c>
       <c r="F40" s="17">
         <f>+[35]Main!$I$4</f>
-        <v>8722.6429726799997</v>
+        <v>8463.1146341200019</v>
       </c>
       <c r="G40" s="17">
         <f>+[35]Main!$I$6-[35]Main!$I$5</f>
-        <v>237.40000000000009</v>
+        <v>65.200000000000045</v>
       </c>
       <c r="H40" s="17">
         <f>F40+G40</f>
-        <v>8960.0429726799994</v>
+        <v>8528.3146341200027</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="J40" s="26">
-        <v>46212</v>
+        <v>46303</v>
       </c>
       <c r="K40" s="17">
         <v>6179</v>
@@ -10273,7 +10271,7 @@
         <v>6303.0978847999995</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J44" s="26">
         <v>46240</v>
@@ -10399,7 +10397,7 @@
         <v>6117.0447439999998</v>
       </c>
       <c r="I46" s="25" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J46" s="26">
         <v>45981</v>
@@ -10639,7 +10637,7 @@
         <v>6086.444200840001</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="J50" s="26"/>
       <c r="K50" s="17"/>
@@ -10696,7 +10694,7 @@
         <v>5389.9408160000003</v>
       </c>
       <c r="I51" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J51" s="26">
         <v>46233</v>
@@ -10822,7 +10820,7 @@
         <v>3115.9011399999999</v>
       </c>
       <c r="I53" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J53" s="26"/>
       <c r="K53" s="17">
@@ -10958,7 +10956,7 @@
         <v>5276.54847668</v>
       </c>
       <c r="I55" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J55" s="26">
         <v>46261</v>
@@ -11084,7 +11082,7 @@
         <v>3965.7477600000002</v>
       </c>
       <c r="I57" s="16" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J57" s="26"/>
       <c r="K57" s="17"/>
@@ -11141,7 +11139,7 @@
         <v>4949.4143572999992</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="J58" s="26">
         <v>45957</v>
@@ -11251,7 +11249,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
@@ -11371,7 +11369,7 @@
         <v>2778.6924601600003</v>
       </c>
       <c r="I62" s="16" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J62" s="26">
         <v>45952</v>
@@ -11430,7 +11428,7 @@
         <v>2544.7523597600002</v>
       </c>
       <c r="I63" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J63" s="26"/>
       <c r="K63" s="17"/>
@@ -11487,7 +11485,7 @@
         <v>2998.4115099999999</v>
       </c>
       <c r="I64" s="16" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J64" s="26">
         <v>46241</v>
@@ -11640,7 +11638,7 @@
         <v>161</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>21</v>
@@ -11662,7 +11660,7 @@
         <v>6736.9305021000009</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J67" s="26">
         <v>46261</v>
@@ -11725,7 +11723,7 @@
         <v>3427.29274708</v>
       </c>
       <c r="I68" s="16" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J68" s="26">
         <v>46232</v>
@@ -11784,7 +11782,7 @@
         <v>2376.9996926600002</v>
       </c>
       <c r="I69" s="16" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J69" s="26">
         <v>46239</v>
@@ -13102,7 +13100,7 @@
         <v>911.16376909709982</v>
       </c>
       <c r="I97" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J97" s="26">
         <v>46233</v>
@@ -14278,7 +14276,7 @@
         <v>371.31401296000001</v>
       </c>
       <c r="I123" s="16" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="J123" s="2"/>
       <c r="K123" s="17"/>
@@ -17806,12 +17804,12 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="97" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.85546875" style="97" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="97" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="97" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.28515625" style="97" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="97"/>
+    <col min="1" max="1" width="5.42578125" style="96" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.85546875" style="96" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="96" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="96" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.28515625" style="96" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="96"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -17824,7 +17822,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D2" s="74" t="s">
         <v>717</v>
@@ -17836,203 +17834,203 @@
         <v>4</v>
       </c>
       <c r="G2" s="75" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2" s="75" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="96" t="s">
         <v>719</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>720</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="96" t="s">
         <v>728</v>
       </c>
-      <c r="E3" s="98">
+      <c r="E3" s="97">
         <v>45757</v>
       </c>
-      <c r="F3" s="99" t="s">
+      <c r="F3" s="98" t="s">
         <v>474</v>
       </c>
-      <c r="G3" s="99">
+      <c r="G3" s="98">
         <v>1250</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="96" t="s">
         <v>692</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>692</v>
       </c>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="96" t="s">
         <v>726</v>
       </c>
-      <c r="E4" s="98">
+      <c r="E4" s="97">
         <v>45782</v>
       </c>
-      <c r="F4" s="100" t="s">
+      <c r="F4" s="99" t="s">
         <v>727</v>
       </c>
-      <c r="G4" s="101">
+      <c r="G4" s="100">
         <v>9420</v>
       </c>
-      <c r="H4" s="97" t="s">
-        <v>801</v>
+      <c r="H4" s="96" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="96" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="97" t="s">
+      <c r="C5" s="96" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="97" t="s">
+      <c r="D5" s="96" t="s">
         <v>729</v>
       </c>
-      <c r="E5" s="98">
+      <c r="E5" s="97">
         <v>45637</v>
       </c>
-      <c r="F5" s="99" t="s">
+      <c r="F5" s="98" t="s">
         <v>474</v>
       </c>
-      <c r="G5" s="101">
+      <c r="G5" s="100">
         <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="96" t="s">
         <v>730</v>
       </c>
-      <c r="C6" s="97" t="s">
+      <c r="C6" s="96" t="s">
         <v>730</v>
       </c>
-      <c r="D6" s="97" t="s">
+      <c r="D6" s="96" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="96" t="s">
         <v>191</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="97" t="s">
+      <c r="D7" s="96" t="s">
         <v>680</v>
       </c>
-      <c r="E7" s="98">
+      <c r="E7" s="97">
         <v>45889</v>
       </c>
-      <c r="F7" s="97">
+      <c r="F7" s="96">
         <v>16.75</v>
       </c>
-      <c r="G7" s="97" t="s">
-        <v>799</v>
-      </c>
-      <c r="H7" s="97" t="s">
+      <c r="G7" s="96" t="s">
         <v>798</v>
       </c>
+      <c r="H7" s="96" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="96" t="s">
         <v>420</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="101" t="s">
         <v>476</v>
       </c>
-      <c r="D8" s="97" t="s">
+      <c r="D8" s="96" t="s">
+        <v>803</v>
+      </c>
+      <c r="E8" s="97">
+        <v>45322</v>
+      </c>
+      <c r="G8" s="96">
+        <v>500</v>
+      </c>
+      <c r="H8" s="96" t="s">
         <v>804</v>
       </c>
-      <c r="E8" s="98">
-        <v>45322</v>
-      </c>
-      <c r="G8" s="97">
-        <v>500</v>
-      </c>
-      <c r="H8" s="97" t="s">
-        <v>805</v>
-      </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="96" t="s">
+        <v>807</v>
+      </c>
+      <c r="C9" s="96" t="s">
         <v>808</v>
       </c>
-      <c r="C9" s="97" t="s">
-        <v>809</v>
-      </c>
-      <c r="D9" s="97" t="s">
+      <c r="D9" s="96" t="s">
         <v>689</v>
       </c>
-      <c r="E9" s="98">
+      <c r="E9" s="97">
         <v>45808</v>
       </c>
-      <c r="G9" s="97">
+      <c r="G9" s="96">
         <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="B10" s="97" t="s">
-        <v>866</v>
-      </c>
-      <c r="C10" s="97" t="s">
-        <v>866</v>
-      </c>
-      <c r="D10" s="97" t="s">
+      <c r="B10" s="96" t="s">
         <v>865</v>
       </c>
-      <c r="E10" s="98">
+      <c r="C10" s="96" t="s">
+        <v>865</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>864</v>
+      </c>
+      <c r="E10" s="97">
         <v>46112</v>
       </c>
-      <c r="F10" s="100" t="s">
+      <c r="F10" s="99" t="s">
         <v>474</v>
       </c>
-      <c r="G10" s="97">
+      <c r="G10" s="96">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="96" t="s">
+        <v>867</v>
+      </c>
+      <c r="C11" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="96" t="s">
         <v>868</v>
       </c>
-      <c r="C11" s="97" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="97" t="s">
-        <v>869</v>
-      </c>
-      <c r="E11" s="98">
+      <c r="E11" s="97">
         <v>46156</v>
       </c>
-      <c r="F11" s="100" t="s">
+      <c r="F11" s="99" t="s">
         <v>474</v>
       </c>
-      <c r="G11" s="97">
+      <c r="G11" s="96">
         <v>850</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="B12" s="97" t="s">
-        <v>872</v>
-      </c>
-      <c r="C12" s="97" t="s">
-        <v>874</v>
-      </c>
-      <c r="D12" s="97" t="s">
+      <c r="B12" s="96" t="s">
         <v>871</v>
       </c>
-      <c r="E12" s="98">
+      <c r="C12" s="96" t="s">
+        <v>873</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>870</v>
+      </c>
+      <c r="E12" s="97">
         <v>46160</v>
       </c>
-      <c r="F12" s="100" t="s">
+      <c r="F12" s="99" t="s">
         <v>474</v>
       </c>
-      <c r="G12" s="97">
+      <c r="G12" s="96">
         <v>100</v>
       </c>
     </row>
@@ -18571,14 +18569,14 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="45"/>
-      <c r="B21" s="91" t="s">
-        <v>824</v>
+      <c r="B21" s="90" t="s">
+        <v>823</v>
       </c>
       <c r="C21" s="45" t="s">
         <v>783</v>
       </c>
       <c r="D21" s="77" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E21" s="77" t="s">
         <v>749</v>
@@ -18604,7 +18602,7 @@
         <v>785</v>
       </c>
       <c r="D22" s="77" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>
@@ -18777,11 +18775,11 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="45"/>
-      <c r="B29" s="91" t="s">
+      <c r="B29" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="91" t="s">
-        <v>863</v>
+      <c r="C29" s="90" t="s">
+        <v>862</v>
       </c>
       <c r="D29" s="45"/>
       <c r="E29" s="45"/>
@@ -18837,68 +18835,68 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="B2" s="92" t="s">
-        <v>850</v>
+      <c r="B2" s="91" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="44" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
   </sheetData>
@@ -18963,7 +18961,7 @@
     <row r="3" spans="1:17">
       <c r="A3" s="45"/>
       <c r="B3" s="72" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C3" s="57"/>
       <c r="D3" s="45"/>
@@ -19222,11 +19220,11 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="45"/>
-      <c r="B15" s="94" t="s">
-        <v>864</v>
-      </c>
-      <c r="C15" s="95" t="s">
-        <v>867</v>
+      <c r="B15" s="93" t="s">
+        <v>863</v>
+      </c>
+      <c r="C15" s="94" t="s">
+        <v>866</v>
       </c>
       <c r="D15" s="45"/>
       <c r="E15" s="58"/>
@@ -19308,15 +19306,15 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="45"/>
-      <c r="B19" s="91" t="s">
-        <v>849</v>
+      <c r="B19" s="90" t="s">
+        <v>848</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D19" s="45"/>
       <c r="E19" s="58" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F19" s="56"/>
       <c r="G19" s="56"/>
@@ -19353,7 +19351,7 @@
     <row r="21" spans="1:17">
       <c r="A21" s="45"/>
       <c r="B21" s="77" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C21" s="57"/>
       <c r="D21" s="45"/>
@@ -19374,10 +19372,10 @@
     <row r="22" spans="1:17">
       <c r="A22" s="45"/>
       <c r="B22" s="77" t="s">
+        <v>821</v>
+      </c>
+      <c r="C22" s="77" t="s">
         <v>822</v>
-      </c>
-      <c r="C22" s="77" t="s">
-        <v>823</v>
       </c>
       <c r="D22" s="45"/>
       <c r="E22" s="58"/>
@@ -20451,8 +20449,8 @@
         <f>+F20+G20</f>
         <v>20863.370999999999</v>
       </c>
-      <c r="I20" s="104" t="s">
-        <v>828</v>
+      <c r="I20" s="103" t="s">
+        <v>827</v>
       </c>
       <c r="J20" s="60">
         <v>46261</v>
@@ -39239,11 +39237,11 @@
         <f t="shared" ref="H5:H6" si="0">+F5+G5</f>
         <v>110066.240368</v>
       </c>
-      <c r="I5" s="90" t="s">
-        <v>819</v>
-      </c>
-      <c r="J5" s="60">
-        <v>46218</v>
+      <c r="I5" s="105" t="s">
+        <v>874</v>
+      </c>
+      <c r="J5" s="104">
+        <v>46339</v>
       </c>
       <c r="K5" s="58"/>
       <c r="L5" s="61"/>
@@ -39305,8 +39303,8 @@
         <f t="shared" si="0"/>
         <v>33339.434250699996</v>
       </c>
-      <c r="I6" s="96" t="s">
-        <v>820</v>
+      <c r="I6" s="95" t="s">
+        <v>819</v>
       </c>
       <c r="J6" s="60"/>
       <c r="K6" s="58"/>
@@ -39369,7 +39367,7 @@
         <f>+F7+G7</f>
         <v>9008.5459472848015</v>
       </c>
-      <c r="I7" s="93" t="s">
+      <c r="I7" s="92" t="s">
         <v>422</v>
       </c>
       <c r="J7" s="60">
@@ -42387,7 +42385,7 @@
         <v>458</v>
       </c>
       <c r="K3" s="67" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="L3" s="70"/>
       <c r="M3" s="67"/>
@@ -42403,13 +42401,13 @@
       <c r="A4" s="55">
         <v>1</v>
       </c>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="91" t="s">
+      <c r="C4" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="91" t="s">
+      <c r="D4" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="45"/>
@@ -42418,8 +42416,8 @@
       <c r="H4" s="45"/>
       <c r="I4" s="45"/>
       <c r="J4" s="45"/>
-      <c r="K4" s="91" t="s">
-        <v>842</v>
+      <c r="K4" s="90" t="s">
+        <v>841</v>
       </c>
       <c r="L4" s="45"/>
       <c r="M4" s="45"/>
@@ -42435,13 +42433,13 @@
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="91" t="s">
-        <v>831</v>
-      </c>
-      <c r="D5" s="91" t="s">
+      <c r="C5" s="90" t="s">
+        <v>830</v>
+      </c>
+      <c r="D5" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="45"/>
@@ -42450,8 +42448,8 @@
       <c r="H5" s="45"/>
       <c r="I5" s="45"/>
       <c r="J5" s="45"/>
-      <c r="K5" s="91" t="s">
-        <v>842</v>
+      <c r="K5" s="90" t="s">
+        <v>841</v>
       </c>
       <c r="L5" s="45"/>
       <c r="M5" s="45"/>
@@ -42467,13 +42465,13 @@
         <f t="shared" ref="A6:A51" si="0">+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" s="91" t="s">
-        <v>830</v>
-      </c>
-      <c r="C6" s="91" t="s">
+      <c r="B6" s="90" t="s">
+        <v>829</v>
+      </c>
+      <c r="C6" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="91" t="s">
+      <c r="D6" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="45"/>
@@ -42482,8 +42480,8 @@
       <c r="H6" s="45"/>
       <c r="I6" s="45"/>
       <c r="J6" s="45"/>
-      <c r="K6" s="91" t="s">
-        <v>843</v>
+      <c r="K6" s="90" t="s">
+        <v>842</v>
       </c>
       <c r="L6" s="45"/>
       <c r="M6" s="45"/>
@@ -42499,13 +42497,13 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="91" t="s">
+      <c r="D7" s="90" t="s">
         <v>85</v>
       </c>
       <c r="E7" s="45"/>
@@ -42514,8 +42512,8 @@
       <c r="H7" s="45"/>
       <c r="I7" s="45"/>
       <c r="J7" s="45"/>
-      <c r="K7" s="91" t="s">
-        <v>845</v>
+      <c r="K7" s="90" t="s">
+        <v>844</v>
       </c>
       <c r="L7" s="45"/>
       <c r="M7" s="45"/>
@@ -42531,13 +42529,13 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="91" t="s">
+      <c r="C8" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="91" t="s">
+      <c r="D8" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="45"/>
@@ -42546,8 +42544,8 @@
       <c r="H8" s="45"/>
       <c r="I8" s="45"/>
       <c r="J8" s="45"/>
-      <c r="K8" s="91" t="s">
-        <v>842</v>
+      <c r="K8" s="90" t="s">
+        <v>841</v>
       </c>
       <c r="L8" s="45"/>
       <c r="M8" s="45"/>
@@ -42563,13 +42561,13 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="91" t="s">
+      <c r="C9" s="90" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="91" t="s">
+      <c r="D9" s="90" t="s">
         <v>185</v>
       </c>
       <c r="E9" s="45"/>
@@ -42578,8 +42576,8 @@
       <c r="H9" s="45"/>
       <c r="I9" s="45"/>
       <c r="J9" s="45"/>
-      <c r="K9" s="91" t="s">
-        <v>845</v>
+      <c r="K9" s="90" t="s">
+        <v>844</v>
       </c>
       <c r="L9" s="45"/>
       <c r="M9" s="45"/>
@@ -42595,13 +42593,13 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="90" t="s">
         <v>446</v>
       </c>
-      <c r="D10" s="91" t="s">
+      <c r="D10" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="45"/>
@@ -42610,8 +42608,8 @@
       <c r="H10" s="45"/>
       <c r="I10" s="45"/>
       <c r="J10" s="45"/>
-      <c r="K10" s="91" t="s">
-        <v>842</v>
+      <c r="K10" s="90" t="s">
+        <v>841</v>
       </c>
       <c r="L10" s="45"/>
       <c r="M10" s="45"/>
@@ -42627,13 +42625,13 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="91" t="s">
+      <c r="C11" s="90" t="s">
         <v>448</v>
       </c>
-      <c r="D11" s="91" t="s">
+      <c r="D11" s="90" t="s">
         <v>165</v>
       </c>
       <c r="E11" s="45"/>
@@ -42642,8 +42640,8 @@
       <c r="H11" s="45"/>
       <c r="I11" s="45"/>
       <c r="J11" s="45"/>
-      <c r="K11" s="91" t="s">
-        <v>846</v>
+      <c r="K11" s="90" t="s">
+        <v>845</v>
       </c>
       <c r="L11" s="45"/>
       <c r="M11" s="45"/>
@@ -42659,13 +42657,13 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="90" t="s">
         <v>339</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="90" t="s">
         <v>340</v>
       </c>
-      <c r="D12" s="91" t="s">
+      <c r="D12" s="90" t="s">
         <v>254</v>
       </c>
       <c r="E12" s="45"/>
@@ -42689,13 +42687,13 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="90" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="91" t="s">
+      <c r="D13" s="90" t="s">
         <v>165</v>
       </c>
       <c r="E13" s="45"/>
@@ -42704,8 +42702,8 @@
       <c r="H13" s="45"/>
       <c r="I13" s="45"/>
       <c r="J13" s="45"/>
-      <c r="K13" s="91" t="s">
-        <v>846</v>
+      <c r="K13" s="90" t="s">
+        <v>845</v>
       </c>
       <c r="L13" s="45"/>
       <c r="M13" s="45"/>
@@ -42721,13 +42719,13 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="90" t="s">
         <v>387</v>
       </c>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="90" t="s">
         <v>386</v>
       </c>
-      <c r="D14" s="91" t="s">
+      <c r="D14" s="90" t="s">
         <v>165</v>
       </c>
       <c r="E14" s="45"/>
@@ -42736,8 +42734,8 @@
       <c r="H14" s="45"/>
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
-      <c r="K14" s="91" t="s">
-        <v>846</v>
+      <c r="K14" s="90" t="s">
+        <v>845</v>
       </c>
       <c r="L14" s="45"/>
       <c r="M14" s="45"/>
@@ -42753,13 +42751,13 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="90" t="s">
+        <v>831</v>
+      </c>
+      <c r="C15" s="90" t="s">
         <v>832</v>
       </c>
-      <c r="C15" s="91" t="s">
-        <v>833</v>
-      </c>
-      <c r="D15" s="91" t="s">
+      <c r="D15" s="90" t="s">
         <v>143</v>
       </c>
       <c r="E15" s="45"/>
@@ -42783,13 +42781,13 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="91" t="s">
-        <v>834</v>
-      </c>
-      <c r="C16" s="91" t="s">
+      <c r="B16" s="90" t="s">
+        <v>833</v>
+      </c>
+      <c r="C16" s="90" t="s">
         <v>455</v>
       </c>
-      <c r="D16" s="91" t="s">
+      <c r="D16" s="90" t="s">
         <v>219</v>
       </c>
       <c r="E16" s="45"/>
@@ -42798,8 +42796,8 @@
       <c r="H16" s="45"/>
       <c r="I16" s="45"/>
       <c r="J16" s="45"/>
-      <c r="K16" s="91" t="s">
-        <v>846</v>
+      <c r="K16" s="90" t="s">
+        <v>845</v>
       </c>
       <c r="L16" s="45"/>
       <c r="M16" s="45"/>
@@ -42815,13 +42813,13 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="91" t="s">
-        <v>835</v>
-      </c>
-      <c r="C17" s="91" t="s">
+      <c r="B17" s="90" t="s">
+        <v>834</v>
+      </c>
+      <c r="C17" s="90" t="s">
         <v>349</v>
       </c>
-      <c r="D17" s="91" t="s">
+      <c r="D17" s="90" t="s">
         <v>347</v>
       </c>
       <c r="E17" s="45"/>
@@ -42845,13 +42843,13 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" s="91" t="s">
-        <v>836</v>
-      </c>
-      <c r="C18" s="91" t="s">
+      <c r="B18" s="90" t="s">
+        <v>835</v>
+      </c>
+      <c r="C18" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="91" t="s">
+      <c r="D18" s="90" t="s">
         <v>165</v>
       </c>
       <c r="E18" s="45"/>
@@ -42875,13 +42873,13 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="91" t="s">
+      <c r="B19" s="90" t="s">
         <v>342</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="90" t="s">
         <v>341</v>
       </c>
-      <c r="D19" s="91" t="s">
+      <c r="D19" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="45"/>
@@ -42890,8 +42888,8 @@
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
       <c r="J19" s="45"/>
-      <c r="K19" s="91" t="s">
-        <v>847</v>
+      <c r="K19" s="90" t="s">
+        <v>846</v>
       </c>
       <c r="L19" s="45"/>
       <c r="M19" s="45"/>
@@ -42907,13 +42905,13 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" s="91" t="s">
+      <c r="B20" s="90" t="s">
+        <v>836</v>
+      </c>
+      <c r="C20" s="90" t="s">
         <v>837</v>
       </c>
-      <c r="C20" s="91" t="s">
-        <v>838</v>
-      </c>
-      <c r="D20" s="91" t="s">
+      <c r="D20" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="45"/>
@@ -42937,14 +42935,14 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="90" t="s">
         <v>350</v>
       </c>
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="90" t="s">
         <v>351</v>
       </c>
-      <c r="D21" s="91" t="s">
-        <v>839</v>
+      <c r="D21" s="90" t="s">
+        <v>838</v>
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
@@ -42967,13 +42965,13 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B22" s="91" t="s">
+      <c r="B22" s="90" t="s">
         <v>532</v>
       </c>
-      <c r="C22" s="91" t="s">
-        <v>840</v>
-      </c>
-      <c r="D22" s="91" t="s">
+      <c r="C22" s="90" t="s">
+        <v>839</v>
+      </c>
+      <c r="D22" s="90" t="s">
         <v>219</v>
       </c>
       <c r="E22" s="45"/>
@@ -42997,7 +42995,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="90" t="s">
         <v>421</v>
       </c>
       <c r="C23" s="57" t="s">
@@ -43027,13 +43025,13 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B24" s="91" t="s">
-        <v>841</v>
-      </c>
-      <c r="C24" s="91" t="s">
+      <c r="B24" s="90" t="s">
+        <v>840</v>
+      </c>
+      <c r="C24" s="90" t="s">
         <v>357</v>
       </c>
-      <c r="D24" s="91" t="s">
+      <c r="D24" s="90" t="s">
         <v>165</v>
       </c>
       <c r="E24" s="45"/>
@@ -43057,13 +43055,13 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B25" s="91" t="s">
+      <c r="B25" s="90" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="91" t="s">
+      <c r="C25" s="90" t="s">
         <v>378</v>
       </c>
-      <c r="D25" s="91" t="s">
+      <c r="D25" s="90" t="s">
         <v>254</v>
       </c>
       <c r="E25" s="45"/>
@@ -43087,13 +43085,13 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B26" s="91" t="s">
-        <v>848</v>
-      </c>
-      <c r="C26" s="91" t="s">
+      <c r="B26" s="90" t="s">
+        <v>847</v>
+      </c>
+      <c r="C26" s="90" t="s">
         <v>699</v>
       </c>
-      <c r="D26" s="91" t="s">
+      <c r="D26" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="45"/>
@@ -50717,7 +50715,7 @@
     </row>
     <row r="19" spans="2:34">
       <c r="B19" s="77" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C19" s="77"/>
       <c r="D19" s="77"/>
@@ -50860,7 +50858,7 @@
         <v>463</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D8" s="45"/>
       <c r="E8" s="45"/>
@@ -50876,7 +50874,7 @@
         <v>464</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D9" s="45"/>
       <c r="E9" s="45"/>
@@ -50937,10 +50935,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="76" t="s">
+        <v>815</v>
+      </c>
+      <c r="C13" s="76" t="s">
         <v>816</v>
-      </c>
-      <c r="C13" s="76" t="s">
-        <v>817</v>
       </c>
       <c r="D13" s="45"/>
       <c r="E13" s="45"/>
@@ -50952,96 +50950,96 @@
       <c r="K13" s="45"/>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="102" t="s">
+        <v>876</v>
+      </c>
+      <c r="C14" s="102" t="s">
         <v>877</v>
       </c>
-      <c r="C14" s="103" t="s">
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="102" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="103" t="s">
+      <c r="C15" s="102" t="s">
         <v>879</v>
       </c>
-      <c r="C15" s="103" t="s">
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="102" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="103" t="s">
+      <c r="C16" s="102" t="s">
         <v>881</v>
       </c>
-      <c r="C16" s="103" t="s">
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="102" t="s">
         <v>882</v>
       </c>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="103" t="s">
+      <c r="C17" s="102" t="s">
         <v>883</v>
       </c>
-      <c r="C17" s="103" t="s">
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="102" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="102" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="103" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="103" t="s">
+    <row r="19" spans="2:3">
+      <c r="B19" s="102" t="s">
         <v>885</v>
       </c>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="103" t="s">
+      <c r="C19" s="102" t="s">
         <v>886</v>
       </c>
-      <c r="C19" s="103" t="s">
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="102" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="103" t="s">
+      <c r="C20" s="102" t="s">
         <v>888</v>
       </c>
-      <c r="C20" s="103" t="s">
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="102" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="103" t="s">
+      <c r="C21" s="102" t="s">
         <v>890</v>
       </c>
-      <c r="C21" s="103" t="s">
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="102" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="103" t="s">
+      <c r="C22" s="102" t="s">
         <v>892</v>
       </c>
-      <c r="C22" s="103" t="s">
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="102" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="103" t="s">
+      <c r="C23" s="102" t="s">
         <v>894</v>
       </c>
-      <c r="C23" s="103" t="s">
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="102" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="103" t="s">
+      <c r="C24" s="102" t="s">
         <v>896</v>
-      </c>
-      <c r="C24" s="103" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" s="44" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
   </sheetData>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6FD525-6E01-454D-8079-EF4D02C3F74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E28E644-925C-4FDA-98FA-61A75365D42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3471,12 +3471,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>256.14999999999998</v>
+            <v>245.3</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>31405.222593799997</v>
+            <v>30074.960383599999</v>
           </cell>
         </row>
         <row r="5">
@@ -3723,12 +3723,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>53.46</v>
+            <v>47.32</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>14462.152790580001</v>
+            <v>12801.14235036</v>
           </cell>
         </row>
         <row r="5">
@@ -3742,8 +3742,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4664,12 +4664,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>102.6</v>
+            <v>136.34</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>5098.1578847999999</v>
+            <v>6774.6866083200002</v>
           </cell>
         </row>
         <row r="5">
@@ -6635,8 +6635,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1825730.7430737263</v>
+        <v>1824296.3482408095</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1840224.023397526</v>
+        <v>1838789.6285646092</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23131.627322343978</v>
+        <v>23113.470425724779</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23899.013290876963</v>
+        <v>23880.384786553368</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -8443,11 +8443,11 @@
       </c>
       <c r="E17" s="24">
         <f>+[12]Main!$H$2</f>
-        <v>256.14999999999998</v>
+        <v>245.3</v>
       </c>
       <c r="F17" s="17">
         <f>+[12]Main!$H$4*FX!C3</f>
-        <v>32661.431497551999</v>
+        <v>31277.958798944001</v>
       </c>
       <c r="G17" s="17">
         <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="H17" s="17">
         <f t="shared" si="1"/>
-        <v>41240.391497552002</v>
+        <v>39856.918798944003</v>
       </c>
       <c r="I17" s="25" t="s">
         <v>827</v>
@@ -8892,11 +8892,11 @@
       </c>
       <c r="E23" s="24">
         <f>+[18]Main!$H$2</f>
-        <v>53.46</v>
+        <v>47.32</v>
       </c>
       <c r="F23" s="17">
         <f>+[18]Main!$H$4*FX!C3</f>
-        <v>15040.638902203202</v>
+        <v>13313.188044374401</v>
       </c>
       <c r="G23" s="17">
         <f>+([18]Main!$H$6-[18]Main!$H$5)*FX!C3</f>
@@ -8904,13 +8904,13 @@
       </c>
       <c r="H23" s="17">
         <f t="shared" si="1"/>
-        <v>14664.319062203202</v>
+        <v>12936.868204374401</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="J23" s="26">
-        <v>46225</v>
+        <v>46316</v>
       </c>
       <c r="K23" s="24"/>
       <c r="L23" s="21"/>
@@ -10256,11 +10256,11 @@
       </c>
       <c r="E44" s="24">
         <f>+[39]Main!$H$2</f>
-        <v>102.6</v>
+        <v>136.34</v>
       </c>
       <c r="F44" s="17">
         <f>+[39]Main!$H$4</f>
-        <v>5098.1578847999999</v>
+        <v>6774.6866083200002</v>
       </c>
       <c r="G44" s="17">
         <f>+[39]Main!$H$6-[39]Main!$H$5</f>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H44" s="17">
         <f>F44+G44</f>
-        <v>6303.0978847999995</v>
+        <v>7979.6266083199998</v>
       </c>
       <c r="I44" s="16" t="s">
         <v>827</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="always" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E28E644-925C-4FDA-98FA-61A75365D42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AA606D-7C09-46AD-91F8-762773BC5149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3337,22 +3337,22 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="I4">
-            <v>499.3</v>
+            <v>459.1</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>248495.08914200001</v>
+            <v>227626.86682800003</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>8794</v>
+            <v>6803</v>
           </cell>
         </row>
         <row r="8">
           <cell r="I8">
-            <v>20343</v>
+            <v>20485</v>
           </cell>
         </row>
       </sheetData>
@@ -3382,12 +3382,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>114.34</v>
+            <v>110.86</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>12398.796003380001</v>
+            <v>12021.43191302</v>
           </cell>
         </row>
         <row r="5">
@@ -3471,33 +3471,33 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>245.3</v>
+            <v>250.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>30074.960383599999</v>
+            <v>30716.233848</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>4313</v>
+            <v>8480</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>12562</v>
+            <v>11804</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3742,8 +3742,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4420,12 +4420,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>86.1</v>
+            <v>81.2</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5854.2555035999994</v>
+            <v>5521.0864911999997</v>
           </cell>
         </row>
         <row r="5">
@@ -7298,15 +7298,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1824296.3482408095</v>
+        <v>1802536.4615739693</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>14493.280323800005</v>
+        <v>11589.600323800001</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1838789.6285646092</v>
+        <v>1814126.0618977693</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7368,15 +7368,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>23113.470425724779</v>
+        <v>22838.028822347056</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>188.22441978961047</v>
+        <v>150.51428991948055</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23880.384786553368</v>
+        <v>23560.078725945055</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -7475,25 +7475,25 @@
       </c>
       <c r="E6" s="24">
         <f>+[1]Main!$I$4</f>
-        <v>499.3</v>
+        <v>459.1</v>
       </c>
       <c r="F6" s="17">
         <f>+[1]Main!$I$6*FX!C3</f>
-        <v>258434.89270768003</v>
+        <v>236731.94150112005</v>
       </c>
       <c r="G6" s="17">
         <f>(+[1]Main!$I$8-[1]Main!$I$7)*FX!C3</f>
-        <v>12010.960000000001</v>
+        <v>14229.28</v>
       </c>
       <c r="H6" s="17">
         <f>F6+G6</f>
-        <v>270445.85270768002</v>
+        <v>250961.22150112005</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="J6" s="26">
-        <v>46231</v>
+        <v>46308</v>
       </c>
       <c r="K6" s="17">
         <f>80807*FX!C3</f>
@@ -8290,11 +8290,11 @@
       </c>
       <c r="E15" s="24">
         <f>+[10]Main!$I$2</f>
-        <v>114.34</v>
+        <v>110.86</v>
       </c>
       <c r="F15" s="17">
         <f>+[10]Main!$I$4</f>
-        <v>12398.796003380001</v>
+        <v>12021.43191302</v>
       </c>
       <c r="G15" s="17">
         <f>+[10]Main!$I$6-[10]Main!$I$5</f>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="H15" s="17">
         <f>F15+G15</f>
-        <v>10884.067003380002</v>
+        <v>10506.702913020001</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>422</v>
@@ -8443,25 +8443,25 @@
       </c>
       <c r="E17" s="24">
         <f>+[12]Main!$H$2</f>
-        <v>245.3</v>
+        <v>250.5</v>
       </c>
       <c r="F17" s="17">
         <f>+[12]Main!$H$4*FX!C3</f>
-        <v>31277.958798944001</v>
+        <v>31944.883201920002</v>
       </c>
       <c r="G17" s="17">
         <f>+([12]Main!$H$6-[12]Main!$H$5)*FX!C3</f>
-        <v>8578.9600000000009</v>
+        <v>3456.96</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" si="1"/>
-        <v>39856.918798944003</v>
+        <v>35401.843201920005</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="J17" s="26">
-        <v>46231</v>
+        <v>46316</v>
       </c>
       <c r="K17" s="17">
         <f>17194*FX!C3</f>
@@ -9878,11 +9878,11 @@
       </c>
       <c r="E38" s="24">
         <f>+[33]Main!$J$2</f>
-        <v>86.1</v>
+        <v>81.2</v>
       </c>
       <c r="F38" s="17">
         <f>+[33]Main!$J$4*FX!C3</f>
-        <v>6088.4257237439997</v>
+        <v>5741.9299508479999</v>
       </c>
       <c r="G38" s="17">
         <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H38" s="17">
         <f>F38+G38</f>
-        <v>6288.9190037439994</v>
+        <v>5942.4232308479995</v>
       </c>
       <c r="I38" s="16" t="s">
         <v>422</v>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AA606D-7C09-46AD-91F8-762773BC5149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C527C6-422B-4B20-B9BB-26267AC2071A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="4890" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3265,38 +3265,38 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3490,14 +3490,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3558,17 +3558,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="M2">
-            <v>107</v>
+            <v>103.91</v>
           </cell>
         </row>
         <row r="4">
           <cell r="M4">
-            <v>14860.262398999999</v>
+            <v>14366.90833</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>1907.249</v>
+            <v>1602.5889999999999</v>
           </cell>
         </row>
         <row r="6">
@@ -3807,22 +3807,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>1751</v>
+            <v>1553</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>184852.040412</v>
+            <v>162743.90016699999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>12239</v>
+            <v>12310</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>34</v>
+            <v>5</v>
           </cell>
         </row>
       </sheetData>
@@ -4664,30 +4664,30 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>136.34</v>
+            <v>121.86</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>6774.6866083200002</v>
+            <v>5842.5868395000007</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>130.881</v>
+            <v>170.27600000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1335.8209999999999</v>
+            <v>1307.6579999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6574,22 +6574,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>173.25</v>
+            <v>165.3</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>79525.020267</v>
+            <v>75875.820202800009</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>3544</v>
+            <v>1931</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>10839</v>
+            <v>11409</v>
           </cell>
         </row>
       </sheetData>
@@ -7298,15 +7298,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1802536.4615739693</v>
+        <v>1778118.5418813494</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>11589.600323800001</v>
+        <v>11722.7023238</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1814126.0618977693</v>
+        <v>1789841.2442051494</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7368,15 +7368,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22838.028822347056</v>
+        <v>22528.941231301233</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>150.51428991948055</v>
+        <v>152.24288732207793</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23560.078725945055</v>
+        <v>23244.691483183757</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -7578,25 +7578,25 @@
       </c>
       <c r="E7" s="29">
         <f>+[2]Main!$K$2</f>
-        <v>1751</v>
+        <v>1553</v>
       </c>
       <c r="F7" s="17">
         <f>+[2]Main!$K$4*FX!C3</f>
-        <v>192246.12202848002</v>
+        <v>169253.65617367998</v>
       </c>
       <c r="G7" s="17">
         <f>+([2]Main!$K$6-[2]Main!$K$5)*FX!C3</f>
-        <v>-12693.2</v>
+        <v>-12797.2</v>
       </c>
       <c r="H7" s="17">
         <f>F7+G7</f>
-        <v>179552.92202848001</v>
+        <v>156456.45617367997</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>338</v>
+        <v>806</v>
       </c>
       <c r="J7" s="26">
-        <v>46232</v>
+        <v>46318</v>
       </c>
       <c r="K7" s="17">
         <f>16002*FX!C3</f>
@@ -8305,10 +8305,10 @@
         <v>10506.702913020001</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>422</v>
+        <v>827</v>
       </c>
       <c r="J15" s="26">
-        <v>46177</v>
+        <v>46268</v>
       </c>
       <c r="K15" s="17">
         <v>9619.2999999999993</v>
@@ -8383,7 +8383,7 @@
         <v>827</v>
       </c>
       <c r="J16" s="26">
-        <v>46268</v>
+        <v>46233</v>
       </c>
       <c r="K16" s="17">
         <f>21427*FX!C3</f>
@@ -8622,19 +8622,19 @@
       </c>
       <c r="E19" s="24">
         <f>+[14]Main!$M$2</f>
-        <v>107</v>
+        <v>103.91</v>
       </c>
       <c r="F19" s="17">
         <f>+[14]Main!$M$4</f>
-        <v>14860.262398999999</v>
+        <v>14366.90833</v>
       </c>
       <c r="G19" s="17">
         <f>+[14]Main!$M$6-[14]Main!$M$5</f>
-        <v>-1907.249</v>
+        <v>-1602.5889999999999</v>
       </c>
       <c r="H19" s="17">
         <f>F19+G19</f>
-        <v>12953.013398999999</v>
+        <v>12764.31933</v>
       </c>
       <c r="I19" s="25" t="s">
         <v>828</v>
@@ -8723,7 +8723,9 @@
       <c r="I20" s="25" t="s">
         <v>806</v>
       </c>
-      <c r="J20" s="26"/>
+      <c r="J20" s="26">
+        <v>46289</v>
+      </c>
       <c r="K20" s="17">
         <f>234478*FX!C4</f>
         <v>22275.41</v>
@@ -10256,25 +10258,25 @@
       </c>
       <c r="E44" s="24">
         <f>+[39]Main!$H$2</f>
-        <v>136.34</v>
+        <v>121.86</v>
       </c>
       <c r="F44" s="17">
         <f>+[39]Main!$H$4</f>
-        <v>6774.6866083200002</v>
+        <v>5842.5868395000007</v>
       </c>
       <c r="G44" s="17">
         <f>+[39]Main!$H$6-[39]Main!$H$5</f>
-        <v>1204.9399999999998</v>
+        <v>1137.3819999999998</v>
       </c>
       <c r="H44" s="17">
         <f>F44+G44</f>
-        <v>7979.6266083199998</v>
+        <v>6979.9688395000003</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="J44" s="26">
-        <v>46240</v>
+        <v>46324</v>
       </c>
       <c r="K44" s="17"/>
       <c r="L44" s="21"/>
@@ -17804,12 +17806,12 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="96" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.85546875" style="96" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="96" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="96" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.28515625" style="96" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="96"/>
+    <col min="1" max="1" width="5.42578125" style="95" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.85546875" style="95" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="95" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="95" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.28515625" style="95" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="95"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -17841,196 +17843,196 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="95" t="s">
         <v>719</v>
       </c>
       <c r="C3" s="44" t="s">
         <v>720</v>
       </c>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="95" t="s">
         <v>728</v>
       </c>
-      <c r="E3" s="97">
+      <c r="E3" s="96">
         <v>45757</v>
       </c>
-      <c r="F3" s="98" t="s">
+      <c r="F3" s="97" t="s">
         <v>474</v>
       </c>
-      <c r="G3" s="98">
+      <c r="G3" s="97">
         <v>1250</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="95" t="s">
         <v>692</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>692</v>
       </c>
-      <c r="D4" s="96" t="s">
+      <c r="D4" s="95" t="s">
         <v>726</v>
       </c>
-      <c r="E4" s="97">
+      <c r="E4" s="96">
         <v>45782</v>
       </c>
-      <c r="F4" s="99" t="s">
+      <c r="F4" s="98" t="s">
         <v>727</v>
       </c>
-      <c r="G4" s="100">
+      <c r="G4" s="99">
         <v>9420</v>
       </c>
-      <c r="H4" s="96" t="s">
+      <c r="H4" s="95" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="95" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="96" t="s">
+      <c r="C5" s="95" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="96" t="s">
+      <c r="D5" s="95" t="s">
         <v>729</v>
       </c>
-      <c r="E5" s="97">
+      <c r="E5" s="96">
         <v>45637</v>
       </c>
-      <c r="F5" s="98" t="s">
+      <c r="F5" s="97" t="s">
         <v>474</v>
       </c>
-      <c r="G5" s="100">
+      <c r="G5" s="99">
         <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="95" t="s">
         <v>730</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="95" t="s">
         <v>730</v>
       </c>
-      <c r="D6" s="96" t="s">
+      <c r="D6" s="95" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="95" t="s">
         <v>191</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="96" t="s">
+      <c r="D7" s="95" t="s">
         <v>680</v>
       </c>
-      <c r="E7" s="97">
+      <c r="E7" s="96">
         <v>45889</v>
       </c>
-      <c r="F7" s="96">
+      <c r="F7" s="95">
         <v>16.75</v>
       </c>
-      <c r="G7" s="96" t="s">
+      <c r="G7" s="95" t="s">
         <v>798</v>
       </c>
-      <c r="H7" s="96" t="s">
+      <c r="H7" s="95" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="95" t="s">
         <v>420</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="100" t="s">
         <v>476</v>
       </c>
-      <c r="D8" s="96" t="s">
+      <c r="D8" s="95" t="s">
         <v>803</v>
       </c>
-      <c r="E8" s="97">
+      <c r="E8" s="96">
         <v>45322</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="95">
         <v>500</v>
       </c>
-      <c r="H8" s="96" t="s">
+      <c r="H8" s="95" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="95" t="s">
         <v>807</v>
       </c>
-      <c r="C9" s="96" t="s">
+      <c r="C9" s="95" t="s">
         <v>808</v>
       </c>
-      <c r="D9" s="96" t="s">
+      <c r="D9" s="95" t="s">
         <v>689</v>
       </c>
-      <c r="E9" s="97">
+      <c r="E9" s="96">
         <v>45808</v>
       </c>
-      <c r="G9" s="96">
+      <c r="G9" s="95">
         <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="95" t="s">
         <v>865</v>
       </c>
-      <c r="C10" s="96" t="s">
+      <c r="C10" s="95" t="s">
         <v>865</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="D10" s="95" t="s">
         <v>864</v>
       </c>
-      <c r="E10" s="97">
+      <c r="E10" s="96">
         <v>46112</v>
       </c>
-      <c r="F10" s="99" t="s">
+      <c r="F10" s="98" t="s">
         <v>474</v>
       </c>
-      <c r="G10" s="96">
+      <c r="G10" s="95">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="95" t="s">
         <v>867</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="95" t="s">
         <v>868</v>
       </c>
-      <c r="E11" s="97">
+      <c r="E11" s="96">
         <v>46156</v>
       </c>
-      <c r="F11" s="99" t="s">
+      <c r="F11" s="98" t="s">
         <v>474</v>
       </c>
-      <c r="G11" s="96">
+      <c r="G11" s="95">
         <v>850</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="95" t="s">
         <v>871</v>
       </c>
-      <c r="C12" s="96" t="s">
+      <c r="C12" s="95" t="s">
         <v>873</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="95" t="s">
         <v>870</v>
       </c>
-      <c r="E12" s="97">
+      <c r="E12" s="96">
         <v>46160</v>
       </c>
-      <c r="F12" s="99" t="s">
+      <c r="F12" s="98" t="s">
         <v>474</v>
       </c>
-      <c r="G12" s="96">
+      <c r="G12" s="95">
         <v>100</v>
       </c>
     </row>
@@ -18569,7 +18571,7 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="45"/>
-      <c r="B21" s="90" t="s">
+      <c r="B21" s="89" t="s">
         <v>823</v>
       </c>
       <c r="C21" s="45" t="s">
@@ -18775,10 +18777,10 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="45"/>
-      <c r="B29" s="90" t="s">
+      <c r="B29" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="90" t="s">
+      <c r="C29" s="89" t="s">
         <v>862</v>
       </c>
       <c r="D29" s="45"/>
@@ -18835,7 +18837,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="90" t="s">
         <v>849</v>
       </c>
     </row>
@@ -19220,10 +19222,10 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="45"/>
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="92" t="s">
         <v>863</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="93" t="s">
         <v>866</v>
       </c>
       <c r="D15" s="45"/>
@@ -19306,7 +19308,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="45"/>
-      <c r="B19" s="90" t="s">
+      <c r="B19" s="89" t="s">
         <v>848</v>
       </c>
       <c r="C19" s="57" t="s">
@@ -20449,7 +20451,7 @@
         <f>+F20+G20</f>
         <v>20863.370999999999</v>
       </c>
-      <c r="I20" s="103" t="s">
+      <c r="I20" s="102" t="s">
         <v>827</v>
       </c>
       <c r="J20" s="60">
@@ -39157,25 +39159,25 @@
       </c>
       <c r="E4" s="58">
         <f>+[81]Main!$I$2</f>
-        <v>173.25</v>
+        <v>165.3</v>
       </c>
       <c r="F4" s="56">
         <f>+[81]Main!$I$4*FX!C3</f>
-        <v>82706.021077680009</v>
+        <v>78910.853010912018</v>
       </c>
       <c r="G4" s="56">
         <f>+([81]Main!$I$6-[81]Main!$I$5)*FX!C3</f>
-        <v>7586.8</v>
+        <v>9857.1200000000008</v>
       </c>
       <c r="H4" s="56">
         <f>+F4+G4</f>
-        <v>90292.821077680012</v>
-      </c>
-      <c r="I4" s="89" t="s">
-        <v>422</v>
+        <v>88767.973010912014</v>
+      </c>
+      <c r="I4" s="105" t="s">
+        <v>806</v>
       </c>
       <c r="J4" s="60">
-        <v>46231</v>
+        <v>46315</v>
       </c>
       <c r="K4" s="58"/>
       <c r="L4" s="61"/>
@@ -39237,10 +39239,10 @@
         <f t="shared" ref="H5:H6" si="0">+F5+G5</f>
         <v>110066.240368</v>
       </c>
-      <c r="I5" s="105" t="s">
+      <c r="I5" s="104" t="s">
         <v>874</v>
       </c>
-      <c r="J5" s="104">
+      <c r="J5" s="103">
         <v>46339</v>
       </c>
       <c r="K5" s="58"/>
@@ -39303,7 +39305,7 @@
         <f t="shared" si="0"/>
         <v>33339.434250699996</v>
       </c>
-      <c r="I6" s="95" t="s">
+      <c r="I6" s="94" t="s">
         <v>819</v>
       </c>
       <c r="J6" s="60"/>
@@ -39367,7 +39369,7 @@
         <f>+F7+G7</f>
         <v>9008.5459472848015</v>
       </c>
-      <c r="I7" s="92" t="s">
+      <c r="I7" s="91" t="s">
         <v>422</v>
       </c>
       <c r="J7" s="60">
@@ -42401,13 +42403,13 @@
       <c r="A4" s="55">
         <v>1</v>
       </c>
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="89" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="90" t="s">
+      <c r="D4" s="89" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="45"/>
@@ -42416,7 +42418,7 @@
       <c r="H4" s="45"/>
       <c r="I4" s="45"/>
       <c r="J4" s="45"/>
-      <c r="K4" s="90" t="s">
+      <c r="K4" s="89" t="s">
         <v>841</v>
       </c>
       <c r="L4" s="45"/>
@@ -42433,13 +42435,13 @@
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="89" t="s">
         <v>830</v>
       </c>
-      <c r="D5" s="90" t="s">
+      <c r="D5" s="89" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="45"/>
@@ -42448,7 +42450,7 @@
       <c r="H5" s="45"/>
       <c r="I5" s="45"/>
       <c r="J5" s="45"/>
-      <c r="K5" s="90" t="s">
+      <c r="K5" s="89" t="s">
         <v>841</v>
       </c>
       <c r="L5" s="45"/>
@@ -42465,13 +42467,13 @@
         <f t="shared" ref="A6:A51" si="0">+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="89" t="s">
         <v>829</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="89" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="89" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="45"/>
@@ -42480,7 +42482,7 @@
       <c r="H6" s="45"/>
       <c r="I6" s="45"/>
       <c r="J6" s="45"/>
-      <c r="K6" s="90" t="s">
+      <c r="K6" s="89" t="s">
         <v>842</v>
       </c>
       <c r="L6" s="45"/>
@@ -42497,13 +42499,13 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="90" t="s">
+      <c r="D7" s="89" t="s">
         <v>85</v>
       </c>
       <c r="E7" s="45"/>
@@ -42512,7 +42514,7 @@
       <c r="H7" s="45"/>
       <c r="I7" s="45"/>
       <c r="J7" s="45"/>
-      <c r="K7" s="90" t="s">
+      <c r="K7" s="89" t="s">
         <v>844</v>
       </c>
       <c r="L7" s="45"/>
@@ -42529,13 +42531,13 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="89" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="90" t="s">
+      <c r="C8" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="90" t="s">
+      <c r="D8" s="89" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="45"/>
@@ -42544,7 +42546,7 @@
       <c r="H8" s="45"/>
       <c r="I8" s="45"/>
       <c r="J8" s="45"/>
-      <c r="K8" s="90" t="s">
+      <c r="K8" s="89" t="s">
         <v>841</v>
       </c>
       <c r="L8" s="45"/>
@@ -42561,13 +42563,13 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="89" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="89" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="90" t="s">
+      <c r="D9" s="89" t="s">
         <v>185</v>
       </c>
       <c r="E9" s="45"/>
@@ -42576,7 +42578,7 @@
       <c r="H9" s="45"/>
       <c r="I9" s="45"/>
       <c r="J9" s="45"/>
-      <c r="K9" s="90" t="s">
+      <c r="K9" s="89" t="s">
         <v>844</v>
       </c>
       <c r="L9" s="45"/>
@@ -42593,13 +42595,13 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="90" t="s">
+      <c r="C10" s="89" t="s">
         <v>446</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="89" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="45"/>
@@ -42608,7 +42610,7 @@
       <c r="H10" s="45"/>
       <c r="I10" s="45"/>
       <c r="J10" s="45"/>
-      <c r="K10" s="90" t="s">
+      <c r="K10" s="89" t="s">
         <v>841</v>
       </c>
       <c r="L10" s="45"/>
@@ -42625,13 +42627,13 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="90" t="s">
+      <c r="C11" s="89" t="s">
         <v>448</v>
       </c>
-      <c r="D11" s="90" t="s">
+      <c r="D11" s="89" t="s">
         <v>165</v>
       </c>
       <c r="E11" s="45"/>
@@ -42640,7 +42642,7 @@
       <c r="H11" s="45"/>
       <c r="I11" s="45"/>
       <c r="J11" s="45"/>
-      <c r="K11" s="90" t="s">
+      <c r="K11" s="89" t="s">
         <v>845</v>
       </c>
       <c r="L11" s="45"/>
@@ -42657,13 +42659,13 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="89" t="s">
         <v>339</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="C12" s="89" t="s">
         <v>340</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="89" t="s">
         <v>254</v>
       </c>
       <c r="E12" s="45"/>
@@ -42687,13 +42689,13 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="89" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="90" t="s">
+      <c r="C13" s="89" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="90" t="s">
+      <c r="D13" s="89" t="s">
         <v>165</v>
       </c>
       <c r="E13" s="45"/>
@@ -42702,7 +42704,7 @@
       <c r="H13" s="45"/>
       <c r="I13" s="45"/>
       <c r="J13" s="45"/>
-      <c r="K13" s="90" t="s">
+      <c r="K13" s="89" t="s">
         <v>845</v>
       </c>
       <c r="L13" s="45"/>
@@ -42719,13 +42721,13 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="89" t="s">
         <v>387</v>
       </c>
-      <c r="C14" s="90" t="s">
+      <c r="C14" s="89" t="s">
         <v>386</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="89" t="s">
         <v>165</v>
       </c>
       <c r="E14" s="45"/>
@@ -42734,7 +42736,7 @@
       <c r="H14" s="45"/>
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
-      <c r="K14" s="90" t="s">
+      <c r="K14" s="89" t="s">
         <v>845</v>
       </c>
       <c r="L14" s="45"/>
@@ -42751,13 +42753,13 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="90" t="s">
+      <c r="B15" s="89" t="s">
         <v>831</v>
       </c>
-      <c r="C15" s="90" t="s">
+      <c r="C15" s="89" t="s">
         <v>832</v>
       </c>
-      <c r="D15" s="90" t="s">
+      <c r="D15" s="89" t="s">
         <v>143</v>
       </c>
       <c r="E15" s="45"/>
@@ -42781,13 +42783,13 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="90" t="s">
+      <c r="B16" s="89" t="s">
         <v>833</v>
       </c>
-      <c r="C16" s="90" t="s">
+      <c r="C16" s="89" t="s">
         <v>455</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="D16" s="89" t="s">
         <v>219</v>
       </c>
       <c r="E16" s="45"/>
@@ -42796,7 +42798,7 @@
       <c r="H16" s="45"/>
       <c r="I16" s="45"/>
       <c r="J16" s="45"/>
-      <c r="K16" s="90" t="s">
+      <c r="K16" s="89" t="s">
         <v>845</v>
       </c>
       <c r="L16" s="45"/>
@@ -42813,13 +42815,13 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="90" t="s">
+      <c r="B17" s="89" t="s">
         <v>834</v>
       </c>
-      <c r="C17" s="90" t="s">
+      <c r="C17" s="89" t="s">
         <v>349</v>
       </c>
-      <c r="D17" s="90" t="s">
+      <c r="D17" s="89" t="s">
         <v>347</v>
       </c>
       <c r="E17" s="45"/>
@@ -42843,13 +42845,13 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" s="90" t="s">
+      <c r="B18" s="89" t="s">
         <v>835</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C18" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="90" t="s">
+      <c r="D18" s="89" t="s">
         <v>165</v>
       </c>
       <c r="E18" s="45"/>
@@ -42873,13 +42875,13 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="90" t="s">
+      <c r="B19" s="89" t="s">
         <v>342</v>
       </c>
-      <c r="C19" s="90" t="s">
+      <c r="C19" s="89" t="s">
         <v>341</v>
       </c>
-      <c r="D19" s="90" t="s">
+      <c r="D19" s="89" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="45"/>
@@ -42888,7 +42890,7 @@
       <c r="H19" s="45"/>
       <c r="I19" s="45"/>
       <c r="J19" s="45"/>
-      <c r="K19" s="90" t="s">
+      <c r="K19" s="89" t="s">
         <v>846</v>
       </c>
       <c r="L19" s="45"/>
@@ -42905,13 +42907,13 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" s="90" t="s">
+      <c r="B20" s="89" t="s">
         <v>836</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C20" s="89" t="s">
         <v>837</v>
       </c>
-      <c r="D20" s="90" t="s">
+      <c r="D20" s="89" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="45"/>
@@ -42935,13 +42937,13 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" s="90" t="s">
+      <c r="B21" s="89" t="s">
         <v>350</v>
       </c>
-      <c r="C21" s="90" t="s">
+      <c r="C21" s="89" t="s">
         <v>351</v>
       </c>
-      <c r="D21" s="90" t="s">
+      <c r="D21" s="89" t="s">
         <v>838</v>
       </c>
       <c r="E21" s="45"/>
@@ -42965,13 +42967,13 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B22" s="90" t="s">
+      <c r="B22" s="89" t="s">
         <v>532</v>
       </c>
-      <c r="C22" s="90" t="s">
+      <c r="C22" s="89" t="s">
         <v>839</v>
       </c>
-      <c r="D22" s="90" t="s">
+      <c r="D22" s="89" t="s">
         <v>219</v>
       </c>
       <c r="E22" s="45"/>
@@ -42995,7 +42997,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B23" s="90" t="s">
+      <c r="B23" s="89" t="s">
         <v>421</v>
       </c>
       <c r="C23" s="57" t="s">
@@ -43025,13 +43027,13 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B24" s="90" t="s">
+      <c r="B24" s="89" t="s">
         <v>840</v>
       </c>
-      <c r="C24" s="90" t="s">
+      <c r="C24" s="89" t="s">
         <v>357</v>
       </c>
-      <c r="D24" s="90" t="s">
+      <c r="D24" s="89" t="s">
         <v>165</v>
       </c>
       <c r="E24" s="45"/>
@@ -43055,13 +43057,13 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="89" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="90" t="s">
+      <c r="C25" s="89" t="s">
         <v>378</v>
       </c>
-      <c r="D25" s="90" t="s">
+      <c r="D25" s="89" t="s">
         <v>254</v>
       </c>
       <c r="E25" s="45"/>
@@ -43085,13 +43087,13 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="89" t="s">
         <v>847</v>
       </c>
-      <c r="C26" s="90" t="s">
+      <c r="C26" s="89" t="s">
         <v>699</v>
       </c>
-      <c r="D26" s="90" t="s">
+      <c r="D26" s="89" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="45"/>
@@ -50950,90 +50952,90 @@
       <c r="K13" s="45"/>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="101" t="s">
         <v>876</v>
       </c>
-      <c r="C14" s="102" t="s">
+      <c r="C14" s="101" t="s">
         <v>877</v>
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="101" t="s">
         <v>878</v>
       </c>
-      <c r="C15" s="102" t="s">
+      <c r="C15" s="101" t="s">
         <v>879</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="101" t="s">
         <v>880</v>
       </c>
-      <c r="C16" s="102" t="s">
+      <c r="C16" s="101" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="101" t="s">
         <v>882</v>
       </c>
-      <c r="C17" s="102" t="s">
+      <c r="C17" s="101" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="101" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="102" t="s">
+      <c r="C18" s="101" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="102" t="s">
+      <c r="B19" s="101" t="s">
         <v>885</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="101" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="101" t="s">
         <v>887</v>
       </c>
-      <c r="C20" s="102" t="s">
+      <c r="C20" s="101" t="s">
         <v>888</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="101" t="s">
         <v>889</v>
       </c>
-      <c r="C21" s="102" t="s">
+      <c r="C21" s="101" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="101" t="s">
         <v>891</v>
       </c>
-      <c r="C22" s="102" t="s">
+      <c r="C22" s="101" t="s">
         <v>892</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="102" t="s">
+      <c r="B23" s="101" t="s">
         <v>893</v>
       </c>
-      <c r="C23" s="102" t="s">
+      <c r="C23" s="101" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="B24" s="102" t="s">
+      <c r="B24" s="101" t="s">
         <v>895</v>
       </c>
-      <c r="C24" s="102" t="s">
+      <c r="C24" s="101" t="s">
         <v>896</v>
       </c>
     </row>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C527C6-422B-4B20-B9BB-26267AC2071A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C04392D-028A-44D3-B071-3E47CED59027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4890" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -3642,22 +3642,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>34.700000000000003</v>
+            <v>43.26</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>10654.943136000002</v>
+            <v>13283.367148799998</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1261.6759999999999</v>
+            <v>1020.558</v>
           </cell>
         </row>
         <row r="7">
           <cell r="H7">
-            <v>1732.366</v>
+            <v>1719.8150000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -4176,26 +4176,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>19.87</v>
+            <v>25.27</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>5174.1480000000001</v>
+            <v>6292.23</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1259.7</v>
+            <v>1397.8</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>715.7</v>
+            <v>939</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4420,22 +4420,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>81.2</v>
+            <v>87.92</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>5521.0864911999997</v>
+            <v>5978.0039939199996</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>203.84100000000001</v>
+            <v>180.76900000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>396.62300000000005</v>
+            <v>399.72299999999996</v>
           </cell>
         </row>
       </sheetData>
@@ -4683,11 +4683,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5474,26 +5474,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>35.700000000000003</v>
+            <v>37.94</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>2463.8772690000001</v>
+            <v>2618.4733759799997</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>314</v>
+            <v>231</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>297</v>
+            <v>179</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7298,15 +7298,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1778118.5418813494</v>
+        <v>1782650.8822887496</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>11722.7023238</v>
+        <v>12039.838883800001</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1789841.2442051494</v>
+        <v>1794690.7211725493</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7368,15 +7368,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22528.941231301233</v>
+        <v>22586.312628863263</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>152.24288732207793</v>
+        <v>156.36154394545457</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23244.691483183757</v>
+        <v>23307.6717035396</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -8774,25 +8774,25 @@
       </c>
       <c r="E21" s="24">
         <f>+[16]Main!$H$2</f>
-        <v>34.700000000000003</v>
+        <v>43.26</v>
       </c>
       <c r="F21" s="17">
         <f>+[16]Main!$H$5*FX!C3</f>
-        <v>11081.140861440002</v>
+        <v>13814.701834751999</v>
       </c>
       <c r="G21" s="17">
         <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
-        <v>489.51760000000007</v>
+        <v>727.22728000000006</v>
       </c>
       <c r="H21" s="17">
         <f t="shared" si="1"/>
-        <v>11570.658461440002</v>
+        <v>14541.929114751998</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>827</v>
+        <v>806</v>
       </c>
       <c r="J21" s="26">
-        <v>46203</v>
+        <v>46317</v>
       </c>
       <c r="K21" s="24"/>
       <c r="L21" s="21"/>
@@ -9555,24 +9555,26 @@
       </c>
       <c r="E33" s="24">
         <f>+[28]Main!$I$2</f>
-        <v>19.87</v>
+        <v>25.27</v>
       </c>
       <c r="F33" s="17">
         <f>+[28]Main!$I$4*FX!C3</f>
-        <v>5381.1139200000007</v>
+        <v>6543.9191999999994</v>
       </c>
       <c r="G33" s="17">
         <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
-        <v>-565.76</v>
+        <v>-477.15199999999999</v>
       </c>
       <c r="H33" s="17">
         <f>F33+G33</f>
-        <v>4815.3539200000005</v>
+        <v>6066.7671999999993</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>827</v>
-      </c>
-      <c r="J33" s="26"/>
+        <v>806</v>
+      </c>
+      <c r="J33" s="26">
+        <v>46329</v>
+      </c>
       <c r="K33" s="24"/>
       <c r="L33" s="21"/>
       <c r="M33" s="24"/>
@@ -9880,25 +9882,25 @@
       </c>
       <c r="E38" s="24">
         <f>+[33]Main!$J$2</f>
-        <v>81.2</v>
+        <v>87.92</v>
       </c>
       <c r="F38" s="17">
         <f>+[33]Main!$J$4*FX!C3</f>
-        <v>5741.9299508479999</v>
+        <v>6217.1241536768002</v>
       </c>
       <c r="G38" s="17">
         <f>+([33]Main!$J$6-[33]Main!$J$5)*FX!C3</f>
-        <v>200.49328000000006</v>
+        <v>227.71215999999995</v>
       </c>
       <c r="H38" s="17">
         <f>F38+G38</f>
-        <v>5942.4232308479995</v>
+        <v>6444.8363136768003</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>422</v>
+        <v>806</v>
       </c>
       <c r="J38" s="26">
-        <v>46210</v>
+        <v>46310</v>
       </c>
       <c r="K38" s="17"/>
       <c r="L38" s="21"/>
@@ -11415,24 +11417,26 @@
       </c>
       <c r="E63" s="24">
         <f>+[57]Main!$J$2</f>
-        <v>35.700000000000003</v>
+        <v>37.94</v>
       </c>
       <c r="F63" s="17">
         <f>+[57]Main!$J$4*FX!C3</f>
-        <v>2562.4323597600001</v>
+        <v>2723.2123110191997</v>
       </c>
       <c r="G63" s="17">
         <f>+([57]Main!$J$6-[57]Main!$J$5)*FX!C3</f>
-        <v>-17.68</v>
+        <v>-54.08</v>
       </c>
       <c r="H63" s="17">
         <f>+F63+G63</f>
-        <v>2544.7523597600002</v>
+        <v>2669.1323110191997</v>
       </c>
       <c r="I63" s="16" t="s">
-        <v>827</v>
-      </c>
-      <c r="J63" s="26"/>
+        <v>806</v>
+      </c>
+      <c r="J63" s="26">
+        <v>46329</v>
+      </c>
       <c r="K63" s="17"/>
       <c r="L63" s="21"/>
       <c r="M63" s="17"/>

--- a/Fashion.xlsx
+++ b/Fashion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C04392D-028A-44D3-B071-3E47CED59027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5295609A-5D33-4B7A-AE9D-A8D3ED684F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E4FC37F3-4088-4285-9A96-75C9B19F2D05}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="898">
   <si>
     <t>Fashion Universe</t>
   </si>
@@ -2766,9 +2766,6 @@
   </si>
   <si>
     <t>WHP Global: (joint venture with G-III Apparel Group)</t>
-  </si>
-  <si>
-    <t>FQ425</t>
   </si>
   <si>
     <t>SHEIN</t>
@@ -3306,7 +3303,18 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3424,26 +3432,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>147.4</v>
+            <v>159.1</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>26118.171109800001</v>
+            <v>28044.802332200001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>873</v>
+            <v>1159</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>2997</v>
+            <v>3049</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3563,7 +3571,7 @@
         </row>
         <row r="4">
           <cell r="M4">
-            <v>14366.90833</v>
+            <v>14174.802327570002</v>
           </cell>
         </row>
         <row r="5">
@@ -3584,6 +3592,46 @@
 </file>
 
 <file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>134.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>27130.56419592</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>1046.5220999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2377.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3623,7 +3671,89 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>389.9</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>23231.114986099998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1941.6</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>1308.0999999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>4496</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3186338.7905119997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>119389</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>75000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3666,124 +3796,6 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5221.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1856195.55198455</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5"/>
-        </row>
-        <row r="6">
-          <cell r="I6"/>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Quarter"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>47.32</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>12801.14235036</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1341.982</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>980.13599999999997</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>304.51</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>19088.948091260001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>584.07899999999995</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2035.424</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3849,23 +3861,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="J2">
-            <v>134.28</v>
+          <cell r="I2">
+            <v>2992.7</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="J4">
-            <v>27130.56419592</v>
+          <cell r="I4">
+            <v>1063867.3245347</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>1046.5220999999999</v>
+          <cell r="I5">
+            <v>262002</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>2377.1</v>
+          <cell r="I6">
+            <v>499890</v>
           </cell>
         </row>
       </sheetData>
@@ -3884,28 +3896,70 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Quarter"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>47.32</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>12801.14235036</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1341.982</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>980.13599999999997</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
       <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>4496</v>
+            <v>358.03</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>3186338.7905119997</v>
+            <v>22535.198014179998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>119389</v>
+            <v>747.35500000000002</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>75000</v>
+            <v>1917.3630000000001</v>
           </cell>
         </row>
       </sheetData>
@@ -3915,7 +3969,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3955,7 +4009,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3973,12 +4027,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>36.42</v>
+            <v>30.85</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>9190.3083888210003</v>
+            <v>7784.7614990425</v>
           </cell>
         </row>
         <row r="6">
@@ -4001,7 +4055,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4041,7 +4095,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -4076,48 +4130,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>376.91</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>22473.766070860001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2065</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>1238.9000000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4195,7 +4207,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5493,7 +5505,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5514,22 +5526,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>4.97</v>
+            <v>5.53</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>2117.1355100000001</v>
+            <v>1932.9868362000002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>309.16800000000001</v>
+            <v>395.98099999999999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>1190.444</v>
+            <v>591.15800000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -6173,22 +6185,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>13.57</v>
+            <v>12.17</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1318.1272015899999</v>
+            <v>1184.3104429100001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>408.2</v>
+            <v>206.9</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>410.59999999999997</v>
+            <v>436.3</v>
           </cell>
         </row>
       </sheetData>
@@ -6493,22 +6505,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="K2">
-            <v>202.53</v>
+            <v>205.28</v>
           </cell>
         </row>
         <row r="4">
           <cell r="K4">
-            <v>81093.012000000002</v>
+            <v>82146.807482079996</v>
           </cell>
         </row>
         <row r="5">
           <cell r="K5">
-            <v>183.20400000000001</v>
+            <v>289.01799999999997</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>2656.7910000000002</v>
+            <v>2428.0729999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -7298,15 +7310,15 @@
       </c>
       <c r="F4" s="17">
         <f>SUM(F6:F153)</f>
-        <v>1782650.8822887496</v>
+        <v>1779153.5618220663</v>
       </c>
       <c r="G4" s="17">
         <f>SUM(G6:G153)</f>
-        <v>12039.838883800001</v>
+        <v>13460.508883800001</v>
       </c>
       <c r="H4" s="17">
         <f>SUM(H6:H153)</f>
-        <v>1794690.7211725493</v>
+        <v>1792614.0707058655</v>
       </c>
       <c r="I4" s="79" t="s">
         <v>422</v>
@@ -7368,15 +7380,15 @@
       </c>
       <c r="F5" s="83">
         <f>+AVERAGE(F6:F181)</f>
-        <v>22586.312628863263</v>
+        <v>22542.042749538155</v>
       </c>
       <c r="G5" s="83">
         <f>AVERAGE(G6:G153)</f>
-        <v>156.36154394545457</v>
+        <v>174.8118036857143</v>
       </c>
       <c r="H5" s="83">
         <f>AVERAGE(H6:H153)</f>
-        <v>23307.6717035396</v>
+        <v>23280.702216959293</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>422</v>
@@ -7767,7 +7779,7 @@
     </row>
     <row r="9" spans="1:34">
       <c r="A9" s="15">
-        <f t="shared" ref="A9:A71" si="2">+A8+1</f>
+        <f t="shared" ref="A9:A72" si="2">+A8+1</f>
         <v>4</v>
       </c>
       <c r="B9" s="23" t="s">
@@ -7796,7 +7808,7 @@
         <v>175560.4</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="J9" s="26">
         <v>46253</v>
@@ -8136,25 +8148,25 @@
       </c>
       <c r="E13" s="24">
         <f>+[8]Main!$K$2</f>
-        <v>202.53</v>
+        <v>205.28</v>
       </c>
       <c r="F13" s="17">
         <f>+[8]Main!$K$4</f>
-        <v>81093.012000000002</v>
+        <v>82146.807482079996</v>
       </c>
       <c r="G13" s="17">
         <f>+[8]Main!$K$6-[8]Main!$K$5</f>
-        <v>2473.587</v>
+        <v>2139.0549999999998</v>
       </c>
       <c r="H13" s="17">
         <f t="shared" si="1"/>
-        <v>83566.599000000002</v>
+        <v>84285.862482079989</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="J13" s="26">
-        <v>46219</v>
+        <v>46288</v>
       </c>
       <c r="K13" s="17">
         <v>8815.7999999999993</v>
@@ -8230,7 +8242,7 @@
         <v>71123.630139999994</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="J14" s="26">
         <v>46254</v>
@@ -8365,25 +8377,25 @@
       </c>
       <c r="E16" s="24">
         <f>+[11]Main!$I$2</f>
-        <v>147.4</v>
+        <v>159.1</v>
       </c>
       <c r="F16" s="17">
         <f>+[11]Main!$I$4*FX!C3</f>
-        <v>27162.897954192002</v>
+        <v>29166.594425488001</v>
       </c>
       <c r="G16" s="17">
         <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C3</f>
-        <v>2208.96</v>
+        <v>1965.6000000000001</v>
       </c>
       <c r="H16" s="17">
         <f>F16+G16</f>
-        <v>29371.857954192001</v>
+        <v>31132.194425488</v>
       </c>
       <c r="I16" s="25" t="s">
         <v>827</v>
       </c>
       <c r="J16" s="26">
-        <v>46233</v>
+        <v>46324</v>
       </c>
       <c r="K16" s="17">
         <f>21427*FX!C3</f>
@@ -8560,7 +8572,7 @@
       <c r="I18" s="25" t="s">
         <v>422</v>
       </c>
-      <c r="J18" s="30">
+      <c r="J18" s="26">
         <v>46260</v>
       </c>
       <c r="K18" s="17">
@@ -8626,7 +8638,7 @@
       </c>
       <c r="F19" s="17">
         <f>+[14]Main!$M$4</f>
-        <v>14366.90833</v>
+        <v>14174.802327570002</v>
       </c>
       <c r="G19" s="17">
         <f>+[14]Main!$M$6-[14]Main!$M$5</f>
@@ -8634,13 +8646,13 @@
       </c>
       <c r="H19" s="17">
         <f>F19+G19</f>
-        <v>12764.31933</v>
+        <v>12572.213327570002</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>828</v>
+        <v>874</v>
       </c>
       <c r="J19" s="26">
-        <v>46226</v>
+        <v>46317</v>
       </c>
       <c r="K19" s="17">
         <v>4985.6120000000001</v>
@@ -8696,43 +8708,38 @@
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>108</v>
+        <v>310</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>109</v>
+        <v>311</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E20" s="24">
-        <f>+[15]Main!$I$2</f>
-        <v>166.25</v>
+        <f>+[15]Main!$J$2</f>
+        <v>134.28</v>
       </c>
       <c r="F20" s="17">
-        <f>+[15]Main!$I$4*FX!C4</f>
-        <v>25232.110793750002</v>
+        <f>+[15]Main!$J$4</f>
+        <v>27130.56419592</v>
       </c>
       <c r="G20" s="17">
-        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C4</f>
-        <v>187.91</v>
+        <f>+[15]Main!$J$6-[15]Main!$J$5</f>
+        <v>1330.5779</v>
       </c>
       <c r="H20" s="17">
-        <f t="shared" si="1"/>
-        <v>25420.020793750002</v>
+        <f>F20+G20</f>
+        <v>28461.14209592</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="J20" s="26">
-        <v>46289</v>
-      </c>
-      <c r="K20" s="17">
-        <f>234478*FX!C4</f>
-        <v>22275.41</v>
-      </c>
-      <c r="L20" s="21">
-        <v>-0.01</v>
-      </c>
+        <v>46247</v>
+      </c>
+      <c r="K20" s="24"/>
+      <c r="L20" s="21"/>
       <c r="M20" s="17"/>
       <c r="N20" s="24"/>
       <c r="O20" s="21"/>
@@ -8751,10 +8758,10 @@
       <c r="AB20" s="17"/>
       <c r="AC20" s="17"/>
       <c r="AD20" s="5">
-        <v>1947</v>
+        <v>2000</v>
       </c>
       <c r="AE20" s="28" t="s">
-        <v>116</v>
+        <v>401</v>
       </c>
       <c r="AF20" s="2"/>
     </row>
@@ -8764,40 +8771,45 @@
         <v>16</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="E21" s="24">
-        <f>+[16]Main!$H$2</f>
-        <v>43.26</v>
+        <f>+[16]Main!$I$2</f>
+        <v>166.25</v>
       </c>
       <c r="F21" s="17">
-        <f>+[16]Main!$H$5*FX!C3</f>
-        <v>13814.701834751999</v>
+        <f>+[16]Main!$I$4*FX!C4</f>
+        <v>25232.110793750002</v>
       </c>
       <c r="G21" s="17">
-        <f>(+[16]Main!$H$7-[16]Main!$H$6)*FX!C3</f>
-        <v>727.22728000000006</v>
+        <f>+([16]Main!$I$6-[16]Main!$I$5)*FX!C4</f>
+        <v>187.91</v>
       </c>
       <c r="H21" s="17">
         <f t="shared" si="1"/>
-        <v>14541.929114751998</v>
+        <v>25420.020793750002</v>
       </c>
       <c r="I21" s="25" t="s">
         <v>806</v>
       </c>
       <c r="J21" s="26">
-        <v>46317</v>
-      </c>
-      <c r="K21" s="24"/>
-      <c r="L21" s="21"/>
+        <v>46289</v>
+      </c>
+      <c r="K21" s="17">
+        <f>234478*FX!C4</f>
+        <v>22275.41</v>
+      </c>
+      <c r="L21" s="21">
+        <v>-0.01</v>
+      </c>
       <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
+      <c r="N21" s="24"/>
       <c r="O21" s="21"/>
       <c r="P21" s="21"/>
       <c r="Q21" s="22"/>
@@ -8814,10 +8826,10 @@
       <c r="AB21" s="17"/>
       <c r="AC21" s="17"/>
       <c r="AD21" s="5">
-        <v>1913</v>
+        <v>1947</v>
       </c>
       <c r="AE21" s="28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF21" s="2"/>
     </row>
@@ -8827,55 +8839,92 @@
         <v>17</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>440</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="E22" s="24">
-        <f>+[17]Main!$I$2</f>
-        <v>5221.55</v>
+        <f>+[17]Main!$H$2</f>
+        <v>389.9</v>
       </c>
       <c r="F22" s="17">
-        <f>+[17]Main!$I$4*FX!C12</f>
-        <v>20418.151071830049</v>
+        <f>+[17]Main!$H$4</f>
+        <v>23231.114986099998</v>
       </c>
       <c r="G22" s="17">
-        <f>+([17]Main!$I$6-[17]Main!$I$5)*FX!C12</f>
-        <v>0</v>
+        <f>+[17]Main!$H$6-[17]Mai